--- a/cache/open_items_2026-06-09.xlsx
+++ b/cache/open_items_2026-06-09.xlsx
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N263"/>
+  <dimension ref="A1:N264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -9970,13 +9970,13 @@
         </is>
       </c>
     </row>
-    <row r="170" ht="45" customHeight="1">
+    <row r="170" ht="60" customHeight="1">
       <c r="A170" s="2" t="n">
         <v>169</v>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>CONFIG-1</t>
+          <t>CONVICTION-VERDICT-ALIGN</t>
         </is>
       </c>
       <c r="C170" s="9" t="inlineStr">
@@ -9986,39 +9986,27 @@
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Config</t>
+          <t>Signals · Sizing</t>
         </is>
       </c>
       <c r="E170" s="6" t="inlineStr">
         <is>
-          <t>Restore regime4_thresholds to documented baseline + variant playbook</t>
+          <t>Verdict=BUY masked 0-conviction names in scanner + executor</t>
         </is>
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08 raised buy_min to 80/80/85; produced 0 live BUYs. The 80 floor was not saving us — Variant F is the actual loser-cut.</t>
+          <t>10 of 12 BUY-verdict names in risk_on_choppy were conviction=AVOID/size_mult 0; scanner ranked + executor traded them as if real buys, killing user confidence + buying 0-conviction names (ARMK/PBI/WDC)</t>
         </is>
       </c>
       <c r="G170" s="5" t="inlineStr">
         <is>
-          <t>Restored: trending 65, choppy 72, risk-off 78 (per CLAUDE.md 4-Regime Detection table). Created config/variants/A/E2/G.json. Updated CLAUDE.md with 4 lessons.</t>
-        </is>
-      </c>
-      <c r="H170" s="2" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="I170" s="5" t="inlineStr">
-        <is>
-          <t>High — restores live BUY flow without losing Variant F protection</t>
-        </is>
-      </c>
-      <c r="J170" s="5" t="inlineStr">
-        <is>
-          <t>Caveat: alone does not unblock todays top-5 WATCH (entry_quality blocked).</t>
-        </is>
-      </c>
+          <t>executor.py conviction gate (skip 0-size, scale by size_mult); surface-signal.jsx conviction-aware Top Buys sort + tier column in Essentials</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr"/>
+      <c r="I170" s="5" t="inlineStr"/>
+      <c r="J170" s="5" t="inlineStr"/>
       <c r="K170" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -10026,27 +10014,23 @@
       </c>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="M170" s="3" t="inlineStr">
         <is>
-          <t>363984181</t>
-        </is>
-      </c>
-      <c r="N170" s="8" t="inlineStr">
-        <is>
-          <t>config/config.json regime4_thresholds.risk_on_trending.buy_min_score = 65. Run /Swing-Trade — BUYs &gt; 0 when market gives FRESH entries.</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="90" customHeight="1">
+          <t>6a5a50549</t>
+        </is>
+      </c>
+      <c r="N170" s="8" t="inlineStr"/>
+    </row>
+    <row r="171" ht="45" customHeight="1">
       <c r="A171" s="2" t="n">
         <v>170</v>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>EW-V1</t>
+          <t>CONFIG-1</t>
         </is>
       </c>
       <c r="C171" s="9" t="inlineStr">
@@ -10056,37 +10040,37 @@
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Elliott Wave</t>
+          <t>Strategy / Config</t>
         </is>
       </c>
       <c r="E171" s="6" t="inlineStr">
         <is>
-          <t>EW Rule Gate v1.0 — 8-state classifier</t>
+          <t>Restore regime4_thresholds to documented baseline + variant playbook</t>
         </is>
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>Legacy classify_elliott_wave was heuristic Wave-3 detector only — 2 states (impulse/corrective). Needed full spec: 8 engine states, 3 absolute impulse rules, fractal pivots, Fibonacci retracements (23.6-88.6%) and extensions (100-423.6%), multi-timeframe alignment.</t>
+          <t>2026-05-08 raised buy_min to 80/80/85; produced 0 live BUYs. The 80 floor was not saving us — Variant F is the actual loser-cut.</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>New classify_elliott_wave_bhe() implements full BHE v1.0 spec. Fractal pivot detector via i±2 rule. 8 states with score 0-4 contribution. Rule 1 (W2 &lt; W1 start) invalidation. Multi-TF ready (Primary/Intermediate/Minor) — daily-only in Phase 1, weekly/4H wire-in Phase 2. Sibling gate_g3_quant_veto() combines EW + Monte Carlo + Wyckoff for the quant veto.</t>
+          <t>Restored: trending 65, choppy 72, risk-off 78 (per CLAUDE.md 4-Regime Detection table). Created config/variants/A/E2/G.json. Updated CLAUDE.md with 4 lessons.</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I171" s="5" t="inlineStr">
         <is>
-          <t>Low / High (transparency + future-proof)</t>
+          <t>High — restores live BUY flow without losing Variant F protection</t>
         </is>
       </c>
       <c r="J171" s="5" t="inlineStr">
         <is>
-          <t>Runs in parallel to legacy classify_elliott_wave for backward compat. New result on plan as elliott_wave_v1. Smoke-tested: synthetic uptrend → WAVE3_IMPULSE score 4, T1/T2 from 1.618×/2.618×W1 fib extension.</t>
+          <t>Caveat: alone does not unblock todays top-5 WATCH (entry_quality blocked).</t>
         </is>
       </c>
       <c r="K171" s="12" t="inlineStr">
@@ -10101,22 +10085,22 @@
       </c>
       <c r="M171" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>363984181</t>
         </is>
       </c>
       <c r="N171" s="8" t="inlineStr">
         <is>
-          <t>python3 -c "from analysis import classify_elliott_wave_bhe, gate_g3_quant_veto; ..." with synthetic uptrend → WAVE3_IMPULSE / score 4. Open a ticker on elite-detail Models tab → elliott_wave_v1 field should populate with ew_state + score + t1/t2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="75" customHeight="1">
+          <t>config/config.json regime4_thresholds.risk_on_trending.buy_min_score = 65. Run /Swing-Trade — BUYs &gt; 0 when market gives FRESH entries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="90" customHeight="1">
       <c r="A172" s="2" t="n">
         <v>171</v>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-M21-INFRA</t>
+          <t>EW-V1</t>
         </is>
       </c>
       <c r="C172" s="9" t="inlineStr">
@@ -10126,27 +10110,39 @@
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Targets</t>
+          <t>Strategy / Elliott Wave</t>
         </is>
       </c>
       <c r="E172" s="6" t="inlineStr">
         <is>
-          <t>Structural targets · M2.1 — engine infra (cache, endpoint, precompute, flag)</t>
+          <t>EW Rule Gate v1.0 — 8-state classifier</t>
         </is>
       </c>
       <c r="F172" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-13: target_engine.py cache layer (12h TTL, atomic writes), GET /v2/trade_engine FastAPI endpoint (hybrid pre-compute + on-demand), scripts/precompute_targets.py batch runner (SP500 + R1000 + watchlist), run_daily_scan.sh hook at 06:00 only, config flag use_structural_targets:false.</t>
+          <t>Legacy classify_elliott_wave was heuristic Wave-3 detector only — 2 states (impulse/corrective). Needed full spec: 8 engine states, 3 absolute impulse rules, fractal pivots, Fibonacci retracements (23.6-88.6%) and extensions (100-423.6%), multi-timeframe alignment.</t>
         </is>
       </c>
       <c r="G172" s="5" t="inlineStr">
         <is>
-          <t>All five infra pieces wired and verified: 2,359× cache speedup, 8 ROST/AVGO/AAPL/NVDA cache files written, server.py syntax valid, feature flag confirmed OFF in config/config.json. Flag stays false until M2.5 cutover.</t>
-        </is>
-      </c>
-      <c r="H172" s="2" t="inlineStr"/>
-      <c r="I172" s="5" t="inlineStr"/>
-      <c r="J172" s="5" t="inlineStr"/>
+          <t>New classify_elliott_wave_bhe() implements full BHE v1.0 spec. Fractal pivot detector via i±2 rule. 8 states with score 0-4 contribution. Rule 1 (W2 &lt; W1 start) invalidation. Multi-TF ready (Primary/Intermediate/Minor) — daily-only in Phase 1, weekly/4H wire-in Phase 2. Sibling gate_g3_quant_veto() combines EW + Monte Carlo + Wyckoff for the quant veto.</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>2 hrs</t>
+        </is>
+      </c>
+      <c r="I172" s="5" t="inlineStr">
+        <is>
+          <t>Low / High (transparency + future-proof)</t>
+        </is>
+      </c>
+      <c r="J172" s="5" t="inlineStr">
+        <is>
+          <t>Runs in parallel to legacy classify_elliott_wave for backward compat. New result on plan as elliott_wave_v1. Smoke-tested: synthetic uptrend → WAVE3_IMPULSE score 4, T1/T2 from 1.618×/2.618×W1 fib extension.</t>
+        </is>
+      </c>
       <c r="K172" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -10154,7 +10150,7 @@
       </c>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M172" s="3" t="inlineStr">
@@ -10162,15 +10158,19 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="N172" s="8" t="inlineStr"/>
-    </row>
-    <row r="173" ht="90" customHeight="1">
+      <c r="N172" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c "from analysis import classify_elliott_wave_bhe, gate_g3_quant_veto; ..." with synthetic uptrend → WAVE3_IMPULSE / score 4. Open a ticker on elite-detail Models tab → elliott_wave_v1 field should populate with ew_state + score + t1/t2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="75" customHeight="1">
       <c r="A173" s="2" t="n">
         <v>172</v>
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-M22-DATA</t>
+          <t>STRUCT-TARGETS-M21-INFRA</t>
         </is>
       </c>
       <c r="C173" s="9" t="inlineStr">
@@ -10185,17 +10185,17 @@
       </c>
       <c r="E173" s="6" t="inlineStr">
         <is>
-          <t>Structural targets · M2.2 — parallel fields in data.json (non-destructive)</t>
+          <t>Structural targets · M2.1 — engine infra (cache, endpoint, precompute, flag)</t>
         </is>
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-13: build_data.py:compact_row now overlays t1_structural, t2_structural, t1_confluence, t1_sources, t1_behavior, t1_p_reach, t1_action, t1_r_multiple (and t2_* counterparts) onto every pickrow when config.use_structural_targets=true. Legacy t1/t2 (ATR-based) remain untouched — every existing consumer keeps working.</t>
+          <t>Shipped 2026-05-13: target_engine.py cache layer (12h TTL, atomic writes), GET /v2/trade_engine FastAPI endpoint (hybrid pre-compute + on-demand), scripts/precompute_targets.py batch runner (SP500 + R1000 + watchlist), run_daily_scan.sh hook at 06:00 only, config flag use_structural_targets:false.</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>Gated by _structural_flag_enabled() lazy-loader; reads cache/target_engine/{TICKER}_{MODE}.json; emits structural_modes summary block (swing/position/invest) plus _te_mode_primary, _te_decision, _te_warnings diagnostics. Three-case unit test validated: flag-off no-op, flag-on with cache attaches fields, flag-on without cache no-op.</t>
+          <t>All five infra pieces wired and verified: 2,359× cache speedup, 8 ROST/AVGO/AAPL/NVDA cache files written, server.py syntax valid, feature flag confirmed OFF in config/config.json. Flag stays false until M2.5 cutover.</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr"/>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-M23-MODES</t>
+          <t>STRUCT-TARGETS-M22-DATA</t>
         </is>
       </c>
       <c r="C174" s="9" t="inlineStr">
@@ -10239,17 +10239,17 @@
       </c>
       <c r="E174" s="6" t="inlineStr">
         <is>
-          <t>Structural targets · M2.3 — mode completeness (short-gate, ETF degrade, earnings flag, INVEST stub)</t>
+          <t>Structural targets · M2.2 — parallel fields in data.json (non-destructive)</t>
         </is>
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-13: target_engine.analyze_trade now (1) rejects direction=short with short_not_supported_v1 warning, (2) detects ETFs via _KNOWN_ETF_TICKERS list and degrades swing-floor 3→2 with etf_degraded warning, (3) flags earnings_imminent when EODHD calendar shows report within 7d, (4) falls back to analyst-PT-based INVEST stub when invest mode produces no structural T1.</t>
+          <t>Shipped 2026-05-13: build_data.py:compact_row now overlays t1_structural, t2_structural, t1_confluence, t1_sources, t1_behavior, t1_p_reach, t1_action, t1_r_multiple (and t2_* counterparts) onto every pickrow when config.use_structural_targets=true. Legacy t1/t2 (ATR-based) remain untouched — every existing consumer keeps working.</t>
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>TradeAnalysis dataclass extended with is_etf:bool, catalyst:dict, invest_stub:bool fields. All four paths green in unit tests: SHORT reject clean, SPY/QQQ/XLF flagged ETF, AMAT earnings-1d flag fired, AAPL invest_stub=true with analyst_pt × 1.0/1.3 targets.</t>
+          <t>Gated by _structural_flag_enabled() lazy-loader; reads cache/target_engine/{TICKER}_{MODE}.json; emits structural_modes summary block (swing/position/invest) plus _te_mode_primary, _te_decision, _te_warnings diagnostics. Three-case unit test validated: flag-off no-op, flag-on with cache attaches fields, flag-on without cache no-op.</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr"/>
@@ -10272,13 +10272,13 @@
       </c>
       <c r="N174" s="8" t="inlineStr"/>
     </row>
-    <row r="175" ht="75" customHeight="1">
+    <row r="175" ht="90" customHeight="1">
       <c r="A175" s="2" t="n">
         <v>174</v>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-M24-VALIDATION</t>
+          <t>STRUCT-TARGETS-M23-MODES</t>
         </is>
       </c>
       <c r="C175" s="9" t="inlineStr">
@@ -10293,17 +10293,17 @@
       </c>
       <c r="E175" s="6" t="inlineStr">
         <is>
-          <t>Structural targets · M2.4 — regression suite + monitoring</t>
+          <t>Structural targets · M2.3 — mode completeness (short-gate, ETF degrade, earnings flag, INVEST stub)</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-13: scripts/te_regression.py runs 20-ticker validation set (mega/mid/small cap + 5 ETFs) across swing+position modes, captures decision/warnings/latency/cache-status/T1-T2 vs legacy ATR diff_pct. Writes cache/logs/te_regression_&lt;TS&gt;.json + .md + append-only te_regression.log.</t>
+          <t>Shipped 2026-05-13: target_engine.analyze_trade now (1) rejects direction=short with short_not_supported_v1 warning, (2) detects ETFs via _KNOWN_ETF_TICKERS list and degrades swing-floor 3→2 with etf_degraded warning, (3) flags earnings_imminent when EODHD calendar shows report within 7d, (4) falls back to analyst-PT-based INVEST stub when invest mode produces no structural T1.</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>Baseline run 2026-05-13: 36/40 trade, 4 reject, 0 errors, median 7ms (cache-warm). ETF graceful-degrade fired 10 rows, earnings-imminent fired 2 (AMAT 1d). Use --quick for 5-ticker smoke, --fail-threshold N to set exit-code threshold. Exit 1 if errors &gt; threshold (default 5), exit 2 if no results.</t>
+          <t>TradeAnalysis dataclass extended with is_etf:bool, catalyst:dict, invest_stub:bool fields. All four paths green in unit tests: SHORT reject clean, SPY/QQQ/XLF flagged ETF, AMAT earnings-1d flag fired, AAPL invest_stub=true with analyst_pt × 1.0/1.3 targets.</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr"/>
@@ -10332,7 +10332,7 @@
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>TARGET-CAP-SWEEP</t>
+          <t>STRUCT-TARGETS-M24-VALIDATION</t>
         </is>
       </c>
       <c r="C176" s="9" t="inlineStr">
@@ -10342,22 +10342,22 @@
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>Strategy/Target Sanity</t>
+          <t>Strategy / Targets</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
         <is>
-          <t>Sweep for naive swing-high-as-target pattern across all scanners</t>
+          <t>Structural targets · M2.4 — regression suite + monitoring</t>
         </is>
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
-          <t>mean_reversion.py:354 (target2 = high.iloc[-20:].max() uncapped, latent) and pullback_scanner.py:113 (target = high_252 uncapped, UI API) had the same class of bug as weekly_pullback.py. Both fixed proactively. analysis.py:7766 calculate_trade_plan also has it but is dead code (no callers).</t>
+          <t>Shipped 2026-05-13: scripts/te_regression.py runs 20-ticker validation set (mega/mid/small cap + 5 ETFs) across swing+position modes, captures decision/warnings/latency/cache-status/T1-T2 vs legacy ATR diff_pct. Writes cache/logs/te_regression_&lt;TS&gt;.json + .md + append-only te_regression.log.</t>
         </is>
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Cap target2 at price*1.10 in mean_reversion.py, cap target at price*1.15 in pullback_scanner.py. Add memory entry feedback_target_must_cap_vs_entry.md.</t>
+          <t>Baseline run 2026-05-13: 36/40 trade, 4 reject, 0 errors, median 7ms (cache-warm). ETF graceful-degrade fired 10 rows, earnings-imminent fired 2 (AMAT 1d). Use --quick for 5-ticker smoke, --fail-threshold N to set exit-code threshold. Exit 1 if errors &gt; threshold (default 5), exit 2 if no results.</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr"/>
@@ -10370,23 +10370,23 @@
       </c>
       <c r="L176" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="M176" s="3" t="inlineStr">
         <is>
-          <t>87336f2de</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N176" s="8" t="inlineStr"/>
     </row>
-    <row r="177" ht="60" customHeight="1">
+    <row r="177" ht="75" customHeight="1">
       <c r="A177" s="2" t="n">
         <v>176</v>
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>TARGET-CAP-SWEEP</t>
         </is>
       </c>
       <c r="C177" s="9" t="inlineStr">
@@ -10396,39 +10396,27 @@
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>UI / Drift</t>
+          <t>Strategy/Target Sanity</t>
         </is>
       </c>
       <c r="E177" s="6" t="inlineStr">
         <is>
-          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
+          <t>Sweep for naive swing-high-as-target pattern across all scanners</t>
         </is>
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
+          <t>mean_reversion.py:354 (target2 = high.iloc[-20:].max() uncapped, latent) and pullback_scanner.py:113 (target = high_252 uncapped, UI API) had the same class of bug as weekly_pullback.py. Both fixed proactively. analysis.py:7766 calculate_trade_plan also has it but is dead code (no callers).</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
-        </is>
-      </c>
-      <c r="H177" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I177" s="5" t="inlineStr">
-        <is>
-          <t>Win: continuous drift visibility between alert events.</t>
-        </is>
-      </c>
-      <c r="J177" s="5" t="inlineStr">
-        <is>
-          <t>Additive — only renders if #driftBody container exists in DOM.</t>
-        </is>
-      </c>
+          <t>Cap target2 at price*1.10 in mean_reversion.py, cap target at price*1.15 in pullback_scanner.py. Add memory entry feedback_target_must_cap_vs_entry.md.</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr"/>
+      <c r="I177" s="5" t="inlineStr"/>
+      <c r="J177" s="5" t="inlineStr"/>
       <c r="K177" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -10436,27 +10424,23 @@
       </c>
       <c r="L177" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M177" s="3" t="inlineStr">
         <is>
-          <t>16a26b201</t>
-        </is>
-      </c>
-      <c r="N177" s="8" t="inlineStr">
-        <is>
-          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="45" customHeight="1">
+          <t>87336f2de</t>
+        </is>
+      </c>
+      <c r="N177" s="8" t="inlineStr"/>
+    </row>
+    <row r="178" ht="60" customHeight="1">
       <c r="A178" s="2" t="n">
         <v>177</v>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>MOD-3</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="C178" s="9" t="inlineStr">
@@ -10466,37 +10450,37 @@
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>UI / Drift</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
         <is>
-          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
+          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
         </is>
       </c>
       <c r="F178" s="5" t="inlineStr">
         <is>
-          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
+          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
         </is>
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
+          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I178" s="5" t="inlineStr">
         <is>
-          <t>Win: full auth-gated test coverage in CI.</t>
+          <t>Win: continuous drift visibility between alert events.</t>
         </is>
       </c>
       <c r="J178" s="5" t="inlineStr">
         <is>
-          <t>Trivial.</t>
+          <t>Additive — only renders if #driftBody container exists in DOM.</t>
         </is>
       </c>
       <c r="K178" s="12" t="inlineStr">
@@ -10511,22 +10495,22 @@
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>16a26b201</t>
         </is>
       </c>
       <c r="N178" s="8" t="inlineStr">
         <is>
-          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="105" customHeight="1">
+          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="45" customHeight="1">
       <c r="A179" s="2" t="n">
         <v>178</v>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>MOD-A</t>
+          <t>MOD-3</t>
         </is>
       </c>
       <c r="C179" s="9" t="inlineStr">
@@ -10541,24 +10525,32 @@
       </c>
       <c r="E179" s="6" t="inlineStr">
         <is>
-          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
+          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
         </is>
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
+          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
         </is>
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
-        </is>
-      </c>
-      <c r="H179" s="2" t="inlineStr"/>
-      <c r="I179" s="5" t="inlineStr"/>
+          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="I179" s="5" t="inlineStr">
+        <is>
+          <t>Win: full auth-gated test coverage in CI.</t>
+        </is>
+      </c>
       <c r="J179" s="5" t="inlineStr">
         <is>
-          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
+          <t>Trivial.</t>
         </is>
       </c>
       <c r="K179" s="12" t="inlineStr">
@@ -10568,17 +10560,17 @@
       </c>
       <c r="L179" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M179" s="3" t="inlineStr">
         <is>
-          <t>9517bbbe9..7229d4ccb</t>
+          <t>2b7d2f40f</t>
         </is>
       </c>
       <c r="N179" s="8" t="inlineStr">
         <is>
-          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
+          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
         </is>
       </c>
     </row>
@@ -10588,7 +10580,7 @@
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>MOD-B</t>
+          <t>MOD-A</t>
         </is>
       </c>
       <c r="C180" s="9" t="inlineStr">
@@ -10603,24 +10595,24 @@
       </c>
       <c r="E180" s="6" t="inlineStr">
         <is>
-          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
+          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
         </is>
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
+          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
         </is>
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr"/>
       <c r="I180" s="5" t="inlineStr"/>
       <c r="J180" s="5" t="inlineStr">
         <is>
-          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
+          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
         </is>
       </c>
       <c r="K180" s="12" t="inlineStr">
@@ -10635,22 +10627,22 @@
       </c>
       <c r="M180" s="3" t="inlineStr">
         <is>
-          <t>18ef1002e..388c316c4</t>
+          <t>9517bbbe9..7229d4ccb</t>
         </is>
       </c>
       <c r="N180" s="8" t="inlineStr">
         <is>
-          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="45" customHeight="1">
+          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="105" customHeight="1">
       <c r="A181" s="2" t="n">
         <v>180</v>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>UI-2</t>
+          <t>MOD-B</t>
         </is>
       </c>
       <c r="C181" s="9" t="inlineStr">
@@ -10660,37 +10652,29 @@
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>UI / Overview</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E181" s="6" t="inlineStr">
         <is>
-          <t>Overview tab: align reads with sibling-tab canonical sources</t>
+          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
         </is>
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>Overview read flat T.* fields that drift from sibling-tab displays. Different precedence rules across tabs.</t>
+          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr">
         <is>
-          <t>Refactored overview.js: T.fund_real, T.insider_full, T.news_sentiment_score, T.options_iv, T.technicals.indicators precedence first.</t>
-        </is>
-      </c>
-      <c r="H181" s="2" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="I181" s="5" t="inlineStr">
-        <is>
-          <t>Low risk / Medium win (consistency)</t>
-        </is>
-      </c>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr"/>
+      <c r="I181" s="5" t="inlineStr"/>
       <c r="J181" s="5" t="inlineStr">
         <is>
-          <t>All reads use ?? fallbacks.</t>
+          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
         </is>
       </c>
       <c r="K181" s="12" t="inlineStr">
@@ -10705,12 +10689,12 @@
       </c>
       <c r="M181" s="3" t="inlineStr">
         <is>
-          <t>5ffdd8e07</t>
+          <t>18ef1002e..388c316c4</t>
         </is>
       </c>
       <c r="N181" s="8" t="inlineStr">
         <is>
-          <t>Compare Overview vs Fundamentals/Sentiment/Insider/Options sub-tabs - numbers should match.</t>
+          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
         </is>
       </c>
     </row>
@@ -10720,7 +10704,7 @@
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>RULE-1</t>
+          <t>UI-2</t>
         </is>
       </c>
       <c r="C182" s="9" t="inlineStr">
@@ -10730,35 +10714,39 @@
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>UI / Rule Engine</t>
+          <t>UI / Overview</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
         <is>
-          <t>Rule Engine: 8-gate cascade + multiplier stack + regime4_thresholds</t>
+          <t>Overview tab: align reads with sibling-tab canonical sources</t>
         </is>
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>Rule Engine read legacy T.gate.passed not T.gates_evaluated. Did not show setup_size_multiplier or kelly_size.* multipliers.</t>
+          <t>Overview read flat T.* fields that drift from sibling-tab displays. Different precedence rules across tabs.</t>
         </is>
       </c>
       <c r="G182" s="5" t="inlineStr">
         <is>
-          <t>Added Stage 2.5 (8-Gate Cascade). Stage 8 surfaces full multiplier stack. Counterfactuals read regime4-aware threshold first.</t>
+          <t>Refactored overview.js: T.fund_real, T.insider_full, T.news_sentiment_score, T.options_iv, T.technicals.indicators precedence first.</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>45 min</t>
         </is>
       </c>
       <c r="I182" s="5" t="inlineStr">
         <is>
-          <t>Low risk / Medium win (transparency)</t>
-        </is>
-      </c>
-      <c r="J182" s="5" t="inlineStr"/>
+          <t>Low risk / Medium win (consistency)</t>
+        </is>
+      </c>
+      <c r="J182" s="5" t="inlineStr">
+        <is>
+          <t>All reads use ?? fallbacks.</t>
+        </is>
+      </c>
       <c r="K182" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -10771,22 +10759,22 @@
       </c>
       <c r="M182" s="3" t="inlineStr">
         <is>
-          <t>40f8452b8</t>
+          <t>5ffdd8e07</t>
         </is>
       </c>
       <c r="N182" s="8" t="inlineStr">
         <is>
-          <t>Open elite-detail Rule Engine sub-tab. Stage 2.5 shows 8 gates pass/fail. TC ticker in bull shows "Setup edge multiplier - KILLED 0.00x".</t>
-        </is>
-      </c>
-    </row>
-    <row r="183" ht="105" customHeight="1">
+          <t>Compare Overview vs Fundamentals/Sentiment/Insider/Options sub-tabs - numbers should match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="45" customHeight="1">
       <c r="A183" s="2" t="n">
         <v>182</v>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>TARGET-SOURCES-P1</t>
+          <t>RULE-1</t>
         </is>
       </c>
       <c r="C183" s="9" t="inlineStr">
@@ -10796,39 +10784,35 @@
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>UI / Trade Plan</t>
+          <t>UI / Rule Engine</t>
         </is>
       </c>
       <c r="E183" s="6" t="inlineStr">
         <is>
-          <t>Phase 1 structural target sources (display-only)</t>
+          <t>Rule Engine: 8-gate cascade + multiplier stack + regime4_thresholds</t>
         </is>
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>Target prices come from generic ATR multiples. User wants targets from objective TA sources: order blocks, fractals, fib levels, EW waves — per horizon (short/medium/long).</t>
+          <t>Rule Engine read legacy T.gate.passed not T.gates_evaluated. Did not show setup_size_multiplier or kelly_size.* multipliers.</t>
         </is>
       </c>
       <c r="G183" s="5" t="inlineStr">
         <is>
-          <t>New plan.target_sources field populated in compute_trade_plan with 5 sources: (1) fractal_high (Williams 5-bar, short horizon), (2) fib_127_extension (medium), (3) fib_162_extension (medium), (4) ew_intermediate_t1 (v1 Wave-3 1.618×W1, medium), (5) ew_intermediate_t2 (v1 2.618×W1, long). DISPLAY ONLY — actual T1/T2 unchanged. Need ≥30 trade evidence per source × regime before changing BUY logic (Phase 2).</t>
+          <t>Added Stage 2.5 (8-Gate Cascade). Stage 8 surfaces full multiplier stack. Counterfactuals read regime4-aware threshold first.</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>1.5 hrs</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I183" s="5" t="inlineStr">
         <is>
-          <t>Low (no behavior change)</t>
-        </is>
-      </c>
-      <c r="J183" s="5" t="inlineStr">
-        <is>
-          <t>Phase 2 (config-driven flip to structural targets) deferred until Phase 1 evidence collected. Order blocks (SMC) not yet sourced — separate sub-task to wire into target_sources.</t>
-        </is>
-      </c>
+          <t>Low risk / Medium win (transparency)</t>
+        </is>
+      </c>
+      <c r="J183" s="5" t="inlineStr"/>
       <c r="K183" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -10841,22 +10825,22 @@
       </c>
       <c r="M183" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>40f8452b8</t>
         </is>
       </c>
       <c r="N183" s="8" t="inlineStr">
         <is>
-          <t>Test ticker → plan.target_sources dict should have 3-5 entries, each with {horizon, level, rationale}. Phase 2 will surface in elite-detail Plan tab and Overview Trade Plan strip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="184" ht="45" customHeight="1">
+          <t>Open elite-detail Rule Engine sub-tab. Stage 2.5 shows 8 gates pass/fail. TC ticker in bull shows "Setup edge multiplier - KILLED 0.00x".</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="105" customHeight="1">
       <c r="A184" s="2" t="n">
         <v>183</v>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>UNIVERSE-NASDAQ-1000</t>
+          <t>TARGET-SOURCES-P1</t>
         </is>
       </c>
       <c r="C184" s="9" t="inlineStr">
@@ -10866,27 +10850,39 @@
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>Universe</t>
+          <t>UI / Trade Plan</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
         <is>
-          <t>NASDAQ 1000 liquidity gate</t>
+          <t>Phase 1 structural target sources (display-only)</t>
         </is>
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>get_nasdaq_all replaced full 4805-name exchange list with top-1000 by dollar volume (one bulk_eod call); config nasdaq_all_top_n/min_dollar_vol</t>
+          <t>Target prices come from generic ATR multiples. User wants targets from objective TA sources: order blocks, fractals, fib levels, EW waves — per horizon (short/medium/long).</t>
         </is>
       </c>
       <c r="G184" s="5" t="inlineStr">
         <is>
-          <t>data_fetcher.get_nasdaq_all + config.json + swing_trade.py</t>
-        </is>
-      </c>
-      <c r="H184" s="2" t="inlineStr"/>
-      <c r="I184" s="5" t="inlineStr"/>
-      <c r="J184" s="5" t="inlineStr"/>
+          <t>New plan.target_sources field populated in compute_trade_plan with 5 sources: (1) fractal_high (Williams 5-bar, short horizon), (2) fib_127_extension (medium), (3) fib_162_extension (medium), (4) ew_intermediate_t1 (v1 Wave-3 1.618×W1, medium), (5) ew_intermediate_t2 (v1 2.618×W1, long). DISPLAY ONLY — actual T1/T2 unchanged. Need ≥30 trade evidence per source × regime before changing BUY logic (Phase 2).</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>1.5 hrs</t>
+        </is>
+      </c>
+      <c r="I184" s="5" t="inlineStr">
+        <is>
+          <t>Low (no behavior change)</t>
+        </is>
+      </c>
+      <c r="J184" s="5" t="inlineStr">
+        <is>
+          <t>Phase 2 (config-driven flip to structural targets) deferred until Phase 1 evidence collected. Order blocks (SMC) not yet sourced — separate sub-task to wire into target_sources.</t>
+        </is>
+      </c>
       <c r="K184" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -10894,15 +10890,19 @@
       </c>
       <c r="L184" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M184" s="3" t="inlineStr">
         <is>
-          <t>ab1deacef</t>
-        </is>
-      </c>
-      <c r="N184" s="8" t="inlineStr"/>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N184" s="8" t="inlineStr">
+        <is>
+          <t>Test ticker → plan.target_sources dict should have 3-5 entries, each with {horizon, level, rationale}. Phase 2 will surface in elite-detail Plan tab and Overview Trade Plan strip.</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="45" customHeight="1">
       <c r="A185" s="2" t="n">
@@ -10910,7 +10910,7 @@
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>STOCKSMITH-KAIROS-DOSSIER</t>
+          <t>UNIVERSE-NASDAQ-1000</t>
         </is>
       </c>
       <c r="C185" s="9" t="inlineStr">
@@ -10920,22 +10920,22 @@
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>V2 Dashboard / Kairos</t>
+          <t>Universe</t>
         </is>
       </c>
       <c r="E185" s="6" t="inlineStr">
         <is>
-          <t>Ask Kairos cross-lens ticker dossier (§4)</t>
+          <t>NASDAQ 1000 liquidity gate</t>
         </is>
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>composite verdict + 9 lens stances + ML projection injected as LLM context; fallbackAnswer offline</t>
+          <t>get_nasdaq_all replaced full 4805-name exchange list with top-1000 by dollar volume (one bulk_eod call); config nasdaq_all_top_n/min_dollar_vol</t>
         </is>
       </c>
       <c r="G185" s="5" t="inlineStr">
         <is>
-          <t>Stocksmith.html kaiTickerDossier</t>
+          <t>data_fetcher.get_nasdaq_all + config.json + swing_trade.py</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr"/>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="M185" s="3" t="inlineStr">
         <is>
-          <t>e3baa715f</t>
+          <t>ab1deacef</t>
         </is>
       </c>
       <c r="N185" s="8" t="inlineStr"/>
@@ -10964,7 +10964,7 @@
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>REGIME-ACCURACY-TEST</t>
+          <t>STOCKSMITH-KAIROS-DOSSIER</t>
         </is>
       </c>
       <c r="C186" s="9" t="inlineStr">
@@ -10974,22 +10974,22 @@
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>Validation / Regime</t>
+          <t>V2 Dashboard / Kairos</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
         <is>
-          <t>Regime-classification accuracy test (principle 18)</t>
+          <t>Ask Kairos cross-lens ticker dossier (§4)</t>
         </is>
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>when model said trending was next 5d actually trending? label regime outcomes, validate classifier</t>
+          <t>composite verdict + 9 lens stances + ML projection injected as LLM context; fallbackAnswer offline</t>
         </is>
       </c>
       <c r="G186" s="5" t="inlineStr">
         <is>
-          <t>scripts/regime_accuracy.py</t>
+          <t>Stocksmith.html kaiTickerDossier</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr"/>
@@ -11002,48 +11002,48 @@
       </c>
       <c r="L186" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
-          <t>d1ea97913</t>
+          <t>e3baa715f</t>
         </is>
       </c>
       <c r="N186" s="8" t="inlineStr"/>
     </row>
-    <row r="187" ht="90" customHeight="1">
+    <row r="187" ht="45" customHeight="1">
       <c r="A187" s="2" t="n">
         <v>186</v>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>WEEKEND-PHANTOMS</t>
-        </is>
-      </c>
-      <c r="C187" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>REGIME-ACCURACY-TEST</t>
+        </is>
+      </c>
+      <c r="C187" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>Audit Trail / Data Quality</t>
+          <t>Validation / Regime</t>
         </is>
       </c>
       <c r="E187" s="6" t="inlineStr">
         <is>
-          <t>Weekend pick_dates (Sat/Sun) in audit ledger</t>
+          <t>Regime-classification accuracy test (principle 18)</t>
         </is>
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
-          <t>signal_log writes pick_date as today.isoformat() — when scan runs on weekend (manual rerun), produces Sat/Sun dates EODHD can't price. 355 such phantoms in ledger. Fix: snap weekend dates forward to next Monday at both write-time (signal_tracker.log_signals) and build-time (build_audit_ledger.py). Preserves original via pick_date_orig field</t>
+          <t>when model said trending was next 5d actually trending? label regime outcomes, validate classifier</t>
         </is>
       </c>
       <c r="G187" s="5" t="inlineStr">
         <is>
-          <t>signal_tracker.py log_signals dow snap + build_audit_ledger.py _compute_returns_for_ticker snap-forward · 353 records normalized · 2 residual edge cases</t>
+          <t>scripts/regime_accuracy.py</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr"/>
@@ -11056,23 +11056,23 @@
       </c>
       <c r="L187" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M187" s="3" t="inlineStr">
         <is>
-          <t>e48edac16</t>
+          <t>d1ea97913</t>
         </is>
       </c>
       <c r="N187" s="8" t="inlineStr"/>
     </row>
-    <row r="188" ht="75" customHeight="1">
+    <row r="188" ht="90" customHeight="1">
       <c r="A188" s="2" t="n">
         <v>187</v>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>BT-GUARD-1</t>
+          <t>WEEKEND-PHANTOMS</t>
         </is>
       </c>
       <c r="C188" s="10" t="inlineStr">
@@ -11082,22 +11082,22 @@
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>Backtest Infrastructure</t>
+          <t>Audit Trail / Data Quality</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
         <is>
-          <t>Backtest min_score guard rail</t>
+          <t>Weekend pick_dates (Sat/Sun) in audit ledger</t>
         </is>
       </c>
       <c r="F188" s="5" t="inlineStr">
         <is>
-          <t>Users (and Claude sessions) repeatedly ran 252d backtests with --min-score 65 (live threshold) producing 0 BUYs across all 252 days. Historical scoring is structurally suppressed because sentiment/options/catalyst pillars depend on real-time data not in EODHD backfill.</t>
+          <t>signal_log writes pick_date as today.isoformat() — when scan runs on weekend (manual rerun), produces Sat/Sun dates EODHD can't price. 355 such phantoms in ledger. Fix: snap weekend dates forward to next Monday at both write-time (signal_tracker.log_signals) and build-time (build_audit_ledger.py). Preserves original via pick_date_orig field</t>
         </is>
       </c>
       <c r="G188" s="5" t="inlineStr">
         <is>
-          <t>backtest.py main() now warns loudly when --min-score &gt; 55 (backtest-safe floor). New --accept-low-buys flag silences the warning for legitimate grid-search explorations. --smoke bypasses the guard. Plus diagnostic doc: docs/backtest_historical_scoring_diagnostic.md.</t>
+          <t>signal_tracker.py log_signals dow snap + build_audit_ledger.py _compute_returns_for_ticker snap-forward · 353 records normalized · 2 residual edge cases</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr"/>
@@ -11115,18 +11115,18 @@
       </c>
       <c r="M188" s="3" t="inlineStr">
         <is>
-          <t>d754830</t>
+          <t>e48edac16</t>
         </is>
       </c>
       <c r="N188" s="8" t="inlineStr"/>
     </row>
-    <row r="189" ht="45" customHeight="1">
+    <row r="189" ht="75" customHeight="1">
       <c r="A189" s="2" t="n">
         <v>188</v>
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-1</t>
+          <t>BT-GUARD-1</t>
         </is>
       </c>
       <c r="C189" s="10" t="inlineStr">
@@ -11136,22 +11136,22 @@
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
-          <t>Choice C Strategy</t>
+          <t>Backtest Infrastructure</t>
         </is>
       </c>
       <c r="E189" s="6" t="inlineStr">
         <is>
-          <t>Design doc — docs/strategy_defensive_rotation.md</t>
+          <t>Backtest min_score guard rail</t>
         </is>
       </c>
       <c r="F189" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 of Defensive Rotation sleeve build</t>
+          <t>Users (and Claude sessions) repeatedly ran 252d backtests with --min-score 65 (live threshold) producing 0 BUYs across all 252 days. Historical scoring is structurally suppressed because sentiment/options/catalyst pillars depend on real-time data not in EODHD backfill.</t>
         </is>
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Full design: mechanism, triggers, universe, validation plan</t>
+          <t>backtest.py main() now warns loudly when --min-score &gt; 55 (backtest-safe floor). New --accept-low-buys flag silences the warning for legitimate grid-search explorations. --smoke bypasses the guard. Plus diagnostic doc: docs/backtest_historical_scoring_diagnostic.md.</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr"/>
@@ -11164,12 +11164,12 @@
       </c>
       <c r="L189" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M189" s="3" t="inlineStr">
         <is>
-          <t>399922797</t>
+          <t>d754830</t>
         </is>
       </c>
       <c r="N189" s="8" t="inlineStr"/>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-2</t>
+          <t>DEFROT-1</t>
         </is>
       </c>
       <c r="C190" s="10" t="inlineStr">
@@ -11195,7 +11195,7 @@
       </c>
       <c r="E190" s="6" t="inlineStr">
         <is>
-          <t>Config block — defensive_rotation_sleeve</t>
+          <t>Design doc — docs/strategy_defensive_rotation.md</t>
         </is>
       </c>
       <c r="F190" s="5" t="inlineStr">
@@ -11205,7 +11205,7 @@
       </c>
       <c r="G190" s="5" t="inlineStr">
         <is>
-          <t>Curated universe, regime gates, sizing, stops; default _enabled=false</t>
+          <t>Full design: mechanism, triggers, universe, validation plan</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr"/>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-3</t>
+          <t>DEFROT-2</t>
         </is>
       </c>
       <c r="C191" s="10" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="E191" s="6" t="inlineStr">
         <is>
-          <t>Detector function — _detect_defensive_rotation</t>
+          <t>Config block — defensive_rotation_sleeve</t>
         </is>
       </c>
       <c r="F191" s="5" t="inlineStr">
@@ -11259,7 +11259,7 @@
       </c>
       <c r="G191" s="5" t="inlineStr">
         <is>
-          <t>Universe + regime + SPY-50EMA + RS + beta + ATR gates with per-criterion audit</t>
+          <t>Curated universe, regime gates, sizing, stops; default _enabled=false</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr"/>
@@ -11288,7 +11288,7 @@
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-4</t>
+          <t>DEFROT-3</t>
         </is>
       </c>
       <c r="C192" s="10" t="inlineStr">
@@ -11303,7 +11303,7 @@
       </c>
       <c r="E192" s="6" t="inlineStr">
         <is>
-          <t>Wire into analyze_ticker</t>
+          <t>Detector function — _detect_defensive_rotation</t>
         </is>
       </c>
       <c r="F192" s="5" t="inlineStr">
@@ -11313,7 +11313,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>Setup family override + trade plan override (1.0 ATR stop, T1+3, T2+6, hold 10-30d, regime exit on SPY 50EMA reclaim)</t>
+          <t>Universe + regime + SPY-50EMA + RS + beta + ATR gates with per-criterion audit</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr"/>
@@ -11342,7 +11342,7 @@
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-5</t>
+          <t>DEFROT-4</t>
         </is>
       </c>
       <c r="C193" s="10" t="inlineStr">
@@ -11357,7 +11357,7 @@
       </c>
       <c r="E193" s="6" t="inlineStr">
         <is>
-          <t>Decision engine bypasses</t>
+          <t>Wire into analyze_ticker</t>
         </is>
       </c>
       <c r="F193" s="5" t="inlineStr">
@@ -11367,7 +11367,7 @@
       </c>
       <c r="G193" s="5" t="inlineStr">
         <is>
-          <t>regime_gate + entry_quality + fund_adequacy bypassed for Defensive Rotation family</t>
+          <t>Setup family override + trade plan override (1.0 ATR stop, T1+3, T2+6, hold 10-30d, regime exit on SPY 50EMA reclaim)</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr"/>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-6</t>
+          <t>DEFROT-5</t>
         </is>
       </c>
       <c r="C194" s="10" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="E194" s="6" t="inlineStr">
         <is>
-          <t>Universe coverage</t>
+          <t>Decision engine bypasses</t>
         </is>
       </c>
       <c r="F194" s="5" t="inlineStr">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>XLP, TLT, IEF added to custom_watchlist (XLU/XLV/GLD already present)</t>
+          <t>regime_gate + entry_quality + fund_adequacy bypassed for Defensive Rotation family</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr"/>
@@ -11450,7 +11450,7 @@
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-7</t>
+          <t>DEFROT-6</t>
         </is>
       </c>
       <c r="C195" s="10" t="inlineStr">
@@ -11465,7 +11465,7 @@
       </c>
       <c r="E195" s="6" t="inlineStr">
         <is>
-          <t>Smoke test + commit</t>
+          <t>Universe coverage</t>
         </is>
       </c>
       <c r="F195" s="5" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>All 4 detector tests pass; ready for Phase 1 paper validation</t>
+          <t>XLP, TLT, IEF added to custom_watchlist (XLU/XLV/GLD already present)</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr"/>
@@ -11504,7 +11504,7 @@
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-1</t>
+          <t>DEFROT-7</t>
         </is>
       </c>
       <c r="C196" s="10" t="inlineStr">
@@ -11519,17 +11519,17 @@
       </c>
       <c r="E196" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion design doc</t>
+          <t>Smoke test + commit</t>
         </is>
       </c>
       <c r="F196" s="5" t="inlineStr">
         <is>
-          <t>Sleeve build</t>
+          <t>Phase 1 of Defensive Rotation sleeve build</t>
         </is>
       </c>
       <c r="G196" s="5" t="inlineStr">
         <is>
-          <t>docs/strategy_mean_reversion.md — full Jegadeesh 1990 mechanism + validation plan</t>
+          <t>All 4 detector tests pass; ready for Phase 1 paper validation</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr"/>
@@ -11547,7 +11547,7 @@
       </c>
       <c r="M196" s="3" t="inlineStr">
         <is>
-          <t>d0c6c4e04</t>
+          <t>399922797</t>
         </is>
       </c>
       <c r="N196" s="8" t="inlineStr"/>
@@ -11558,7 +11558,7 @@
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-2</t>
+          <t>MEANREV-1</t>
         </is>
       </c>
       <c r="C197" s="10" t="inlineStr">
@@ -11573,7 +11573,7 @@
       </c>
       <c r="E197" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion config</t>
+          <t>Mean Reversion design doc</t>
         </is>
       </c>
       <c r="F197" s="5" t="inlineStr">
@@ -11583,7 +11583,7 @@
       </c>
       <c r="G197" s="5" t="inlineStr">
         <is>
-          <t>RSI&lt;30, EMA200 floor, 3-5d hold; default _enabled=true (fires in current choppy regime)</t>
+          <t>docs/strategy_mean_reversion.md — full Jegadeesh 1990 mechanism + validation plan</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr"/>
@@ -11612,7 +11612,7 @@
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-3</t>
+          <t>MEANREV-2</t>
         </is>
       </c>
       <c r="C198" s="10" t="inlineStr">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="E198" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion detector</t>
+          <t>Mean Reversion config</t>
         </is>
       </c>
       <c r="F198" s="5" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G198" s="5" t="inlineStr">
         <is>
-          <t>_detect_mean_reversion — 8-gate audit (regime/score/RSI/EMA200/recent_low/RVOL/ADV/earnings)</t>
+          <t>RSI&lt;30, EMA200 floor, 3-5d hold; default _enabled=true (fires in current choppy regime)</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr"/>
@@ -11666,7 +11666,7 @@
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-4</t>
+          <t>MEANREV-3</t>
         </is>
       </c>
       <c r="C199" s="10" t="inlineStr">
@@ -11681,7 +11681,7 @@
       </c>
       <c r="E199" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion wiring</t>
+          <t>Mean Reversion detector</t>
         </is>
       </c>
       <c r="F199" s="5" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Setup family override + plan (1.0 ATR stop, +3/+5% T1/T2, 3-5d hold, hard time-stop)</t>
+          <t>_detect_mean_reversion — 8-gate audit (regime/score/RSI/EMA200/recent_low/RVOL/ADV/earnings)</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr"/>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-5</t>
+          <t>MEANREV-4</t>
         </is>
       </c>
       <c r="C200" s="10" t="inlineStr">
@@ -11735,7 +11735,7 @@
       </c>
       <c r="E200" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion bypass</t>
+          <t>Mean Reversion wiring</t>
         </is>
       </c>
       <c r="F200" s="5" t="inlineStr">
@@ -11745,7 +11745,7 @@
       </c>
       <c r="G200" s="5" t="inlineStr">
         <is>
-          <t>entry_quality bypass (EXTENDED-down IS the trigger)</t>
+          <t>Setup family override + plan (1.0 ATR stop, +3/+5% T1/T2, 3-5d hold, hard time-stop)</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr"/>
@@ -11774,7 +11774,7 @@
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-6</t>
+          <t>MEANREV-5</t>
         </is>
       </c>
       <c r="C201" s="10" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="E201" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion smoke test</t>
+          <t>Mean Reversion bypass</t>
         </is>
       </c>
       <c r="F201" s="5" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="G201" s="5" t="inlineStr">
         <is>
-          <t>4 detector tests pass — fired=True on choppy+RSI=25+EMA200, rejected on RSI=55/below-EMA200/trending</t>
+          <t>entry_quality bypass (EXTENDED-down IS the trigger)</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr"/>
@@ -11828,7 +11828,7 @@
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>PEAD-1</t>
+          <t>MEANREV-6</t>
         </is>
       </c>
       <c r="C202" s="10" t="inlineStr">
@@ -11843,7 +11843,7 @@
       </c>
       <c r="E202" s="6" t="inlineStr">
         <is>
-          <t>PEAD design doc</t>
+          <t>Mean Reversion smoke test</t>
         </is>
       </c>
       <c r="F202" s="5" t="inlineStr">
@@ -11853,7 +11853,7 @@
       </c>
       <c r="G202" s="5" t="inlineStr">
         <is>
-          <t>docs/strategy_pead.md — Bernard-Thomas 1989, all-regime catalyst sleeve</t>
+          <t>4 detector tests pass — fired=True on choppy+RSI=25+EMA200, rejected on RSI=55/below-EMA200/trending</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr"/>
@@ -11882,7 +11882,7 @@
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>PEAD-2</t>
+          <t>PEAD-1</t>
         </is>
       </c>
       <c r="C203" s="10" t="inlineStr">
@@ -11897,7 +11897,7 @@
       </c>
       <c r="E203" s="6" t="inlineStr">
         <is>
-          <t>PEAD config</t>
+          <t>PEAD design doc</t>
         </is>
       </c>
       <c r="F203" s="5" t="inlineStr">
@@ -11907,7 +11907,7 @@
       </c>
       <c r="G203" s="5" t="inlineStr">
         <is>
-          <t>Day1-3 post-earnings, EPS+5/Rev+2/Gap+3/Revisions&gt;=2, full Kelly with regime caps</t>
+          <t>docs/strategy_pead.md — Bernard-Thomas 1989, all-regime catalyst sleeve</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr"/>
@@ -11936,7 +11936,7 @@
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>PEAD-3</t>
+          <t>PEAD-2</t>
         </is>
       </c>
       <c r="C204" s="10" t="inlineStr">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="E204" s="6" t="inlineStr">
         <is>
-          <t>PEAD detector</t>
+          <t>PEAD config</t>
         </is>
       </c>
       <c r="F204" s="5" t="inlineStr">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="G204" s="5" t="inlineStr">
         <is>
-          <t>_detect_pead — 7-gate audit; regime-independent</t>
+          <t>Day1-3 post-earnings, EPS+5/Rev+2/Gap+3/Revisions&gt;=2, full Kelly with regime caps</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr"/>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>PEAD-4</t>
+          <t>PEAD-3</t>
         </is>
       </c>
       <c r="C205" s="10" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="E205" s="6" t="inlineStr">
         <is>
-          <t>PEAD wiring</t>
+          <t>PEAD detector</t>
         </is>
       </c>
       <c r="F205" s="5" t="inlineStr">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="G205" s="5" t="inlineStr">
         <is>
-          <t>Setup family override + plan (1.0 ATR stop, +5/+10/+15 targets, 10-30d drift hold)</t>
+          <t>_detect_pead — 7-gate audit; regime-independent</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr"/>
@@ -12044,7 +12044,7 @@
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>PEAD-5</t>
+          <t>PEAD-4</t>
         </is>
       </c>
       <c r="C206" s="10" t="inlineStr">
@@ -12059,7 +12059,7 @@
       </c>
       <c r="E206" s="6" t="inlineStr">
         <is>
-          <t>PEAD bypasses</t>
+          <t>PEAD wiring</t>
         </is>
       </c>
       <c r="F206" s="5" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="G206" s="5" t="inlineStr">
         <is>
-          <t>regime_gate bypassed (catalyst regime-independent), entry_quality bypassed (gap-up IS trigger)</t>
+          <t>Setup family override + plan (1.0 ATR stop, +5/+10/+15 targets, 10-30d drift hold)</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr"/>
@@ -12098,7 +12098,7 @@
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>PEAD-6</t>
+          <t>PEAD-5</t>
         </is>
       </c>
       <c r="C207" s="10" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="E207" s="6" t="inlineStr">
         <is>
-          <t>PEAD smoke test</t>
+          <t>PEAD bypasses</t>
         </is>
       </c>
       <c r="F207" s="5" t="inlineStr">
@@ -12123,7 +12123,7 @@
       </c>
       <c r="G207" s="5" t="inlineStr">
         <is>
-          <t>Perfect-setup test fires with all 7 audit checks ✓</t>
+          <t>regime_gate bypassed (catalyst regime-independent), entry_quality bypassed (gap-up IS trigger)</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr"/>
@@ -12152,7 +12152,7 @@
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>CLEANUP-HOT-SECTORS</t>
+          <t>PEAD-6</t>
         </is>
       </c>
       <c r="C208" s="10" t="inlineStr">
@@ -12162,22 +12162,22 @@
       </c>
       <c r="D208" s="5" t="inlineStr">
         <is>
-          <t>Code Hygiene / Signal Scanner</t>
+          <t>Choice C Strategy</t>
         </is>
       </c>
       <c r="E208" s="6" t="inlineStr">
         <is>
-          <t>Remove dead panelHotSectors function</t>
+          <t>PEAD smoke test</t>
         </is>
       </c>
       <c r="F208" s="5" t="inlineStr">
         <is>
-          <t>User asked to remove Hot Sectors panel from grid earlier; function left in file as dead code. Removed 53 lines.</t>
+          <t>Sleeve build</t>
         </is>
       </c>
       <c r="G208" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantScanner module · panelHotSectors() deleted</t>
+          <t>Perfect-setup test fires with all 7 audit checks ✓</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr"/>
@@ -12190,23 +12190,23 @@
       </c>
       <c r="L208" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="M208" s="3" t="inlineStr">
         <is>
-          <t>e48edac16</t>
+          <t>d0c6c4e04</t>
         </is>
       </c>
       <c r="N208" s="8" t="inlineStr"/>
     </row>
-    <row r="209" ht="105" customHeight="1">
+    <row r="209" ht="45" customHeight="1">
       <c r="A209" s="2" t="n">
         <v>208</v>
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>UI-CRYPTO-1</t>
+          <t>CLEANUP-HOT-SECTORS</t>
         </is>
       </c>
       <c r="C209" s="10" t="inlineStr">
@@ -12216,22 +12216,22 @@
       </c>
       <c r="D209" s="5" t="inlineStr">
         <is>
-          <t>Crypto Tab</t>
+          <t>Code Hygiene / Signal Scanner</t>
         </is>
       </c>
       <c r="E209" s="6" t="inlineStr">
         <is>
-          <t>20yr HF analyst Crypto tab rebuild</t>
+          <t>Remove dead panelHotSectors function</t>
         </is>
       </c>
       <c r="F209" s="5" t="inlineStr">
         <is>
-          <t>Crypto tab was stub with 4 cards of placeholder data. Needed a senior HF/Graham-Buffett/swing-trader fused lens for the 24/7 risk-asset bellwether.</t>
+          <t>User asked to remove Hot Sectors panel from grid earlier; function left in file as dead code. Removed 53 lines.</t>
         </is>
       </c>
       <c r="G209" s="5" t="inlineStr">
         <is>
-          <t>13-section renderCrypto in kairos.html: cycle posture banner (Pi-Cycle/MVRV-Z/NUPL/200wk MA), spot KPIs, Graham margin-of-safety floors (realized price, thermo-cap, cost of production, LTH/STH cost), ETH owner-earnings DCF, BTC hard-money compounding, stablecoin liquidity, macro drivers, spot ETF flows, derivatives tape, on-chain valuation composite, catalyst calendar, adjacent equities, L1/L2 rotation, regime-conditional playbook, pre-mortem.</t>
+          <t>kairos.html QuantScanner module · panelHotSectors() deleted</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr"/>
@@ -12249,18 +12249,18 @@
       </c>
       <c r="M209" s="3" t="inlineStr">
         <is>
-          <t>696731a4d</t>
+          <t>e48edac16</t>
         </is>
       </c>
       <c r="N209" s="8" t="inlineStr"/>
     </row>
-    <row r="210" ht="75" customHeight="1">
+    <row r="210" ht="105" customHeight="1">
       <c r="A210" s="2" t="n">
         <v>209</v>
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>EODHD-EDGAR-FUNDAMENTALS</t>
+          <t>UI-CRYPTO-1</t>
         </is>
       </c>
       <c r="C210" s="10" t="inlineStr">
@@ -12270,22 +12270,22 @@
       </c>
       <c r="D210" s="5" t="inlineStr">
         <is>
-          <t>Data / SEC EDGAR (future quality)</t>
+          <t>Crypto Tab</t>
         </is>
       </c>
       <c r="E210" s="6" t="inlineStr">
         <is>
-          <t>Offload fundamentals to SEC EDGAR (FIX 4)</t>
+          <t>20yr HF analyst Crypto tab rebuild</t>
         </is>
       </c>
       <c r="F210" s="5" t="inlineStr">
         <is>
-          <t>new edgar_client.py behind data_fetcher interface; data.sec.gov companyfacts (User-Agent + &lt;=10 req/s); map XBRL tags to fundamentals.db; nightly batch. Quality upgrade (point-in-time, fixes audit #1/#4) + zeroes per-ticker EODHD fundamentals calls.</t>
+          <t>Crypto tab was stub with 4 cards of placeholder data. Needed a senior HF/Graham-Buffett/swing-trader fused lens for the 24/7 risk-asset bellwether.</t>
         </is>
       </c>
       <c r="G210" s="5" t="inlineStr">
         <is>
-          <t>edgar_client.py + nightly batch</t>
+          <t>13-section renderCrypto in kairos.html: cycle posture banner (Pi-Cycle/MVRV-Z/NUPL/200wk MA), spot KPIs, Graham margin-of-safety floors (realized price, thermo-cap, cost of production, LTH/STH cost), ETH owner-earnings DCF, BTC hard-money compounding, stablecoin liquidity, macro drivers, spot ETF flows, derivatives tape, on-chain valuation composite, catalyst calendar, adjacent equities, L1/L2 rotation, regime-conditional playbook, pre-mortem.</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr"/>
@@ -12298,23 +12298,23 @@
       </c>
       <c r="L210" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M210" s="3" t="inlineStr">
         <is>
-          <t>5d05268ef</t>
+          <t>696731a4d</t>
         </is>
       </c>
       <c r="N210" s="8" t="inlineStr"/>
     </row>
-    <row r="211" ht="60" customHeight="1">
+    <row r="211" ht="75" customHeight="1">
       <c r="A211" s="2" t="n">
         <v>210</v>
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>SETDETAIL-FALLBACK</t>
+          <t>EODHD-EDGAR-FUNDAMENTALS</t>
         </is>
       </c>
       <c r="C211" s="10" t="inlineStr">
@@ -12324,22 +12324,22 @@
       </c>
       <c r="D211" s="5" t="inlineStr">
         <is>
-          <t>Detail UI / Routing</t>
+          <t>Data / SEC EDGAR (future quality)</t>
         </is>
       </c>
       <c r="E211" s="6" t="inlineStr">
         <is>
-          <t>setDetailTicker failed for R2000-only tickers</t>
+          <t>Offload fundamentals to SEC EDGAR (FIX 4)</t>
         </is>
       </c>
       <c r="F211" s="5" t="inlineStr">
         <is>
-          <t>Clicking ML Edge picks not in scan bundle (HOOD, ARES, STEM etc.) printed '[kairos] ticker not in scan' and never opened. Now synthesizes minimal t row from window.__mlEdgeCache so detail page opens with _fromMlEdge:true flag</t>
+          <t>new edgar_client.py behind data_fetcher interface; data.sec.gov companyfacts (User-Agent + &lt;=10 req/s); map XBRL tags to fundamentals.db; nightly batch. Quality upgrade (point-in-time, fixes audit #1/#4) + zeroes per-ticker EODHD fundamentals calls.</t>
         </is>
       </c>
       <c r="G211" s="5" t="inlineStr">
         <is>
-          <t>kairos.html window.setDetailTicker fallback block</t>
+          <t>edgar_client.py + nightly batch</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr"/>
@@ -12352,12 +12352,12 @@
       </c>
       <c r="L211" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M211" s="3" t="inlineStr">
         <is>
-          <t>27fd646b1</t>
+          <t>5d05268ef</t>
         </is>
       </c>
       <c r="N211" s="8" t="inlineStr"/>
@@ -12368,7 +12368,7 @@
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>SETDETAIL-FALLBACK</t>
         </is>
       </c>
       <c r="C212" s="10" t="inlineStr">
@@ -12378,34 +12378,26 @@
       </c>
       <c r="D212" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Detail UI / Routing</t>
         </is>
       </c>
       <c r="E212" s="6" t="inlineStr">
         <is>
-          <t>Update CLAUDE.md with new tools</t>
+          <t>setDetailTicker failed for R2000-only tickers</t>
         </is>
       </c>
       <c r="F212" s="5" t="inlineStr">
         <is>
-          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
+          <t>Clicking ML Edge picks not in scan bundle (HOOD, ARES, STEM etc.) printed '[kairos] ticker not in scan' and never opened. Now synthesizes minimal t row from window.__mlEdgeCache so detail page opens with _fromMlEdge:true flag</t>
         </is>
       </c>
       <c r="G212" s="5" t="inlineStr">
         <is>
-          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
-        </is>
-      </c>
-      <c r="H212" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I212" s="5" t="inlineStr">
-        <is>
-          <t>Win: future Claude sessions discover new tools.</t>
-        </is>
-      </c>
+          <t>kairos.html window.setDetailTicker fallback block</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr"/>
+      <c r="I212" s="5" t="inlineStr"/>
       <c r="J212" s="5" t="inlineStr"/>
       <c r="K212" s="12" t="inlineStr">
         <is>
@@ -12414,27 +12406,23 @@
       </c>
       <c r="L212" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M212" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-      <c r="N212" s="8" t="inlineStr">
-        <is>
-          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="213" ht="75" customHeight="1">
+          <t>27fd646b1</t>
+        </is>
+      </c>
+      <c r="N212" s="8" t="inlineStr"/>
+    </row>
+    <row r="213" ht="60" customHeight="1">
       <c r="A213" s="2" t="n">
         <v>212</v>
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="C213" s="10" t="inlineStr">
@@ -12449,17 +12437,17 @@
       </c>
       <c r="E213" s="6" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
+          <t>Update CLAUDE.md with new tools</t>
         </is>
       </c>
       <c r="F213" s="5" t="inlineStr">
         <is>
-          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
+          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
         </is>
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
+          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -12469,14 +12457,10 @@
       </c>
       <c r="I213" s="5" t="inlineStr">
         <is>
-          <t>Win: clear activation procedure before flipping live.</t>
-        </is>
-      </c>
-      <c r="J213" s="5" t="inlineStr">
-        <is>
-          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
-        </is>
-      </c>
+          <t>Win: future Claude sessions discover new tools.</t>
+        </is>
+      </c>
+      <c r="J213" s="5" t="inlineStr"/>
       <c r="K213" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -12489,12 +12473,12 @@
       </c>
       <c r="M213" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N213" s="8" t="inlineStr">
         <is>
-          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
+          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
         </is>
       </c>
     </row>
@@ -12504,7 +12488,7 @@
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>TWO-LOG-DOC</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="C214" s="10" t="inlineStr">
@@ -12519,22 +12503,34 @@
       </c>
       <c r="E214" s="6" t="inlineStr">
         <is>
-          <t>Two-log architecture (picks_history vs signal_log) was undocumented</t>
+          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
         </is>
       </c>
       <c r="F214" s="5" t="inlineStr">
         <is>
-          <t>Discovered 2026-05-10 during inflection diagnosis: cache/picks_history.json and data/signal_log.json track different realities (61.2% vs 12.7% recent WR). Tracker feedback reads picks_history; drift alerts read signal_log. Mis-attributing which log feeds which consumer wastes diagnostic time.</t>
+          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
         </is>
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>Add 'Two-Log Architecture' section to CLAUDE.md after EODHD section, with table mapping consumers + WR snapshots. Cross-reference portfolio_state.json as the ONLY real-trades log.</t>
-        </is>
-      </c>
-      <c r="H214" s="2" t="inlineStr"/>
-      <c r="I214" s="5" t="inlineStr"/>
-      <c r="J214" s="5" t="inlineStr"/>
+          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I214" s="5" t="inlineStr">
+        <is>
+          <t>Win: clear activation procedure before flipping live.</t>
+        </is>
+      </c>
+      <c r="J214" s="5" t="inlineStr">
+        <is>
+          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
+        </is>
+      </c>
       <c r="K214" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -12542,23 +12538,27 @@
       </c>
       <c r="L214" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M214" s="3" t="inlineStr">
         <is>
-          <t>8b06e56ae</t>
-        </is>
-      </c>
-      <c r="N214" s="8" t="inlineStr"/>
-    </row>
-    <row r="215" ht="60" customHeight="1">
+          <t>d8c08399b</t>
+        </is>
+      </c>
+      <c r="N214" s="8" t="inlineStr">
+        <is>
+          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="75" customHeight="1">
       <c r="A215" s="2" t="n">
         <v>214</v>
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>UI-HELP-1</t>
+          <t>TWO-LOG-DOC</t>
         </is>
       </c>
       <c r="C215" s="10" t="inlineStr">
@@ -12568,22 +12568,22 @@
       </c>
       <c r="D215" s="5" t="inlineStr">
         <is>
-          <t>Help System</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E215" s="6" t="inlineStr">
         <is>
-          <t>Help registry expanded 14 to 38 entries</t>
+          <t>Two-log architecture (picks_history vs signal_log) was undocumented</t>
         </is>
       </c>
       <c r="F215" s="5" t="inlineStr">
         <is>
-          <t>Help registry covered only workspace tabs. Detail sub-tabs and MarketsV2 ports had no help content.</t>
+          <t>Discovered 2026-05-10 during inflection diagnosis: cache/picks_history.json and data/signal_log.json track different realities (61.2% vs 12.7% recent WR). Tracker feedback reads picks_history; drift alerts read signal_log. Mis-attributing which log feeds which consumer wastes diagnostic time.</t>
         </is>
       </c>
       <c r="G215" s="5" t="inlineStr">
         <is>
-          <t>Added 24 new entries. kairosHelpFor threads isDetail through dispatcher — prefers detail_ namespace, falls back to bare key. Resolves portfolio workspace vs detail-subtab collision. MarketsV2 render block calls _injectHelpBtn.</t>
+          <t>Add 'Two-Log Architecture' section to CLAUDE.md after EODHD section, with table mapping consumers + WR snapshots. Cross-reference portfolio_state.json as the ONLY real-trades log.</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr"/>
@@ -12596,23 +12596,23 @@
       </c>
       <c r="L215" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M215" s="3" t="inlineStr">
         <is>
-          <t>696731a4d</t>
+          <t>8b06e56ae</t>
         </is>
       </c>
       <c r="N215" s="8" t="inlineStr"/>
     </row>
-    <row r="216" ht="45" customHeight="1">
+    <row r="216" ht="60" customHeight="1">
       <c r="A216" s="2" t="n">
         <v>215</v>
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>UI-HELP-1</t>
         </is>
       </c>
       <c r="C216" s="10" t="inlineStr">
@@ -12622,34 +12622,26 @@
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Help System</t>
         </is>
       </c>
       <c r="E216" s="6" t="inlineStr">
         <is>
-          <t>Git committer.email set globally</t>
+          <t>Help registry expanded 14 to 38 entries</t>
         </is>
       </c>
       <c r="F216" s="5" t="inlineStr">
         <is>
-          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
+          <t>Help registry covered only workspace tabs. Detail sub-tabs and MarketsV2 ports had no help content.</t>
         </is>
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
-        </is>
-      </c>
-      <c r="H216" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I216" s="5" t="inlineStr">
-        <is>
-          <t>Win: clean attribution in git log.</t>
-        </is>
-      </c>
+          <t>Added 24 new entries. kairosHelpFor threads isDetail through dispatcher — prefers detail_ namespace, falls back to bare key. Resolves portfolio workspace vs detail-subtab collision. MarketsV2 render block calls _injectHelpBtn.</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr"/>
+      <c r="I216" s="5" t="inlineStr"/>
       <c r="J216" s="5" t="inlineStr"/>
       <c r="K216" s="12" t="inlineStr">
         <is>
@@ -12658,27 +12650,23 @@
       </c>
       <c r="L216" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M216" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
-        </is>
-      </c>
-      <c r="N216" s="8" t="inlineStr">
-        <is>
-          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
-        </is>
-      </c>
-    </row>
-    <row r="217" ht="90" customHeight="1">
+          <t>696731a4d</t>
+        </is>
+      </c>
+      <c r="N216" s="8" t="inlineStr"/>
+    </row>
+    <row r="217" ht="45" customHeight="1">
       <c r="A217" s="2" t="n">
         <v>216</v>
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>UI-MLEDGE-1</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="C217" s="10" t="inlineStr">
@@ -12688,26 +12676,34 @@
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>ML Edge Tab</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E217" s="6" t="inlineStr">
         <is>
-          <t>Theme switching + tf-* visual port</t>
+          <t>Git committer.email set globally</t>
         </is>
       </c>
       <c r="F217" s="5" t="inlineStr">
         <is>
-          <t>ML Edge per-ticker sub-tab had hardcoded dark CSS vars inline on #qd-ml-root, blocking the body.light theme toggle. Workspace ML Edge used legacy rk-* class system, not the prototype tf-* design language.</t>
+          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
         </is>
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Moved palette from inline style to _ensureMlEdgeStyles() with body.light overrides. Then ported workspace QuantMlEdge module to tf-* visual system: tf-hero 3-col + tf-pulse-strip 4 live feeds (top bulls/bears/flips/health) + tf-confluence (4 KPI cells + X/4 score) + tf-vbar (verdict badge). All 6 sections rewritten. Memory: feedback_inline_css_vars_break_theming.md.</t>
-        </is>
-      </c>
-      <c r="H217" s="2" t="inlineStr"/>
-      <c r="I217" s="5" t="inlineStr"/>
+          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I217" s="5" t="inlineStr">
+        <is>
+          <t>Win: clean attribution in git log.</t>
+        </is>
+      </c>
       <c r="J217" s="5" t="inlineStr"/>
       <c r="K217" s="12" t="inlineStr">
         <is>
@@ -12716,23 +12712,27 @@
       </c>
       <c r="L217" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M217" s="3" t="inlineStr">
         <is>
-          <t>696731a4d</t>
-        </is>
-      </c>
-      <c r="N217" s="8" t="inlineStr"/>
-    </row>
-    <row r="218" ht="45" customHeight="1">
+          <t>4129e5565</t>
+        </is>
+      </c>
+      <c r="N217" s="8" t="inlineStr">
+        <is>
+          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="90" customHeight="1">
       <c r="A218" s="2" t="n">
         <v>217</v>
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>IPAD-2</t>
+          <t>UI-MLEDGE-1</t>
         </is>
       </c>
       <c r="C218" s="10" t="inlineStr">
@@ -12742,39 +12742,27 @@
       </c>
       <c r="D218" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>ML Edge Tab</t>
         </is>
       </c>
       <c r="E218" s="6" t="inlineStr">
         <is>
-          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
+          <t>Theme switching + tf-* visual port</t>
         </is>
       </c>
       <c r="F218" s="5" t="inlineStr">
         <is>
-          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
+          <t>ML Edge per-ticker sub-tab had hardcoded dark CSS vars inline on #qd-ml-root, blocking the body.light theme toggle. Workspace ML Edge used legacy rk-* class system, not the prototype tf-* design language.</t>
         </is>
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
-        </is>
-      </c>
-      <c r="H218" s="2" t="inlineStr">
-        <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="I218" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J218" s="5" t="inlineStr">
-        <is>
-          <t>Sub-task of IPAD-1.</t>
-        </is>
-      </c>
+          <t>Moved palette from inline style to _ensureMlEdgeStyles() with body.light overrides. Then ported workspace QuantMlEdge module to tf-* visual system: tf-hero 3-col + tf-pulse-strip 4 live feeds (top bulls/bears/flips/health) + tf-confluence (4 KPI cells + X/4 score) + tf-vbar (verdict badge). All 6 sections rewritten. Memory: feedback_inline_css_vars_break_theming.md.</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="inlineStr"/>
+      <c r="I218" s="5" t="inlineStr"/>
+      <c r="J218" s="5" t="inlineStr"/>
       <c r="K218" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -12782,19 +12770,15 @@
       </c>
       <c r="L218" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>
-          <t>79fa01a75</t>
-        </is>
-      </c>
-      <c r="N218" s="8" t="inlineStr">
-        <is>
-          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
-        </is>
-      </c>
+          <t>696731a4d</t>
+        </is>
+      </c>
+      <c r="N218" s="8" t="inlineStr"/>
     </row>
     <row r="219" ht="45" customHeight="1">
       <c r="A219" s="2" t="n">
@@ -12802,7 +12786,7 @@
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>SLACK-NEWSLETTER-MLALERT</t>
+          <t>IPAD-2</t>
         </is>
       </c>
       <c r="C219" s="10" t="inlineStr">
@@ -12812,27 +12796,39 @@
       </c>
       <c r="D219" s="5" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E219" s="6" t="inlineStr">
         <is>
-          <t>Re-enable newsletter + add ML-predictions Slack alert</t>
+          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
         </is>
       </c>
       <c r="F219" s="5" t="inlineStr">
         <is>
-          <t>re-enable daily-newsletter from disabled/; build ml-alert Slack for top ML-edge/AI picks</t>
+          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
         </is>
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd + scripts/ml_alert_slack.py</t>
-        </is>
-      </c>
-      <c r="H219" s="2" t="inlineStr"/>
-      <c r="I219" s="5" t="inlineStr"/>
-      <c r="J219" s="5" t="inlineStr"/>
+          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="I219" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J219" s="5" t="inlineStr">
+        <is>
+          <t>Sub-task of IPAD-1.</t>
+        </is>
+      </c>
       <c r="K219" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -12840,15 +12836,19 @@
       </c>
       <c r="L219" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M219" s="3" t="inlineStr">
         <is>
-          <t>d1ea97913</t>
-        </is>
-      </c>
-      <c r="N219" s="8" t="inlineStr"/>
+          <t>79fa01a75</t>
+        </is>
+      </c>
+      <c r="N219" s="8" t="inlineStr">
+        <is>
+          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="45" customHeight="1">
       <c r="A220" s="2" t="n">
@@ -12856,7 +12856,7 @@
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>FORENSICS-WEEKLY-SLACK</t>
+          <t>SLACK-NEWSLETTER-MLALERT</t>
         </is>
       </c>
       <c r="C220" s="10" t="inlineStr">
@@ -12866,22 +12866,22 @@
       </c>
       <c r="D220" s="5" t="inlineStr">
         <is>
-          <t>Notifications / Audit</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="E220" s="6" t="inlineStr">
         <is>
-          <t>Weekly pick-forensics Slack digest</t>
+          <t>Re-enable newsletter + add ML-predictions Slack alert</t>
         </is>
       </c>
       <c r="F220" s="5" t="inlineStr">
         <is>
-          <t>Sun 17:30 — 14d verdict-truth + per-sleeve EXTENDED/MISSED bleeding monitor to Slack</t>
+          <t>re-enable daily-newsletter from disabled/; build ml-alert Slack for top ML-edge/AI picks</t>
         </is>
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>com.swingtrade.forensics-weekly + pick_forensics --slack</t>
+          <t>infra/launchd + scripts/ml_alert_slack.py</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr"/>
@@ -12899,18 +12899,18 @@
       </c>
       <c r="M220" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>d1ea97913</t>
         </is>
       </c>
       <c r="N220" s="8" t="inlineStr"/>
     </row>
-    <row r="221" ht="75" customHeight="1">
+    <row r="221" ht="45" customHeight="1">
       <c r="A221" s="2" t="n">
         <v>220</v>
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>F11-followup</t>
+          <t>FORENSICS-WEEKLY-SLACK</t>
         </is>
       </c>
       <c r="C221" s="10" t="inlineStr">
@@ -12920,39 +12920,27 @@
       </c>
       <c r="D221" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Notifications / Audit</t>
         </is>
       </c>
       <c r="E221" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook scoped to NEW drift only</t>
+          <t>Weekly pick-forensics Slack digest</t>
         </is>
       </c>
       <c r="F221" s="5" t="inlineStr">
         <is>
-          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
+          <t>Sun 17:30 — 14d verdict-truth + per-sleeve EXTENDED/MISSED bleeding monitor to Slack</t>
         </is>
       </c>
       <c r="G221" s="5" t="inlineStr">
         <is>
-          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
-        </is>
-      </c>
-      <c r="H221" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I221" s="5" t="inlineStr">
-        <is>
-          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
-        </is>
-      </c>
-      <c r="J221" s="5" t="inlineStr">
-        <is>
-          <t>User can still bypass with --no-verify in emergencies.</t>
-        </is>
-      </c>
+          <t>com.swingtrade.forensics-weekly + pick_forensics --slack</t>
+        </is>
+      </c>
+      <c r="H221" s="2" t="inlineStr"/>
+      <c r="I221" s="5" t="inlineStr"/>
+      <c r="J221" s="5" t="inlineStr"/>
       <c r="K221" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -12960,27 +12948,23 @@
       </c>
       <c r="L221" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-      <c r="N221" s="8" t="inlineStr">
-        <is>
-          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
-        </is>
-      </c>
-    </row>
-    <row r="222" ht="60" customHeight="1">
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N221" s="8" t="inlineStr"/>
+    </row>
+    <row r="222" ht="75" customHeight="1">
       <c r="A222" s="2" t="n">
         <v>221</v>
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>OPS-2</t>
+          <t>F11-followup</t>
         </is>
       </c>
       <c r="C222" s="10" t="inlineStr">
@@ -12990,37 +12974,37 @@
       </c>
       <c r="D222" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E222" s="6" t="inlineStr">
         <is>
-          <t>Uptime monitoring (launchd ping → dashboard)</t>
+          <t>Pre-commit hook scoped to NEW drift only</t>
         </is>
       </c>
       <c r="F222" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
+          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
         </is>
       </c>
       <c r="G222" s="5" t="inlineStr">
         <is>
-          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
+          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I222" s="5" t="inlineStr">
         <is>
-          <t>Win: detect FastAPI hang independent of tunnel.</t>
+          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
         </is>
       </c>
       <c r="J222" s="5" t="inlineStr">
         <is>
-          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
+          <t>User can still bypass with --no-verify in emergencies.</t>
         </is>
       </c>
       <c r="K222" s="12" t="inlineStr">
@@ -13030,17 +13014,17 @@
       </c>
       <c r="L222" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M222" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N222" s="8" t="inlineStr">
         <is>
-          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
+          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
         </is>
       </c>
     </row>
@@ -13050,7 +13034,7 @@
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>OPS-3</t>
+          <t>OPS-2</t>
         </is>
       </c>
       <c r="C223" s="10" t="inlineStr">
@@ -13065,32 +13049,32 @@
       </c>
       <c r="E223" s="6" t="inlineStr">
         <is>
-          <t>Admin endpoint for capability_registry edits</t>
+          <t>Uptime monitoring (launchd ping → dashboard)</t>
         </is>
       </c>
       <c r="F223" s="5" t="inlineStr">
         <is>
-          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
+          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
         </is>
       </c>
       <c r="G223" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
+          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I223" s="5" t="inlineStr">
         <is>
-          <t>Win: safer registry edits + audit trail.</t>
+          <t>Win: detect FastAPI hang independent of tunnel.</t>
         </is>
       </c>
       <c r="J223" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
+          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
         </is>
       </c>
       <c r="K223" s="12" t="inlineStr">
@@ -13110,7 +13094,7 @@
       </c>
       <c r="N223" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
+          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
         </is>
       </c>
     </row>
@@ -13120,7 +13104,7 @@
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>OPS-4</t>
+          <t>OPS-3</t>
         </is>
       </c>
       <c r="C224" s="10" t="inlineStr">
@@ -13135,32 +13119,32 @@
       </c>
       <c r="E224" s="6" t="inlineStr">
         <is>
-          <t>CapStudio audit log UI</t>
+          <t>Admin endpoint for capability_registry edits</t>
         </is>
       </c>
       <c r="F224" s="5" t="inlineStr">
         <is>
-          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
+          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
         </is>
       </c>
       <c r="G224" s="5" t="inlineStr">
         <is>
-          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I224" s="5" t="inlineStr">
         <is>
-          <t>Win: visibility into RBAC changes.</t>
+          <t>Win: safer registry edits + audit trail.</t>
         </is>
       </c>
       <c r="J224" s="5" t="inlineStr">
         <is>
-          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
+          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
         </is>
       </c>
       <c r="K224" s="12" t="inlineStr">
@@ -13180,7 +13164,7 @@
       </c>
       <c r="N224" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
         </is>
       </c>
     </row>
@@ -13190,7 +13174,7 @@
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>OPS-5</t>
+          <t>OPS-4</t>
         </is>
       </c>
       <c r="C225" s="10" t="inlineStr">
@@ -13205,32 +13189,32 @@
       </c>
       <c r="E225" s="6" t="inlineStr">
         <is>
-          <t>Backtest report manual 'regen' button</t>
+          <t>CapStudio audit log UI</t>
         </is>
       </c>
       <c r="F225" s="5" t="inlineStr">
         <is>
-          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
+          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
         </is>
       </c>
       <c r="G225" s="5" t="inlineStr">
         <is>
-          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>2 hrs</t>
         </is>
       </c>
       <c r="I225" s="5" t="inlineStr">
         <is>
-          <t>Win: fast iteration on report templates.</t>
+          <t>Win: visibility into RBAC changes.</t>
         </is>
       </c>
       <c r="J225" s="5" t="inlineStr">
         <is>
-          <t>Trivial CLI wrapper.</t>
+          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
         </is>
       </c>
       <c r="K225" s="12" t="inlineStr">
@@ -13240,27 +13224,27 @@
       </c>
       <c r="L225" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M225" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N225" s="8" t="inlineStr">
         <is>
-          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
-        </is>
-      </c>
-    </row>
-    <row r="226" ht="45" customHeight="1">
+          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="60" customHeight="1">
       <c r="A226" s="2" t="n">
         <v>225</v>
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>SCAN-FAILURE-ALERT</t>
+          <t>OPS-5</t>
         </is>
       </c>
       <c r="C226" s="10" t="inlineStr">
@@ -13270,27 +13254,39 @@
       </c>
       <c r="D226" s="5" t="inlineStr">
         <is>
-          <t>Ops / Alerts</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E226" s="6" t="inlineStr">
         <is>
-          <t>Scan-failure + EODHD-quota Slack alert</t>
+          <t>Backtest report manual 'regen' button</t>
         </is>
       </c>
       <c r="F226" s="5" t="inlineStr">
         <is>
-          <t>failed scan / 402 quota is silent today; 1-line health alert on scan exit</t>
+          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
         </is>
       </c>
       <c r="G226" s="5" t="inlineStr">
         <is>
-          <t>swing_trade.py exit hook</t>
-        </is>
-      </c>
-      <c r="H226" s="2" t="inlineStr"/>
-      <c r="I226" s="5" t="inlineStr"/>
-      <c r="J226" s="5" t="inlineStr"/>
+          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="I226" s="5" t="inlineStr">
+        <is>
+          <t>Win: fast iteration on report templates.</t>
+        </is>
+      </c>
+      <c r="J226" s="5" t="inlineStr">
+        <is>
+          <t>Trivial CLI wrapper.</t>
+        </is>
+      </c>
       <c r="K226" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -13298,15 +13294,19 @@
       </c>
       <c r="L226" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M226" s="3" t="inlineStr">
         <is>
-          <t>0dc7675ee</t>
-        </is>
-      </c>
-      <c r="N226" s="8" t="inlineStr"/>
+          <t>2b7d2f40f</t>
+        </is>
+      </c>
+      <c r="N226" s="8" t="inlineStr">
+        <is>
+          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
+        </is>
+      </c>
     </row>
     <row r="227" ht="45" customHeight="1">
       <c r="A227" s="2" t="n">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>MOMENTUM-SNAPSHOT-DECIDE</t>
+          <t>SCAN-FAILURE-ALERT</t>
         </is>
       </c>
       <c r="C227" s="10" t="inlineStr">
@@ -13324,22 +13324,22 @@
       </c>
       <c r="D227" s="5" t="inlineStr">
         <is>
-          <t>Ops / Launchd</t>
+          <t>Ops / Alerts</t>
         </is>
       </c>
       <c r="E227" s="6" t="inlineStr">
         <is>
-          <t>Decide momentum-snapshot: load or retire</t>
+          <t>Scan-failure + EODHD-quota Slack alert</t>
         </is>
       </c>
       <c r="F227" s="5" t="inlineStr">
         <is>
-          <t>valid plist, not loaded; PARSE-ERR on lint earlier</t>
+          <t>failed scan / 402 quota is silent today; 1-line health alert on scan exit</t>
         </is>
       </c>
       <c r="G227" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd</t>
+          <t>swing_trade.py exit hook</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr"/>
@@ -13362,13 +13362,13 @@
       </c>
       <c r="N227" s="8" t="inlineStr"/>
     </row>
-    <row r="228" ht="150" customHeight="1">
+    <row r="228" ht="45" customHeight="1">
       <c r="A228" s="2" t="n">
         <v>227</v>
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>PERF-7b</t>
+          <t>MOMENTUM-SNAPSHOT-DECIDE</t>
         </is>
       </c>
       <c r="C228" s="10" t="inlineStr">
@@ -13378,31 +13378,27 @@
       </c>
       <c r="D228" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Ops / Launchd</t>
         </is>
       </c>
       <c r="E228" s="6" t="inlineStr">
         <is>
-          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
+          <t>Decide momentum-snapshot: load or retire</t>
         </is>
       </c>
       <c r="F228" s="5" t="inlineStr">
         <is>
-          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
+          <t>valid plist, not loaded; PARSE-ERR on lint earlier</t>
         </is>
       </c>
       <c r="G228" s="5" t="inlineStr">
         <is>
-          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
+          <t>infra/launchd</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr"/>
       <c r="I228" s="5" t="inlineStr"/>
-      <c r="J228" s="5" t="inlineStr">
-        <is>
-          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
-        </is>
-      </c>
+      <c r="J228" s="5" t="inlineStr"/>
       <c r="K228" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -13410,27 +13406,23 @@
       </c>
       <c r="L228" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M228" s="3" t="inlineStr">
         <is>
-          <t>cf30df858</t>
-        </is>
-      </c>
-      <c r="N228" s="8" t="inlineStr">
-        <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="229" ht="45" customHeight="1">
+          <t>0dc7675ee</t>
+        </is>
+      </c>
+      <c r="N228" s="8" t="inlineStr"/>
+    </row>
+    <row r="229" ht="150" customHeight="1">
       <c r="A229" s="2" t="n">
         <v>228</v>
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-1</t>
+          <t>PERF-7b</t>
         </is>
       </c>
       <c r="C229" s="10" t="inlineStr">
@@ -13440,27 +13432,31 @@
       </c>
       <c r="D229" s="5" t="inlineStr">
         <is>
-          <t>Sharpe Roadmap</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E229" s="6" t="inlineStr">
         <is>
-          <t>Sharpe gate in momentum detector</t>
+          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
         </is>
       </c>
       <c r="F229" s="5" t="inlineStr">
         <is>
-          <t>Wire 126d Sharpe threshold (≥1.5) into _detect_momentum_continuation</t>
+          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
         </is>
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Computed inline in analyze_ticker via lib.sharpe_utils.sharpe_annualized; passed to detector as kwarg</t>
+          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr"/>
       <c r="I229" s="5" t="inlineStr"/>
-      <c r="J229" s="5" t="inlineStr"/>
+      <c r="J229" s="5" t="inlineStr">
+        <is>
+          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
+        </is>
+      </c>
       <c r="K229" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -13468,15 +13464,19 @@
       </c>
       <c r="L229" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M229" s="3" t="inlineStr">
         <is>
-          <t>dbbd6b5f6</t>
-        </is>
-      </c>
-      <c r="N229" s="8" t="inlineStr"/>
+          <t>cf30df858</t>
+        </is>
+      </c>
+      <c r="N229" s="8" t="inlineStr">
+        <is>
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
+        </is>
+      </c>
     </row>
     <row r="230" ht="45" customHeight="1">
       <c r="A230" s="2" t="n">
@@ -13484,7 +13484,7 @@
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-10</t>
+          <t>SHARPE-1</t>
         </is>
       </c>
       <c r="C230" s="10" t="inlineStr">
@@ -13499,17 +13499,17 @@
       </c>
       <c r="E230" s="6" t="inlineStr">
         <is>
-          <t>Sharpe alerts for watchlist</t>
+          <t>Sharpe gate in momentum detector</t>
         </is>
       </c>
       <c r="F230" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Wire 126d Sharpe threshold (≥1.5) into _detect_momentum_continuation</t>
         </is>
       </c>
       <c r="G230" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_alert.py — tracks state across runs, posts to SLACK_WEBHOOK_URL</t>
+          <t>Computed inline in analyze_ticker via lib.sharpe_utils.sharpe_annualized; passed to detector as kwarg</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr"/>
@@ -13538,7 +13538,7 @@
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-11</t>
+          <t>SHARPE-10</t>
         </is>
       </c>
       <c r="C231" s="10" t="inlineStr">
@@ -13553,17 +13553,17 @@
       </c>
       <c r="E231" s="6" t="inlineStr">
         <is>
-          <t>Per-trade Sharpe attribution</t>
+          <t>Sharpe alerts for watchlist</t>
         </is>
       </c>
       <c r="F231" s="5" t="inlineStr">
         <is>
-          <t>Decompose portfolio Sharpe by ticker / setup / regime contribution</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G231" s="5" t="inlineStr">
         <is>
-          <t>Built into scripts/sharpe_kpi.py — top contributors / detractors + setup + regime contribution tables</t>
+          <t>scripts/sharpe_alert.py — tracks state across runs, posts to SLACK_WEBHOOK_URL</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr"/>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-12</t>
+          <t>SHARPE-11</t>
         </is>
       </c>
       <c r="C232" s="10" t="inlineStr">
@@ -13607,17 +13607,17 @@
       </c>
       <c r="E232" s="6" t="inlineStr">
         <is>
-          <t>Sharpe consistency check</t>
+          <t>Per-trade Sharpe attribution</t>
         </is>
       </c>
       <c r="F232" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Decompose portfolio Sharpe by ticker / setup / regime contribution</t>
         </is>
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>lib.sharpe_utils.rolling_sharpe + consistency_score; surfaced on per-ticker result dict</t>
+          <t>Built into scripts/sharpe_kpi.py — top contributors / detractors + setup + regime contribution tables</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr"/>
@@ -13646,7 +13646,7 @@
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-2</t>
+          <t>SHARPE-12</t>
         </is>
       </c>
       <c r="C233" s="10" t="inlineStr">
@@ -13661,17 +13661,17 @@
       </c>
       <c r="E233" s="6" t="inlineStr">
         <is>
-          <t>Sharpe column in v2 dashboard</t>
+          <t>Sharpe consistency check</t>
         </is>
       </c>
       <c r="F233" s="5" t="inlineStr">
         <is>
-          <t>Surface 126d Sharpe per ticker as sortable column</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G233" s="5" t="inlineStr">
         <is>
-          <t>Added sharpe_126d / sortino_126d / sharpe_consistency to compact_row in build_data.py</t>
+          <t>lib.sharpe_utils.rolling_sharpe + consistency_score; surfaced on per-ticker result dict</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr"/>
@@ -13700,7 +13700,7 @@
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-3</t>
+          <t>SHARPE-2</t>
         </is>
       </c>
       <c r="C234" s="10" t="inlineStr">
@@ -13715,17 +13715,17 @@
       </c>
       <c r="E234" s="6" t="inlineStr">
         <is>
-          <t>Per-stock Sharpe by regime</t>
+          <t>Sharpe column in v2 dashboard</t>
         </is>
       </c>
       <c r="F234" s="5" t="inlineStr">
         <is>
-          <t>Decompose per-stock Sharpe by historical regime tags</t>
+          <t>Surface 126d Sharpe per ticker as sortable column</t>
         </is>
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_per_regime.py — segments OHLCV by regime, computes per-bucket Sharpe</t>
+          <t>Added sharpe_126d / sortino_126d / sharpe_consistency to compact_row in build_data.py</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr"/>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-4</t>
+          <t>SHARPE-3</t>
         </is>
       </c>
       <c r="C235" s="10" t="inlineStr">
@@ -13769,17 +13769,17 @@
       </c>
       <c r="E235" s="6" t="inlineStr">
         <is>
-          <t>Edge-erosion radar (per-setup Sharpe trend)</t>
+          <t>Per-stock Sharpe by regime</t>
         </is>
       </c>
       <c r="F235" s="5" t="inlineStr">
         <is>
-          <t>Per-setup Sharpe across rolling windows w/ HTML viz</t>
+          <t>Decompose per-stock Sharpe by historical regime tags</t>
         </is>
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_setup_trend.py — emits trend table + dark-themed HTML chart per setup</t>
+          <t>scripts/sharpe_per_regime.py — segments OHLCV by regime, computes per-bucket Sharpe</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr"/>
@@ -13808,7 +13808,7 @@
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-5</t>
+          <t>SHARPE-4</t>
         </is>
       </c>
       <c r="C236" s="10" t="inlineStr">
@@ -13823,17 +13823,17 @@
       </c>
       <c r="E236" s="6" t="inlineStr">
         <is>
-          <t>Sharpe-weighted position sizing</t>
+          <t>Edge-erosion radar (per-setup Sharpe trend)</t>
         </is>
       </c>
       <c r="F236" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Per-setup Sharpe across rolling windows w/ HTML viz</t>
         </is>
       </c>
       <c r="G236" s="5" t="inlineStr">
         <is>
-          <t>kelly_position_size new sharpe_126d kwarg + portfolio.sharpe_size_tilt config block (default OFF)</t>
+          <t>scripts/sharpe_setup_trend.py — emits trend table + dark-themed HTML chart per setup</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr"/>
@@ -13862,7 +13862,7 @@
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-6</t>
+          <t>SHARPE-5</t>
         </is>
       </c>
       <c r="C237" s="10" t="inlineStr">
@@ -13877,17 +13877,17 @@
       </c>
       <c r="E237" s="6" t="inlineStr">
         <is>
-          <t>Portfolio Sharpe KPI vs target</t>
+          <t>Sharpe-weighted position sizing</t>
         </is>
       </c>
       <c r="F237" s="5" t="inlineStr">
         <is>
-          <t>Annualized Sharpe target tracking + gap report</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G237" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_kpi.py — reports actual vs target/floor, exits 2 on below-floor for cron alerts</t>
+          <t>kelly_position_size new sharpe_126d kwarg + portfolio.sharpe_size_tilt config block (default OFF)</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr"/>
@@ -13916,7 +13916,7 @@
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-7</t>
+          <t>SHARPE-6</t>
         </is>
       </c>
       <c r="C238" s="10" t="inlineStr">
@@ -13931,17 +13931,17 @@
       </c>
       <c r="E238" s="6" t="inlineStr">
         <is>
-          <t>Sharpe-based stop sizing</t>
+          <t>Portfolio Sharpe KPI vs target</t>
         </is>
       </c>
       <c r="F238" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Annualized Sharpe target tracking + gap report</t>
         </is>
       </c>
       <c r="G238" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan reads runtime sharpe; portfolio.sharpe_stop_tilt config block (default OFF)</t>
+          <t>scripts/sharpe_kpi.py — reports actual vs target/floor, exits 2 on below-floor for cron alerts</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr"/>
@@ -13970,7 +13970,7 @@
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-8</t>
+          <t>SHARPE-7</t>
         </is>
       </c>
       <c r="C239" s="10" t="inlineStr">
@@ -13985,17 +13985,17 @@
       </c>
       <c r="E239" s="6" t="inlineStr">
         <is>
-          <t>Sortino computation alongside Sharpe</t>
+          <t>Sharpe-based stop sizing</t>
         </is>
       </c>
       <c r="F239" s="5" t="inlineStr">
         <is>
-          <t>Downside-only vol denominator added everywhere</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>lib.sharpe_utils.sortino_annualized + per_trade_sortino; surfaced on result dict</t>
+          <t>compute_trade_plan reads runtime sharpe; portfolio.sharpe_stop_tilt config block (default OFF)</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr"/>
@@ -14024,7 +14024,7 @@
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-9</t>
+          <t>SHARPE-8</t>
         </is>
       </c>
       <c r="C240" s="10" t="inlineStr">
@@ -14039,17 +14039,17 @@
       </c>
       <c r="E240" s="6" t="inlineStr">
         <is>
-          <t>SPY-Sharpe regime cross-validation</t>
+          <t>Sortino computation alongside Sharpe</t>
         </is>
       </c>
       <c r="F240" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Downside-only vol denominator added everywhere</t>
         </is>
       </c>
       <c r="G240" s="5" t="inlineStr">
         <is>
-          <t>data_fetcher.get_market_regime now includes spy_sharpe payload</t>
+          <t>lib.sharpe_utils.sortino_annualized + per_trade_sortino; surfaced on result dict</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr"/>
@@ -14072,13 +14072,13 @@
       </c>
       <c r="N240" s="8" t="inlineStr"/>
     </row>
-    <row r="241" ht="120" customHeight="1">
+    <row r="241" ht="45" customHeight="1">
       <c r="A241" s="2" t="n">
         <v>240</v>
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>CONVICTION-TIER-WIRE</t>
+          <t>SHARPE-9</t>
         </is>
       </c>
       <c r="C241" s="10" t="inlineStr">
@@ -14088,39 +14088,27 @@
       </c>
       <c r="D241" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Conviction</t>
+          <t>Sharpe Roadmap</t>
         </is>
       </c>
       <c r="E241" s="6" t="inlineStr">
         <is>
-          <t>Conviction tier: simplified to score-band only</t>
+          <t>SPY-Sharpe regime cross-validation</t>
         </is>
       </c>
       <c r="F241" s="5" t="inlineStr">
         <is>
-          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G241" s="5" t="inlineStr">
         <is>
-          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
-        </is>
-      </c>
-      <c r="H241" s="2" t="inlineStr">
-        <is>
-          <t>2-4 hrs + backtest validation</t>
-        </is>
-      </c>
-      <c r="I241" s="5" t="inlineStr">
-        <is>
-          <t>Medium — changes live size or eliminates a layer</t>
-        </is>
-      </c>
-      <c r="J241" s="5" t="inlineStr">
-        <is>
-          <t>Resolved 2026-05-11 by SIMPLIFYING (not deleting). The complex tier criteria (AND of score+RR+RS+regime+catalyst+entry_quality) had 0 T1/T2 trades ever fire in 423 closed signals. The intersection was empty — system was decorative. Replaced with score-only band: T1 score&gt;=88, T2 score&gt;=78, T3 score&gt;=70, WATCH 60-69, AVOID &lt;60. Win-rate setup adjustment retained (single-factor, evidence-driven). All callers preserved — they now get real tier labels instead of mostly-empty results.</t>
-        </is>
-      </c>
+          <t>data_fetcher.get_market_regime now includes spy_sharpe payload</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="inlineStr"/>
+      <c r="I241" s="5" t="inlineStr"/>
+      <c r="J241" s="5" t="inlineStr"/>
       <c r="K241" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14128,27 +14116,23 @@
       </c>
       <c r="L241" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="M241" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N241" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'from analysis import assign_conviction_tier; print([assign_conviction_tier(s)["label"] for s in [95,87,75,65,55]])' → ['T1','T2','T3','WATCH','AVOID']</t>
-        </is>
-      </c>
-    </row>
-    <row r="242" ht="75" customHeight="1">
+          <t>dbbd6b5f6</t>
+        </is>
+      </c>
+      <c r="N241" s="8" t="inlineStr"/>
+    </row>
+    <row r="242" ht="120" customHeight="1">
       <c r="A242" s="2" t="n">
         <v>241</v>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>ENTRY-Q-AB</t>
+          <t>CONVICTION-TIER-WIRE</t>
         </is>
       </c>
       <c r="C242" s="10" t="inlineStr">
@@ -14158,27 +14142,39 @@
       </c>
       <c r="D242" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Gates</t>
+          <t>Strategy / Conviction</t>
         </is>
       </c>
       <c r="E242" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional entry_quality A/B</t>
+          <t>Conviction tier: simplified to score-band only</t>
         </is>
       </c>
       <c r="F242" s="5" t="inlineStr">
         <is>
-          <t>Test relaxing entry_quality EXTENDED/MISSED to caveat-only in risk_on_choppy regime. Evidence (n=257 EXTENDED PF 1.63, n=179 MISSED PF 2.89 in choppy) suggests gate is upside-down for that regime, but selection bias + market-cycle asymmetry concerns warrant explicit A/B before promoting to default.</t>
+          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
         </is>
       </c>
       <c r="G242" s="5" t="inlineStr">
         <is>
-          <t>Add config flag regime4_thresholds.risk_on_choppy.entry_quality_caveat_only (default false). Modify decision_engine to honor it. Run 30 days control + 30 days test. Compare WR/PF stratified by entry_quality band. Promote if test PF &gt; control by &gt;=0.3 with n&gt;=30 per band.</t>
-        </is>
-      </c>
-      <c r="H242" s="2" t="inlineStr"/>
-      <c r="I242" s="5" t="inlineStr"/>
-      <c r="J242" s="5" t="inlineStr"/>
+          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="inlineStr">
+        <is>
+          <t>2-4 hrs + backtest validation</t>
+        </is>
+      </c>
+      <c r="I242" s="5" t="inlineStr">
+        <is>
+          <t>Medium — changes live size or eliminates a layer</t>
+        </is>
+      </c>
+      <c r="J242" s="5" t="inlineStr">
+        <is>
+          <t>Resolved 2026-05-11 by SIMPLIFYING (not deleting). The complex tier criteria (AND of score+RR+RS+regime+catalyst+entry_quality) had 0 T1/T2 trades ever fire in 423 closed signals. The intersection was empty — system was decorative. Replaced with score-only band: T1 score&gt;=88, T2 score&gt;=78, T3 score&gt;=70, WATCH 60-69, AVOID &lt;60. Win-rate setup adjustment retained (single-factor, evidence-driven). All callers preserved — they now get real tier labels instead of mostly-empty results.</t>
+        </is>
+      </c>
       <c r="K242" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14186,23 +14182,27 @@
       </c>
       <c r="L242" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
-          <t>07c3af6a3</t>
-        </is>
-      </c>
-      <c r="N242" s="8" t="inlineStr"/>
-    </row>
-    <row r="243" ht="60" customHeight="1">
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N242" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'from analysis import assign_conviction_tier; print([assign_conviction_tier(s)["label"] for s in [95,87,75,65,55]])' → ['T1','T2','T3','WATCH','AVOID']</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="75" customHeight="1">
       <c r="A243" s="2" t="n">
         <v>242</v>
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-1</t>
+          <t>ENTRY-Q-AB</t>
         </is>
       </c>
       <c r="C243" s="10" t="inlineStr">
@@ -14212,22 +14212,22 @@
       </c>
       <c r="D243" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Options Paper</t>
+          <t>Strategy / Gates</t>
         </is>
       </c>
       <c r="E243" s="6" t="inlineStr">
         <is>
-          <t>Signal -&gt; options-structure mapper</t>
+          <t>Regime-conditional entry_quality A/B</t>
         </is>
       </c>
       <c r="F243" s="5" t="inlineStr">
         <is>
-          <t>Engine emits equity plans only; no layer maps a stock BUY to a defined-risk options structure. GATED: equity sleeves still Phase-1. See docs/scope_options_paper.md.</t>
+          <t>Test relaxing entry_quality EXTENDED/MISSED to caveat-only in risk_on_choppy regime. Evidence (n=257 EXTENDED PF 1.63, n=179 MISSED PF 2.89 in choppy) suggests gate is upside-down for that regime, but selection bias + market-cycle asymmetry concerns warrant explicit A/B before promoting to default.</t>
         </is>
       </c>
       <c r="G243" s="5" t="inlineStr">
         <is>
-          <t>Map equity plan -&gt; defined-risk structure by setup family / R:R / IV rank (3:1 high-conviction -&gt; debit call spread; clean trend -&gt; long call 30-45 DTE). Underlying stop = thesis invalidation. Defined-risk ONLY, paper ONLY.</t>
+          <t>Add config flag regime4_thresholds.risk_on_choppy.entry_quality_caveat_only (default false). Modify decision_engine to honor it. Run 30 days control + 30 days test. Compare WR/PF stratified by entry_quality band. Promote if test PF &gt; control by &gt;=0.3 with n&gt;=30 per band.</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr"/>
@@ -14240,23 +14240,23 @@
       </c>
       <c r="L243" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="M243" s="3" t="inlineStr">
         <is>
-          <t>9c3a2a58d</t>
+          <t>07c3af6a3</t>
         </is>
       </c>
       <c r="N243" s="8" t="inlineStr"/>
     </row>
-    <row r="244" ht="45" customHeight="1">
+    <row r="244" ht="60" customHeight="1">
       <c r="A244" s="2" t="n">
         <v>243</v>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-2</t>
+          <t>OPT-PAPER-1</t>
         </is>
       </c>
       <c r="C244" s="10" t="inlineStr">
@@ -14271,17 +14271,17 @@
       </c>
       <c r="E244" s="6" t="inlineStr">
         <is>
-          <t>Contract selection from Schwab chain</t>
+          <t>Signal -&gt; options-structure mapper</t>
         </is>
       </c>
       <c r="F244" s="5" t="inlineStr">
         <is>
-          <t>We have chain+Greeks data (schwab_client.get_chains/extract_chain_greeks) but no contract picker. Dep: SCHWAB-REAUTH-PENDING (Greeks freshness).</t>
+          <t>Engine emits equity plans only; no layer maps a stock BUY to a defined-risk options structure. GATED: equity sleeves still Phase-1. See docs/scope_options_paper.md.</t>
         </is>
       </c>
       <c r="G244" s="5" t="inlineStr">
         <is>
-          <t>Pick by delta/DTE/spread width from the Schwab chain; size on premium-at-risk &lt;=1% equity. No naked options.</t>
+          <t>Map equity plan -&gt; defined-risk structure by setup family / R:R / IV rank (3:1 high-conviction -&gt; debit call spread; clean trend -&gt; long call 30-45 DTE). Underlying stop = thesis invalidation. Defined-risk ONLY, paper ONLY.</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr"/>
@@ -14304,13 +14304,13 @@
       </c>
       <c r="N244" s="8" t="inlineStr"/>
     </row>
-    <row r="245" ht="60" customHeight="1">
+    <row r="245" ht="45" customHeight="1">
       <c r="A245" s="2" t="n">
         <v>244</v>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-3</t>
+          <t>OPT-PAPER-2</t>
         </is>
       </c>
       <c r="C245" s="10" t="inlineStr">
@@ -14325,17 +14325,17 @@
       </c>
       <c r="E245" s="6" t="inlineStr">
         <is>
-          <t>Alpaca paper options orders in executor.py</t>
+          <t>Contract selection from Schwab chain</t>
         </is>
       </c>
       <c r="F245" s="5" t="inlineStr">
         <is>
-          <t>executor.py has zero options code (equity brackets only); Alpaca SDK supports OptionLegRequest/GetOptionContractsRequest.</t>
+          <t>We have chain+Greeks data (schwab_client.get_chains/extract_chain_greeks) but no contract picker. Dep: SCHWAB-REAUTH-PENDING (Greeks freshness).</t>
         </is>
       </c>
       <c r="G245" s="5" t="inlineStr">
         <is>
-          <t>Construct+submit single + vertical OptionLegRequest in executor.py, PAPER only behind the config.alpaca.paper hard guard. Never live (feedback_paper_only_automation).</t>
+          <t>Pick by delta/DTE/spread width from the Schwab chain; size on premium-at-risk &lt;=1% equity. No naked options.</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr"/>
@@ -14358,13 +14358,13 @@
       </c>
       <c r="N245" s="8" t="inlineStr"/>
     </row>
-    <row r="246" ht="45" customHeight="1">
+    <row r="246" ht="60" customHeight="1">
       <c r="A246" s="2" t="n">
         <v>245</v>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-4</t>
+          <t>OPT-PAPER-3</t>
         </is>
       </c>
       <c r="C246" s="10" t="inlineStr">
@@ -14379,17 +14379,17 @@
       </c>
       <c r="E246" s="6" t="inlineStr">
         <is>
-          <t>Options position tracking + contract P&amp;L</t>
+          <t>Alpaca paper options orders in executor.py</t>
         </is>
       </c>
       <c r="F246" s="5" t="inlineStr">
         <is>
-          <t>Portfolio tracker is share-P&amp;L only; can't track premium/Greeks/theta/DTE.</t>
+          <t>executor.py has zero options code (equity brackets only); Alpaca SDK supports OptionLegRequest/GetOptionContractsRequest.</t>
         </is>
       </c>
       <c r="G246" s="5" t="inlineStr">
         <is>
-          <t>Extend portfolio tracker for contracts: premium, Greeks, theta decay, IV, DTE, mark-to-market.</t>
+          <t>Construct+submit single + vertical OptionLegRequest in executor.py, PAPER only behind the config.alpaca.paper hard guard. Never live (feedback_paper_only_automation).</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr"/>
@@ -14407,7 +14407,7 @@
       </c>
       <c r="M246" s="3" t="inlineStr">
         <is>
-          <t>635ae960f</t>
+          <t>9c3a2a58d</t>
         </is>
       </c>
       <c r="N246" s="8" t="inlineStr"/>
@@ -14418,7 +14418,7 @@
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-5</t>
+          <t>OPT-PAPER-4</t>
         </is>
       </c>
       <c r="C247" s="10" t="inlineStr">
@@ -14433,17 +14433,17 @@
       </c>
       <c r="E247" s="6" t="inlineStr">
         <is>
-          <t>Options-specific exits</t>
+          <t>Options position tracking + contract P&amp;L</t>
         </is>
       </c>
       <c r="F247" s="5" t="inlineStr">
         <is>
-          <t>Equity exits are price-stop only; options need IV/theta/expiry-aware exits.</t>
+          <t>Portfolio tracker is share-P&amp;L only; can't track premium/Greeks/theta/DTE.</t>
         </is>
       </c>
       <c r="G247" s="5" t="inlineStr">
         <is>
-          <t>IV-crush-around-earnings rule, time-stop before expiry, profit-take on the CONTRACT not the underlying, assignment handling.</t>
+          <t>Extend portfolio tracker for contracts: premium, Greeks, theta decay, IV, DTE, mark-to-market.</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr"/>
@@ -14466,13 +14466,13 @@
       </c>
       <c r="N247" s="8" t="inlineStr"/>
     </row>
-    <row r="248" ht="120" customHeight="1">
+    <row r="248" ht="45" customHeight="1">
       <c r="A248" s="2" t="n">
         <v>247</v>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>UI-STRAT-1</t>
+          <t>OPT-PAPER-5</t>
         </is>
       </c>
       <c r="C248" s="10" t="inlineStr">
@@ -14482,22 +14482,22 @@
       </c>
       <c r="D248" s="5" t="inlineStr">
         <is>
-          <t>Strategy Lab</t>
+          <t>Strategy / Options Paper</t>
         </is>
       </c>
       <c r="E248" s="6" t="inlineStr">
         <is>
-          <t>13-section HF cockpit rebuild + live setup_stats wiring</t>
+          <t>Options-specific exits</t>
         </is>
       </c>
       <c r="F248" s="5" t="inlineStr">
         <is>
-          <t>Old Strategy Lab was 4-section table with fake numbers and 3x3 correlation. Didn't match 20yr HF analyst standard (no capital allocation cascade, no Wilson CI on PF, no edge-erosion radar, no BT vs Live divergence, no auto-quarantine surface).</t>
+          <t>Equity exits are price-stop only; options need IV/theta/expiry-aware exits.</t>
         </is>
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Rebuilt renderStrategies in kairos.html with 13 sections: portfolio cockpit, setup-family perf (LIVE from setup_stats.json with Wilson bars + PF haircut), edge erosion radar, BT vs Live divergence (surfaces PEAD canary BT 2.04 vs live 0.88), phase promotion ledger, regime×sleeve grid 8x4, correlation 8x8 + eigenvalue λ₁, sleeve interaction overlap, recent picks roster, auto-quarantine surface, mechanism+falsifier, playbook, pre-mortem. async _stratLabPatch() fetches live data.</t>
+          <t>IV-crush-around-earnings rule, time-stop before expiry, profit-take on the CONTRACT not the underlying, assignment handling.</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr"/>
@@ -14510,23 +14510,23 @@
       </c>
       <c r="L248" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
-          <t>93ec11842</t>
+          <t>635ae960f</t>
         </is>
       </c>
       <c r="N248" s="8" t="inlineStr"/>
     </row>
-    <row r="249" ht="105" customHeight="1">
+    <row r="249" ht="120" customHeight="1">
       <c r="A249" s="2" t="n">
         <v>248</v>
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>TRACKER-BUY-FILTER</t>
+          <t>UI-STRAT-1</t>
         </is>
       </c>
       <c r="C249" s="10" t="inlineStr">
@@ -14536,31 +14536,27 @@
       </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
-          <t>Tracker/Feedback Loop</t>
+          <t>Strategy Lab</t>
         </is>
       </c>
       <c r="E249" s="6" t="inlineStr">
         <is>
-          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
+          <t>13-section HF cockpit rebuild + live setup_stats wiring</t>
         </is>
       </c>
       <c r="F249" s="5" t="inlineStr">
         <is>
-          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
+          <t>Old Strategy Lab was 4-section table with fake numbers and 3x3 correlation. Didn't match 20yr HF analyst standard (no capital allocation cascade, no Wilson CI on PF, no edge-erosion radar, no BT vs Live divergence, no auto-quarantine surface).</t>
         </is>
       </c>
       <c r="G249" s="5" t="inlineStr">
         <is>
-          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
+          <t>Rebuilt renderStrategies in kairos.html with 13 sections: portfolio cockpit, setup-family perf (LIVE from setup_stats.json with Wilson bars + PF haircut), edge erosion radar, BT vs Live divergence (surfaces PEAD canary BT 2.04 vs live 0.88), phase promotion ledger, regime×sleeve grid 8x4, correlation 8x8 + eigenvalue λ₁, sleeve interaction overlap, recent picks roster, auto-quarantine surface, mechanism+falsifier, playbook, pre-mortem. async _stratLabPatch() fetches live data.</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr"/>
       <c r="I249" s="5" t="inlineStr"/>
-      <c r="J249" s="5" t="inlineStr">
-        <is>
-          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
-        </is>
-      </c>
+      <c r="J249" s="5" t="inlineStr"/>
       <c r="K249" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14568,27 +14564,23 @@
       </c>
       <c r="L249" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M249" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N249" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
-        </is>
-      </c>
-    </row>
-    <row r="250" ht="135" customHeight="1">
+          <t>93ec11842</t>
+        </is>
+      </c>
+      <c r="N249" s="8" t="inlineStr"/>
+    </row>
+    <row r="250" ht="105" customHeight="1">
       <c r="A250" s="2" t="n">
         <v>249</v>
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>MOD-1</t>
+          <t>TRACKER-BUY-FILTER</t>
         </is>
       </c>
       <c r="C250" s="10" t="inlineStr">
@@ -14598,37 +14590,29 @@
       </c>
       <c r="D250" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Tracker/Feedback Loop</t>
         </is>
       </c>
       <c r="E250" s="6" t="inlineStr">
         <is>
-          <t>Scanner deep refactor</t>
+          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
         </is>
       </c>
       <c r="F250" s="5" t="inlineStr">
         <is>
-          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
+          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
         </is>
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
-        </is>
-      </c>
-      <c r="H250" s="2" t="inlineStr">
-        <is>
-          <t>1-2 hrs</t>
-        </is>
-      </c>
-      <c r="I250" s="5" t="inlineStr">
-        <is>
-          <t>Risk: low (works fine inline). Win: consistency.</t>
-        </is>
-      </c>
+          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
+        </is>
+      </c>
+      <c r="H250" s="2" t="inlineStr"/>
+      <c r="I250" s="5" t="inlineStr"/>
       <c r="J250" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
+          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
         </is>
       </c>
       <c r="K250" s="12" t="inlineStr">
@@ -14638,27 +14622,27 @@
       </c>
       <c r="L250" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
-          <t>42c36ef91</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N250" s="8" t="inlineStr">
         <is>
-          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
-        </is>
-      </c>
-    </row>
-    <row r="251" ht="45" customHeight="1">
+          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="135" customHeight="1">
       <c r="A251" s="2" t="n">
         <v>250</v>
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>STOCKSMITH-BOOK-RISK</t>
+          <t>MOD-1</t>
         </is>
       </c>
       <c r="C251" s="10" t="inlineStr">
@@ -14668,27 +14652,39 @@
       </c>
       <c r="D251" s="5" t="inlineStr">
         <is>
-          <t>V2 Dashboard / Risk</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E251" s="6" t="inlineStr">
         <is>
-          <t>Book Risk surface + per-lens analytics (§6)</t>
+          <t>Scanner deep refactor</t>
         </is>
       </c>
       <c r="F251" s="5" t="inlineStr">
         <is>
-          <t>Book Risk (exposure/Greeks/optimizer/attribution/crowding/hedge) + VaR mode-aware + DCF grid + Earnings whisper; honest dashes</t>
+          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
         </is>
       </c>
       <c r="G251" s="5" t="inlineStr">
         <is>
-          <t>Stocksmith.html BookRiskPanel + InvDcfSensitivity + EoWhisperRevisions</t>
-        </is>
-      </c>
-      <c r="H251" s="2" t="inlineStr"/>
-      <c r="I251" s="5" t="inlineStr"/>
-      <c r="J251" s="5" t="inlineStr"/>
+          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
+        </is>
+      </c>
+      <c r="H251" s="2" t="inlineStr">
+        <is>
+          <t>1-2 hrs</t>
+        </is>
+      </c>
+      <c r="I251" s="5" t="inlineStr">
+        <is>
+          <t>Risk: low (works fine inline). Win: consistency.</t>
+        </is>
+      </c>
+      <c r="J251" s="5" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
+        </is>
+      </c>
       <c r="K251" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14696,23 +14692,27 @@
       </c>
       <c r="L251" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M251" s="3" t="inlineStr">
         <is>
-          <t>50cace567</t>
-        </is>
-      </c>
-      <c r="N251" s="8" t="inlineStr"/>
-    </row>
-    <row r="252" ht="120" customHeight="1">
+          <t>42c36ef91</t>
+        </is>
+      </c>
+      <c r="N251" s="8" t="inlineStr">
+        <is>
+          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="45" customHeight="1">
       <c r="A252" s="2" t="n">
         <v>251</v>
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>RECENCY-FLOOR</t>
+          <t>STOCKSMITH-BOOK-RISK</t>
         </is>
       </c>
       <c r="C252" s="10" t="inlineStr">
@@ -14722,31 +14722,27 @@
       </c>
       <c r="D252" s="5" t="inlineStr">
         <is>
-          <t>Validation Hygiene</t>
+          <t>V2 Dashboard / Risk</t>
         </is>
       </c>
       <c r="E252" s="6" t="inlineStr">
         <is>
-          <t>_validations needs recency floor — auto-revert stale boosts</t>
+          <t>Book Risk surface + per-lens analytics (§6)</t>
         </is>
       </c>
       <c r="F252" s="5" t="inlineStr">
         <is>
-          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
+          <t>Book Risk (exposure/Greeks/optimizer/attribution/crowding/hedge) + VaR mode-aware + DCF grid + Earnings whisper; honest dashes</t>
         </is>
       </c>
       <c r="G252" s="5" t="inlineStr">
         <is>
-          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
+          <t>Stocksmith.html BookRiskPanel + InvDcfSensitivity + EoWhisperRevisions</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr"/>
       <c r="I252" s="5" t="inlineStr"/>
-      <c r="J252" s="5" t="inlineStr">
-        <is>
-          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
-        </is>
-      </c>
+      <c r="J252" s="5" t="inlineStr"/>
       <c r="K252" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14754,27 +14750,23 @@
       </c>
       <c r="L252" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M252" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N252" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="253" ht="60" customHeight="1">
+          <t>50cace567</t>
+        </is>
+      </c>
+      <c r="N252" s="8" t="inlineStr"/>
+    </row>
+    <row r="253" ht="120" customHeight="1">
       <c r="A253" s="2" t="n">
         <v>252</v>
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>MOMENTUM-TAB</t>
+          <t>RECENCY-FLOOR</t>
         </is>
       </c>
       <c r="C253" s="10" t="inlineStr">
@@ -14784,27 +14776,31 @@
       </c>
       <c r="D253" s="5" t="inlineStr">
         <is>
-          <t>Workspaces / Momentum</t>
+          <t>Validation Hygiene</t>
         </is>
       </c>
       <c r="E253" s="6" t="inlineStr">
         <is>
-          <t>New 🚀 Momentum workspace tab</t>
+          <t>_validations needs recency floor — auto-revert stale boosts</t>
         </is>
       </c>
       <c r="F253" s="5" t="inlineStr">
         <is>
-          <t>Ranks scan universe by composite (raw_momentum_score×0.5 + sharpe_norm×0.25 + rs_rank×0.25). Filterable by setup family + grade A/B/C. Click row → detail. Sidebar count = Grade-A + composite≥80 tickers</t>
+          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantMomentum IIFE + V3_WORKSPACES.momentum + dispatcher branch</t>
+          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr"/>
       <c r="I253" s="5" t="inlineStr"/>
-      <c r="J253" s="5" t="inlineStr"/>
+      <c r="J253" s="5" t="inlineStr">
+        <is>
+          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
+        </is>
+      </c>
       <c r="K253" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14812,15 +14808,19 @@
       </c>
       <c r="L253" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M253" s="3" t="inlineStr">
         <is>
-          <t>27fd646b1</t>
-        </is>
-      </c>
-      <c r="N253" s="8" t="inlineStr"/>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N253" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
+        </is>
+      </c>
     </row>
     <row r="254" ht="60" customHeight="1">
       <c r="A254" s="2" t="n">
@@ -14828,7 +14828,7 @@
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>SCANNER-QUICK-PANELS</t>
+          <t>MOMENTUM-TAB</t>
         </is>
       </c>
       <c r="C254" s="10" t="inlineStr">
@@ -14838,22 +14838,22 @@
       </c>
       <c r="D254" s="5" t="inlineStr">
         <is>
-          <t>Workspaces / Signal Scanner</t>
+          <t>Workspaces / Momentum</t>
         </is>
       </c>
       <c r="E254" s="6" t="inlineStr">
         <is>
-          <t>5 quick-glance panels above watchlist table</t>
+          <t>New 🚀 Momentum workspace tab</t>
         </is>
       </c>
       <c r="F254" s="5" t="inlineStr">
         <is>
-          <t>Top 5 AI Predictions · Fresh Entries · Top Momentum · Earnings This Week · Volume Surges. Each panel uses shared _qpCard + _qpFrame helpers. Click row → setDetailTicker (with ML cache fallback for R2000)</t>
+          <t>Ranks scan universe by composite (raw_momentum_score×0.5 + sharpe_norm×0.25 + rs_rank×0.25). Filterable by setup family + grade A/B/C. Click row → detail. Sidebar count = Grade-A + composite≥80 tickers</t>
         </is>
       </c>
       <c r="G254" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantScanner.renderQuickPanels + panelXxx helpers + .qs-quick-* CSS</t>
+          <t>kairos.html QuantMomentum IIFE + V3_WORKSPACES.momentum + dispatcher branch</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr"/>
@@ -14871,60 +14871,48 @@
       </c>
       <c r="M254" s="3" t="inlineStr">
         <is>
-          <t>dfbe955fe</t>
+          <t>27fd646b1</t>
         </is>
       </c>
       <c r="N254" s="8" t="inlineStr"/>
     </row>
-    <row r="255" ht="45" customHeight="1">
+    <row r="255" ht="60" customHeight="1">
       <c r="A255" s="2" t="n">
         <v>254</v>
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="C255" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>SCANNER-QUICK-PANELS</t>
+        </is>
+      </c>
+      <c r="C255" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D255" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Workspaces / Signal Scanner</t>
         </is>
       </c>
       <c r="E255" s="6" t="inlineStr">
         <is>
-          <t>Verify backtest persistence (cb1f5a010)</t>
+          <t>5 quick-glance panels above watchlist table</t>
         </is>
       </c>
       <c r="F255" s="5" t="inlineStr">
         <is>
-          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
+          <t>Top 5 AI Predictions · Fresh Entries · Top Momentum · Earnings This Week · Volume Surges. Each panel uses shared _qpCard + _qpFrame helpers. Click row → setDetailTicker (with ML cache fallback for R2000)</t>
         </is>
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
-        </is>
-      </c>
-      <c r="H255" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="I255" s="5" t="inlineStr">
-        <is>
-          <t>Win: persistence works; no silent overwrites.</t>
-        </is>
-      </c>
-      <c r="J255" s="5" t="inlineStr">
-        <is>
-          <t>3 snapshot files present. Validates cb1f5a010.</t>
-        </is>
-      </c>
+          <t>kairos.html QuantScanner.renderQuickPanels + panelXxx helpers + .qs-quick-* CSS</t>
+        </is>
+      </c>
+      <c r="H255" s="2" t="inlineStr"/>
+      <c r="I255" s="5" t="inlineStr"/>
+      <c r="J255" s="5" t="inlineStr"/>
       <c r="K255" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14932,15 +14920,15 @@
       </c>
       <c r="L255" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M255" s="3" t="inlineStr"/>
-      <c r="N255" s="8" t="inlineStr">
-        <is>
-          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
-        </is>
-      </c>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="M255" s="3" t="inlineStr">
+        <is>
+          <t>dfbe955fe</t>
+        </is>
+      </c>
+      <c r="N255" s="8" t="inlineStr"/>
     </row>
     <row r="256" ht="45" customHeight="1">
       <c r="A256" s="2" t="n">
@@ -14948,7 +14936,7 @@
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>I4</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="C256" s="13" t="inlineStr">
@@ -14963,32 +14951,32 @@
       </c>
       <c r="E256" s="6" t="inlineStr">
         <is>
-          <t>Verify state_backup.py post-Mode-1 dual-write</t>
+          <t>Verify backtest persistence (cb1f5a010)</t>
         </is>
       </c>
       <c r="F256" s="5" t="inlineStr">
         <is>
-          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
+          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
         </is>
       </c>
       <c r="G256" s="5" t="inlineStr">
         <is>
-          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
+          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>verified (no change needed)</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="I256" s="5" t="inlineStr">
         <is>
-          <t>Win: confirms infrastructure still healthy.</t>
+          <t>Win: persistence works; no silent overwrites.</t>
         </is>
       </c>
       <c r="J256" s="5" t="inlineStr">
         <is>
-          <t>7 backup dirs present, latest 2026-05-08.</t>
+          <t>3 snapshot files present. Validates cb1f5a010.</t>
         </is>
       </c>
       <c r="K256" s="12" t="inlineStr">
@@ -15004,7 +14992,7 @@
       <c r="M256" s="3" t="inlineStr"/>
       <c r="N256" s="8" t="inlineStr">
         <is>
-          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
+          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15002,7 @@
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>UI-3</t>
+          <t>I4</t>
         </is>
       </c>
       <c r="C257" s="13" t="inlineStr">
@@ -15024,35 +15012,39 @@
       </c>
       <c r="D257" s="5" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E257" s="6" t="inlineStr">
         <is>
-          <t>Remove emoji icons from Thesis + Research labels</t>
+          <t>Verify state_backup.py post-Mode-1 dual-write</t>
         </is>
       </c>
       <c r="F257" s="5" t="inlineStr">
         <is>
-          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
+          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
         </is>
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>Removed emojis from FD sub-tab nav + section headers.</t>
+          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>verified (no change needed)</t>
         </is>
       </c>
       <c r="I257" s="5" t="inlineStr">
         <is>
-          <t>Low / cosmetic</t>
-        </is>
-      </c>
-      <c r="J257" s="5" t="inlineStr"/>
+          <t>Win: confirms infrastructure still healthy.</t>
+        </is>
+      </c>
+      <c r="J257" s="5" t="inlineStr">
+        <is>
+          <t>7 backup dirs present, latest 2026-05-08.</t>
+        </is>
+      </c>
       <c r="K257" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -15060,17 +15052,13 @@
       </c>
       <c r="L257" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="M257" s="3" t="inlineStr">
-        <is>
-          <t>24fd7c273</t>
-        </is>
-      </c>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M257" s="3" t="inlineStr"/>
       <c r="N257" s="8" t="inlineStr">
         <is>
-          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
+          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
         </is>
       </c>
     </row>
@@ -15080,59 +15068,63 @@
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-2</t>
-        </is>
-      </c>
-      <c r="C258" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>UI-3</t>
+        </is>
+      </c>
+      <c r="C258" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D258" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="E258" s="6" t="inlineStr">
         <is>
-          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
+          <t>Remove emoji icons from Thesis + Research labels</t>
         </is>
       </c>
       <c r="F258" s="5" t="inlineStr">
         <is>
-          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
+          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
         </is>
       </c>
       <c r="G258" s="5" t="inlineStr">
         <is>
-          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
+          <t>Removed emojis from FD sub-tab nav + section headers.</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>5 min after answer</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I258" s="5" t="inlineStr">
         <is>
-          <t>Win: -671 lines.</t>
-        </is>
-      </c>
-      <c r="J258" s="5" t="inlineStr">
-        <is>
-          <t>Standard data-migration retention practice.</t>
-        </is>
-      </c>
-      <c r="K258" s="14" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L258" s="2" t="inlineStr"/>
-      <c r="M258" s="3" t="inlineStr"/>
+          <t>Low / cosmetic</t>
+        </is>
+      </c>
+      <c r="J258" s="5" t="inlineStr"/>
+      <c r="K258" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L258" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M258" s="3" t="inlineStr">
+        <is>
+          <t>24fd7c273</t>
+        </is>
+      </c>
       <c r="N258" s="8" t="inlineStr">
         <is>
-          <t>n/a — deferred</t>
+          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
         </is>
       </c>
     </row>
@@ -15142,7 +15134,7 @@
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>PERF-8-13</t>
+          <t>CLEAN-2</t>
         </is>
       </c>
       <c r="C259" s="10" t="inlineStr">
@@ -15152,37 +15144,37 @@
       </c>
       <c r="D259" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E259" s="6" t="inlineStr">
         <is>
-          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
+          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
         </is>
       </c>
       <c r="F259" s="5" t="inlineStr">
         <is>
-          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
+          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
         </is>
       </c>
       <c r="G259" s="5" t="inlineStr">
         <is>
-          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
+          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
-          <t>hours-days each</t>
+          <t>5 min after answer</t>
         </is>
       </c>
       <c r="I259" s="5" t="inlineStr">
         <is>
-          <t>Win varies; defer until PERF-7 measured.</t>
+          <t>Win: -671 lines.</t>
         </is>
       </c>
       <c r="J259" s="5" t="inlineStr">
         <is>
-          <t>Don't pre-implement.</t>
+          <t>Standard data-migration retention practice.</t>
         </is>
       </c>
       <c r="K259" s="14" t="inlineStr">
@@ -15204,109 +15196,109 @@
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>Q1-step7</t>
-        </is>
-      </c>
-      <c r="C260" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>PERF-8-13</t>
+        </is>
+      </c>
+      <c r="C260" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D260" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E260" s="6" t="inlineStr">
         <is>
-          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
         </is>
       </c>
       <c r="F260" s="5" t="inlineStr">
         <is>
-          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
         </is>
       </c>
       <c r="G260" s="5" t="inlineStr">
         <is>
-          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
+          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>hours-days each</t>
         </is>
       </c>
       <c r="I260" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Win varies; defer until PERF-7 measured.</t>
         </is>
       </c>
       <c r="J260" s="5" t="inlineStr">
         <is>
-          <t>Agents skim and miss post-filter subset analysis.</t>
-        </is>
-      </c>
-      <c r="K260" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
+          <t>Don't pre-implement.</t>
+        </is>
+      </c>
+      <c r="K260" s="14" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
         </is>
       </c>
       <c r="L260" s="2" t="inlineStr"/>
       <c r="M260" s="3" t="inlineStr"/>
       <c r="N260" s="8" t="inlineStr">
         <is>
-          <t>n/a — rejected</t>
-        </is>
-      </c>
-    </row>
-    <row r="261" ht="75" customHeight="1">
+          <t>n/a — deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="45" customHeight="1">
       <c r="A261" s="2" t="n">
         <v>260</v>
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>MOD-2</t>
-        </is>
-      </c>
-      <c r="C261" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Q1-step7</t>
+        </is>
+      </c>
+      <c r="C261" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D261" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E261" s="6" t="inlineStr">
         <is>
-          <t>Pixel-diff regression baseline</t>
+          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
         </is>
       </c>
       <c r="F261" s="5" t="inlineStr">
         <is>
-          <t>After modularization, no automated visual-regression catch.</t>
+          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
         </is>
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I261" s="5" t="inlineStr">
         <is>
-          <t>Win: catches accidental layout regressions.</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J261" s="5" t="inlineStr">
         <is>
-          <t>User declared out of scope 2026-05-11. Pixel-diff regression testing not needed; visual regressions can be caught by manual review when CSS/markup changes ship. Test scaffold remains in tests/04-pixel-diff.spec.js for future opt-in but no baseline PNGs will be generated.</t>
+          <t>Agents skim and miss post-filter subset analysis.</t>
         </is>
       </c>
       <c r="K261" s="15" t="inlineStr">
@@ -15314,147 +15306,209 @@
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="L261" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
+      <c r="L261" s="2" t="inlineStr"/>
       <c r="M261" s="3" t="inlineStr"/>
       <c r="N261" s="8" t="inlineStr">
         <is>
-          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="262" ht="195" customHeight="1">
+          <t>n/a — rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="75" customHeight="1">
       <c r="A262" s="2" t="n">
         <v>261</v>
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
+          <t>MOD-2</t>
+        </is>
+      </c>
+      <c r="C262" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D262" s="5" t="inlineStr">
+        <is>
+          <t>UI / Modularization</t>
+        </is>
+      </c>
+      <c r="E262" s="6" t="inlineStr">
+        <is>
+          <t>Pixel-diff regression baseline</t>
+        </is>
+      </c>
+      <c r="F262" s="5" t="inlineStr">
+        <is>
+          <t>After modularization, no automated visual-regression catch.</t>
+        </is>
+      </c>
+      <c r="G262" s="5" t="inlineStr">
+        <is>
+          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+        </is>
+      </c>
+      <c r="H262" s="2" t="inlineStr">
+        <is>
+          <t>2-3 hrs</t>
+        </is>
+      </c>
+      <c r="I262" s="5" t="inlineStr">
+        <is>
+          <t>Win: catches accidental layout regressions.</t>
+        </is>
+      </c>
+      <c r="J262" s="5" t="inlineStr">
+        <is>
+          <t>User declared out of scope 2026-05-11. Pixel-diff regression testing not needed; visual regressions can be caught by manual review when CSS/markup changes ship. Test scaffold remains in tests/04-pixel-diff.spec.js for future opt-in but no baseline PNGs will be generated.</t>
+        </is>
+      </c>
+      <c r="K262" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L262" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="M262" s="3" t="inlineStr"/>
+      <c r="N262" s="8" t="inlineStr">
+        <is>
+          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="195" customHeight="1">
+      <c r="A263" s="2" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" s="3" t="inlineStr">
+        <is>
           <t>OB-CONFLUENCE-PROPOSAL-REJECTED</t>
         </is>
       </c>
-      <c r="C262" s="10" t="inlineStr">
+      <c r="C263" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D262" s="5" t="inlineStr">
+      <c r="D263" s="5" t="inlineStr">
         <is>
           <t>Signals / Cross-Check</t>
         </is>
       </c>
-      <c r="E262" s="6" t="inlineStr">
+      <c r="E263" s="6" t="inlineStr">
         <is>
           <t>OB-confluence Wilson bump + OB-aware stop — proposals KILLED by backtest evidence</t>
         </is>
       </c>
-      <c r="F262" s="5" t="inlineStr">
+      <c r="F263" s="5" t="inlineStr">
         <is>
           <t>User asked 2026-05-12 to ship #2 (Wilson-bump score factor for bullish OB confluence within 5% of entry) and #5 (OB-low as stop instead of 1.25xATR). Per Principle 1 / Principle 7, ran post-hoc validation: scripts/validate_ob_confluence.py retroactively tags every closed trade from existing portfolio_backtest outputs with SMC state at entry date, computes Wilson 95% LB per subset.
 RESULT (750-day backtest · n=384): Bull OB confluence within 5% of entry DECREASES Wilson LB by -8.6pp (14.6% vs baseline 23.1%). BOS-bullish boost: -3.4pp. SMC-bullish direction boost: -3.6pp. Per #5 simulation, 35 of 39 (90%) OB-low-as-stop would have loosened the stop; 25 of those still ended in losses (looser stops do not rescue broken setups, they extend exposure).
 Principle 4 fires: proposals FALSIFIED, killed permanently (not retuned). Doing the change without this validation would have introduced a 6-9pp Wilson-LB drag on every BUY signal.</t>
         </is>
       </c>
-      <c r="G262" s="5" t="inlineStr">
+      <c r="G263" s="5" t="inlineStr">
         <is>
           <t>Built scripts/validate_ob_confluence.py to retroactively run smart_money.score_smc() on the historical OHLCV at each trade's entry date, tag with OB-confluence + BOS + CHoCH flags, compute Wilson 95% LB per subset, and apply Principle 1 gates (n&gt;=30, lift&gt;=5pp). Cross-validated on 250d (n=142) and 750d (n=384) backtest outputs. Both agree: NO EDGE.</t>
         </is>
       </c>
-      <c r="H262" s="2" t="inlineStr">
+      <c r="H263" s="2" t="inlineStr">
         <is>
           <t>Days of work avoided (would have shipped a degrading change).</t>
         </is>
       </c>
-      <c r="I262" s="5" t="inlineStr">
+      <c r="I263" s="5" t="inlineStr">
         <is>
           <t>Mechanism (Principle 2): institutional OBs are supposed to mark re-add zones for smart money. Falsification (Principle 4): if the data doesn't show OB-confluent trades winning more, the mechanism either doesn't exist for retail-accessible OB detection at daily resolution OR is already priced into our 5-pillar score. Either way: ship nothing. The proposals are dead. Win: prevented a 6-9pp Wilson-LB drag from being added to live scoring. Lost: nothing — we didn't change live scoring, no opportunity cost.</t>
         </is>
       </c>
-      <c r="J262" s="5" t="inlineStr">
+      <c r="J263" s="5" t="inlineStr">
         <is>
           <t>Validator script is reusable infrastructure. Re-run any time the SMC detection logic or score thresholds change. NOTE: baseline WR in 750d backtest is 27.3% (low) — the absolute level reflects backtest-window-specific market conditions; the SUBSET comparisons are valid regardless because they share the same baseline. Do not interpret 23.1% Wilson LB as a system-level edge — that's a separate question. This validation answers ONLY: does OB-confluence improve selection within whatever the system already does.</t>
         </is>
       </c>
-      <c r="K262" s="15" t="inlineStr">
+      <c r="K263" s="15" t="inlineStr">
         <is>
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="L262" s="2" t="inlineStr">
+      <c r="L263" s="2" t="inlineStr">
         <is>
           <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="M262" s="3" t="inlineStr"/>
-      <c r="N262" s="8" t="inlineStr">
-        <is>
-          <t>python3 scripts/validate_ob_confluence.py --backtest cache/portfolio_backtest_750d_20260509_100501.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="263" ht="90" customHeight="1">
-      <c r="A263" s="2" t="n">
-        <v>262</v>
-      </c>
-      <c r="B263" s="3" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C263" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="D263" s="5" t="inlineStr">
-        <is>
-          <t>Data / Universe</t>
-        </is>
-      </c>
-      <c r="E263" s="6" t="inlineStr">
-        <is>
-          <t>Russell 1000 historical membership (Sharadar SF1)</t>
-        </is>
-      </c>
-      <c r="F263" s="5" t="inlineStr">
-        <is>
-          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
-        </is>
-      </c>
-      <c r="G263" s="5" t="inlineStr">
-        <is>
-          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
-        </is>
-      </c>
-      <c r="H263" s="2" t="inlineStr">
-        <is>
-          <t>$$ + 1 day</t>
-        </is>
-      </c>
-      <c r="I263" s="5" t="inlineStr">
-        <is>
-          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
-        </is>
-      </c>
-      <c r="J263" s="5" t="inlineStr">
-        <is>
-          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
-        </is>
-      </c>
-      <c r="K263" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="L263" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M263" s="3" t="inlineStr"/>
       <c r="N263" s="8" t="inlineStr">
+        <is>
+          <t>python3 scripts/validate_ob_confluence.py --backtest cache/portfolio_backtest_750d_20260509_100501.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="90" customHeight="1">
+      <c r="A264" s="2" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C264" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D264" s="5" t="inlineStr">
+        <is>
+          <t>Data / Universe</t>
+        </is>
+      </c>
+      <c r="E264" s="6" t="inlineStr">
+        <is>
+          <t>Russell 1000 historical membership (Sharadar SF1)</t>
+        </is>
+      </c>
+      <c r="F264" s="5" t="inlineStr">
+        <is>
+          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
+        </is>
+      </c>
+      <c r="G264" s="5" t="inlineStr">
+        <is>
+          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="inlineStr">
+        <is>
+          <t>$$ + 1 day</t>
+        </is>
+      </c>
+      <c r="I264" s="5" t="inlineStr">
+        <is>
+          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
+        </is>
+      </c>
+      <c r="J264" s="5" t="inlineStr">
+        <is>
+          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
+        </is>
+      </c>
+      <c r="K264" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L264" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M264" s="3" t="inlineStr"/>
+      <c r="N264" s="8" t="inlineStr">
         <is>
           <t>n/a — rejected</t>
         </is>
@@ -15556,13 +15610,13 @@
         <v>31</v>
       </c>
       <c r="C4" s="18" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D4" s="18" t="n">
         <v>68</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5">
@@ -15613,13 +15667,13 @@
         <v>33</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D7" s="23" t="n">
         <v>129</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>

--- a/cache/open_items_2026-06-09.xlsx
+++ b/cache/open_items_2026-06-09.xlsx
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N264"/>
+  <dimension ref="A1:N265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -9970,13 +9970,13 @@
         </is>
       </c>
     </row>
-    <row r="170" ht="60" customHeight="1">
+    <row r="170" ht="90" customHeight="1">
       <c r="A170" s="2" t="n">
         <v>169</v>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>CONVICTION-VERDICT-ALIGN</t>
+          <t>BREAKOUT-BYPASS-LIVE</t>
         </is>
       </c>
       <c r="C170" s="9" t="inlineStr">
@@ -9986,22 +9986,22 @@
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>Signals · Sizing</t>
+          <t>Signals · Gating</t>
         </is>
       </c>
       <c r="E170" s="6" t="inlineStr">
         <is>
-          <t>Verdict=BUY masked 0-conviction names in scanner + executor</t>
+          <t>Breakout-alpha entry_quality bypass enabled</t>
         </is>
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
-          <t>10 of 12 BUY-verdict names in risk_on_choppy were conviction=AVOID/size_mult 0; scanner ranked + executor traded them as if real buys, killing user confidence + buying 0-conviction names (ARMK/PBI/WDC)</t>
+          <t>Alpha setups (VCP/52wk/10WP) were demoted to WATCH by entry_quality EXTENDED/MISSED gate (their natural state) + hidden under broad families. Surfaced granular setup_type in scanner + enabled entry_quality_breakout_bypass for alpha sub-types only (TC/BE excluded). Regime score floor still applies. Paper observation; backtest cant validate verdict changes.</t>
         </is>
       </c>
       <c r="G170" s="5" t="inlineStr">
         <is>
-          <t>executor.py conviction gate (skip 0-size, scale by size_mult); surface-signal.jsx conviction-aware Top Buys sort + tier column in Essentials</t>
+          <t>config.entry_quality_breakout_bypass._enabled=true + analysis.make_decision bypass + server setup_type surfacing</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr"/>
@@ -10019,18 +10019,18 @@
       </c>
       <c r="M170" s="3" t="inlineStr">
         <is>
-          <t>6a5a50549</t>
+          <t>cc4338d9d</t>
         </is>
       </c>
       <c r="N170" s="8" t="inlineStr"/>
     </row>
-    <row r="171" ht="45" customHeight="1">
+    <row r="171" ht="60" customHeight="1">
       <c r="A171" s="2" t="n">
         <v>170</v>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>CONFIG-1</t>
+          <t>CONVICTION-VERDICT-ALIGN</t>
         </is>
       </c>
       <c r="C171" s="9" t="inlineStr">
@@ -10040,39 +10040,27 @@
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Config</t>
+          <t>Signals · Sizing</t>
         </is>
       </c>
       <c r="E171" s="6" t="inlineStr">
         <is>
-          <t>Restore regime4_thresholds to documented baseline + variant playbook</t>
+          <t>Verdict=BUY masked 0-conviction names in scanner + executor</t>
         </is>
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08 raised buy_min to 80/80/85; produced 0 live BUYs. The 80 floor was not saving us — Variant F is the actual loser-cut.</t>
+          <t>10 of 12 BUY-verdict names in risk_on_choppy were conviction=AVOID/size_mult 0; scanner ranked + executor traded them as if real buys, killing user confidence + buying 0-conviction names (ARMK/PBI/WDC)</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>Restored: trending 65, choppy 72, risk-off 78 (per CLAUDE.md 4-Regime Detection table). Created config/variants/A/E2/G.json. Updated CLAUDE.md with 4 lessons.</t>
-        </is>
-      </c>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="I171" s="5" t="inlineStr">
-        <is>
-          <t>High — restores live BUY flow without losing Variant F protection</t>
-        </is>
-      </c>
-      <c r="J171" s="5" t="inlineStr">
-        <is>
-          <t>Caveat: alone does not unblock todays top-5 WATCH (entry_quality blocked).</t>
-        </is>
-      </c>
+          <t>executor.py conviction gate (skip 0-size, scale by size_mult); surface-signal.jsx conviction-aware Top Buys sort + tier column in Essentials</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr"/>
+      <c r="I171" s="5" t="inlineStr"/>
+      <c r="J171" s="5" t="inlineStr"/>
       <c r="K171" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -10080,27 +10068,23 @@
       </c>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="M171" s="3" t="inlineStr">
         <is>
-          <t>363984181</t>
-        </is>
-      </c>
-      <c r="N171" s="8" t="inlineStr">
-        <is>
-          <t>config/config.json regime4_thresholds.risk_on_trending.buy_min_score = 65. Run /Swing-Trade — BUYs &gt; 0 when market gives FRESH entries.</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="90" customHeight="1">
+          <t>6a5a50549</t>
+        </is>
+      </c>
+      <c r="N171" s="8" t="inlineStr"/>
+    </row>
+    <row r="172" ht="45" customHeight="1">
       <c r="A172" s="2" t="n">
         <v>171</v>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>EW-V1</t>
+          <t>CONFIG-1</t>
         </is>
       </c>
       <c r="C172" s="9" t="inlineStr">
@@ -10110,37 +10094,37 @@
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Elliott Wave</t>
+          <t>Strategy / Config</t>
         </is>
       </c>
       <c r="E172" s="6" t="inlineStr">
         <is>
-          <t>EW Rule Gate v1.0 — 8-state classifier</t>
+          <t>Restore regime4_thresholds to documented baseline + variant playbook</t>
         </is>
       </c>
       <c r="F172" s="5" t="inlineStr">
         <is>
-          <t>Legacy classify_elliott_wave was heuristic Wave-3 detector only — 2 states (impulse/corrective). Needed full spec: 8 engine states, 3 absolute impulse rules, fractal pivots, Fibonacci retracements (23.6-88.6%) and extensions (100-423.6%), multi-timeframe alignment.</t>
+          <t>2026-05-08 raised buy_min to 80/80/85; produced 0 live BUYs. The 80 floor was not saving us — Variant F is the actual loser-cut.</t>
         </is>
       </c>
       <c r="G172" s="5" t="inlineStr">
         <is>
-          <t>New classify_elliott_wave_bhe() implements full BHE v1.0 spec. Fractal pivot detector via i±2 rule. 8 states with score 0-4 contribution. Rule 1 (W2 &lt; W1 start) invalidation. Multi-TF ready (Primary/Intermediate/Minor) — daily-only in Phase 1, weekly/4H wire-in Phase 2. Sibling gate_g3_quant_veto() combines EW + Monte Carlo + Wyckoff for the quant veto.</t>
+          <t>Restored: trending 65, choppy 72, risk-off 78 (per CLAUDE.md 4-Regime Detection table). Created config/variants/A/E2/G.json. Updated CLAUDE.md with 4 lessons.</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I172" s="5" t="inlineStr">
         <is>
-          <t>Low / High (transparency + future-proof)</t>
+          <t>High — restores live BUY flow without losing Variant F protection</t>
         </is>
       </c>
       <c r="J172" s="5" t="inlineStr">
         <is>
-          <t>Runs in parallel to legacy classify_elliott_wave for backward compat. New result on plan as elliott_wave_v1. Smoke-tested: synthetic uptrend → WAVE3_IMPULSE score 4, T1/T2 from 1.618×/2.618×W1 fib extension.</t>
+          <t>Caveat: alone does not unblock todays top-5 WATCH (entry_quality blocked).</t>
         </is>
       </c>
       <c r="K172" s="12" t="inlineStr">
@@ -10155,22 +10139,22 @@
       </c>
       <c r="M172" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>363984181</t>
         </is>
       </c>
       <c r="N172" s="8" t="inlineStr">
         <is>
-          <t>python3 -c "from analysis import classify_elliott_wave_bhe, gate_g3_quant_veto; ..." with synthetic uptrend → WAVE3_IMPULSE / score 4. Open a ticker on elite-detail Models tab → elliott_wave_v1 field should populate with ew_state + score + t1/t2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="75" customHeight="1">
+          <t>config/config.json regime4_thresholds.risk_on_trending.buy_min_score = 65. Run /Swing-Trade — BUYs &gt; 0 when market gives FRESH entries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="90" customHeight="1">
       <c r="A173" s="2" t="n">
         <v>172</v>
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-M21-INFRA</t>
+          <t>EW-V1</t>
         </is>
       </c>
       <c r="C173" s="9" t="inlineStr">
@@ -10180,27 +10164,39 @@
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Targets</t>
+          <t>Strategy / Elliott Wave</t>
         </is>
       </c>
       <c r="E173" s="6" t="inlineStr">
         <is>
-          <t>Structural targets · M2.1 — engine infra (cache, endpoint, precompute, flag)</t>
+          <t>EW Rule Gate v1.0 — 8-state classifier</t>
         </is>
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-13: target_engine.py cache layer (12h TTL, atomic writes), GET /v2/trade_engine FastAPI endpoint (hybrid pre-compute + on-demand), scripts/precompute_targets.py batch runner (SP500 + R1000 + watchlist), run_daily_scan.sh hook at 06:00 only, config flag use_structural_targets:false.</t>
+          <t>Legacy classify_elliott_wave was heuristic Wave-3 detector only — 2 states (impulse/corrective). Needed full spec: 8 engine states, 3 absolute impulse rules, fractal pivots, Fibonacci retracements (23.6-88.6%) and extensions (100-423.6%), multi-timeframe alignment.</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>All five infra pieces wired and verified: 2,359× cache speedup, 8 ROST/AVGO/AAPL/NVDA cache files written, server.py syntax valid, feature flag confirmed OFF in config/config.json. Flag stays false until M2.5 cutover.</t>
-        </is>
-      </c>
-      <c r="H173" s="2" t="inlineStr"/>
-      <c r="I173" s="5" t="inlineStr"/>
-      <c r="J173" s="5" t="inlineStr"/>
+          <t>New classify_elliott_wave_bhe() implements full BHE v1.0 spec. Fractal pivot detector via i±2 rule. 8 states with score 0-4 contribution. Rule 1 (W2 &lt; W1 start) invalidation. Multi-TF ready (Primary/Intermediate/Minor) — daily-only in Phase 1, weekly/4H wire-in Phase 2. Sibling gate_g3_quant_veto() combines EW + Monte Carlo + Wyckoff for the quant veto.</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>2 hrs</t>
+        </is>
+      </c>
+      <c r="I173" s="5" t="inlineStr">
+        <is>
+          <t>Low / High (transparency + future-proof)</t>
+        </is>
+      </c>
+      <c r="J173" s="5" t="inlineStr">
+        <is>
+          <t>Runs in parallel to legacy classify_elliott_wave for backward compat. New result on plan as elliott_wave_v1. Smoke-tested: synthetic uptrend → WAVE3_IMPULSE score 4, T1/T2 from 1.618×/2.618×W1 fib extension.</t>
+        </is>
+      </c>
       <c r="K173" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -10208,7 +10204,7 @@
       </c>
       <c r="L173" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M173" s="3" t="inlineStr">
@@ -10216,15 +10212,19 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="N173" s="8" t="inlineStr"/>
-    </row>
-    <row r="174" ht="90" customHeight="1">
+      <c r="N173" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c "from analysis import classify_elliott_wave_bhe, gate_g3_quant_veto; ..." with synthetic uptrend → WAVE3_IMPULSE / score 4. Open a ticker on elite-detail Models tab → elliott_wave_v1 field should populate with ew_state + score + t1/t2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="75" customHeight="1">
       <c r="A174" s="2" t="n">
         <v>173</v>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-M22-DATA</t>
+          <t>STRUCT-TARGETS-M21-INFRA</t>
         </is>
       </c>
       <c r="C174" s="9" t="inlineStr">
@@ -10239,17 +10239,17 @@
       </c>
       <c r="E174" s="6" t="inlineStr">
         <is>
-          <t>Structural targets · M2.2 — parallel fields in data.json (non-destructive)</t>
+          <t>Structural targets · M2.1 — engine infra (cache, endpoint, precompute, flag)</t>
         </is>
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-13: build_data.py:compact_row now overlays t1_structural, t2_structural, t1_confluence, t1_sources, t1_behavior, t1_p_reach, t1_action, t1_r_multiple (and t2_* counterparts) onto every pickrow when config.use_structural_targets=true. Legacy t1/t2 (ATR-based) remain untouched — every existing consumer keeps working.</t>
+          <t>Shipped 2026-05-13: target_engine.py cache layer (12h TTL, atomic writes), GET /v2/trade_engine FastAPI endpoint (hybrid pre-compute + on-demand), scripts/precompute_targets.py batch runner (SP500 + R1000 + watchlist), run_daily_scan.sh hook at 06:00 only, config flag use_structural_targets:false.</t>
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>Gated by _structural_flag_enabled() lazy-loader; reads cache/target_engine/{TICKER}_{MODE}.json; emits structural_modes summary block (swing/position/invest) plus _te_mode_primary, _te_decision, _te_warnings diagnostics. Three-case unit test validated: flag-off no-op, flag-on with cache attaches fields, flag-on without cache no-op.</t>
+          <t>All five infra pieces wired and verified: 2,359× cache speedup, 8 ROST/AVGO/AAPL/NVDA cache files written, server.py syntax valid, feature flag confirmed OFF in config/config.json. Flag stays false until M2.5 cutover.</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr"/>
@@ -10278,7 +10278,7 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-M23-MODES</t>
+          <t>STRUCT-TARGETS-M22-DATA</t>
         </is>
       </c>
       <c r="C175" s="9" t="inlineStr">
@@ -10293,17 +10293,17 @@
       </c>
       <c r="E175" s="6" t="inlineStr">
         <is>
-          <t>Structural targets · M2.3 — mode completeness (short-gate, ETF degrade, earnings flag, INVEST stub)</t>
+          <t>Structural targets · M2.2 — parallel fields in data.json (non-destructive)</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-13: target_engine.analyze_trade now (1) rejects direction=short with short_not_supported_v1 warning, (2) detects ETFs via _KNOWN_ETF_TICKERS list and degrades swing-floor 3→2 with etf_degraded warning, (3) flags earnings_imminent when EODHD calendar shows report within 7d, (4) falls back to analyst-PT-based INVEST stub when invest mode produces no structural T1.</t>
+          <t>Shipped 2026-05-13: build_data.py:compact_row now overlays t1_structural, t2_structural, t1_confluence, t1_sources, t1_behavior, t1_p_reach, t1_action, t1_r_multiple (and t2_* counterparts) onto every pickrow when config.use_structural_targets=true. Legacy t1/t2 (ATR-based) remain untouched — every existing consumer keeps working.</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>TradeAnalysis dataclass extended with is_etf:bool, catalyst:dict, invest_stub:bool fields. All four paths green in unit tests: SHORT reject clean, SPY/QQQ/XLF flagged ETF, AMAT earnings-1d flag fired, AAPL invest_stub=true with analyst_pt × 1.0/1.3 targets.</t>
+          <t>Gated by _structural_flag_enabled() lazy-loader; reads cache/target_engine/{TICKER}_{MODE}.json; emits structural_modes summary block (swing/position/invest) plus _te_mode_primary, _te_decision, _te_warnings diagnostics. Three-case unit test validated: flag-off no-op, flag-on with cache attaches fields, flag-on without cache no-op.</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr"/>
@@ -10326,13 +10326,13 @@
       </c>
       <c r="N175" s="8" t="inlineStr"/>
     </row>
-    <row r="176" ht="75" customHeight="1">
+    <row r="176" ht="90" customHeight="1">
       <c r="A176" s="2" t="n">
         <v>175</v>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-M24-VALIDATION</t>
+          <t>STRUCT-TARGETS-M23-MODES</t>
         </is>
       </c>
       <c r="C176" s="9" t="inlineStr">
@@ -10347,17 +10347,17 @@
       </c>
       <c r="E176" s="6" t="inlineStr">
         <is>
-          <t>Structural targets · M2.4 — regression suite + monitoring</t>
+          <t>Structural targets · M2.3 — mode completeness (short-gate, ETF degrade, earnings flag, INVEST stub)</t>
         </is>
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-13: scripts/te_regression.py runs 20-ticker validation set (mega/mid/small cap + 5 ETFs) across swing+position modes, captures decision/warnings/latency/cache-status/T1-T2 vs legacy ATR diff_pct. Writes cache/logs/te_regression_&lt;TS&gt;.json + .md + append-only te_regression.log.</t>
+          <t>Shipped 2026-05-13: target_engine.analyze_trade now (1) rejects direction=short with short_not_supported_v1 warning, (2) detects ETFs via _KNOWN_ETF_TICKERS list and degrades swing-floor 3→2 with etf_degraded warning, (3) flags earnings_imminent when EODHD calendar shows report within 7d, (4) falls back to analyst-PT-based INVEST stub when invest mode produces no structural T1.</t>
         </is>
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Baseline run 2026-05-13: 36/40 trade, 4 reject, 0 errors, median 7ms (cache-warm). ETF graceful-degrade fired 10 rows, earnings-imminent fired 2 (AMAT 1d). Use --quick for 5-ticker smoke, --fail-threshold N to set exit-code threshold. Exit 1 if errors &gt; threshold (default 5), exit 2 if no results.</t>
+          <t>TradeAnalysis dataclass extended with is_etf:bool, catalyst:dict, invest_stub:bool fields. All four paths green in unit tests: SHORT reject clean, SPY/QQQ/XLF flagged ETF, AMAT earnings-1d flag fired, AAPL invest_stub=true with analyst_pt × 1.0/1.3 targets.</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr"/>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>TARGET-CAP-SWEEP</t>
+          <t>STRUCT-TARGETS-M24-VALIDATION</t>
         </is>
       </c>
       <c r="C177" s="9" t="inlineStr">
@@ -10396,22 +10396,22 @@
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>Strategy/Target Sanity</t>
+          <t>Strategy / Targets</t>
         </is>
       </c>
       <c r="E177" s="6" t="inlineStr">
         <is>
-          <t>Sweep for naive swing-high-as-target pattern across all scanners</t>
+          <t>Structural targets · M2.4 — regression suite + monitoring</t>
         </is>
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>mean_reversion.py:354 (target2 = high.iloc[-20:].max() uncapped, latent) and pullback_scanner.py:113 (target = high_252 uncapped, UI API) had the same class of bug as weekly_pullback.py. Both fixed proactively. analysis.py:7766 calculate_trade_plan also has it but is dead code (no callers).</t>
+          <t>Shipped 2026-05-13: scripts/te_regression.py runs 20-ticker validation set (mega/mid/small cap + 5 ETFs) across swing+position modes, captures decision/warnings/latency/cache-status/T1-T2 vs legacy ATR diff_pct. Writes cache/logs/te_regression_&lt;TS&gt;.json + .md + append-only te_regression.log.</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Cap target2 at price*1.10 in mean_reversion.py, cap target at price*1.15 in pullback_scanner.py. Add memory entry feedback_target_must_cap_vs_entry.md.</t>
+          <t>Baseline run 2026-05-13: 36/40 trade, 4 reject, 0 errors, median 7ms (cache-warm). ETF graceful-degrade fired 10 rows, earnings-imminent fired 2 (AMAT 1d). Use --quick for 5-ticker smoke, --fail-threshold N to set exit-code threshold. Exit 1 if errors &gt; threshold (default 5), exit 2 if no results.</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr"/>
@@ -10424,23 +10424,23 @@
       </c>
       <c r="L177" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="M177" s="3" t="inlineStr">
         <is>
-          <t>87336f2de</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N177" s="8" t="inlineStr"/>
     </row>
-    <row r="178" ht="60" customHeight="1">
+    <row r="178" ht="75" customHeight="1">
       <c r="A178" s="2" t="n">
         <v>177</v>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>TARGET-CAP-SWEEP</t>
         </is>
       </c>
       <c r="C178" s="9" t="inlineStr">
@@ -10450,39 +10450,27 @@
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>UI / Drift</t>
+          <t>Strategy/Target Sanity</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
         <is>
-          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
+          <t>Sweep for naive swing-high-as-target pattern across all scanners</t>
         </is>
       </c>
       <c r="F178" s="5" t="inlineStr">
         <is>
-          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
+          <t>mean_reversion.py:354 (target2 = high.iloc[-20:].max() uncapped, latent) and pullback_scanner.py:113 (target = high_252 uncapped, UI API) had the same class of bug as weekly_pullback.py. Both fixed proactively. analysis.py:7766 calculate_trade_plan also has it but is dead code (no callers).</t>
         </is>
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
-        </is>
-      </c>
-      <c r="H178" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I178" s="5" t="inlineStr">
-        <is>
-          <t>Win: continuous drift visibility between alert events.</t>
-        </is>
-      </c>
-      <c r="J178" s="5" t="inlineStr">
-        <is>
-          <t>Additive — only renders if #driftBody container exists in DOM.</t>
-        </is>
-      </c>
+          <t>Cap target2 at price*1.10 in mean_reversion.py, cap target at price*1.15 in pullback_scanner.py. Add memory entry feedback_target_must_cap_vs_entry.md.</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr"/>
+      <c r="I178" s="5" t="inlineStr"/>
+      <c r="J178" s="5" t="inlineStr"/>
       <c r="K178" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -10490,27 +10478,23 @@
       </c>
       <c r="L178" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
-          <t>16a26b201</t>
-        </is>
-      </c>
-      <c r="N178" s="8" t="inlineStr">
-        <is>
-          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="45" customHeight="1">
+          <t>87336f2de</t>
+        </is>
+      </c>
+      <c r="N178" s="8" t="inlineStr"/>
+    </row>
+    <row r="179" ht="60" customHeight="1">
       <c r="A179" s="2" t="n">
         <v>178</v>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>MOD-3</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="C179" s="9" t="inlineStr">
@@ -10520,37 +10504,37 @@
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>UI / Drift</t>
         </is>
       </c>
       <c r="E179" s="6" t="inlineStr">
         <is>
-          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
+          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
         </is>
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
+          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
         </is>
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
+          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I179" s="5" t="inlineStr">
         <is>
-          <t>Win: full auth-gated test coverage in CI.</t>
+          <t>Win: continuous drift visibility between alert events.</t>
         </is>
       </c>
       <c r="J179" s="5" t="inlineStr">
         <is>
-          <t>Trivial.</t>
+          <t>Additive — only renders if #driftBody container exists in DOM.</t>
         </is>
       </c>
       <c r="K179" s="12" t="inlineStr">
@@ -10565,22 +10549,22 @@
       </c>
       <c r="M179" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>16a26b201</t>
         </is>
       </c>
       <c r="N179" s="8" t="inlineStr">
         <is>
-          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" ht="105" customHeight="1">
+          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="45" customHeight="1">
       <c r="A180" s="2" t="n">
         <v>179</v>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>MOD-A</t>
+          <t>MOD-3</t>
         </is>
       </c>
       <c r="C180" s="9" t="inlineStr">
@@ -10595,24 +10579,32 @@
       </c>
       <c r="E180" s="6" t="inlineStr">
         <is>
-          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
+          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
         </is>
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
+          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
         </is>
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
-        </is>
-      </c>
-      <c r="H180" s="2" t="inlineStr"/>
-      <c r="I180" s="5" t="inlineStr"/>
+          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="I180" s="5" t="inlineStr">
+        <is>
+          <t>Win: full auth-gated test coverage in CI.</t>
+        </is>
+      </c>
       <c r="J180" s="5" t="inlineStr">
         <is>
-          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
+          <t>Trivial.</t>
         </is>
       </c>
       <c r="K180" s="12" t="inlineStr">
@@ -10622,17 +10614,17 @@
       </c>
       <c r="L180" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M180" s="3" t="inlineStr">
         <is>
-          <t>9517bbbe9..7229d4ccb</t>
+          <t>2b7d2f40f</t>
         </is>
       </c>
       <c r="N180" s="8" t="inlineStr">
         <is>
-          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
+          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
         </is>
       </c>
     </row>
@@ -10642,7 +10634,7 @@
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>MOD-B</t>
+          <t>MOD-A</t>
         </is>
       </c>
       <c r="C181" s="9" t="inlineStr">
@@ -10657,24 +10649,24 @@
       </c>
       <c r="E181" s="6" t="inlineStr">
         <is>
-          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
+          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
         </is>
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
+          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr">
         <is>
-          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr"/>
       <c r="I181" s="5" t="inlineStr"/>
       <c r="J181" s="5" t="inlineStr">
         <is>
-          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
+          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
         </is>
       </c>
       <c r="K181" s="12" t="inlineStr">
@@ -10689,22 +10681,22 @@
       </c>
       <c r="M181" s="3" t="inlineStr">
         <is>
-          <t>18ef1002e..388c316c4</t>
+          <t>9517bbbe9..7229d4ccb</t>
         </is>
       </c>
       <c r="N181" s="8" t="inlineStr">
         <is>
-          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="45" customHeight="1">
+          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="105" customHeight="1">
       <c r="A182" s="2" t="n">
         <v>181</v>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>UI-2</t>
+          <t>MOD-B</t>
         </is>
       </c>
       <c r="C182" s="9" t="inlineStr">
@@ -10714,37 +10706,29 @@
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>UI / Overview</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
         <is>
-          <t>Overview tab: align reads with sibling-tab canonical sources</t>
+          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
         </is>
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>Overview read flat T.* fields that drift from sibling-tab displays. Different precedence rules across tabs.</t>
+          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
         </is>
       </c>
       <c r="G182" s="5" t="inlineStr">
         <is>
-          <t>Refactored overview.js: T.fund_real, T.insider_full, T.news_sentiment_score, T.options_iv, T.technicals.indicators precedence first.</t>
-        </is>
-      </c>
-      <c r="H182" s="2" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="I182" s="5" t="inlineStr">
-        <is>
-          <t>Low risk / Medium win (consistency)</t>
-        </is>
-      </c>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr"/>
+      <c r="I182" s="5" t="inlineStr"/>
       <c r="J182" s="5" t="inlineStr">
         <is>
-          <t>All reads use ?? fallbacks.</t>
+          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
         </is>
       </c>
       <c r="K182" s="12" t="inlineStr">
@@ -10759,12 +10743,12 @@
       </c>
       <c r="M182" s="3" t="inlineStr">
         <is>
-          <t>5ffdd8e07</t>
+          <t>18ef1002e..388c316c4</t>
         </is>
       </c>
       <c r="N182" s="8" t="inlineStr">
         <is>
-          <t>Compare Overview vs Fundamentals/Sentiment/Insider/Options sub-tabs - numbers should match.</t>
+          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
         </is>
       </c>
     </row>
@@ -10774,7 +10758,7 @@
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>RULE-1</t>
+          <t>UI-2</t>
         </is>
       </c>
       <c r="C183" s="9" t="inlineStr">
@@ -10784,35 +10768,39 @@
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>UI / Rule Engine</t>
+          <t>UI / Overview</t>
         </is>
       </c>
       <c r="E183" s="6" t="inlineStr">
         <is>
-          <t>Rule Engine: 8-gate cascade + multiplier stack + regime4_thresholds</t>
+          <t>Overview tab: align reads with sibling-tab canonical sources</t>
         </is>
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>Rule Engine read legacy T.gate.passed not T.gates_evaluated. Did not show setup_size_multiplier or kelly_size.* multipliers.</t>
+          <t>Overview read flat T.* fields that drift from sibling-tab displays. Different precedence rules across tabs.</t>
         </is>
       </c>
       <c r="G183" s="5" t="inlineStr">
         <is>
-          <t>Added Stage 2.5 (8-Gate Cascade). Stage 8 surfaces full multiplier stack. Counterfactuals read regime4-aware threshold first.</t>
+          <t>Refactored overview.js: T.fund_real, T.insider_full, T.news_sentiment_score, T.options_iv, T.technicals.indicators precedence first.</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>45 min</t>
         </is>
       </c>
       <c r="I183" s="5" t="inlineStr">
         <is>
-          <t>Low risk / Medium win (transparency)</t>
-        </is>
-      </c>
-      <c r="J183" s="5" t="inlineStr"/>
+          <t>Low risk / Medium win (consistency)</t>
+        </is>
+      </c>
+      <c r="J183" s="5" t="inlineStr">
+        <is>
+          <t>All reads use ?? fallbacks.</t>
+        </is>
+      </c>
       <c r="K183" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -10825,22 +10813,22 @@
       </c>
       <c r="M183" s="3" t="inlineStr">
         <is>
-          <t>40f8452b8</t>
+          <t>5ffdd8e07</t>
         </is>
       </c>
       <c r="N183" s="8" t="inlineStr">
         <is>
-          <t>Open elite-detail Rule Engine sub-tab. Stage 2.5 shows 8 gates pass/fail. TC ticker in bull shows "Setup edge multiplier - KILLED 0.00x".</t>
-        </is>
-      </c>
-    </row>
-    <row r="184" ht="105" customHeight="1">
+          <t>Compare Overview vs Fundamentals/Sentiment/Insider/Options sub-tabs - numbers should match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="45" customHeight="1">
       <c r="A184" s="2" t="n">
         <v>183</v>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>TARGET-SOURCES-P1</t>
+          <t>RULE-1</t>
         </is>
       </c>
       <c r="C184" s="9" t="inlineStr">
@@ -10850,39 +10838,35 @@
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>UI / Trade Plan</t>
+          <t>UI / Rule Engine</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
         <is>
-          <t>Phase 1 structural target sources (display-only)</t>
+          <t>Rule Engine: 8-gate cascade + multiplier stack + regime4_thresholds</t>
         </is>
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>Target prices come from generic ATR multiples. User wants targets from objective TA sources: order blocks, fractals, fib levels, EW waves — per horizon (short/medium/long).</t>
+          <t>Rule Engine read legacy T.gate.passed not T.gates_evaluated. Did not show setup_size_multiplier or kelly_size.* multipliers.</t>
         </is>
       </c>
       <c r="G184" s="5" t="inlineStr">
         <is>
-          <t>New plan.target_sources field populated in compute_trade_plan with 5 sources: (1) fractal_high (Williams 5-bar, short horizon), (2) fib_127_extension (medium), (3) fib_162_extension (medium), (4) ew_intermediate_t1 (v1 Wave-3 1.618×W1, medium), (5) ew_intermediate_t2 (v1 2.618×W1, long). DISPLAY ONLY — actual T1/T2 unchanged. Need ≥30 trade evidence per source × regime before changing BUY logic (Phase 2).</t>
+          <t>Added Stage 2.5 (8-Gate Cascade). Stage 8 surfaces full multiplier stack. Counterfactuals read regime4-aware threshold first.</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>1.5 hrs</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I184" s="5" t="inlineStr">
         <is>
-          <t>Low (no behavior change)</t>
-        </is>
-      </c>
-      <c r="J184" s="5" t="inlineStr">
-        <is>
-          <t>Phase 2 (config-driven flip to structural targets) deferred until Phase 1 evidence collected. Order blocks (SMC) not yet sourced — separate sub-task to wire into target_sources.</t>
-        </is>
-      </c>
+          <t>Low risk / Medium win (transparency)</t>
+        </is>
+      </c>
+      <c r="J184" s="5" t="inlineStr"/>
       <c r="K184" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -10895,22 +10879,22 @@
       </c>
       <c r="M184" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>40f8452b8</t>
         </is>
       </c>
       <c r="N184" s="8" t="inlineStr">
         <is>
-          <t>Test ticker → plan.target_sources dict should have 3-5 entries, each with {horizon, level, rationale}. Phase 2 will surface in elite-detail Plan tab and Overview Trade Plan strip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="185" ht="45" customHeight="1">
+          <t>Open elite-detail Rule Engine sub-tab. Stage 2.5 shows 8 gates pass/fail. TC ticker in bull shows "Setup edge multiplier - KILLED 0.00x".</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="105" customHeight="1">
       <c r="A185" s="2" t="n">
         <v>184</v>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>UNIVERSE-NASDAQ-1000</t>
+          <t>TARGET-SOURCES-P1</t>
         </is>
       </c>
       <c r="C185" s="9" t="inlineStr">
@@ -10920,27 +10904,39 @@
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>Universe</t>
+          <t>UI / Trade Plan</t>
         </is>
       </c>
       <c r="E185" s="6" t="inlineStr">
         <is>
-          <t>NASDAQ 1000 liquidity gate</t>
+          <t>Phase 1 structural target sources (display-only)</t>
         </is>
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>get_nasdaq_all replaced full 4805-name exchange list with top-1000 by dollar volume (one bulk_eod call); config nasdaq_all_top_n/min_dollar_vol</t>
+          <t>Target prices come from generic ATR multiples. User wants targets from objective TA sources: order blocks, fractals, fib levels, EW waves — per horizon (short/medium/long).</t>
         </is>
       </c>
       <c r="G185" s="5" t="inlineStr">
         <is>
-          <t>data_fetcher.get_nasdaq_all + config.json + swing_trade.py</t>
-        </is>
-      </c>
-      <c r="H185" s="2" t="inlineStr"/>
-      <c r="I185" s="5" t="inlineStr"/>
-      <c r="J185" s="5" t="inlineStr"/>
+          <t>New plan.target_sources field populated in compute_trade_plan with 5 sources: (1) fractal_high (Williams 5-bar, short horizon), (2) fib_127_extension (medium), (3) fib_162_extension (medium), (4) ew_intermediate_t1 (v1 Wave-3 1.618×W1, medium), (5) ew_intermediate_t2 (v1 2.618×W1, long). DISPLAY ONLY — actual T1/T2 unchanged. Need ≥30 trade evidence per source × regime before changing BUY logic (Phase 2).</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>1.5 hrs</t>
+        </is>
+      </c>
+      <c r="I185" s="5" t="inlineStr">
+        <is>
+          <t>Low (no behavior change)</t>
+        </is>
+      </c>
+      <c r="J185" s="5" t="inlineStr">
+        <is>
+          <t>Phase 2 (config-driven flip to structural targets) deferred until Phase 1 evidence collected. Order blocks (SMC) not yet sourced — separate sub-task to wire into target_sources.</t>
+        </is>
+      </c>
       <c r="K185" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -10948,15 +10944,19 @@
       </c>
       <c r="L185" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M185" s="3" t="inlineStr">
         <is>
-          <t>ab1deacef</t>
-        </is>
-      </c>
-      <c r="N185" s="8" t="inlineStr"/>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N185" s="8" t="inlineStr">
+        <is>
+          <t>Test ticker → plan.target_sources dict should have 3-5 entries, each with {horizon, level, rationale}. Phase 2 will surface in elite-detail Plan tab and Overview Trade Plan strip.</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="45" customHeight="1">
       <c r="A186" s="2" t="n">
@@ -10964,7 +10964,7 @@
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>STOCKSMITH-KAIROS-DOSSIER</t>
+          <t>UNIVERSE-NASDAQ-1000</t>
         </is>
       </c>
       <c r="C186" s="9" t="inlineStr">
@@ -10974,22 +10974,22 @@
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>V2 Dashboard / Kairos</t>
+          <t>Universe</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
         <is>
-          <t>Ask Kairos cross-lens ticker dossier (§4)</t>
+          <t>NASDAQ 1000 liquidity gate</t>
         </is>
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>composite verdict + 9 lens stances + ML projection injected as LLM context; fallbackAnswer offline</t>
+          <t>get_nasdaq_all replaced full 4805-name exchange list with top-1000 by dollar volume (one bulk_eod call); config nasdaq_all_top_n/min_dollar_vol</t>
         </is>
       </c>
       <c r="G186" s="5" t="inlineStr">
         <is>
-          <t>Stocksmith.html kaiTickerDossier</t>
+          <t>data_fetcher.get_nasdaq_all + config.json + swing_trade.py</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr"/>
@@ -11007,7 +11007,7 @@
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
-          <t>e3baa715f</t>
+          <t>ab1deacef</t>
         </is>
       </c>
       <c r="N186" s="8" t="inlineStr"/>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>REGIME-ACCURACY-TEST</t>
+          <t>STOCKSMITH-KAIROS-DOSSIER</t>
         </is>
       </c>
       <c r="C187" s="9" t="inlineStr">
@@ -11028,22 +11028,22 @@
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>Validation / Regime</t>
+          <t>V2 Dashboard / Kairos</t>
         </is>
       </c>
       <c r="E187" s="6" t="inlineStr">
         <is>
-          <t>Regime-classification accuracy test (principle 18)</t>
+          <t>Ask Kairos cross-lens ticker dossier (§4)</t>
         </is>
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
-          <t>when model said trending was next 5d actually trending? label regime outcomes, validate classifier</t>
+          <t>composite verdict + 9 lens stances + ML projection injected as LLM context; fallbackAnswer offline</t>
         </is>
       </c>
       <c r="G187" s="5" t="inlineStr">
         <is>
-          <t>scripts/regime_accuracy.py</t>
+          <t>Stocksmith.html kaiTickerDossier</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr"/>
@@ -11056,48 +11056,48 @@
       </c>
       <c r="L187" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M187" s="3" t="inlineStr">
         <is>
-          <t>d1ea97913</t>
+          <t>e3baa715f</t>
         </is>
       </c>
       <c r="N187" s="8" t="inlineStr"/>
     </row>
-    <row r="188" ht="90" customHeight="1">
+    <row r="188" ht="45" customHeight="1">
       <c r="A188" s="2" t="n">
         <v>187</v>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>WEEKEND-PHANTOMS</t>
-        </is>
-      </c>
-      <c r="C188" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>REGIME-ACCURACY-TEST</t>
+        </is>
+      </c>
+      <c r="C188" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>Audit Trail / Data Quality</t>
+          <t>Validation / Regime</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
         <is>
-          <t>Weekend pick_dates (Sat/Sun) in audit ledger</t>
+          <t>Regime-classification accuracy test (principle 18)</t>
         </is>
       </c>
       <c r="F188" s="5" t="inlineStr">
         <is>
-          <t>signal_log writes pick_date as today.isoformat() — when scan runs on weekend (manual rerun), produces Sat/Sun dates EODHD can't price. 355 such phantoms in ledger. Fix: snap weekend dates forward to next Monday at both write-time (signal_tracker.log_signals) and build-time (build_audit_ledger.py). Preserves original via pick_date_orig field</t>
+          <t>when model said trending was next 5d actually trending? label regime outcomes, validate classifier</t>
         </is>
       </c>
       <c r="G188" s="5" t="inlineStr">
         <is>
-          <t>signal_tracker.py log_signals dow snap + build_audit_ledger.py _compute_returns_for_ticker snap-forward · 353 records normalized · 2 residual edge cases</t>
+          <t>scripts/regime_accuracy.py</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr"/>
@@ -11110,23 +11110,23 @@
       </c>
       <c r="L188" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M188" s="3" t="inlineStr">
         <is>
-          <t>e48edac16</t>
+          <t>d1ea97913</t>
         </is>
       </c>
       <c r="N188" s="8" t="inlineStr"/>
     </row>
-    <row r="189" ht="75" customHeight="1">
+    <row r="189" ht="90" customHeight="1">
       <c r="A189" s="2" t="n">
         <v>188</v>
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>BT-GUARD-1</t>
+          <t>WEEKEND-PHANTOMS</t>
         </is>
       </c>
       <c r="C189" s="10" t="inlineStr">
@@ -11136,22 +11136,22 @@
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
-          <t>Backtest Infrastructure</t>
+          <t>Audit Trail / Data Quality</t>
         </is>
       </c>
       <c r="E189" s="6" t="inlineStr">
         <is>
-          <t>Backtest min_score guard rail</t>
+          <t>Weekend pick_dates (Sat/Sun) in audit ledger</t>
         </is>
       </c>
       <c r="F189" s="5" t="inlineStr">
         <is>
-          <t>Users (and Claude sessions) repeatedly ran 252d backtests with --min-score 65 (live threshold) producing 0 BUYs across all 252 days. Historical scoring is structurally suppressed because sentiment/options/catalyst pillars depend on real-time data not in EODHD backfill.</t>
+          <t>signal_log writes pick_date as today.isoformat() — when scan runs on weekend (manual rerun), produces Sat/Sun dates EODHD can't price. 355 such phantoms in ledger. Fix: snap weekend dates forward to next Monday at both write-time (signal_tracker.log_signals) and build-time (build_audit_ledger.py). Preserves original via pick_date_orig field</t>
         </is>
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>backtest.py main() now warns loudly when --min-score &gt; 55 (backtest-safe floor). New --accept-low-buys flag silences the warning for legitimate grid-search explorations. --smoke bypasses the guard. Plus diagnostic doc: docs/backtest_historical_scoring_diagnostic.md.</t>
+          <t>signal_tracker.py log_signals dow snap + build_audit_ledger.py _compute_returns_for_ticker snap-forward · 353 records normalized · 2 residual edge cases</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr"/>
@@ -11169,18 +11169,18 @@
       </c>
       <c r="M189" s="3" t="inlineStr">
         <is>
-          <t>d754830</t>
+          <t>e48edac16</t>
         </is>
       </c>
       <c r="N189" s="8" t="inlineStr"/>
     </row>
-    <row r="190" ht="45" customHeight="1">
+    <row r="190" ht="75" customHeight="1">
       <c r="A190" s="2" t="n">
         <v>189</v>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-1</t>
+          <t>BT-GUARD-1</t>
         </is>
       </c>
       <c r="C190" s="10" t="inlineStr">
@@ -11190,22 +11190,22 @@
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>Choice C Strategy</t>
+          <t>Backtest Infrastructure</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
         <is>
-          <t>Design doc — docs/strategy_defensive_rotation.md</t>
+          <t>Backtest min_score guard rail</t>
         </is>
       </c>
       <c r="F190" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 of Defensive Rotation sleeve build</t>
+          <t>Users (and Claude sessions) repeatedly ran 252d backtests with --min-score 65 (live threshold) producing 0 BUYs across all 252 days. Historical scoring is structurally suppressed because sentiment/options/catalyst pillars depend on real-time data not in EODHD backfill.</t>
         </is>
       </c>
       <c r="G190" s="5" t="inlineStr">
         <is>
-          <t>Full design: mechanism, triggers, universe, validation plan</t>
+          <t>backtest.py main() now warns loudly when --min-score &gt; 55 (backtest-safe floor). New --accept-low-buys flag silences the warning for legitimate grid-search explorations. --smoke bypasses the guard. Plus diagnostic doc: docs/backtest_historical_scoring_diagnostic.md.</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr"/>
@@ -11218,12 +11218,12 @@
       </c>
       <c r="L190" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M190" s="3" t="inlineStr">
         <is>
-          <t>399922797</t>
+          <t>d754830</t>
         </is>
       </c>
       <c r="N190" s="8" t="inlineStr"/>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-2</t>
+          <t>DEFROT-1</t>
         </is>
       </c>
       <c r="C191" s="10" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="E191" s="6" t="inlineStr">
         <is>
-          <t>Config block — defensive_rotation_sleeve</t>
+          <t>Design doc — docs/strategy_defensive_rotation.md</t>
         </is>
       </c>
       <c r="F191" s="5" t="inlineStr">
@@ -11259,7 +11259,7 @@
       </c>
       <c r="G191" s="5" t="inlineStr">
         <is>
-          <t>Curated universe, regime gates, sizing, stops; default _enabled=false</t>
+          <t>Full design: mechanism, triggers, universe, validation plan</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr"/>
@@ -11288,7 +11288,7 @@
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-3</t>
+          <t>DEFROT-2</t>
         </is>
       </c>
       <c r="C192" s="10" t="inlineStr">
@@ -11303,7 +11303,7 @@
       </c>
       <c r="E192" s="6" t="inlineStr">
         <is>
-          <t>Detector function — _detect_defensive_rotation</t>
+          <t>Config block — defensive_rotation_sleeve</t>
         </is>
       </c>
       <c r="F192" s="5" t="inlineStr">
@@ -11313,7 +11313,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>Universe + regime + SPY-50EMA + RS + beta + ATR gates with per-criterion audit</t>
+          <t>Curated universe, regime gates, sizing, stops; default _enabled=false</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr"/>
@@ -11342,7 +11342,7 @@
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-4</t>
+          <t>DEFROT-3</t>
         </is>
       </c>
       <c r="C193" s="10" t="inlineStr">
@@ -11357,7 +11357,7 @@
       </c>
       <c r="E193" s="6" t="inlineStr">
         <is>
-          <t>Wire into analyze_ticker</t>
+          <t>Detector function — _detect_defensive_rotation</t>
         </is>
       </c>
       <c r="F193" s="5" t="inlineStr">
@@ -11367,7 +11367,7 @@
       </c>
       <c r="G193" s="5" t="inlineStr">
         <is>
-          <t>Setup family override + trade plan override (1.0 ATR stop, T1+3, T2+6, hold 10-30d, regime exit on SPY 50EMA reclaim)</t>
+          <t>Universe + regime + SPY-50EMA + RS + beta + ATR gates with per-criterion audit</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr"/>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-5</t>
+          <t>DEFROT-4</t>
         </is>
       </c>
       <c r="C194" s="10" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="E194" s="6" t="inlineStr">
         <is>
-          <t>Decision engine bypasses</t>
+          <t>Wire into analyze_ticker</t>
         </is>
       </c>
       <c r="F194" s="5" t="inlineStr">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>regime_gate + entry_quality + fund_adequacy bypassed for Defensive Rotation family</t>
+          <t>Setup family override + trade plan override (1.0 ATR stop, T1+3, T2+6, hold 10-30d, regime exit on SPY 50EMA reclaim)</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr"/>
@@ -11450,7 +11450,7 @@
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-6</t>
+          <t>DEFROT-5</t>
         </is>
       </c>
       <c r="C195" s="10" t="inlineStr">
@@ -11465,7 +11465,7 @@
       </c>
       <c r="E195" s="6" t="inlineStr">
         <is>
-          <t>Universe coverage</t>
+          <t>Decision engine bypasses</t>
         </is>
       </c>
       <c r="F195" s="5" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>XLP, TLT, IEF added to custom_watchlist (XLU/XLV/GLD already present)</t>
+          <t>regime_gate + entry_quality + fund_adequacy bypassed for Defensive Rotation family</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr"/>
@@ -11504,7 +11504,7 @@
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-7</t>
+          <t>DEFROT-6</t>
         </is>
       </c>
       <c r="C196" s="10" t="inlineStr">
@@ -11519,7 +11519,7 @@
       </c>
       <c r="E196" s="6" t="inlineStr">
         <is>
-          <t>Smoke test + commit</t>
+          <t>Universe coverage</t>
         </is>
       </c>
       <c r="F196" s="5" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="G196" s="5" t="inlineStr">
         <is>
-          <t>All 4 detector tests pass; ready for Phase 1 paper validation</t>
+          <t>XLP, TLT, IEF added to custom_watchlist (XLU/XLV/GLD already present)</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr"/>
@@ -11558,7 +11558,7 @@
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-1</t>
+          <t>DEFROT-7</t>
         </is>
       </c>
       <c r="C197" s="10" t="inlineStr">
@@ -11573,17 +11573,17 @@
       </c>
       <c r="E197" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion design doc</t>
+          <t>Smoke test + commit</t>
         </is>
       </c>
       <c r="F197" s="5" t="inlineStr">
         <is>
-          <t>Sleeve build</t>
+          <t>Phase 1 of Defensive Rotation sleeve build</t>
         </is>
       </c>
       <c r="G197" s="5" t="inlineStr">
         <is>
-          <t>docs/strategy_mean_reversion.md — full Jegadeesh 1990 mechanism + validation plan</t>
+          <t>All 4 detector tests pass; ready for Phase 1 paper validation</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr"/>
@@ -11601,7 +11601,7 @@
       </c>
       <c r="M197" s="3" t="inlineStr">
         <is>
-          <t>d0c6c4e04</t>
+          <t>399922797</t>
         </is>
       </c>
       <c r="N197" s="8" t="inlineStr"/>
@@ -11612,7 +11612,7 @@
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-2</t>
+          <t>MEANREV-1</t>
         </is>
       </c>
       <c r="C198" s="10" t="inlineStr">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="E198" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion config</t>
+          <t>Mean Reversion design doc</t>
         </is>
       </c>
       <c r="F198" s="5" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G198" s="5" t="inlineStr">
         <is>
-          <t>RSI&lt;30, EMA200 floor, 3-5d hold; default _enabled=true (fires in current choppy regime)</t>
+          <t>docs/strategy_mean_reversion.md — full Jegadeesh 1990 mechanism + validation plan</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr"/>
@@ -11666,7 +11666,7 @@
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-3</t>
+          <t>MEANREV-2</t>
         </is>
       </c>
       <c r="C199" s="10" t="inlineStr">
@@ -11681,7 +11681,7 @@
       </c>
       <c r="E199" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion detector</t>
+          <t>Mean Reversion config</t>
         </is>
       </c>
       <c r="F199" s="5" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>_detect_mean_reversion — 8-gate audit (regime/score/RSI/EMA200/recent_low/RVOL/ADV/earnings)</t>
+          <t>RSI&lt;30, EMA200 floor, 3-5d hold; default _enabled=true (fires in current choppy regime)</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr"/>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-4</t>
+          <t>MEANREV-3</t>
         </is>
       </c>
       <c r="C200" s="10" t="inlineStr">
@@ -11735,7 +11735,7 @@
       </c>
       <c r="E200" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion wiring</t>
+          <t>Mean Reversion detector</t>
         </is>
       </c>
       <c r="F200" s="5" t="inlineStr">
@@ -11745,7 +11745,7 @@
       </c>
       <c r="G200" s="5" t="inlineStr">
         <is>
-          <t>Setup family override + plan (1.0 ATR stop, +3/+5% T1/T2, 3-5d hold, hard time-stop)</t>
+          <t>_detect_mean_reversion — 8-gate audit (regime/score/RSI/EMA200/recent_low/RVOL/ADV/earnings)</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr"/>
@@ -11774,7 +11774,7 @@
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-5</t>
+          <t>MEANREV-4</t>
         </is>
       </c>
       <c r="C201" s="10" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="E201" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion bypass</t>
+          <t>Mean Reversion wiring</t>
         </is>
       </c>
       <c r="F201" s="5" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="G201" s="5" t="inlineStr">
         <is>
-          <t>entry_quality bypass (EXTENDED-down IS the trigger)</t>
+          <t>Setup family override + plan (1.0 ATR stop, +3/+5% T1/T2, 3-5d hold, hard time-stop)</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr"/>
@@ -11828,7 +11828,7 @@
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-6</t>
+          <t>MEANREV-5</t>
         </is>
       </c>
       <c r="C202" s="10" t="inlineStr">
@@ -11843,7 +11843,7 @@
       </c>
       <c r="E202" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion smoke test</t>
+          <t>Mean Reversion bypass</t>
         </is>
       </c>
       <c r="F202" s="5" t="inlineStr">
@@ -11853,7 +11853,7 @@
       </c>
       <c r="G202" s="5" t="inlineStr">
         <is>
-          <t>4 detector tests pass — fired=True on choppy+RSI=25+EMA200, rejected on RSI=55/below-EMA200/trending</t>
+          <t>entry_quality bypass (EXTENDED-down IS the trigger)</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr"/>
@@ -11882,7 +11882,7 @@
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>PEAD-1</t>
+          <t>MEANREV-6</t>
         </is>
       </c>
       <c r="C203" s="10" t="inlineStr">
@@ -11897,7 +11897,7 @@
       </c>
       <c r="E203" s="6" t="inlineStr">
         <is>
-          <t>PEAD design doc</t>
+          <t>Mean Reversion smoke test</t>
         </is>
       </c>
       <c r="F203" s="5" t="inlineStr">
@@ -11907,7 +11907,7 @@
       </c>
       <c r="G203" s="5" t="inlineStr">
         <is>
-          <t>docs/strategy_pead.md — Bernard-Thomas 1989, all-regime catalyst sleeve</t>
+          <t>4 detector tests pass — fired=True on choppy+RSI=25+EMA200, rejected on RSI=55/below-EMA200/trending</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr"/>
@@ -11936,7 +11936,7 @@
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>PEAD-2</t>
+          <t>PEAD-1</t>
         </is>
       </c>
       <c r="C204" s="10" t="inlineStr">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="E204" s="6" t="inlineStr">
         <is>
-          <t>PEAD config</t>
+          <t>PEAD design doc</t>
         </is>
       </c>
       <c r="F204" s="5" t="inlineStr">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="G204" s="5" t="inlineStr">
         <is>
-          <t>Day1-3 post-earnings, EPS+5/Rev+2/Gap+3/Revisions&gt;=2, full Kelly with regime caps</t>
+          <t>docs/strategy_pead.md — Bernard-Thomas 1989, all-regime catalyst sleeve</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr"/>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>PEAD-3</t>
+          <t>PEAD-2</t>
         </is>
       </c>
       <c r="C205" s="10" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="E205" s="6" t="inlineStr">
         <is>
-          <t>PEAD detector</t>
+          <t>PEAD config</t>
         </is>
       </c>
       <c r="F205" s="5" t="inlineStr">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="G205" s="5" t="inlineStr">
         <is>
-          <t>_detect_pead — 7-gate audit; regime-independent</t>
+          <t>Day1-3 post-earnings, EPS+5/Rev+2/Gap+3/Revisions&gt;=2, full Kelly with regime caps</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr"/>
@@ -12044,7 +12044,7 @@
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>PEAD-4</t>
+          <t>PEAD-3</t>
         </is>
       </c>
       <c r="C206" s="10" t="inlineStr">
@@ -12059,7 +12059,7 @@
       </c>
       <c r="E206" s="6" t="inlineStr">
         <is>
-          <t>PEAD wiring</t>
+          <t>PEAD detector</t>
         </is>
       </c>
       <c r="F206" s="5" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="G206" s="5" t="inlineStr">
         <is>
-          <t>Setup family override + plan (1.0 ATR stop, +5/+10/+15 targets, 10-30d drift hold)</t>
+          <t>_detect_pead — 7-gate audit; regime-independent</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr"/>
@@ -12098,7 +12098,7 @@
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>PEAD-5</t>
+          <t>PEAD-4</t>
         </is>
       </c>
       <c r="C207" s="10" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="E207" s="6" t="inlineStr">
         <is>
-          <t>PEAD bypasses</t>
+          <t>PEAD wiring</t>
         </is>
       </c>
       <c r="F207" s="5" t="inlineStr">
@@ -12123,7 +12123,7 @@
       </c>
       <c r="G207" s="5" t="inlineStr">
         <is>
-          <t>regime_gate bypassed (catalyst regime-independent), entry_quality bypassed (gap-up IS trigger)</t>
+          <t>Setup family override + plan (1.0 ATR stop, +5/+10/+15 targets, 10-30d drift hold)</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr"/>
@@ -12152,7 +12152,7 @@
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>PEAD-6</t>
+          <t>PEAD-5</t>
         </is>
       </c>
       <c r="C208" s="10" t="inlineStr">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="E208" s="6" t="inlineStr">
         <is>
-          <t>PEAD smoke test</t>
+          <t>PEAD bypasses</t>
         </is>
       </c>
       <c r="F208" s="5" t="inlineStr">
@@ -12177,7 +12177,7 @@
       </c>
       <c r="G208" s="5" t="inlineStr">
         <is>
-          <t>Perfect-setup test fires with all 7 audit checks ✓</t>
+          <t>regime_gate bypassed (catalyst regime-independent), entry_quality bypassed (gap-up IS trigger)</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr"/>
@@ -12206,7 +12206,7 @@
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>CLEANUP-HOT-SECTORS</t>
+          <t>PEAD-6</t>
         </is>
       </c>
       <c r="C209" s="10" t="inlineStr">
@@ -12216,22 +12216,22 @@
       </c>
       <c r="D209" s="5" t="inlineStr">
         <is>
-          <t>Code Hygiene / Signal Scanner</t>
+          <t>Choice C Strategy</t>
         </is>
       </c>
       <c r="E209" s="6" t="inlineStr">
         <is>
-          <t>Remove dead panelHotSectors function</t>
+          <t>PEAD smoke test</t>
         </is>
       </c>
       <c r="F209" s="5" t="inlineStr">
         <is>
-          <t>User asked to remove Hot Sectors panel from grid earlier; function left in file as dead code. Removed 53 lines.</t>
+          <t>Sleeve build</t>
         </is>
       </c>
       <c r="G209" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantScanner module · panelHotSectors() deleted</t>
+          <t>Perfect-setup test fires with all 7 audit checks ✓</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr"/>
@@ -12244,23 +12244,23 @@
       </c>
       <c r="L209" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="M209" s="3" t="inlineStr">
         <is>
-          <t>e48edac16</t>
+          <t>d0c6c4e04</t>
         </is>
       </c>
       <c r="N209" s="8" t="inlineStr"/>
     </row>
-    <row r="210" ht="105" customHeight="1">
+    <row r="210" ht="45" customHeight="1">
       <c r="A210" s="2" t="n">
         <v>209</v>
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>UI-CRYPTO-1</t>
+          <t>CLEANUP-HOT-SECTORS</t>
         </is>
       </c>
       <c r="C210" s="10" t="inlineStr">
@@ -12270,22 +12270,22 @@
       </c>
       <c r="D210" s="5" t="inlineStr">
         <is>
-          <t>Crypto Tab</t>
+          <t>Code Hygiene / Signal Scanner</t>
         </is>
       </c>
       <c r="E210" s="6" t="inlineStr">
         <is>
-          <t>20yr HF analyst Crypto tab rebuild</t>
+          <t>Remove dead panelHotSectors function</t>
         </is>
       </c>
       <c r="F210" s="5" t="inlineStr">
         <is>
-          <t>Crypto tab was stub with 4 cards of placeholder data. Needed a senior HF/Graham-Buffett/swing-trader fused lens for the 24/7 risk-asset bellwether.</t>
+          <t>User asked to remove Hot Sectors panel from grid earlier; function left in file as dead code. Removed 53 lines.</t>
         </is>
       </c>
       <c r="G210" s="5" t="inlineStr">
         <is>
-          <t>13-section renderCrypto in kairos.html: cycle posture banner (Pi-Cycle/MVRV-Z/NUPL/200wk MA), spot KPIs, Graham margin-of-safety floors (realized price, thermo-cap, cost of production, LTH/STH cost), ETH owner-earnings DCF, BTC hard-money compounding, stablecoin liquidity, macro drivers, spot ETF flows, derivatives tape, on-chain valuation composite, catalyst calendar, adjacent equities, L1/L2 rotation, regime-conditional playbook, pre-mortem.</t>
+          <t>kairos.html QuantScanner module · panelHotSectors() deleted</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr"/>
@@ -12303,18 +12303,18 @@
       </c>
       <c r="M210" s="3" t="inlineStr">
         <is>
-          <t>696731a4d</t>
+          <t>e48edac16</t>
         </is>
       </c>
       <c r="N210" s="8" t="inlineStr"/>
     </row>
-    <row r="211" ht="75" customHeight="1">
+    <row r="211" ht="105" customHeight="1">
       <c r="A211" s="2" t="n">
         <v>210</v>
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>EODHD-EDGAR-FUNDAMENTALS</t>
+          <t>UI-CRYPTO-1</t>
         </is>
       </c>
       <c r="C211" s="10" t="inlineStr">
@@ -12324,22 +12324,22 @@
       </c>
       <c r="D211" s="5" t="inlineStr">
         <is>
-          <t>Data / SEC EDGAR (future quality)</t>
+          <t>Crypto Tab</t>
         </is>
       </c>
       <c r="E211" s="6" t="inlineStr">
         <is>
-          <t>Offload fundamentals to SEC EDGAR (FIX 4)</t>
+          <t>20yr HF analyst Crypto tab rebuild</t>
         </is>
       </c>
       <c r="F211" s="5" t="inlineStr">
         <is>
-          <t>new edgar_client.py behind data_fetcher interface; data.sec.gov companyfacts (User-Agent + &lt;=10 req/s); map XBRL tags to fundamentals.db; nightly batch. Quality upgrade (point-in-time, fixes audit #1/#4) + zeroes per-ticker EODHD fundamentals calls.</t>
+          <t>Crypto tab was stub with 4 cards of placeholder data. Needed a senior HF/Graham-Buffett/swing-trader fused lens for the 24/7 risk-asset bellwether.</t>
         </is>
       </c>
       <c r="G211" s="5" t="inlineStr">
         <is>
-          <t>edgar_client.py + nightly batch</t>
+          <t>13-section renderCrypto in kairos.html: cycle posture banner (Pi-Cycle/MVRV-Z/NUPL/200wk MA), spot KPIs, Graham margin-of-safety floors (realized price, thermo-cap, cost of production, LTH/STH cost), ETH owner-earnings DCF, BTC hard-money compounding, stablecoin liquidity, macro drivers, spot ETF flows, derivatives tape, on-chain valuation composite, catalyst calendar, adjacent equities, L1/L2 rotation, regime-conditional playbook, pre-mortem.</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr"/>
@@ -12352,23 +12352,23 @@
       </c>
       <c r="L211" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M211" s="3" t="inlineStr">
         <is>
-          <t>5d05268ef</t>
+          <t>696731a4d</t>
         </is>
       </c>
       <c r="N211" s="8" t="inlineStr"/>
     </row>
-    <row r="212" ht="60" customHeight="1">
+    <row r="212" ht="75" customHeight="1">
       <c r="A212" s="2" t="n">
         <v>211</v>
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>SETDETAIL-FALLBACK</t>
+          <t>EODHD-EDGAR-FUNDAMENTALS</t>
         </is>
       </c>
       <c r="C212" s="10" t="inlineStr">
@@ -12378,22 +12378,22 @@
       </c>
       <c r="D212" s="5" t="inlineStr">
         <is>
-          <t>Detail UI / Routing</t>
+          <t>Data / SEC EDGAR (future quality)</t>
         </is>
       </c>
       <c r="E212" s="6" t="inlineStr">
         <is>
-          <t>setDetailTicker failed for R2000-only tickers</t>
+          <t>Offload fundamentals to SEC EDGAR (FIX 4)</t>
         </is>
       </c>
       <c r="F212" s="5" t="inlineStr">
         <is>
-          <t>Clicking ML Edge picks not in scan bundle (HOOD, ARES, STEM etc.) printed '[kairos] ticker not in scan' and never opened. Now synthesizes minimal t row from window.__mlEdgeCache so detail page opens with _fromMlEdge:true flag</t>
+          <t>new edgar_client.py behind data_fetcher interface; data.sec.gov companyfacts (User-Agent + &lt;=10 req/s); map XBRL tags to fundamentals.db; nightly batch. Quality upgrade (point-in-time, fixes audit #1/#4) + zeroes per-ticker EODHD fundamentals calls.</t>
         </is>
       </c>
       <c r="G212" s="5" t="inlineStr">
         <is>
-          <t>kairos.html window.setDetailTicker fallback block</t>
+          <t>edgar_client.py + nightly batch</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr"/>
@@ -12406,12 +12406,12 @@
       </c>
       <c r="L212" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M212" s="3" t="inlineStr">
         <is>
-          <t>27fd646b1</t>
+          <t>5d05268ef</t>
         </is>
       </c>
       <c r="N212" s="8" t="inlineStr"/>
@@ -12422,7 +12422,7 @@
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>SETDETAIL-FALLBACK</t>
         </is>
       </c>
       <c r="C213" s="10" t="inlineStr">
@@ -12432,34 +12432,26 @@
       </c>
       <c r="D213" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Detail UI / Routing</t>
         </is>
       </c>
       <c r="E213" s="6" t="inlineStr">
         <is>
-          <t>Update CLAUDE.md with new tools</t>
+          <t>setDetailTicker failed for R2000-only tickers</t>
         </is>
       </c>
       <c r="F213" s="5" t="inlineStr">
         <is>
-          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
+          <t>Clicking ML Edge picks not in scan bundle (HOOD, ARES, STEM etc.) printed '[kairos] ticker not in scan' and never opened. Now synthesizes minimal t row from window.__mlEdgeCache so detail page opens with _fromMlEdge:true flag</t>
         </is>
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
-        </is>
-      </c>
-      <c r="H213" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I213" s="5" t="inlineStr">
-        <is>
-          <t>Win: future Claude sessions discover new tools.</t>
-        </is>
-      </c>
+          <t>kairos.html window.setDetailTicker fallback block</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr"/>
+      <c r="I213" s="5" t="inlineStr"/>
       <c r="J213" s="5" t="inlineStr"/>
       <c r="K213" s="12" t="inlineStr">
         <is>
@@ -12468,27 +12460,23 @@
       </c>
       <c r="L213" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M213" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-      <c r="N213" s="8" t="inlineStr">
-        <is>
-          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="214" ht="75" customHeight="1">
+          <t>27fd646b1</t>
+        </is>
+      </c>
+      <c r="N213" s="8" t="inlineStr"/>
+    </row>
+    <row r="214" ht="60" customHeight="1">
       <c r="A214" s="2" t="n">
         <v>213</v>
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="C214" s="10" t="inlineStr">
@@ -12503,17 +12491,17 @@
       </c>
       <c r="E214" s="6" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
+          <t>Update CLAUDE.md with new tools</t>
         </is>
       </c>
       <c r="F214" s="5" t="inlineStr">
         <is>
-          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
+          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
         </is>
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
+          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
@@ -12523,14 +12511,10 @@
       </c>
       <c r="I214" s="5" t="inlineStr">
         <is>
-          <t>Win: clear activation procedure before flipping live.</t>
-        </is>
-      </c>
-      <c r="J214" s="5" t="inlineStr">
-        <is>
-          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
-        </is>
-      </c>
+          <t>Win: future Claude sessions discover new tools.</t>
+        </is>
+      </c>
+      <c r="J214" s="5" t="inlineStr"/>
       <c r="K214" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -12543,12 +12527,12 @@
       </c>
       <c r="M214" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N214" s="8" t="inlineStr">
         <is>
-          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
+          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
         </is>
       </c>
     </row>
@@ -12558,7 +12542,7 @@
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>TWO-LOG-DOC</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="C215" s="10" t="inlineStr">
@@ -12573,22 +12557,34 @@
       </c>
       <c r="E215" s="6" t="inlineStr">
         <is>
-          <t>Two-log architecture (picks_history vs signal_log) was undocumented</t>
+          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
         </is>
       </c>
       <c r="F215" s="5" t="inlineStr">
         <is>
-          <t>Discovered 2026-05-10 during inflection diagnosis: cache/picks_history.json and data/signal_log.json track different realities (61.2% vs 12.7% recent WR). Tracker feedback reads picks_history; drift alerts read signal_log. Mis-attributing which log feeds which consumer wastes diagnostic time.</t>
+          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
         </is>
       </c>
       <c r="G215" s="5" t="inlineStr">
         <is>
-          <t>Add 'Two-Log Architecture' section to CLAUDE.md after EODHD section, with table mapping consumers + WR snapshots. Cross-reference portfolio_state.json as the ONLY real-trades log.</t>
-        </is>
-      </c>
-      <c r="H215" s="2" t="inlineStr"/>
-      <c r="I215" s="5" t="inlineStr"/>
-      <c r="J215" s="5" t="inlineStr"/>
+          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I215" s="5" t="inlineStr">
+        <is>
+          <t>Win: clear activation procedure before flipping live.</t>
+        </is>
+      </c>
+      <c r="J215" s="5" t="inlineStr">
+        <is>
+          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
+        </is>
+      </c>
       <c r="K215" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -12596,23 +12592,27 @@
       </c>
       <c r="L215" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M215" s="3" t="inlineStr">
         <is>
-          <t>8b06e56ae</t>
-        </is>
-      </c>
-      <c r="N215" s="8" t="inlineStr"/>
-    </row>
-    <row r="216" ht="60" customHeight="1">
+          <t>d8c08399b</t>
+        </is>
+      </c>
+      <c r="N215" s="8" t="inlineStr">
+        <is>
+          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="75" customHeight="1">
       <c r="A216" s="2" t="n">
         <v>215</v>
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>UI-HELP-1</t>
+          <t>TWO-LOG-DOC</t>
         </is>
       </c>
       <c r="C216" s="10" t="inlineStr">
@@ -12622,22 +12622,22 @@
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>Help System</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E216" s="6" t="inlineStr">
         <is>
-          <t>Help registry expanded 14 to 38 entries</t>
+          <t>Two-log architecture (picks_history vs signal_log) was undocumented</t>
         </is>
       </c>
       <c r="F216" s="5" t="inlineStr">
         <is>
-          <t>Help registry covered only workspace tabs. Detail sub-tabs and MarketsV2 ports had no help content.</t>
+          <t>Discovered 2026-05-10 during inflection diagnosis: cache/picks_history.json and data/signal_log.json track different realities (61.2% vs 12.7% recent WR). Tracker feedback reads picks_history; drift alerts read signal_log. Mis-attributing which log feeds which consumer wastes diagnostic time.</t>
         </is>
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Added 24 new entries. kairosHelpFor threads isDetail through dispatcher — prefers detail_ namespace, falls back to bare key. Resolves portfolio workspace vs detail-subtab collision. MarketsV2 render block calls _injectHelpBtn.</t>
+          <t>Add 'Two-Log Architecture' section to CLAUDE.md after EODHD section, with table mapping consumers + WR snapshots. Cross-reference portfolio_state.json as the ONLY real-trades log.</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr"/>
@@ -12650,23 +12650,23 @@
       </c>
       <c r="L216" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M216" s="3" t="inlineStr">
         <is>
-          <t>696731a4d</t>
+          <t>8b06e56ae</t>
         </is>
       </c>
       <c r="N216" s="8" t="inlineStr"/>
     </row>
-    <row r="217" ht="45" customHeight="1">
+    <row r="217" ht="60" customHeight="1">
       <c r="A217" s="2" t="n">
         <v>216</v>
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>UI-HELP-1</t>
         </is>
       </c>
       <c r="C217" s="10" t="inlineStr">
@@ -12676,34 +12676,26 @@
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Help System</t>
         </is>
       </c>
       <c r="E217" s="6" t="inlineStr">
         <is>
-          <t>Git committer.email set globally</t>
+          <t>Help registry expanded 14 to 38 entries</t>
         </is>
       </c>
       <c r="F217" s="5" t="inlineStr">
         <is>
-          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
+          <t>Help registry covered only workspace tabs. Detail sub-tabs and MarketsV2 ports had no help content.</t>
         </is>
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
-        </is>
-      </c>
-      <c r="H217" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I217" s="5" t="inlineStr">
-        <is>
-          <t>Win: clean attribution in git log.</t>
-        </is>
-      </c>
+          <t>Added 24 new entries. kairosHelpFor threads isDetail through dispatcher — prefers detail_ namespace, falls back to bare key. Resolves portfolio workspace vs detail-subtab collision. MarketsV2 render block calls _injectHelpBtn.</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="inlineStr"/>
+      <c r="I217" s="5" t="inlineStr"/>
       <c r="J217" s="5" t="inlineStr"/>
       <c r="K217" s="12" t="inlineStr">
         <is>
@@ -12712,27 +12704,23 @@
       </c>
       <c r="L217" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M217" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
-        </is>
-      </c>
-      <c r="N217" s="8" t="inlineStr">
-        <is>
-          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
-        </is>
-      </c>
-    </row>
-    <row r="218" ht="90" customHeight="1">
+          <t>696731a4d</t>
+        </is>
+      </c>
+      <c r="N217" s="8" t="inlineStr"/>
+    </row>
+    <row r="218" ht="45" customHeight="1">
       <c r="A218" s="2" t="n">
         <v>217</v>
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>UI-MLEDGE-1</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="C218" s="10" t="inlineStr">
@@ -12742,26 +12730,34 @@
       </c>
       <c r="D218" s="5" t="inlineStr">
         <is>
-          <t>ML Edge Tab</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E218" s="6" t="inlineStr">
         <is>
-          <t>Theme switching + tf-* visual port</t>
+          <t>Git committer.email set globally</t>
         </is>
       </c>
       <c r="F218" s="5" t="inlineStr">
         <is>
-          <t>ML Edge per-ticker sub-tab had hardcoded dark CSS vars inline on #qd-ml-root, blocking the body.light theme toggle. Workspace ML Edge used legacy rk-* class system, not the prototype tf-* design language.</t>
+          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
         </is>
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>Moved palette from inline style to _ensureMlEdgeStyles() with body.light overrides. Then ported workspace QuantMlEdge module to tf-* visual system: tf-hero 3-col + tf-pulse-strip 4 live feeds (top bulls/bears/flips/health) + tf-confluence (4 KPI cells + X/4 score) + tf-vbar (verdict badge). All 6 sections rewritten. Memory: feedback_inline_css_vars_break_theming.md.</t>
-        </is>
-      </c>
-      <c r="H218" s="2" t="inlineStr"/>
-      <c r="I218" s="5" t="inlineStr"/>
+          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I218" s="5" t="inlineStr">
+        <is>
+          <t>Win: clean attribution in git log.</t>
+        </is>
+      </c>
       <c r="J218" s="5" t="inlineStr"/>
       <c r="K218" s="12" t="inlineStr">
         <is>
@@ -12770,23 +12766,27 @@
       </c>
       <c r="L218" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>
-          <t>696731a4d</t>
-        </is>
-      </c>
-      <c r="N218" s="8" t="inlineStr"/>
-    </row>
-    <row r="219" ht="45" customHeight="1">
+          <t>4129e5565</t>
+        </is>
+      </c>
+      <c r="N218" s="8" t="inlineStr">
+        <is>
+          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="90" customHeight="1">
       <c r="A219" s="2" t="n">
         <v>218</v>
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>IPAD-2</t>
+          <t>UI-MLEDGE-1</t>
         </is>
       </c>
       <c r="C219" s="10" t="inlineStr">
@@ -12796,39 +12796,27 @@
       </c>
       <c r="D219" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>ML Edge Tab</t>
         </is>
       </c>
       <c r="E219" s="6" t="inlineStr">
         <is>
-          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
+          <t>Theme switching + tf-* visual port</t>
         </is>
       </c>
       <c r="F219" s="5" t="inlineStr">
         <is>
-          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
+          <t>ML Edge per-ticker sub-tab had hardcoded dark CSS vars inline on #qd-ml-root, blocking the body.light theme toggle. Workspace ML Edge used legacy rk-* class system, not the prototype tf-* design language.</t>
         </is>
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
-        </is>
-      </c>
-      <c r="H219" s="2" t="inlineStr">
-        <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="I219" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J219" s="5" t="inlineStr">
-        <is>
-          <t>Sub-task of IPAD-1.</t>
-        </is>
-      </c>
+          <t>Moved palette from inline style to _ensureMlEdgeStyles() with body.light overrides. Then ported workspace QuantMlEdge module to tf-* visual system: tf-hero 3-col + tf-pulse-strip 4 live feeds (top bulls/bears/flips/health) + tf-confluence (4 KPI cells + X/4 score) + tf-vbar (verdict badge). All 6 sections rewritten. Memory: feedback_inline_css_vars_break_theming.md.</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="inlineStr"/>
+      <c r="I219" s="5" t="inlineStr"/>
+      <c r="J219" s="5" t="inlineStr"/>
       <c r="K219" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -12836,19 +12824,15 @@
       </c>
       <c r="L219" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M219" s="3" t="inlineStr">
         <is>
-          <t>79fa01a75</t>
-        </is>
-      </c>
-      <c r="N219" s="8" t="inlineStr">
-        <is>
-          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
-        </is>
-      </c>
+          <t>696731a4d</t>
+        </is>
+      </c>
+      <c r="N219" s="8" t="inlineStr"/>
     </row>
     <row r="220" ht="45" customHeight="1">
       <c r="A220" s="2" t="n">
@@ -12856,7 +12840,7 @@
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>SLACK-NEWSLETTER-MLALERT</t>
+          <t>IPAD-2</t>
         </is>
       </c>
       <c r="C220" s="10" t="inlineStr">
@@ -12866,27 +12850,39 @@
       </c>
       <c r="D220" s="5" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E220" s="6" t="inlineStr">
         <is>
-          <t>Re-enable newsletter + add ML-predictions Slack alert</t>
+          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
         </is>
       </c>
       <c r="F220" s="5" t="inlineStr">
         <is>
-          <t>re-enable daily-newsletter from disabled/; build ml-alert Slack for top ML-edge/AI picks</t>
+          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
         </is>
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd + scripts/ml_alert_slack.py</t>
-        </is>
-      </c>
-      <c r="H220" s="2" t="inlineStr"/>
-      <c r="I220" s="5" t="inlineStr"/>
-      <c r="J220" s="5" t="inlineStr"/>
+          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="I220" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J220" s="5" t="inlineStr">
+        <is>
+          <t>Sub-task of IPAD-1.</t>
+        </is>
+      </c>
       <c r="K220" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -12894,15 +12890,19 @@
       </c>
       <c r="L220" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M220" s="3" t="inlineStr">
         <is>
-          <t>d1ea97913</t>
-        </is>
-      </c>
-      <c r="N220" s="8" t="inlineStr"/>
+          <t>79fa01a75</t>
+        </is>
+      </c>
+      <c r="N220" s="8" t="inlineStr">
+        <is>
+          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="45" customHeight="1">
       <c r="A221" s="2" t="n">
@@ -12910,7 +12910,7 @@
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>FORENSICS-WEEKLY-SLACK</t>
+          <t>SLACK-NEWSLETTER-MLALERT</t>
         </is>
       </c>
       <c r="C221" s="10" t="inlineStr">
@@ -12920,22 +12920,22 @@
       </c>
       <c r="D221" s="5" t="inlineStr">
         <is>
-          <t>Notifications / Audit</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="E221" s="6" t="inlineStr">
         <is>
-          <t>Weekly pick-forensics Slack digest</t>
+          <t>Re-enable newsletter + add ML-predictions Slack alert</t>
         </is>
       </c>
       <c r="F221" s="5" t="inlineStr">
         <is>
-          <t>Sun 17:30 — 14d verdict-truth + per-sleeve EXTENDED/MISSED bleeding monitor to Slack</t>
+          <t>re-enable daily-newsletter from disabled/; build ml-alert Slack for top ML-edge/AI picks</t>
         </is>
       </c>
       <c r="G221" s="5" t="inlineStr">
         <is>
-          <t>com.swingtrade.forensics-weekly + pick_forensics --slack</t>
+          <t>infra/launchd + scripts/ml_alert_slack.py</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr"/>
@@ -12953,18 +12953,18 @@
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>d1ea97913</t>
         </is>
       </c>
       <c r="N221" s="8" t="inlineStr"/>
     </row>
-    <row r="222" ht="75" customHeight="1">
+    <row r="222" ht="45" customHeight="1">
       <c r="A222" s="2" t="n">
         <v>221</v>
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>F11-followup</t>
+          <t>FORENSICS-WEEKLY-SLACK</t>
         </is>
       </c>
       <c r="C222" s="10" t="inlineStr">
@@ -12974,39 +12974,27 @@
       </c>
       <c r="D222" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Notifications / Audit</t>
         </is>
       </c>
       <c r="E222" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook scoped to NEW drift only</t>
+          <t>Weekly pick-forensics Slack digest</t>
         </is>
       </c>
       <c r="F222" s="5" t="inlineStr">
         <is>
-          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
+          <t>Sun 17:30 — 14d verdict-truth + per-sleeve EXTENDED/MISSED bleeding monitor to Slack</t>
         </is>
       </c>
       <c r="G222" s="5" t="inlineStr">
         <is>
-          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
-        </is>
-      </c>
-      <c r="H222" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I222" s="5" t="inlineStr">
-        <is>
-          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
-        </is>
-      </c>
-      <c r="J222" s="5" t="inlineStr">
-        <is>
-          <t>User can still bypass with --no-verify in emergencies.</t>
-        </is>
-      </c>
+          <t>com.swingtrade.forensics-weekly + pick_forensics --slack</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="inlineStr"/>
+      <c r="I222" s="5" t="inlineStr"/>
+      <c r="J222" s="5" t="inlineStr"/>
       <c r="K222" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -13014,27 +13002,23 @@
       </c>
       <c r="L222" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M222" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-      <c r="N222" s="8" t="inlineStr">
-        <is>
-          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
-        </is>
-      </c>
-    </row>
-    <row r="223" ht="60" customHeight="1">
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N222" s="8" t="inlineStr"/>
+    </row>
+    <row r="223" ht="75" customHeight="1">
       <c r="A223" s="2" t="n">
         <v>222</v>
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>OPS-2</t>
+          <t>F11-followup</t>
         </is>
       </c>
       <c r="C223" s="10" t="inlineStr">
@@ -13044,37 +13028,37 @@
       </c>
       <c r="D223" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E223" s="6" t="inlineStr">
         <is>
-          <t>Uptime monitoring (launchd ping → dashboard)</t>
+          <t>Pre-commit hook scoped to NEW drift only</t>
         </is>
       </c>
       <c r="F223" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
+          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
         </is>
       </c>
       <c r="G223" s="5" t="inlineStr">
         <is>
-          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
+          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I223" s="5" t="inlineStr">
         <is>
-          <t>Win: detect FastAPI hang independent of tunnel.</t>
+          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
         </is>
       </c>
       <c r="J223" s="5" t="inlineStr">
         <is>
-          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
+          <t>User can still bypass with --no-verify in emergencies.</t>
         </is>
       </c>
       <c r="K223" s="12" t="inlineStr">
@@ -13084,17 +13068,17 @@
       </c>
       <c r="L223" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M223" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N223" s="8" t="inlineStr">
         <is>
-          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
+          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
         </is>
       </c>
     </row>
@@ -13104,7 +13088,7 @@
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>OPS-3</t>
+          <t>OPS-2</t>
         </is>
       </c>
       <c r="C224" s="10" t="inlineStr">
@@ -13119,32 +13103,32 @@
       </c>
       <c r="E224" s="6" t="inlineStr">
         <is>
-          <t>Admin endpoint for capability_registry edits</t>
+          <t>Uptime monitoring (launchd ping → dashboard)</t>
         </is>
       </c>
       <c r="F224" s="5" t="inlineStr">
         <is>
-          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
+          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
         </is>
       </c>
       <c r="G224" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
+          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I224" s="5" t="inlineStr">
         <is>
-          <t>Win: safer registry edits + audit trail.</t>
+          <t>Win: detect FastAPI hang independent of tunnel.</t>
         </is>
       </c>
       <c r="J224" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
+          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
         </is>
       </c>
       <c r="K224" s="12" t="inlineStr">
@@ -13164,7 +13148,7 @@
       </c>
       <c r="N224" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
+          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
         </is>
       </c>
     </row>
@@ -13174,7 +13158,7 @@
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>OPS-4</t>
+          <t>OPS-3</t>
         </is>
       </c>
       <c r="C225" s="10" t="inlineStr">
@@ -13189,32 +13173,32 @@
       </c>
       <c r="E225" s="6" t="inlineStr">
         <is>
-          <t>CapStudio audit log UI</t>
+          <t>Admin endpoint for capability_registry edits</t>
         </is>
       </c>
       <c r="F225" s="5" t="inlineStr">
         <is>
-          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
+          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
         </is>
       </c>
       <c r="G225" s="5" t="inlineStr">
         <is>
-          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I225" s="5" t="inlineStr">
         <is>
-          <t>Win: visibility into RBAC changes.</t>
+          <t>Win: safer registry edits + audit trail.</t>
         </is>
       </c>
       <c r="J225" s="5" t="inlineStr">
         <is>
-          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
+          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
         </is>
       </c>
       <c r="K225" s="12" t="inlineStr">
@@ -13234,7 +13218,7 @@
       </c>
       <c r="N225" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
         </is>
       </c>
     </row>
@@ -13244,7 +13228,7 @@
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>OPS-5</t>
+          <t>OPS-4</t>
         </is>
       </c>
       <c r="C226" s="10" t="inlineStr">
@@ -13259,32 +13243,32 @@
       </c>
       <c r="E226" s="6" t="inlineStr">
         <is>
-          <t>Backtest report manual 'regen' button</t>
+          <t>CapStudio audit log UI</t>
         </is>
       </c>
       <c r="F226" s="5" t="inlineStr">
         <is>
-          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
+          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
         </is>
       </c>
       <c r="G226" s="5" t="inlineStr">
         <is>
-          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>2 hrs</t>
         </is>
       </c>
       <c r="I226" s="5" t="inlineStr">
         <is>
-          <t>Win: fast iteration on report templates.</t>
+          <t>Win: visibility into RBAC changes.</t>
         </is>
       </c>
       <c r="J226" s="5" t="inlineStr">
         <is>
-          <t>Trivial CLI wrapper.</t>
+          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
         </is>
       </c>
       <c r="K226" s="12" t="inlineStr">
@@ -13294,27 +13278,27 @@
       </c>
       <c r="L226" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M226" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N226" s="8" t="inlineStr">
         <is>
-          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
-        </is>
-      </c>
-    </row>
-    <row r="227" ht="45" customHeight="1">
+          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="60" customHeight="1">
       <c r="A227" s="2" t="n">
         <v>226</v>
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>SCAN-FAILURE-ALERT</t>
+          <t>OPS-5</t>
         </is>
       </c>
       <c r="C227" s="10" t="inlineStr">
@@ -13324,27 +13308,39 @@
       </c>
       <c r="D227" s="5" t="inlineStr">
         <is>
-          <t>Ops / Alerts</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E227" s="6" t="inlineStr">
         <is>
-          <t>Scan-failure + EODHD-quota Slack alert</t>
+          <t>Backtest report manual 'regen' button</t>
         </is>
       </c>
       <c r="F227" s="5" t="inlineStr">
         <is>
-          <t>failed scan / 402 quota is silent today; 1-line health alert on scan exit</t>
+          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
         </is>
       </c>
       <c r="G227" s="5" t="inlineStr">
         <is>
-          <t>swing_trade.py exit hook</t>
-        </is>
-      </c>
-      <c r="H227" s="2" t="inlineStr"/>
-      <c r="I227" s="5" t="inlineStr"/>
-      <c r="J227" s="5" t="inlineStr"/>
+          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+        </is>
+      </c>
+      <c r="H227" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="I227" s="5" t="inlineStr">
+        <is>
+          <t>Win: fast iteration on report templates.</t>
+        </is>
+      </c>
+      <c r="J227" s="5" t="inlineStr">
+        <is>
+          <t>Trivial CLI wrapper.</t>
+        </is>
+      </c>
       <c r="K227" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -13352,15 +13348,19 @@
       </c>
       <c r="L227" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M227" s="3" t="inlineStr">
         <is>
-          <t>0dc7675ee</t>
-        </is>
-      </c>
-      <c r="N227" s="8" t="inlineStr"/>
+          <t>2b7d2f40f</t>
+        </is>
+      </c>
+      <c r="N227" s="8" t="inlineStr">
+        <is>
+          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="45" customHeight="1">
       <c r="A228" s="2" t="n">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>MOMENTUM-SNAPSHOT-DECIDE</t>
+          <t>SCAN-FAILURE-ALERT</t>
         </is>
       </c>
       <c r="C228" s="10" t="inlineStr">
@@ -13378,22 +13378,22 @@
       </c>
       <c r="D228" s="5" t="inlineStr">
         <is>
-          <t>Ops / Launchd</t>
+          <t>Ops / Alerts</t>
         </is>
       </c>
       <c r="E228" s="6" t="inlineStr">
         <is>
-          <t>Decide momentum-snapshot: load or retire</t>
+          <t>Scan-failure + EODHD-quota Slack alert</t>
         </is>
       </c>
       <c r="F228" s="5" t="inlineStr">
         <is>
-          <t>valid plist, not loaded; PARSE-ERR on lint earlier</t>
+          <t>failed scan / 402 quota is silent today; 1-line health alert on scan exit</t>
         </is>
       </c>
       <c r="G228" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd</t>
+          <t>swing_trade.py exit hook</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr"/>
@@ -13416,13 +13416,13 @@
       </c>
       <c r="N228" s="8" t="inlineStr"/>
     </row>
-    <row r="229" ht="150" customHeight="1">
+    <row r="229" ht="45" customHeight="1">
       <c r="A229" s="2" t="n">
         <v>228</v>
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>PERF-7b</t>
+          <t>MOMENTUM-SNAPSHOT-DECIDE</t>
         </is>
       </c>
       <c r="C229" s="10" t="inlineStr">
@@ -13432,31 +13432,27 @@
       </c>
       <c r="D229" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Ops / Launchd</t>
         </is>
       </c>
       <c r="E229" s="6" t="inlineStr">
         <is>
-          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
+          <t>Decide momentum-snapshot: load or retire</t>
         </is>
       </c>
       <c r="F229" s="5" t="inlineStr">
         <is>
-          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
+          <t>valid plist, not loaded; PARSE-ERR on lint earlier</t>
         </is>
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
+          <t>infra/launchd</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr"/>
       <c r="I229" s="5" t="inlineStr"/>
-      <c r="J229" s="5" t="inlineStr">
-        <is>
-          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
-        </is>
-      </c>
+      <c r="J229" s="5" t="inlineStr"/>
       <c r="K229" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -13464,27 +13460,23 @@
       </c>
       <c r="L229" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M229" s="3" t="inlineStr">
         <is>
-          <t>cf30df858</t>
-        </is>
-      </c>
-      <c r="N229" s="8" t="inlineStr">
-        <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="230" ht="45" customHeight="1">
+          <t>0dc7675ee</t>
+        </is>
+      </c>
+      <c r="N229" s="8" t="inlineStr"/>
+    </row>
+    <row r="230" ht="150" customHeight="1">
       <c r="A230" s="2" t="n">
         <v>229</v>
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-1</t>
+          <t>PERF-7b</t>
         </is>
       </c>
       <c r="C230" s="10" t="inlineStr">
@@ -13494,27 +13486,31 @@
       </c>
       <c r="D230" s="5" t="inlineStr">
         <is>
-          <t>Sharpe Roadmap</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E230" s="6" t="inlineStr">
         <is>
-          <t>Sharpe gate in momentum detector</t>
+          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
         </is>
       </c>
       <c r="F230" s="5" t="inlineStr">
         <is>
-          <t>Wire 126d Sharpe threshold (≥1.5) into _detect_momentum_continuation</t>
+          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
         </is>
       </c>
       <c r="G230" s="5" t="inlineStr">
         <is>
-          <t>Computed inline in analyze_ticker via lib.sharpe_utils.sharpe_annualized; passed to detector as kwarg</t>
+          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr"/>
       <c r="I230" s="5" t="inlineStr"/>
-      <c r="J230" s="5" t="inlineStr"/>
+      <c r="J230" s="5" t="inlineStr">
+        <is>
+          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
+        </is>
+      </c>
       <c r="K230" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -13522,15 +13518,19 @@
       </c>
       <c r="L230" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M230" s="3" t="inlineStr">
         <is>
-          <t>dbbd6b5f6</t>
-        </is>
-      </c>
-      <c r="N230" s="8" t="inlineStr"/>
+          <t>cf30df858</t>
+        </is>
+      </c>
+      <c r="N230" s="8" t="inlineStr">
+        <is>
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="45" customHeight="1">
       <c r="A231" s="2" t="n">
@@ -13538,7 +13538,7 @@
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-10</t>
+          <t>SHARPE-1</t>
         </is>
       </c>
       <c r="C231" s="10" t="inlineStr">
@@ -13553,17 +13553,17 @@
       </c>
       <c r="E231" s="6" t="inlineStr">
         <is>
-          <t>Sharpe alerts for watchlist</t>
+          <t>Sharpe gate in momentum detector</t>
         </is>
       </c>
       <c r="F231" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Wire 126d Sharpe threshold (≥1.5) into _detect_momentum_continuation</t>
         </is>
       </c>
       <c r="G231" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_alert.py — tracks state across runs, posts to SLACK_WEBHOOK_URL</t>
+          <t>Computed inline in analyze_ticker via lib.sharpe_utils.sharpe_annualized; passed to detector as kwarg</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr"/>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-11</t>
+          <t>SHARPE-10</t>
         </is>
       </c>
       <c r="C232" s="10" t="inlineStr">
@@ -13607,17 +13607,17 @@
       </c>
       <c r="E232" s="6" t="inlineStr">
         <is>
-          <t>Per-trade Sharpe attribution</t>
+          <t>Sharpe alerts for watchlist</t>
         </is>
       </c>
       <c r="F232" s="5" t="inlineStr">
         <is>
-          <t>Decompose portfolio Sharpe by ticker / setup / regime contribution</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Built into scripts/sharpe_kpi.py — top contributors / detractors + setup + regime contribution tables</t>
+          <t>scripts/sharpe_alert.py — tracks state across runs, posts to SLACK_WEBHOOK_URL</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr"/>
@@ -13646,7 +13646,7 @@
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-12</t>
+          <t>SHARPE-11</t>
         </is>
       </c>
       <c r="C233" s="10" t="inlineStr">
@@ -13661,17 +13661,17 @@
       </c>
       <c r="E233" s="6" t="inlineStr">
         <is>
-          <t>Sharpe consistency check</t>
+          <t>Per-trade Sharpe attribution</t>
         </is>
       </c>
       <c r="F233" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Decompose portfolio Sharpe by ticker / setup / regime contribution</t>
         </is>
       </c>
       <c r="G233" s="5" t="inlineStr">
         <is>
-          <t>lib.sharpe_utils.rolling_sharpe + consistency_score; surfaced on per-ticker result dict</t>
+          <t>Built into scripts/sharpe_kpi.py — top contributors / detractors + setup + regime contribution tables</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr"/>
@@ -13700,7 +13700,7 @@
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-2</t>
+          <t>SHARPE-12</t>
         </is>
       </c>
       <c r="C234" s="10" t="inlineStr">
@@ -13715,17 +13715,17 @@
       </c>
       <c r="E234" s="6" t="inlineStr">
         <is>
-          <t>Sharpe column in v2 dashboard</t>
+          <t>Sharpe consistency check</t>
         </is>
       </c>
       <c r="F234" s="5" t="inlineStr">
         <is>
-          <t>Surface 126d Sharpe per ticker as sortable column</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>Added sharpe_126d / sortino_126d / sharpe_consistency to compact_row in build_data.py</t>
+          <t>lib.sharpe_utils.rolling_sharpe + consistency_score; surfaced on per-ticker result dict</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr"/>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-3</t>
+          <t>SHARPE-2</t>
         </is>
       </c>
       <c r="C235" s="10" t="inlineStr">
@@ -13769,17 +13769,17 @@
       </c>
       <c r="E235" s="6" t="inlineStr">
         <is>
-          <t>Per-stock Sharpe by regime</t>
+          <t>Sharpe column in v2 dashboard</t>
         </is>
       </c>
       <c r="F235" s="5" t="inlineStr">
         <is>
-          <t>Decompose per-stock Sharpe by historical regime tags</t>
+          <t>Surface 126d Sharpe per ticker as sortable column</t>
         </is>
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_per_regime.py — segments OHLCV by regime, computes per-bucket Sharpe</t>
+          <t>Added sharpe_126d / sortino_126d / sharpe_consistency to compact_row in build_data.py</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr"/>
@@ -13808,7 +13808,7 @@
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-4</t>
+          <t>SHARPE-3</t>
         </is>
       </c>
       <c r="C236" s="10" t="inlineStr">
@@ -13823,17 +13823,17 @@
       </c>
       <c r="E236" s="6" t="inlineStr">
         <is>
-          <t>Edge-erosion radar (per-setup Sharpe trend)</t>
+          <t>Per-stock Sharpe by regime</t>
         </is>
       </c>
       <c r="F236" s="5" t="inlineStr">
         <is>
-          <t>Per-setup Sharpe across rolling windows w/ HTML viz</t>
+          <t>Decompose per-stock Sharpe by historical regime tags</t>
         </is>
       </c>
       <c r="G236" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_setup_trend.py — emits trend table + dark-themed HTML chart per setup</t>
+          <t>scripts/sharpe_per_regime.py — segments OHLCV by regime, computes per-bucket Sharpe</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr"/>
@@ -13862,7 +13862,7 @@
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-5</t>
+          <t>SHARPE-4</t>
         </is>
       </c>
       <c r="C237" s="10" t="inlineStr">
@@ -13877,17 +13877,17 @@
       </c>
       <c r="E237" s="6" t="inlineStr">
         <is>
-          <t>Sharpe-weighted position sizing</t>
+          <t>Edge-erosion radar (per-setup Sharpe trend)</t>
         </is>
       </c>
       <c r="F237" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Per-setup Sharpe across rolling windows w/ HTML viz</t>
         </is>
       </c>
       <c r="G237" s="5" t="inlineStr">
         <is>
-          <t>kelly_position_size new sharpe_126d kwarg + portfolio.sharpe_size_tilt config block (default OFF)</t>
+          <t>scripts/sharpe_setup_trend.py — emits trend table + dark-themed HTML chart per setup</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr"/>
@@ -13916,7 +13916,7 @@
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-6</t>
+          <t>SHARPE-5</t>
         </is>
       </c>
       <c r="C238" s="10" t="inlineStr">
@@ -13931,17 +13931,17 @@
       </c>
       <c r="E238" s="6" t="inlineStr">
         <is>
-          <t>Portfolio Sharpe KPI vs target</t>
+          <t>Sharpe-weighted position sizing</t>
         </is>
       </c>
       <c r="F238" s="5" t="inlineStr">
         <is>
-          <t>Annualized Sharpe target tracking + gap report</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G238" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_kpi.py — reports actual vs target/floor, exits 2 on below-floor for cron alerts</t>
+          <t>kelly_position_size new sharpe_126d kwarg + portfolio.sharpe_size_tilt config block (default OFF)</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr"/>
@@ -13970,7 +13970,7 @@
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-7</t>
+          <t>SHARPE-6</t>
         </is>
       </c>
       <c r="C239" s="10" t="inlineStr">
@@ -13985,17 +13985,17 @@
       </c>
       <c r="E239" s="6" t="inlineStr">
         <is>
-          <t>Sharpe-based stop sizing</t>
+          <t>Portfolio Sharpe KPI vs target</t>
         </is>
       </c>
       <c r="F239" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Annualized Sharpe target tracking + gap report</t>
         </is>
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan reads runtime sharpe; portfolio.sharpe_stop_tilt config block (default OFF)</t>
+          <t>scripts/sharpe_kpi.py — reports actual vs target/floor, exits 2 on below-floor for cron alerts</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr"/>
@@ -14024,7 +14024,7 @@
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-8</t>
+          <t>SHARPE-7</t>
         </is>
       </c>
       <c r="C240" s="10" t="inlineStr">
@@ -14039,17 +14039,17 @@
       </c>
       <c r="E240" s="6" t="inlineStr">
         <is>
-          <t>Sortino computation alongside Sharpe</t>
+          <t>Sharpe-based stop sizing</t>
         </is>
       </c>
       <c r="F240" s="5" t="inlineStr">
         <is>
-          <t>Downside-only vol denominator added everywhere</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G240" s="5" t="inlineStr">
         <is>
-          <t>lib.sharpe_utils.sortino_annualized + per_trade_sortino; surfaced on result dict</t>
+          <t>compute_trade_plan reads runtime sharpe; portfolio.sharpe_stop_tilt config block (default OFF)</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr"/>
@@ -14078,7 +14078,7 @@
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-9</t>
+          <t>SHARPE-8</t>
         </is>
       </c>
       <c r="C241" s="10" t="inlineStr">
@@ -14093,17 +14093,17 @@
       </c>
       <c r="E241" s="6" t="inlineStr">
         <is>
-          <t>SPY-Sharpe regime cross-validation</t>
+          <t>Sortino computation alongside Sharpe</t>
         </is>
       </c>
       <c r="F241" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Downside-only vol denominator added everywhere</t>
         </is>
       </c>
       <c r="G241" s="5" t="inlineStr">
         <is>
-          <t>data_fetcher.get_market_regime now includes spy_sharpe payload</t>
+          <t>lib.sharpe_utils.sortino_annualized + per_trade_sortino; surfaced on result dict</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr"/>
@@ -14126,13 +14126,13 @@
       </c>
       <c r="N241" s="8" t="inlineStr"/>
     </row>
-    <row r="242" ht="120" customHeight="1">
+    <row r="242" ht="45" customHeight="1">
       <c r="A242" s="2" t="n">
         <v>241</v>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>CONVICTION-TIER-WIRE</t>
+          <t>SHARPE-9</t>
         </is>
       </c>
       <c r="C242" s="10" t="inlineStr">
@@ -14142,39 +14142,27 @@
       </c>
       <c r="D242" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Conviction</t>
+          <t>Sharpe Roadmap</t>
         </is>
       </c>
       <c r="E242" s="6" t="inlineStr">
         <is>
-          <t>Conviction tier: simplified to score-band only</t>
+          <t>SPY-Sharpe regime cross-validation</t>
         </is>
       </c>
       <c r="F242" s="5" t="inlineStr">
         <is>
-          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G242" s="5" t="inlineStr">
         <is>
-          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
-        </is>
-      </c>
-      <c r="H242" s="2" t="inlineStr">
-        <is>
-          <t>2-4 hrs + backtest validation</t>
-        </is>
-      </c>
-      <c r="I242" s="5" t="inlineStr">
-        <is>
-          <t>Medium — changes live size or eliminates a layer</t>
-        </is>
-      </c>
-      <c r="J242" s="5" t="inlineStr">
-        <is>
-          <t>Resolved 2026-05-11 by SIMPLIFYING (not deleting). The complex tier criteria (AND of score+RR+RS+regime+catalyst+entry_quality) had 0 T1/T2 trades ever fire in 423 closed signals. The intersection was empty — system was decorative. Replaced with score-only band: T1 score&gt;=88, T2 score&gt;=78, T3 score&gt;=70, WATCH 60-69, AVOID &lt;60. Win-rate setup adjustment retained (single-factor, evidence-driven). All callers preserved — they now get real tier labels instead of mostly-empty results.</t>
-        </is>
-      </c>
+          <t>data_fetcher.get_market_regime now includes spy_sharpe payload</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="inlineStr"/>
+      <c r="I242" s="5" t="inlineStr"/>
+      <c r="J242" s="5" t="inlineStr"/>
       <c r="K242" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14182,27 +14170,23 @@
       </c>
       <c r="L242" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N242" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'from analysis import assign_conviction_tier; print([assign_conviction_tier(s)["label"] for s in [95,87,75,65,55]])' → ['T1','T2','T3','WATCH','AVOID']</t>
-        </is>
-      </c>
-    </row>
-    <row r="243" ht="75" customHeight="1">
+          <t>dbbd6b5f6</t>
+        </is>
+      </c>
+      <c r="N242" s="8" t="inlineStr"/>
+    </row>
+    <row r="243" ht="120" customHeight="1">
       <c r="A243" s="2" t="n">
         <v>242</v>
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>ENTRY-Q-AB</t>
+          <t>CONVICTION-TIER-WIRE</t>
         </is>
       </c>
       <c r="C243" s="10" t="inlineStr">
@@ -14212,27 +14196,39 @@
       </c>
       <c r="D243" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Gates</t>
+          <t>Strategy / Conviction</t>
         </is>
       </c>
       <c r="E243" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional entry_quality A/B</t>
+          <t>Conviction tier: simplified to score-band only</t>
         </is>
       </c>
       <c r="F243" s="5" t="inlineStr">
         <is>
-          <t>Test relaxing entry_quality EXTENDED/MISSED to caveat-only in risk_on_choppy regime. Evidence (n=257 EXTENDED PF 1.63, n=179 MISSED PF 2.89 in choppy) suggests gate is upside-down for that regime, but selection bias + market-cycle asymmetry concerns warrant explicit A/B before promoting to default.</t>
+          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
         </is>
       </c>
       <c r="G243" s="5" t="inlineStr">
         <is>
-          <t>Add config flag regime4_thresholds.risk_on_choppy.entry_quality_caveat_only (default false). Modify decision_engine to honor it. Run 30 days control + 30 days test. Compare WR/PF stratified by entry_quality band. Promote if test PF &gt; control by &gt;=0.3 with n&gt;=30 per band.</t>
-        </is>
-      </c>
-      <c r="H243" s="2" t="inlineStr"/>
-      <c r="I243" s="5" t="inlineStr"/>
-      <c r="J243" s="5" t="inlineStr"/>
+          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="inlineStr">
+        <is>
+          <t>2-4 hrs + backtest validation</t>
+        </is>
+      </c>
+      <c r="I243" s="5" t="inlineStr">
+        <is>
+          <t>Medium — changes live size or eliminates a layer</t>
+        </is>
+      </c>
+      <c r="J243" s="5" t="inlineStr">
+        <is>
+          <t>Resolved 2026-05-11 by SIMPLIFYING (not deleting). The complex tier criteria (AND of score+RR+RS+regime+catalyst+entry_quality) had 0 T1/T2 trades ever fire in 423 closed signals. The intersection was empty — system was decorative. Replaced with score-only band: T1 score&gt;=88, T2 score&gt;=78, T3 score&gt;=70, WATCH 60-69, AVOID &lt;60. Win-rate setup adjustment retained (single-factor, evidence-driven). All callers preserved — they now get real tier labels instead of mostly-empty results.</t>
+        </is>
+      </c>
       <c r="K243" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14240,23 +14236,27 @@
       </c>
       <c r="L243" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M243" s="3" t="inlineStr">
         <is>
-          <t>07c3af6a3</t>
-        </is>
-      </c>
-      <c r="N243" s="8" t="inlineStr"/>
-    </row>
-    <row r="244" ht="60" customHeight="1">
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N243" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'from analysis import assign_conviction_tier; print([assign_conviction_tier(s)["label"] for s in [95,87,75,65,55]])' → ['T1','T2','T3','WATCH','AVOID']</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="75" customHeight="1">
       <c r="A244" s="2" t="n">
         <v>243</v>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-1</t>
+          <t>ENTRY-Q-AB</t>
         </is>
       </c>
       <c r="C244" s="10" t="inlineStr">
@@ -14266,22 +14266,22 @@
       </c>
       <c r="D244" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Options Paper</t>
+          <t>Strategy / Gates</t>
         </is>
       </c>
       <c r="E244" s="6" t="inlineStr">
         <is>
-          <t>Signal -&gt; options-structure mapper</t>
+          <t>Regime-conditional entry_quality A/B</t>
         </is>
       </c>
       <c r="F244" s="5" t="inlineStr">
         <is>
-          <t>Engine emits equity plans only; no layer maps a stock BUY to a defined-risk options structure. GATED: equity sleeves still Phase-1. See docs/scope_options_paper.md.</t>
+          <t>Test relaxing entry_quality EXTENDED/MISSED to caveat-only in risk_on_choppy regime. Evidence (n=257 EXTENDED PF 1.63, n=179 MISSED PF 2.89 in choppy) suggests gate is upside-down for that regime, but selection bias + market-cycle asymmetry concerns warrant explicit A/B before promoting to default.</t>
         </is>
       </c>
       <c r="G244" s="5" t="inlineStr">
         <is>
-          <t>Map equity plan -&gt; defined-risk structure by setup family / R:R / IV rank (3:1 high-conviction -&gt; debit call spread; clean trend -&gt; long call 30-45 DTE). Underlying stop = thesis invalidation. Defined-risk ONLY, paper ONLY.</t>
+          <t>Add config flag regime4_thresholds.risk_on_choppy.entry_quality_caveat_only (default false). Modify decision_engine to honor it. Run 30 days control + 30 days test. Compare WR/PF stratified by entry_quality band. Promote if test PF &gt; control by &gt;=0.3 with n&gt;=30 per band.</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr"/>
@@ -14294,23 +14294,23 @@
       </c>
       <c r="L244" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="M244" s="3" t="inlineStr">
         <is>
-          <t>9c3a2a58d</t>
+          <t>07c3af6a3</t>
         </is>
       </c>
       <c r="N244" s="8" t="inlineStr"/>
     </row>
-    <row r="245" ht="45" customHeight="1">
+    <row r="245" ht="60" customHeight="1">
       <c r="A245" s="2" t="n">
         <v>244</v>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-2</t>
+          <t>OPT-PAPER-1</t>
         </is>
       </c>
       <c r="C245" s="10" t="inlineStr">
@@ -14325,17 +14325,17 @@
       </c>
       <c r="E245" s="6" t="inlineStr">
         <is>
-          <t>Contract selection from Schwab chain</t>
+          <t>Signal -&gt; options-structure mapper</t>
         </is>
       </c>
       <c r="F245" s="5" t="inlineStr">
         <is>
-          <t>We have chain+Greeks data (schwab_client.get_chains/extract_chain_greeks) but no contract picker. Dep: SCHWAB-REAUTH-PENDING (Greeks freshness).</t>
+          <t>Engine emits equity plans only; no layer maps a stock BUY to a defined-risk options structure. GATED: equity sleeves still Phase-1. See docs/scope_options_paper.md.</t>
         </is>
       </c>
       <c r="G245" s="5" t="inlineStr">
         <is>
-          <t>Pick by delta/DTE/spread width from the Schwab chain; size on premium-at-risk &lt;=1% equity. No naked options.</t>
+          <t>Map equity plan -&gt; defined-risk structure by setup family / R:R / IV rank (3:1 high-conviction -&gt; debit call spread; clean trend -&gt; long call 30-45 DTE). Underlying stop = thesis invalidation. Defined-risk ONLY, paper ONLY.</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr"/>
@@ -14358,13 +14358,13 @@
       </c>
       <c r="N245" s="8" t="inlineStr"/>
     </row>
-    <row r="246" ht="60" customHeight="1">
+    <row r="246" ht="45" customHeight="1">
       <c r="A246" s="2" t="n">
         <v>245</v>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-3</t>
+          <t>OPT-PAPER-2</t>
         </is>
       </c>
       <c r="C246" s="10" t="inlineStr">
@@ -14379,17 +14379,17 @@
       </c>
       <c r="E246" s="6" t="inlineStr">
         <is>
-          <t>Alpaca paper options orders in executor.py</t>
+          <t>Contract selection from Schwab chain</t>
         </is>
       </c>
       <c r="F246" s="5" t="inlineStr">
         <is>
-          <t>executor.py has zero options code (equity brackets only); Alpaca SDK supports OptionLegRequest/GetOptionContractsRequest.</t>
+          <t>We have chain+Greeks data (schwab_client.get_chains/extract_chain_greeks) but no contract picker. Dep: SCHWAB-REAUTH-PENDING (Greeks freshness).</t>
         </is>
       </c>
       <c r="G246" s="5" t="inlineStr">
         <is>
-          <t>Construct+submit single + vertical OptionLegRequest in executor.py, PAPER only behind the config.alpaca.paper hard guard. Never live (feedback_paper_only_automation).</t>
+          <t>Pick by delta/DTE/spread width from the Schwab chain; size on premium-at-risk &lt;=1% equity. No naked options.</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr"/>
@@ -14412,13 +14412,13 @@
       </c>
       <c r="N246" s="8" t="inlineStr"/>
     </row>
-    <row r="247" ht="45" customHeight="1">
+    <row r="247" ht="60" customHeight="1">
       <c r="A247" s="2" t="n">
         <v>246</v>
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-4</t>
+          <t>OPT-PAPER-3</t>
         </is>
       </c>
       <c r="C247" s="10" t="inlineStr">
@@ -14433,17 +14433,17 @@
       </c>
       <c r="E247" s="6" t="inlineStr">
         <is>
-          <t>Options position tracking + contract P&amp;L</t>
+          <t>Alpaca paper options orders in executor.py</t>
         </is>
       </c>
       <c r="F247" s="5" t="inlineStr">
         <is>
-          <t>Portfolio tracker is share-P&amp;L only; can't track premium/Greeks/theta/DTE.</t>
+          <t>executor.py has zero options code (equity brackets only); Alpaca SDK supports OptionLegRequest/GetOptionContractsRequest.</t>
         </is>
       </c>
       <c r="G247" s="5" t="inlineStr">
         <is>
-          <t>Extend portfolio tracker for contracts: premium, Greeks, theta decay, IV, DTE, mark-to-market.</t>
+          <t>Construct+submit single + vertical OptionLegRequest in executor.py, PAPER only behind the config.alpaca.paper hard guard. Never live (feedback_paper_only_automation).</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr"/>
@@ -14461,7 +14461,7 @@
       </c>
       <c r="M247" s="3" t="inlineStr">
         <is>
-          <t>635ae960f</t>
+          <t>9c3a2a58d</t>
         </is>
       </c>
       <c r="N247" s="8" t="inlineStr"/>
@@ -14472,7 +14472,7 @@
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-5</t>
+          <t>OPT-PAPER-4</t>
         </is>
       </c>
       <c r="C248" s="10" t="inlineStr">
@@ -14487,17 +14487,17 @@
       </c>
       <c r="E248" s="6" t="inlineStr">
         <is>
-          <t>Options-specific exits</t>
+          <t>Options position tracking + contract P&amp;L</t>
         </is>
       </c>
       <c r="F248" s="5" t="inlineStr">
         <is>
-          <t>Equity exits are price-stop only; options need IV/theta/expiry-aware exits.</t>
+          <t>Portfolio tracker is share-P&amp;L only; can't track premium/Greeks/theta/DTE.</t>
         </is>
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>IV-crush-around-earnings rule, time-stop before expiry, profit-take on the CONTRACT not the underlying, assignment handling.</t>
+          <t>Extend portfolio tracker for contracts: premium, Greeks, theta decay, IV, DTE, mark-to-market.</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr"/>
@@ -14520,13 +14520,13 @@
       </c>
       <c r="N248" s="8" t="inlineStr"/>
     </row>
-    <row r="249" ht="120" customHeight="1">
+    <row r="249" ht="45" customHeight="1">
       <c r="A249" s="2" t="n">
         <v>248</v>
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>UI-STRAT-1</t>
+          <t>OPT-PAPER-5</t>
         </is>
       </c>
       <c r="C249" s="10" t="inlineStr">
@@ -14536,22 +14536,22 @@
       </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
-          <t>Strategy Lab</t>
+          <t>Strategy / Options Paper</t>
         </is>
       </c>
       <c r="E249" s="6" t="inlineStr">
         <is>
-          <t>13-section HF cockpit rebuild + live setup_stats wiring</t>
+          <t>Options-specific exits</t>
         </is>
       </c>
       <c r="F249" s="5" t="inlineStr">
         <is>
-          <t>Old Strategy Lab was 4-section table with fake numbers and 3x3 correlation. Didn't match 20yr HF analyst standard (no capital allocation cascade, no Wilson CI on PF, no edge-erosion radar, no BT vs Live divergence, no auto-quarantine surface).</t>
+          <t>Equity exits are price-stop only; options need IV/theta/expiry-aware exits.</t>
         </is>
       </c>
       <c r="G249" s="5" t="inlineStr">
         <is>
-          <t>Rebuilt renderStrategies in kairos.html with 13 sections: portfolio cockpit, setup-family perf (LIVE from setup_stats.json with Wilson bars + PF haircut), edge erosion radar, BT vs Live divergence (surfaces PEAD canary BT 2.04 vs live 0.88), phase promotion ledger, regime×sleeve grid 8x4, correlation 8x8 + eigenvalue λ₁, sleeve interaction overlap, recent picks roster, auto-quarantine surface, mechanism+falsifier, playbook, pre-mortem. async _stratLabPatch() fetches live data.</t>
+          <t>IV-crush-around-earnings rule, time-stop before expiry, profit-take on the CONTRACT not the underlying, assignment handling.</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr"/>
@@ -14564,23 +14564,23 @@
       </c>
       <c r="L249" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="M249" s="3" t="inlineStr">
         <is>
-          <t>93ec11842</t>
+          <t>635ae960f</t>
         </is>
       </c>
       <c r="N249" s="8" t="inlineStr"/>
     </row>
-    <row r="250" ht="105" customHeight="1">
+    <row r="250" ht="120" customHeight="1">
       <c r="A250" s="2" t="n">
         <v>249</v>
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>TRACKER-BUY-FILTER</t>
+          <t>UI-STRAT-1</t>
         </is>
       </c>
       <c r="C250" s="10" t="inlineStr">
@@ -14590,31 +14590,27 @@
       </c>
       <c r="D250" s="5" t="inlineStr">
         <is>
-          <t>Tracker/Feedback Loop</t>
+          <t>Strategy Lab</t>
         </is>
       </c>
       <c r="E250" s="6" t="inlineStr">
         <is>
-          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
+          <t>13-section HF cockpit rebuild + live setup_stats wiring</t>
         </is>
       </c>
       <c r="F250" s="5" t="inlineStr">
         <is>
-          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
+          <t>Old Strategy Lab was 4-section table with fake numbers and 3x3 correlation. Didn't match 20yr HF analyst standard (no capital allocation cascade, no Wilson CI on PF, no edge-erosion radar, no BT vs Live divergence, no auto-quarantine surface).</t>
         </is>
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
+          <t>Rebuilt renderStrategies in kairos.html with 13 sections: portfolio cockpit, setup-family perf (LIVE from setup_stats.json with Wilson bars + PF haircut), edge erosion radar, BT vs Live divergence (surfaces PEAD canary BT 2.04 vs live 0.88), phase promotion ledger, regime×sleeve grid 8x4, correlation 8x8 + eigenvalue λ₁, sleeve interaction overlap, recent picks roster, auto-quarantine surface, mechanism+falsifier, playbook, pre-mortem. async _stratLabPatch() fetches live data.</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr"/>
       <c r="I250" s="5" t="inlineStr"/>
-      <c r="J250" s="5" t="inlineStr">
-        <is>
-          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
-        </is>
-      </c>
+      <c r="J250" s="5" t="inlineStr"/>
       <c r="K250" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14622,27 +14618,23 @@
       </c>
       <c r="L250" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N250" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
-        </is>
-      </c>
-    </row>
-    <row r="251" ht="135" customHeight="1">
+          <t>93ec11842</t>
+        </is>
+      </c>
+      <c r="N250" s="8" t="inlineStr"/>
+    </row>
+    <row r="251" ht="105" customHeight="1">
       <c r="A251" s="2" t="n">
         <v>250</v>
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>MOD-1</t>
+          <t>TRACKER-BUY-FILTER</t>
         </is>
       </c>
       <c r="C251" s="10" t="inlineStr">
@@ -14652,37 +14644,29 @@
       </c>
       <c r="D251" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Tracker/Feedback Loop</t>
         </is>
       </c>
       <c r="E251" s="6" t="inlineStr">
         <is>
-          <t>Scanner deep refactor</t>
+          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
         </is>
       </c>
       <c r="F251" s="5" t="inlineStr">
         <is>
-          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
+          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
         </is>
       </c>
       <c r="G251" s="5" t="inlineStr">
         <is>
-          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
-        </is>
-      </c>
-      <c r="H251" s="2" t="inlineStr">
-        <is>
-          <t>1-2 hrs</t>
-        </is>
-      </c>
-      <c r="I251" s="5" t="inlineStr">
-        <is>
-          <t>Risk: low (works fine inline). Win: consistency.</t>
-        </is>
-      </c>
+          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
+        </is>
+      </c>
+      <c r="H251" s="2" t="inlineStr"/>
+      <c r="I251" s="5" t="inlineStr"/>
       <c r="J251" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
+          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
         </is>
       </c>
       <c r="K251" s="12" t="inlineStr">
@@ -14692,27 +14676,27 @@
       </c>
       <c r="L251" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M251" s="3" t="inlineStr">
         <is>
-          <t>42c36ef91</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N251" s="8" t="inlineStr">
         <is>
-          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
-        </is>
-      </c>
-    </row>
-    <row r="252" ht="45" customHeight="1">
+          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="135" customHeight="1">
       <c r="A252" s="2" t="n">
         <v>251</v>
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>STOCKSMITH-BOOK-RISK</t>
+          <t>MOD-1</t>
         </is>
       </c>
       <c r="C252" s="10" t="inlineStr">
@@ -14722,27 +14706,39 @@
       </c>
       <c r="D252" s="5" t="inlineStr">
         <is>
-          <t>V2 Dashboard / Risk</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E252" s="6" t="inlineStr">
         <is>
-          <t>Book Risk surface + per-lens analytics (§6)</t>
+          <t>Scanner deep refactor</t>
         </is>
       </c>
       <c r="F252" s="5" t="inlineStr">
         <is>
-          <t>Book Risk (exposure/Greeks/optimizer/attribution/crowding/hedge) + VaR mode-aware + DCF grid + Earnings whisper; honest dashes</t>
+          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
         </is>
       </c>
       <c r="G252" s="5" t="inlineStr">
         <is>
-          <t>Stocksmith.html BookRiskPanel + InvDcfSensitivity + EoWhisperRevisions</t>
-        </is>
-      </c>
-      <c r="H252" s="2" t="inlineStr"/>
-      <c r="I252" s="5" t="inlineStr"/>
-      <c r="J252" s="5" t="inlineStr"/>
+          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="inlineStr">
+        <is>
+          <t>1-2 hrs</t>
+        </is>
+      </c>
+      <c r="I252" s="5" t="inlineStr">
+        <is>
+          <t>Risk: low (works fine inline). Win: consistency.</t>
+        </is>
+      </c>
+      <c r="J252" s="5" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
+        </is>
+      </c>
       <c r="K252" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14750,23 +14746,27 @@
       </c>
       <c r="L252" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M252" s="3" t="inlineStr">
         <is>
-          <t>50cace567</t>
-        </is>
-      </c>
-      <c r="N252" s="8" t="inlineStr"/>
-    </row>
-    <row r="253" ht="120" customHeight="1">
+          <t>42c36ef91</t>
+        </is>
+      </c>
+      <c r="N252" s="8" t="inlineStr">
+        <is>
+          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="45" customHeight="1">
       <c r="A253" s="2" t="n">
         <v>252</v>
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>RECENCY-FLOOR</t>
+          <t>STOCKSMITH-BOOK-RISK</t>
         </is>
       </c>
       <c r="C253" s="10" t="inlineStr">
@@ -14776,31 +14776,27 @@
       </c>
       <c r="D253" s="5" t="inlineStr">
         <is>
-          <t>Validation Hygiene</t>
+          <t>V2 Dashboard / Risk</t>
         </is>
       </c>
       <c r="E253" s="6" t="inlineStr">
         <is>
-          <t>_validations needs recency floor — auto-revert stale boosts</t>
+          <t>Book Risk surface + per-lens analytics (§6)</t>
         </is>
       </c>
       <c r="F253" s="5" t="inlineStr">
         <is>
-          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
+          <t>Book Risk (exposure/Greeks/optimizer/attribution/crowding/hedge) + VaR mode-aware + DCF grid + Earnings whisper; honest dashes</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
+          <t>Stocksmith.html BookRiskPanel + InvDcfSensitivity + EoWhisperRevisions</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr"/>
       <c r="I253" s="5" t="inlineStr"/>
-      <c r="J253" s="5" t="inlineStr">
-        <is>
-          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
-        </is>
-      </c>
+      <c r="J253" s="5" t="inlineStr"/>
       <c r="K253" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14808,27 +14804,23 @@
       </c>
       <c r="L253" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M253" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N253" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="254" ht="60" customHeight="1">
+          <t>50cace567</t>
+        </is>
+      </c>
+      <c r="N253" s="8" t="inlineStr"/>
+    </row>
+    <row r="254" ht="120" customHeight="1">
       <c r="A254" s="2" t="n">
         <v>253</v>
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>MOMENTUM-TAB</t>
+          <t>RECENCY-FLOOR</t>
         </is>
       </c>
       <c r="C254" s="10" t="inlineStr">
@@ -14838,27 +14830,31 @@
       </c>
       <c r="D254" s="5" t="inlineStr">
         <is>
-          <t>Workspaces / Momentum</t>
+          <t>Validation Hygiene</t>
         </is>
       </c>
       <c r="E254" s="6" t="inlineStr">
         <is>
-          <t>New 🚀 Momentum workspace tab</t>
+          <t>_validations needs recency floor — auto-revert stale boosts</t>
         </is>
       </c>
       <c r="F254" s="5" t="inlineStr">
         <is>
-          <t>Ranks scan universe by composite (raw_momentum_score×0.5 + sharpe_norm×0.25 + rs_rank×0.25). Filterable by setup family + grade A/B/C. Click row → detail. Sidebar count = Grade-A + composite≥80 tickers</t>
+          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
         </is>
       </c>
       <c r="G254" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantMomentum IIFE + V3_WORKSPACES.momentum + dispatcher branch</t>
+          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr"/>
       <c r="I254" s="5" t="inlineStr"/>
-      <c r="J254" s="5" t="inlineStr"/>
+      <c r="J254" s="5" t="inlineStr">
+        <is>
+          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
+        </is>
+      </c>
       <c r="K254" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14866,15 +14862,19 @@
       </c>
       <c r="L254" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M254" s="3" t="inlineStr">
         <is>
-          <t>27fd646b1</t>
-        </is>
-      </c>
-      <c r="N254" s="8" t="inlineStr"/>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N254" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
+        </is>
+      </c>
     </row>
     <row r="255" ht="60" customHeight="1">
       <c r="A255" s="2" t="n">
@@ -14882,7 +14882,7 @@
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>SCANNER-QUICK-PANELS</t>
+          <t>MOMENTUM-TAB</t>
         </is>
       </c>
       <c r="C255" s="10" t="inlineStr">
@@ -14892,22 +14892,22 @@
       </c>
       <c r="D255" s="5" t="inlineStr">
         <is>
-          <t>Workspaces / Signal Scanner</t>
+          <t>Workspaces / Momentum</t>
         </is>
       </c>
       <c r="E255" s="6" t="inlineStr">
         <is>
-          <t>5 quick-glance panels above watchlist table</t>
+          <t>New 🚀 Momentum workspace tab</t>
         </is>
       </c>
       <c r="F255" s="5" t="inlineStr">
         <is>
-          <t>Top 5 AI Predictions · Fresh Entries · Top Momentum · Earnings This Week · Volume Surges. Each panel uses shared _qpCard + _qpFrame helpers. Click row → setDetailTicker (with ML cache fallback for R2000)</t>
+          <t>Ranks scan universe by composite (raw_momentum_score×0.5 + sharpe_norm×0.25 + rs_rank×0.25). Filterable by setup family + grade A/B/C. Click row → detail. Sidebar count = Grade-A + composite≥80 tickers</t>
         </is>
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantScanner.renderQuickPanels + panelXxx helpers + .qs-quick-* CSS</t>
+          <t>kairos.html QuantMomentum IIFE + V3_WORKSPACES.momentum + dispatcher branch</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr"/>
@@ -14925,60 +14925,48 @@
       </c>
       <c r="M255" s="3" t="inlineStr">
         <is>
-          <t>dfbe955fe</t>
+          <t>27fd646b1</t>
         </is>
       </c>
       <c r="N255" s="8" t="inlineStr"/>
     </row>
-    <row r="256" ht="45" customHeight="1">
+    <row r="256" ht="60" customHeight="1">
       <c r="A256" s="2" t="n">
         <v>255</v>
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="C256" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>SCANNER-QUICK-PANELS</t>
+        </is>
+      </c>
+      <c r="C256" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D256" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Workspaces / Signal Scanner</t>
         </is>
       </c>
       <c r="E256" s="6" t="inlineStr">
         <is>
-          <t>Verify backtest persistence (cb1f5a010)</t>
+          <t>5 quick-glance panels above watchlist table</t>
         </is>
       </c>
       <c r="F256" s="5" t="inlineStr">
         <is>
-          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
+          <t>Top 5 AI Predictions · Fresh Entries · Top Momentum · Earnings This Week · Volume Surges. Each panel uses shared _qpCard + _qpFrame helpers. Click row → setDetailTicker (with ML cache fallback for R2000)</t>
         </is>
       </c>
       <c r="G256" s="5" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
-        </is>
-      </c>
-      <c r="H256" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="I256" s="5" t="inlineStr">
-        <is>
-          <t>Win: persistence works; no silent overwrites.</t>
-        </is>
-      </c>
-      <c r="J256" s="5" t="inlineStr">
-        <is>
-          <t>3 snapshot files present. Validates cb1f5a010.</t>
-        </is>
-      </c>
+          <t>kairos.html QuantScanner.renderQuickPanels + panelXxx helpers + .qs-quick-* CSS</t>
+        </is>
+      </c>
+      <c r="H256" s="2" t="inlineStr"/>
+      <c r="I256" s="5" t="inlineStr"/>
+      <c r="J256" s="5" t="inlineStr"/>
       <c r="K256" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -14986,15 +14974,15 @@
       </c>
       <c r="L256" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M256" s="3" t="inlineStr"/>
-      <c r="N256" s="8" t="inlineStr">
-        <is>
-          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
-        </is>
-      </c>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="M256" s="3" t="inlineStr">
+        <is>
+          <t>dfbe955fe</t>
+        </is>
+      </c>
+      <c r="N256" s="8" t="inlineStr"/>
     </row>
     <row r="257" ht="45" customHeight="1">
       <c r="A257" s="2" t="n">
@@ -15002,7 +14990,7 @@
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>I4</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="C257" s="13" t="inlineStr">
@@ -15017,32 +15005,32 @@
       </c>
       <c r="E257" s="6" t="inlineStr">
         <is>
-          <t>Verify state_backup.py post-Mode-1 dual-write</t>
+          <t>Verify backtest persistence (cb1f5a010)</t>
         </is>
       </c>
       <c r="F257" s="5" t="inlineStr">
         <is>
-          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
+          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
         </is>
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
+          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
-          <t>verified (no change needed)</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="I257" s="5" t="inlineStr">
         <is>
-          <t>Win: confirms infrastructure still healthy.</t>
+          <t>Win: persistence works; no silent overwrites.</t>
         </is>
       </c>
       <c r="J257" s="5" t="inlineStr">
         <is>
-          <t>7 backup dirs present, latest 2026-05-08.</t>
+          <t>3 snapshot files present. Validates cb1f5a010.</t>
         </is>
       </c>
       <c r="K257" s="12" t="inlineStr">
@@ -15058,7 +15046,7 @@
       <c r="M257" s="3" t="inlineStr"/>
       <c r="N257" s="8" t="inlineStr">
         <is>
-          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
+          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
         </is>
       </c>
     </row>
@@ -15068,7 +15056,7 @@
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>UI-3</t>
+          <t>I4</t>
         </is>
       </c>
       <c r="C258" s="13" t="inlineStr">
@@ -15078,35 +15066,39 @@
       </c>
       <c r="D258" s="5" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E258" s="6" t="inlineStr">
         <is>
-          <t>Remove emoji icons from Thesis + Research labels</t>
+          <t>Verify state_backup.py post-Mode-1 dual-write</t>
         </is>
       </c>
       <c r="F258" s="5" t="inlineStr">
         <is>
-          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
+          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
         </is>
       </c>
       <c r="G258" s="5" t="inlineStr">
         <is>
-          <t>Removed emojis from FD sub-tab nav + section headers.</t>
+          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>verified (no change needed)</t>
         </is>
       </c>
       <c r="I258" s="5" t="inlineStr">
         <is>
-          <t>Low / cosmetic</t>
-        </is>
-      </c>
-      <c r="J258" s="5" t="inlineStr"/>
+          <t>Win: confirms infrastructure still healthy.</t>
+        </is>
+      </c>
+      <c r="J258" s="5" t="inlineStr">
+        <is>
+          <t>7 backup dirs present, latest 2026-05-08.</t>
+        </is>
+      </c>
       <c r="K258" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -15114,17 +15106,13 @@
       </c>
       <c r="L258" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="M258" s="3" t="inlineStr">
-        <is>
-          <t>24fd7c273</t>
-        </is>
-      </c>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M258" s="3" t="inlineStr"/>
       <c r="N258" s="8" t="inlineStr">
         <is>
-          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
+          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
         </is>
       </c>
     </row>
@@ -15134,59 +15122,63 @@
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-2</t>
-        </is>
-      </c>
-      <c r="C259" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>UI-3</t>
+        </is>
+      </c>
+      <c r="C259" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D259" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="E259" s="6" t="inlineStr">
         <is>
-          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
+          <t>Remove emoji icons from Thesis + Research labels</t>
         </is>
       </c>
       <c r="F259" s="5" t="inlineStr">
         <is>
-          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
+          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
         </is>
       </c>
       <c r="G259" s="5" t="inlineStr">
         <is>
-          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
+          <t>Removed emojis from FD sub-tab nav + section headers.</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
-          <t>5 min after answer</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I259" s="5" t="inlineStr">
         <is>
-          <t>Win: -671 lines.</t>
-        </is>
-      </c>
-      <c r="J259" s="5" t="inlineStr">
-        <is>
-          <t>Standard data-migration retention practice.</t>
-        </is>
-      </c>
-      <c r="K259" s="14" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L259" s="2" t="inlineStr"/>
-      <c r="M259" s="3" t="inlineStr"/>
+          <t>Low / cosmetic</t>
+        </is>
+      </c>
+      <c r="J259" s="5" t="inlineStr"/>
+      <c r="K259" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L259" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M259" s="3" t="inlineStr">
+        <is>
+          <t>24fd7c273</t>
+        </is>
+      </c>
       <c r="N259" s="8" t="inlineStr">
         <is>
-          <t>n/a — deferred</t>
+          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
         </is>
       </c>
     </row>
@@ -15196,7 +15188,7 @@
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>PERF-8-13</t>
+          <t>CLEAN-2</t>
         </is>
       </c>
       <c r="C260" s="10" t="inlineStr">
@@ -15206,37 +15198,37 @@
       </c>
       <c r="D260" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E260" s="6" t="inlineStr">
         <is>
-          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
+          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
         </is>
       </c>
       <c r="F260" s="5" t="inlineStr">
         <is>
-          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
+          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
         </is>
       </c>
       <c r="G260" s="5" t="inlineStr">
         <is>
-          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
+          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>hours-days each</t>
+          <t>5 min after answer</t>
         </is>
       </c>
       <c r="I260" s="5" t="inlineStr">
         <is>
-          <t>Win varies; defer until PERF-7 measured.</t>
+          <t>Win: -671 lines.</t>
         </is>
       </c>
       <c r="J260" s="5" t="inlineStr">
         <is>
-          <t>Don't pre-implement.</t>
+          <t>Standard data-migration retention practice.</t>
         </is>
       </c>
       <c r="K260" s="14" t="inlineStr">
@@ -15258,109 +15250,109 @@
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>Q1-step7</t>
-        </is>
-      </c>
-      <c r="C261" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>PERF-8-13</t>
+        </is>
+      </c>
+      <c r="C261" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D261" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E261" s="6" t="inlineStr">
         <is>
-          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
         </is>
       </c>
       <c r="F261" s="5" t="inlineStr">
         <is>
-          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
         </is>
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
+          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>hours-days each</t>
         </is>
       </c>
       <c r="I261" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Win varies; defer until PERF-7 measured.</t>
         </is>
       </c>
       <c r="J261" s="5" t="inlineStr">
         <is>
-          <t>Agents skim and miss post-filter subset analysis.</t>
-        </is>
-      </c>
-      <c r="K261" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
+          <t>Don't pre-implement.</t>
+        </is>
+      </c>
+      <c r="K261" s="14" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
         </is>
       </c>
       <c r="L261" s="2" t="inlineStr"/>
       <c r="M261" s="3" t="inlineStr"/>
       <c r="N261" s="8" t="inlineStr">
         <is>
-          <t>n/a — rejected</t>
-        </is>
-      </c>
-    </row>
-    <row r="262" ht="75" customHeight="1">
+          <t>n/a — deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="45" customHeight="1">
       <c r="A262" s="2" t="n">
         <v>261</v>
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>MOD-2</t>
-        </is>
-      </c>
-      <c r="C262" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Q1-step7</t>
+        </is>
+      </c>
+      <c r="C262" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D262" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E262" s="6" t="inlineStr">
         <is>
-          <t>Pixel-diff regression baseline</t>
+          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
         </is>
       </c>
       <c r="F262" s="5" t="inlineStr">
         <is>
-          <t>After modularization, no automated visual-regression catch.</t>
+          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
         </is>
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I262" s="5" t="inlineStr">
         <is>
-          <t>Win: catches accidental layout regressions.</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J262" s="5" t="inlineStr">
         <is>
-          <t>User declared out of scope 2026-05-11. Pixel-diff regression testing not needed; visual regressions can be caught by manual review when CSS/markup changes ship. Test scaffold remains in tests/04-pixel-diff.spec.js for future opt-in but no baseline PNGs will be generated.</t>
+          <t>Agents skim and miss post-filter subset analysis.</t>
         </is>
       </c>
       <c r="K262" s="15" t="inlineStr">
@@ -15368,147 +15360,209 @@
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="L262" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
+      <c r="L262" s="2" t="inlineStr"/>
       <c r="M262" s="3" t="inlineStr"/>
       <c r="N262" s="8" t="inlineStr">
         <is>
-          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="263" ht="195" customHeight="1">
+          <t>n/a — rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="75" customHeight="1">
       <c r="A263" s="2" t="n">
         <v>262</v>
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
+          <t>MOD-2</t>
+        </is>
+      </c>
+      <c r="C263" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D263" s="5" t="inlineStr">
+        <is>
+          <t>UI / Modularization</t>
+        </is>
+      </c>
+      <c r="E263" s="6" t="inlineStr">
+        <is>
+          <t>Pixel-diff regression baseline</t>
+        </is>
+      </c>
+      <c r="F263" s="5" t="inlineStr">
+        <is>
+          <t>After modularization, no automated visual-regression catch.</t>
+        </is>
+      </c>
+      <c r="G263" s="5" t="inlineStr">
+        <is>
+          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+        </is>
+      </c>
+      <c r="H263" s="2" t="inlineStr">
+        <is>
+          <t>2-3 hrs</t>
+        </is>
+      </c>
+      <c r="I263" s="5" t="inlineStr">
+        <is>
+          <t>Win: catches accidental layout regressions.</t>
+        </is>
+      </c>
+      <c r="J263" s="5" t="inlineStr">
+        <is>
+          <t>User declared out of scope 2026-05-11. Pixel-diff regression testing not needed; visual regressions can be caught by manual review when CSS/markup changes ship. Test scaffold remains in tests/04-pixel-diff.spec.js for future opt-in but no baseline PNGs will be generated.</t>
+        </is>
+      </c>
+      <c r="K263" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L263" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="M263" s="3" t="inlineStr"/>
+      <c r="N263" s="8" t="inlineStr">
+        <is>
+          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="195" customHeight="1">
+      <c r="A264" s="2" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
           <t>OB-CONFLUENCE-PROPOSAL-REJECTED</t>
         </is>
       </c>
-      <c r="C263" s="10" t="inlineStr">
+      <c r="C264" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D263" s="5" t="inlineStr">
+      <c r="D264" s="5" t="inlineStr">
         <is>
           <t>Signals / Cross-Check</t>
         </is>
       </c>
-      <c r="E263" s="6" t="inlineStr">
+      <c r="E264" s="6" t="inlineStr">
         <is>
           <t>OB-confluence Wilson bump + OB-aware stop — proposals KILLED by backtest evidence</t>
         </is>
       </c>
-      <c r="F263" s="5" t="inlineStr">
+      <c r="F264" s="5" t="inlineStr">
         <is>
           <t>User asked 2026-05-12 to ship #2 (Wilson-bump score factor for bullish OB confluence within 5% of entry) and #5 (OB-low as stop instead of 1.25xATR). Per Principle 1 / Principle 7, ran post-hoc validation: scripts/validate_ob_confluence.py retroactively tags every closed trade from existing portfolio_backtest outputs with SMC state at entry date, computes Wilson 95% LB per subset.
 RESULT (750-day backtest · n=384): Bull OB confluence within 5% of entry DECREASES Wilson LB by -8.6pp (14.6% vs baseline 23.1%). BOS-bullish boost: -3.4pp. SMC-bullish direction boost: -3.6pp. Per #5 simulation, 35 of 39 (90%) OB-low-as-stop would have loosened the stop; 25 of those still ended in losses (looser stops do not rescue broken setups, they extend exposure).
 Principle 4 fires: proposals FALSIFIED, killed permanently (not retuned). Doing the change without this validation would have introduced a 6-9pp Wilson-LB drag on every BUY signal.</t>
         </is>
       </c>
-      <c r="G263" s="5" t="inlineStr">
+      <c r="G264" s="5" t="inlineStr">
         <is>
           <t>Built scripts/validate_ob_confluence.py to retroactively run smart_money.score_smc() on the historical OHLCV at each trade's entry date, tag with OB-confluence + BOS + CHoCH flags, compute Wilson 95% LB per subset, and apply Principle 1 gates (n&gt;=30, lift&gt;=5pp). Cross-validated on 250d (n=142) and 750d (n=384) backtest outputs. Both agree: NO EDGE.</t>
         </is>
       </c>
-      <c r="H263" s="2" t="inlineStr">
+      <c r="H264" s="2" t="inlineStr">
         <is>
           <t>Days of work avoided (would have shipped a degrading change).</t>
         </is>
       </c>
-      <c r="I263" s="5" t="inlineStr">
+      <c r="I264" s="5" t="inlineStr">
         <is>
           <t>Mechanism (Principle 2): institutional OBs are supposed to mark re-add zones for smart money. Falsification (Principle 4): if the data doesn't show OB-confluent trades winning more, the mechanism either doesn't exist for retail-accessible OB detection at daily resolution OR is already priced into our 5-pillar score. Either way: ship nothing. The proposals are dead. Win: prevented a 6-9pp Wilson-LB drag from being added to live scoring. Lost: nothing — we didn't change live scoring, no opportunity cost.</t>
         </is>
       </c>
-      <c r="J263" s="5" t="inlineStr">
+      <c r="J264" s="5" t="inlineStr">
         <is>
           <t>Validator script is reusable infrastructure. Re-run any time the SMC detection logic or score thresholds change. NOTE: baseline WR in 750d backtest is 27.3% (low) — the absolute level reflects backtest-window-specific market conditions; the SUBSET comparisons are valid regardless because they share the same baseline. Do not interpret 23.1% Wilson LB as a system-level edge — that's a separate question. This validation answers ONLY: does OB-confluence improve selection within whatever the system already does.</t>
         </is>
       </c>
-      <c r="K263" s="15" t="inlineStr">
+      <c r="K264" s="15" t="inlineStr">
         <is>
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="L263" s="2" t="inlineStr">
+      <c r="L264" s="2" t="inlineStr">
         <is>
           <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="M263" s="3" t="inlineStr"/>
-      <c r="N263" s="8" t="inlineStr">
-        <is>
-          <t>python3 scripts/validate_ob_confluence.py --backtest cache/portfolio_backtest_750d_20260509_100501.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="264" ht="90" customHeight="1">
-      <c r="A264" s="2" t="n">
-        <v>263</v>
-      </c>
-      <c r="B264" s="3" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C264" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="D264" s="5" t="inlineStr">
-        <is>
-          <t>Data / Universe</t>
-        </is>
-      </c>
-      <c r="E264" s="6" t="inlineStr">
-        <is>
-          <t>Russell 1000 historical membership (Sharadar SF1)</t>
-        </is>
-      </c>
-      <c r="F264" s="5" t="inlineStr">
-        <is>
-          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
-        </is>
-      </c>
-      <c r="G264" s="5" t="inlineStr">
-        <is>
-          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
-        </is>
-      </c>
-      <c r="H264" s="2" t="inlineStr">
-        <is>
-          <t>$$ + 1 day</t>
-        </is>
-      </c>
-      <c r="I264" s="5" t="inlineStr">
-        <is>
-          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
-        </is>
-      </c>
-      <c r="J264" s="5" t="inlineStr">
-        <is>
-          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
-        </is>
-      </c>
-      <c r="K264" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="L264" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M264" s="3" t="inlineStr"/>
       <c r="N264" s="8" t="inlineStr">
+        <is>
+          <t>python3 scripts/validate_ob_confluence.py --backtest cache/portfolio_backtest_750d_20260509_100501.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="90" customHeight="1">
+      <c r="A265" s="2" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" s="3" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C265" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D265" s="5" t="inlineStr">
+        <is>
+          <t>Data / Universe</t>
+        </is>
+      </c>
+      <c r="E265" s="6" t="inlineStr">
+        <is>
+          <t>Russell 1000 historical membership (Sharadar SF1)</t>
+        </is>
+      </c>
+      <c r="F265" s="5" t="inlineStr">
+        <is>
+          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
+        </is>
+      </c>
+      <c r="G265" s="5" t="inlineStr">
+        <is>
+          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
+        </is>
+      </c>
+      <c r="H265" s="2" t="inlineStr">
+        <is>
+          <t>$$ + 1 day</t>
+        </is>
+      </c>
+      <c r="I265" s="5" t="inlineStr">
+        <is>
+          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
+        </is>
+      </c>
+      <c r="J265" s="5" t="inlineStr">
+        <is>
+          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
+        </is>
+      </c>
+      <c r="K265" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L265" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M265" s="3" t="inlineStr"/>
+      <c r="N265" s="8" t="inlineStr">
         <is>
           <t>n/a — rejected</t>
         </is>
@@ -15610,13 +15664,13 @@
         <v>31</v>
       </c>
       <c r="C4" s="18" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D4" s="18" t="n">
         <v>68</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5">
@@ -15667,13 +15721,13 @@
         <v>33</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D7" s="23" t="n">
         <v>129</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>

--- a/cache/open_items_2026-06-09.xlsx
+++ b/cache/open_items_2026-06-09.xlsx
@@ -706,13 +706,13 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="105" customHeight="1">
+    <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>ML-FEATURE-MISMATCH</t>
+          <t>STRUCT-TARGETS-M25-CUTOVER</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -722,22 +722,22 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>ML · Inference</t>
+          <t>Strategy / Targets</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>Live predict_one degenerate — 29-feat model vs 17-feat extractor</t>
+          <t>Structural targets · M2.5 — cutover gate (flip use_structural_targets=true)</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>Models retrained 2026-06-09 on 29 features but ml.feature_extractor.FEATURE_COLS still emits 17, so live predict_one feeds a mismatched vector and returns ~0 p_up for EVERY ticker (AI Edge 0% bug, all names). Batch ml-predict path extracts 29 correctly. /api/ml now prefers the batch cache + rejects degenerate live; ROOT FIX still needed: align FEATURE_COLS to 29 (or guard retrain to the live feature set). Also cache 4d stale.</t>
+          <t>Pending. After M2.1-2.4 settle in production (one week of nightly precompute + dashboard observation with flag=false), flip use_structural_targets=true in config/config.json so build_data.py overlays structural fields into data.json. Frontend consumers (Plan tab, candidate ladder, target behavior) start picking up t1_structural/t2_structural in parallel with legacy t1/t2.</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>server /api/ml cache-first + degenerate guard (done); align ml/feature_extractor.FEATURE_COLS to model n_features_in_ (pending)</t>
+          <t>Cutover requires: (1) one week of clean nightly precompute (no &gt;10 percent failure rate per scripts/precompute_targets.py exit code), (2) one clean te_regression run with errors &lt;= 1, (3) v2 dashboard frontend updated to read t1_structural fields when present (still falls back to t1 legacy when not). Until all three pass, leave flag=false.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -752,38 +752,38 @@
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="8" t="inlineStr"/>
     </row>
-    <row r="3" ht="90" customHeight="1">
+    <row r="3" ht="60" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-M25-CUTOVER</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>SCALE-2</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Targets</t>
+          <t>Auth · 500-user</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Structural targets · M2.5 — cutover gate (flip use_structural_targets=true)</t>
+          <t>Enforce per-user Supabase login (not shared basic-auth)</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Pending. After M2.1-2.4 settle in production (one week of nightly precompute + dashboard observation with flag=false), flip use_structural_targets=true in config/config.json so build_data.py overlays structural fields into data.json. Frontend consumers (Plan tab, candidate ladder, target behavior) start picking up t1_structural/t2_structural in parallel with legacy t1/t2.</t>
+          <t>Per-user UserPrefs isolation (NAV/plans/watchlist) only holds when users authenticate via Supabase; if they share the single basic-auth (gari/Swing2026), UserPrefs falls back to per-browser localStorage = no true per-user separation</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Cutover requires: (1) one week of clean nightly precompute (no &gt;10 percent failure rate per scripts/precompute_targets.py exit code), (2) one clean te_regression run with errors &lt;= 1, (3) v2 dashboard frontend updated to read t1_structural fields when present (still falls back to t1 legacy when not). Until all three pass, leave flag=false.</t>
+          <t>Require Supabase login for multi-user; verify UserPrefs keys per auth id end-to-end (user-prefs.jsx setUser binds sb.auth.getUser)</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
@@ -798,13 +798,13 @@
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="8" t="inlineStr"/>
     </row>
-    <row r="4" ht="60" customHeight="1">
+    <row r="4" ht="75" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>SCALE-2</t>
+          <t>BUG-WEEKEND-PHANTOM-PICKS</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
@@ -814,22 +814,22 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Auth · 500-user</t>
+          <t>Bugs / Audit Ledger</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Enforce per-user Supabase login (not shared basic-auth)</t>
+          <t>Weekend phantom picks in audit ledger</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Per-user UserPrefs isolation (NAV/plans/watchlist) only holds when users authenticate via Supabase; if they share the single basic-auth (gari/Swing2026), UserPrefs falls back to per-browser localStorage = no true per-user separation</t>
+          <t>Audit ledger shows phantom picks on May 10 (Sun), May 16 (Sat), May 17 (Sun) — markets closed. Likely a scan-date assignment bug (writing today's date to a Friday pick that re-scans on Sat/Sun, or weekend cron runs that should skip).</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Require Supabase login for multi-user; verify UserPrefs keys per auth id end-to-end (user-prefs.jsx setUser binds sb.auth.getUser)</t>
+          <t>Trace which writer emits these entries: check run_daily_scan.sh weekday gate, swing_trade.py scan-date logic, and infra/prototype/build_audit_ledger.py date assignment. Weekend launchd should be gated; if it runs intentionally for paper-resolve, mark those rows as REPLAY not PICK.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -844,13 +844,13 @@
       <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="8" t="inlineStr"/>
     </row>
-    <row r="5" ht="75" customHeight="1">
+    <row r="5" ht="60" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>BUG-WEEKEND-PHANTOM-PICKS</t>
+          <t>DATA-BROKEN-IPO-CALENDAR</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Bugs / Audit Ledger</t>
+          <t>Data / Calendars (broken)</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Weekend phantom picks in audit ledger</t>
+          <t>ipo_calendar — NASDAQ API times out</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Audit ledger shows phantom picks on May 10 (Sun), May 16 (Sat), May 17 (Sun) — markets closed. Likely a scan-date assignment bug (writing today's date to a Friday pick that re-scans on Sat/Sun, or weekend cron runs that should skip).</t>
+          <t>NASDAQ public IPO API times out from this host (~30s no response). Calendar slot is wired but produces 0 rows.</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Trace which writer emits these entries: check run_daily_scan.sh weekday gate, swing_trade.py scan-date logic, and infra/prototype/build_audit_ledger.py date assignment. Weekend launchd should be gated; if it runs intentionally for paper-resolve, mark those rows as REPLAY not PICK.</t>
+          <t>Investigate timeout first (UA headers / proxy / rate-limited IP) before alt-source. Candidate alternates: SEC S-1 filings via EDGAR full-text-search, IPO Monitor RSS, Yahoo Finance IPO page.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -896,7 +896,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>DATA-BROKEN-IPO-CALENDAR</t>
+          <t>DATA-BROKEN-CONGRESSIONAL-TRADES</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -906,22 +906,22 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Data / Calendars (broken)</t>
+          <t>Data / Catalysts (broken)</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>ipo_calendar — NASDAQ API times out</t>
+          <t>congressional_trades — sources dead</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>NASDAQ public IPO API times out from this host (~30s no response). Calendar slot is wired but produces 0 rows.</t>
+          <t>Senate Stock Watcher GitHub + S3 mirror both return dead/empty responses. The catalysts slot is wired but the scraper produces 0 rows.</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Investigate timeout first (UA headers / proxy / rate-limited IP) before alt-source. Candidate alternates: SEC S-1 filings via EDGAR full-text-search, IPO Monitor RSS, Yahoo Finance IPO page.</t>
+          <t>Replace dead source with direct efts.sec.gov integration (Form 4 XBRL parsing); add House Clerk site fallback for House STOCK Act filings. Scope: 1-2d dev + XBRL schema work. Free-data only per CLAUDE.md.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -942,7 +942,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>DATA-BROKEN-CONGRESSIONAL-TRADES</t>
+          <t>PARITY-REALTIME-DATA</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -952,22 +952,22 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Data / Catalysts (broken)</t>
+          <t>Data / Infrastructure / Platform Parity</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>congressional_trades — sources dead</t>
+          <t>Real-Time Data (streaming quotes)</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Senate Stock Watcher GitHub + S3 mirror both return dead/empty responses. The catalysts slot is wired but the scraper produces 0 rows.</t>
+          <t>Replace the 5-minute batch refresh with sub-second streaming quotes during market hours so charts + price ladder + Trade Plan PnL update in real time.</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Replace dead source with direct efts.sec.gov integration (Form 4 XBRL parsing); add House Clerk site fallback for House STOCK Act filings. Scope: 1-2d dev + XBRL schema work. Free-data only per CLAUDE.md.</t>
+          <t>Use the Schwab websocket feed (already in the paid stack — no new license per CLAUDE.md) into a local pub/sub buffer; kairos sub-tabs subscribe via SSE/WebSocket from server.py; cache TTL pinned at 1s during RTH.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
@@ -988,7 +988,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>PARITY-REALTIME-DATA</t>
+          <t>BARSTORE-1</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -998,22 +998,22 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Data / Infrastructure / Platform Parity</t>
+          <t>Data Infra / Bar-Store</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Real-Time Data (streaming quotes)</t>
+          <t>SQLite daily_bars schema + read/write</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Replace the 5-minute batch refresh with sub-second streaming quotes during market hours so charts + price ladder + Trade Plan PnL update in real time.</t>
+          <t>No local OHLCV history store exists; scans re-fetch per-ticker daily bars from EODHD (~10K calls/day, ~68% of 2026-06-08 usage; tripped 95K quota guard). See docs/scope_bar_store.md.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Use the Schwab websocket feed (already in the paid stack — no new license per CLAUDE.md) into a local pub/sub buffer; kairos sub-tabs subscribe via SSE/WebSocket from server.py; cache TTL pinned at 1s during RTH.</t>
+          <t>Add daily_bars(ticker,date,o,h,l,c,v,adjusted_close,source,ingested_at) to data/swingtrade.db (PK ticker+date, idx). Idempotent upsert writer + DB reader + tests. SQLite stays primary; no new deps.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>BARSTORE-1</t>
+          <t>BARSTORE-2</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -1049,17 +1049,17 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>SQLite daily_bars schema + read/write</t>
+          <t>One-time 20yr backfill</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>No local OHLCV history store exists; scans re-fetch per-ticker daily bars from EODHD (~10K calls/day, ~68% of 2026-06-08 usage; tripped 95K quota guard). See docs/scope_bar_store.md.</t>
+          <t>One eod(ticker,from_date=2005) returns full history = 1 call/ticker; backfilling the universe is ~6-8K calls ONCE vs ~10K/day recurring.</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Add daily_bars(ticker,date,o,h,l,c,v,adjusted_close,source,ingested_at) to data/swingtrade.db (PK ticker+date, idx). Idempotent upsert writer + DB reader + tests. SQLite stays primary; no new deps.</t>
+          <t>eodhd_client.backfill_history() pages the universe 1-call/ticker, paced under EODHD_SHARED_LIMITER (950/min), overnight launchd only, resumable. NO new license (uses existing EODHD).</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>BARSTORE-2</t>
+          <t>BARSTORE-3</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -1095,17 +1095,17 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>One-time 20yr backfill</t>
+          <t>DB-first failover in fetch_ohlcv_with_failover</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>One eod(ticker,from_date=2005) returns full history = 1 call/ticker; backfilling the universe is ~6-8K calls ONCE vs ~10K/day recurring.</t>
+          <t>Once history is local, scans/backtests must read DB-first and hit EODHD only for the current incomplete day + gaps.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>eodhd_client.backfill_history() pages the universe 1-call/ticker, paced under EODHD_SHARED_LIMITER (950/min), overnight launchd only, resumable. NO new license (uses existing EODHD).</t>
+          <t>Repoint data_fetcher.fetch_ohlcv_with_failover to read daily_bars first; EODHD fallback for today/gaps. Parity-check 100 tickers vs current cache/eodhd within float tol.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
@@ -1120,13 +1120,13 @@
       <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="8" t="inlineStr"/>
     </row>
-    <row r="11" ht="60" customHeight="1">
+    <row r="11" ht="75" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>BARSTORE-3</t>
+          <t>MODE-4</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -1136,22 +1136,22 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Data Infra / Bar-Store</t>
+          <t>Decision Engine</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>DB-first failover in fetch_ohlcv_with_failover</t>
+          <t>Walk-forward validation of Phase-3 per-mode pillar weights</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Once history is local, scans/backtests must read DB-first and hit EODHD only for the current incomplete day + gaps.</t>
+          <t>MODE-3 shipped intuition-based pillar weights without backtest evidence (principle 7 override). Need walk-forward validation that the per-mode weights don't degrade vs the single-set baseline.</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Repoint data_fetcher.fetch_ohlcv_with_failover to read daily_bars first; EODHD fallback for today/gaps. Parity-check 100 tickers vs current cache/eodhd within float tol.</t>
+          <t>scripts/validate_per_mode_weights.py: runs baseline backtest + 3 mode-weighted backtests (252d, min_score=50), compares WR/PF/maxDD/Sharpe per mode. Revert criterion: any mode ≤1.0× PF or ≤-5pp WR vs baseline → flip per_mode_pillar_reweight._enabled to false. See docs/per_mode_decisions_roadmap.md Phase 3.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
@@ -1166,13 +1166,13 @@
       <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="8" t="inlineStr"/>
     </row>
-    <row r="12" ht="75" customHeight="1">
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>MODE-4</t>
+          <t>SCALE-1</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -1182,22 +1182,22 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Decision Engine</t>
+          <t>Deployment · 500-user</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Walk-forward validation of Phase-3 per-mode pillar weights</t>
+          <t>Multi-worker server + concurrency load test</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>MODE-3 shipped intuition-based pillar weights without backtest evidence (principle 7 override). Need walk-forward validation that the per-mode weights don't degrade vs the single-set baseline.</t>
+          <t>Single uvicorn worker (uvicorn.run, no workers=); CPU-bound paths (65MB ML-file parse, scoring) block the event loop; untested at 500 concurrent on one Cloudflare tunnel</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>scripts/validate_per_mode_weights.py: runs baseline backtest + 3 mode-weighted backtests (252d, min_score=50), compares WR/PF/maxDD/Sharpe per mode. Revert criterion: any mode ≤1.0× PF or ≤-5pp WR vs baseline → flip per_mode_pillar_reweight._enabled to false. See docs/per_mode_decisions_roadmap.md Phase 3.</t>
+          <t>gunicorn/uvicorn --workers N (or app server), profile + offload blocking calls, run a 500-concurrent load test before certifying</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
@@ -1212,13 +1212,13 @@
       <c r="M12" s="3" t="inlineStr"/>
       <c r="N12" s="8" t="inlineStr"/>
     </row>
-    <row r="13" ht="60" customHeight="1">
+    <row r="13" ht="75" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>SCALE-1</t>
+          <t>PARITY-PAPER-TRADING-RT</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -1228,22 +1228,22 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Deployment · 500-user</t>
+          <t>Execution / Paper / Platform Parity</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Multi-worker server + concurrency load test</t>
+          <t>Real-Time Paper Trading</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Single uvicorn worker (uvicorn.run, no workers=); CPU-bound paths (65MB ML-file parse, scoring) block the event loop; untested at 500 concurrent on one Cloudflare tunnel</t>
+          <t>Execute simulated trades against live market prices via the Alpaca paper account; track fills, slippage and PnL in real time so paper validation mirrors what live trading would look like.</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>gunicorn/uvicorn --workers N (or app server), profile + offload blocking calls, run a 500-concurrent load test before certifying</t>
+          <t>Extend executor.py to route signals through the Alpaca paper REST + websocket API; webhook fills back into cache/portfolio.json; expose a 'Paper Trade' toggle on the Trade Plan card. Partially built (executor.py --submit), needs always-on wrapper.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
@@ -1258,13 +1258,13 @@
       <c r="M13" s="3" t="inlineStr"/>
       <c r="N13" s="8" t="inlineStr"/>
     </row>
-    <row r="14" ht="75" customHeight="1">
+    <row r="14" ht="45" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>PARITY-PAPER-TRADING-RT</t>
+          <t>REGIME-CONDITIONAL-MODELS</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -1274,22 +1274,22 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Execution / Paper / Platform Parity</t>
+          <t>ML / Accuracy</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Real-Time Paper Trading</t>
+          <t>Regime-conditional ML models (principle 5)</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Execute simulated trades against live market prices via the Alpaca paper account; track fills, slippage and PnL in real time so paper validation mirrors what live trading would look like.</t>
+          <t>train separate direction models per regime instead of one spanning all; #1 accuracy lever</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Extend executor.py to route signals through the Alpaca paper REST + websocket API; webhook fills back into cache/portfolio.json; expose a 'Paper Trade' toggle on the Trade Plan card. Partially built (executor.py --submit), needs always-on wrapper.</t>
+          <t>ml/train.py regime split</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>REGIME-CONDITIONAL-MODELS</t>
+          <t>OPS-1</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -1320,27 +1320,39 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>ML / Accuracy</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional ML models (principle 5)</t>
+          <t>Snapshot cleanup (scripts/cleanup_after_2026_05_16.sh)</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>train separate direction models per regime instead of one spanning all; #1 accuracy lever</t>
+          <t>Pre-Saturday session migration created intermediate snapshot files safe to remove after a week.</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>ml/train.py regime split</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="5" t="inlineStr"/>
-      <c r="J15" s="5" t="inlineStr"/>
+          <t>Run scripts/cleanup_after_2026_05_16.sh after 2026-05-16 cutoff.</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2 min</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Win: cleaner repo.</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Calendar reminder for 2026-05-16.</t>
+        </is>
+      </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1348,15 +1360,19 @@
       </c>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="3" t="inlineStr"/>
-      <c r="N15" s="8" t="inlineStr"/>
-    </row>
-    <row r="16" ht="45" customHeight="1">
+      <c r="N15" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>OPS-1</t>
+          <t>SCHWAB-REAUTH-PENDING</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -1366,39 +1382,27 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Ops / Schwab (operational)</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Snapshot cleanup (scripts/cleanup_after_2026_05_16.sh)</t>
+          <t>Schwab re-auth to unlock option Greeks</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Pre-Saturday session migration created intermediate snapshot files safe to remove after a week.</t>
+          <t>refresh token expired (invalid_grant, 7-day). Run python3 schwab_auth.py oauth -&gt; real option premiums/Greeks flow into the Options calc (currently honest BS-model fallback).</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Run scripts/cleanup_after_2026_05_16.sh after 2026-05-16 cutoff.</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2 min</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>Win: cleaner repo.</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>Calendar reminder for 2026-05-16.</t>
-        </is>
-      </c>
+          <t>user action: schwab_auth.py oauth</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
       <c r="K16" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1406,11 +1410,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="3" t="inlineStr"/>
-      <c r="N16" s="8" t="inlineStr">
-        <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
+      <c r="N16" s="8" t="inlineStr"/>
     </row>
     <row r="17" ht="60" customHeight="1">
       <c r="A17" s="2" t="n">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>SCHWAB-REAUTH-PENDING</t>
+          <t>QUANT-5</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -1428,27 +1428,39 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Ops / Schwab (operational)</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Schwab re-auth to unlock option Greeks</t>
+          <t>Mover predictor v3 — NLP earnings tone + options flow features</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>refresh token expired (invalid_grant, 7-day). Run python3 schwab_auth.py oauth -&gt; real option premiums/Greeks flow into the Options calc (currently honest BS-model fallback).</t>
+          <t>v1 had leakage. v2 fixed leakage but AUC stuck at 0.546 — pure technical features at entry don't predict mover success.</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>user action: schwab_auth.py oauth</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
+          <t>Build v3 with NEW feature classes (don't retrain): NLP earnings-call tone embeddings, options-flow IV skew + UOA put/call delta, catalyst-conditional models (subset by tag). A6 logger captures most inputs going forward.</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Caveat: exploratory research, not config-tuning.</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Don't retrain v1/v2 — both definitive AUC 0.546 negative.</t>
+        </is>
+      </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1456,15 +1468,19 @@
       </c>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="3" t="inlineStr"/>
-      <c r="N17" s="8" t="inlineStr"/>
-    </row>
-    <row r="18" ht="60" customHeight="1">
+      <c r="N17" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="165" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>QUANT-5</t>
+          <t>TV-RATING-CROSS-CHECK</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -1474,37 +1490,37 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Signals / Cross-Check</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Mover predictor v3 — NLP earnings tone + options flow features</t>
+          <t>Validate (or zero out) the ±3 TV-rating tech-score bonus</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>v1 had leakage. v2 fixed leakage but AUC stuck at 0.546 — pure technical features at entry don't predict mover success.</t>
+          <t>DISCOVERY 2026-05-11: TV-rating ±3 score bonus has been live in analysis.py:8627 for some time, modifying every BUY signal's technical pillar score. NO _validations entry, NO Wilson-CI, NO walk-forward justification for the ±3 magnitude. Worse: tv_rating was never captured on the 689 closed trades in picks_history or 1,301 signal_log entries — retroactive validation is impossible. Violates Principle 1 (n&lt;30 refusal) + Principle 7 (no knob-tweaking without evidence).</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Build v3 with NEW feature classes (don't retrain): NLP earnings-call tone embeddings, options-flow IV skew + UOA put/call delta, catalyst-conditional models (subset by tag). A6 logger captures most inputs going forward.</t>
+          <t>Phase 1 (SHIPPED 2026-05-11): (a) tv_bonus zeroed in analysis.py:8627 — score no longer mutated; (b) tv_recommendation + tv_rec_value + buy/sell/neutral counts now logged per signal in signal_tracker.log_signals() so prospective evidence accumulates; (c) tv_rating still surfaced in tech['details'] as INFORMATIONAL only — no score impact. Phase 2 (PENDING n&gt;=30, est. 6-12 weeks): run Wilson-LB(BUY|TV STRONG_BUY) vs Wilson-LB(BUY) over the prospectively-logged signals. If the agreement-conditional Wilson-LB beats unconditional by a meaningful margin (&gt;=3pp), re-enable with a magnitude justified by the regression. If not, kill the cross-check permanently (Principle 4 falsification — do not retune, do not lower the threshold).</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>Phase 1: hours (done). Phase 2: hours of analysis + calendar wait for n&gt;=30.</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Caveat: exploratory research, not config-tuning.</t>
+          <t>Mechanism (Principle 2): TV rating is an independent server-side aggregation of ~26 indicators. Two independent technical aggregations may improve precision over our 5-pillar score alone. Falsification (Principle 4): if agreement-conditional Wilson-LB &lt;= unconditional after n&gt;=30, the cross-check has no edge — kill, don't retune. Risk of CURRENT state (Phase 1): we have been over-weighting TV-STRONG_BUY signals by +3 tech-pts with zero evidence; this could have systematically biased BUY selection. Capping at 0 removes that bias going forward but does not undo past trade selection bias.</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Don't retrain v1/v2 — both definitive AUC 0.546 negative.</t>
+          <t>Default apply_to_score=false locked. Validation requires logged tv_rating on &gt;=30 CLOSED BUY trades (currently 0). Earliest Phase-2 validation window: ~6-12 weeks of scans from 2026-05-11. Pairs with the v2 dashboard TV sub-tab (infra/prototype/subtabs/tv/) which is iframe-only today. Do NOT add per-mode / per-regime elaboration until Phase 2 evidence justifies even the basic bonus.</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
@@ -1516,17 +1532,17 @@
       <c r="M18" s="3" t="inlineStr"/>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="165" customHeight="1">
+          <t>Phase 1 smoke: run python3 swing_trade.py and confirm (1) tech['details']['tv_rating'] still appears in deep-dive output labeled 'informational — bonus disabled pending validation'; (2) signal_log.json entries for new scans contain tv_recommendation + tv_rec_value + buy/sell/neutral_count populated. Phase 2 trigger: when `python3 -c 'import json; print(sum(1 for r in json.load(open("data/signal_log.json")) if r.get("tv_recommendation") and r.get("result")))'` &gt;= 30, run the agreement-conditional Wilson-LB analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="90" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>TV-RATING-CROSS-CHECK</t>
+          <t>TEST-MAE-MFE</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -1536,39 +1552,27 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Signals / Cross-Check</t>
+          <t>Testing / Validation (Tier 1)</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Validate (or zero out) the ±3 TV-rating tech-score bonus</t>
+          <t>MAE / MFE Analyzer — tune stops + targets from data</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>DISCOVERY 2026-05-11: TV-rating ±3 score bonus has been live in analysis.py:8627 for some time, modifying every BUY signal's technical pillar score. NO _validations entry, NO Wilson-CI, NO walk-forward justification for the ±3 magnitude. Worse: tv_rating was never captured on the 689 closed trades in picks_history or 1,301 signal_log entries — retroactive validation is impossible. Violates Principle 1 (n&lt;30 refusal) + Principle 7 (no knob-tweaking without evidence).</t>
+          <t>Maximum Adverse Excursion vs Maximum Favorable Excursion analyzer. signal_log.json already tracks mae_pct + mfe_pct for closed trades. Output: 'Stops triggered at -5% on winners that later hit +20% → stops too tight' or 'Trades exited at +6% target left avg +12% on table → targets too conservative'. Directly improves trade-plan math.</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 (SHIPPED 2026-05-11): (a) tv_bonus zeroed in analysis.py:8627 — score no longer mutated; (b) tv_recommendation + tv_rec_value + buy/sell/neutral counts now logged per signal in signal_tracker.log_signals() so prospective evidence accumulates; (c) tv_rating still surfaced in tech['details'] as INFORMATIONAL only — no score impact. Phase 2 (PENDING n&gt;=30, est. 6-12 weeks): run Wilson-LB(BUY|TV STRONG_BUY) vs Wilson-LB(BUY) over the prospectively-logged signals. If the agreement-conditional Wilson-LB beats unconditional by a meaningful margin (&gt;=3pp), re-enable with a magnitude justified by the regression. If not, kill the cross-check permanently (Principle 4 falsification — do not retune, do not lower the threshold).</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Phase 1: hours (done). Phase 2: hours of analysis + calendar wait for n&gt;=30.</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>Mechanism (Principle 2): TV rating is an independent server-side aggregation of ~26 indicators. Two independent technical aggregations may improve precision over our 5-pillar score alone. Falsification (Principle 4): if agreement-conditional Wilson-LB &lt;= unconditional after n&gt;=30, the cross-check has no edge — kill, don't retune. Risk of CURRENT state (Phase 1): we have been over-weighting TV-STRONG_BUY signals by +3 tech-pts with zero evidence; this could have systematically biased BUY selection. Capping at 0 removes that bias going forward but does not undo past trade selection bias.</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>Default apply_to_score=false locked. Validation requires logged tv_rating on &gt;=30 CLOSED BUY trades (currently 0). Earliest Phase-2 validation window: ~6-12 weeks of scans from 2026-05-11. Pairs with the v2 dashboard TV sub-tab (infra/prototype/subtabs/tv/) which is iframe-only today. Do NOT add per-mode / per-regime elaboration until Phase 2 evidence justifies even the basic bonus.</t>
-        </is>
-      </c>
+          <t>Read signal_log.json closed entries; scatter-plot mae vs realized PnL + mfe vs realized PnL; quantile bins (10/25/50/75/90); render as a new Testing tab card. Effort ~30min — data already there.</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
       <c r="K19" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1576,11 +1580,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="3" t="inlineStr"/>
-      <c r="N19" s="8" t="inlineStr">
-        <is>
-          <t>Phase 1 smoke: run python3 swing_trade.py and confirm (1) tech['details']['tv_rating'] still appears in deep-dive output labeled 'informational — bonus disabled pending validation'; (2) signal_log.json entries for new scans contain tv_recommendation + tv_rec_value + buy/sell/neutral_count populated. Phase 2 trigger: when `python3 -c 'import json; print(sum(1 for r in json.load(open("data/signal_log.json")) if r.get("tv_recommendation") and r.get("result")))'` &gt;= 30, run the agreement-conditional Wilson-LB analysis.</t>
-        </is>
-      </c>
+      <c r="N19" s="8" t="inlineStr"/>
     </row>
     <row r="20" ht="90" customHeight="1">
       <c r="A20" s="2" t="n">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>TEST-MAE-MFE</t>
+          <t>TEST-MC-BOOTSTRAP</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -1603,17 +1603,17 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>MAE / MFE Analyzer — tune stops + targets from data</t>
+          <t>Monte Carlo Bootstrap — confidence intervals on Sharpe/PF/WR</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Maximum Adverse Excursion vs Maximum Favorable Excursion analyzer. signal_log.json already tracks mae_pct + mfe_pct for closed trades. Output: 'Stops triggered at -5% on winners that later hit +20% → stops too tight' or 'Trades exited at +6% target left avg +12% on table → targets too conservative'. Directly improves trade-plan math.</t>
+          <t>Randomly resample closed trades 10,000x to build distributions over each metric. Wilson LB only covers WR; this covers Sharpe, Sortino, PF, max-DD, hit-rate, payoff ratio. Output: 'Sharpe 1.42, 95% CI [0.88, 1.94]' — you would know whether 1.42 is robust or noise. Standard hedge-fund metric, supports principle #1 (statistical rigor).</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Read signal_log.json closed entries; scatter-plot mae vs realized PnL + mfe vs realized PnL; quantile bins (10/25/50/75/90); render as a new Testing tab card. Effort ~30min — data already there.</t>
+          <t>Numpy bootstrap on signal_log trade PnL array, k=10000 resamples; compute distributions over each metric; render percentile bands. Effort 1-2hr.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>TEST-MC-BOOTSTRAP</t>
+          <t>TEST-PERMUTATION</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -1649,17 +1649,17 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Monte Carlo Bootstrap — confidence intervals on Sharpe/PF/WR</t>
+          <t>Permutation Test — is the edge REAL or coin flip?</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Randomly resample closed trades 10,000x to build distributions over each metric. Wilson LB only covers WR; this covers Sharpe, Sortino, PF, max-DD, hit-rate, payoff ratio. Output: 'Sharpe 1.42, 95% CI [0.88, 1.94]' — you would know whether 1.42 is robust or noise. Standard hedge-fund metric, supports principle #1 (statistical rigor).</t>
+          <t>Randomly shuffle BUY/SELL/AVOID labels on historical signals 1000x, recompute strategy returns. If real returns are not significantly better than scrambled returns, there is no edge. Direct test of principle #4 (adversarial mindset / falsification). Output: 'Real strategy: +18.7%. Random labels (1000 sims): +0.2% +/- 4.1%. p-value: 0.0001'.</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Numpy bootstrap on signal_log trade PnL array, k=10000 resamples; compute distributions over each metric; render percentile bands. Effort 1-2hr.</t>
+          <t>Shuffle decision-column of signal_log 1000x; recompute portfolio return per shuffle; rank real return vs null distribution; report p-value. Effort ~1hr.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>TEST-PERMUTATION</t>
+          <t>TEST-REGIME-COND</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Permutation Test — is the edge REAL or coin flip?</t>
+          <t>Regime-Conditional Performance — where does it work?</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Randomly shuffle BUY/SELL/AVOID labels on historical signals 1000x, recompute strategy returns. If real returns are not significantly better than scrambled returns, there is no edge. Direct test of principle #4 (adversarial mindset / falsification). Output: 'Real strategy: +18.7%. Random labels (1000 sims): +0.2% +/- 4.1%. p-value: 0.0001'.</t>
+          <t>Partition closed trades by regime (risk_on_trending / choppy / risk_off / panic) and compute WR / PF / Sharpe per regime. Per principle #5 (regime conditioning over averages). Example output: 'Trend Continuation WR: 41% overall · 62% in risk_on_trending · 18% in choppy'. Tells you which sleeves to size up/down per regime.</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Shuffle decision-column of signal_log 1000x; recompute portfolio return per shuffle; rank real return vs null distribution; report p-value. Effort ~1hr.</t>
+          <t>Group signal_log entries by regime_at_signal (already logged); compute Wilson LB on WR + bootstrapped PF/Sharpe per regime; output a (setup x regime) heatmap. Effort ~1hr.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
@@ -1720,38 +1720,38 @@
       <c r="M22" s="3" t="inlineStr"/>
       <c r="N22" s="8" t="inlineStr"/>
     </row>
-    <row r="23" ht="90" customHeight="1">
+    <row r="23" ht="60" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>TEST-REGIME-COND</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>PARITY-BACKTEST-UI</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Testing / Validation (Tier 1)</t>
+          <t>Backtesting / Platform Parity</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Regime-Conditional Performance — where does it work?</t>
+          <t>In-app Backtesting UI</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Partition closed trades by regime (risk_on_trending / choppy / risk_off / panic) and compute WR / PF / Sharpe per regime. Per principle #5 (regime conditioning over averages). Example output: 'Trend Continuation WR: 41% overall · 62% in risk_on_trending · 18% in choppy'. Tells you which sleeves to size up/down per regime.</t>
+          <t>Expose backtest.py + walk_forward_v2.py inside the kairos UI — a user picks a strategy/date range/universe and runs it without dropping to the terminal.</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Group signal_log entries by regime_at_signal (already logged); compute Wilson LB on WR + bootstrapped PF/Sharpe per regime; output a (setup x regime) heatmap. Effort ~1hr.</t>
+          <t>Add a 'Backtest' workspace in the kairos sidebar; wire a form to a /v2/backtest endpoint that shells out to backtest.py and streams stdout via SSE; render Sharpe / PF / Wilson-LB / equity curve when the run completes.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>PARITY-BACKTEST-UI</t>
+          <t>BUG-MISSING-D1S</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
@@ -1782,22 +1782,22 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Backtesting / Platform Parity</t>
+          <t>Bugs / Audit Ledger</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>In-app Backtesting UI</t>
+          <t>4 missing D1s for May 15 (out of 87)</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Expose backtest.py + walk_forward_v2.py inside the kairos UI — a user picks a strategy/date range/universe and runs it without dropping to the terminal.</t>
+          <t>4 of 87 May-15 picks have null D1 (next-day close). Probably thin EODHD coverage on small-caps — acceptable noise band but worth confirming.</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Add a 'Backtest' workspace in the kairos sidebar; wire a form to a /v2/backtest endpoint that shells out to backtest.py and streams stdout via SSE; render Sharpe / PF / Wilson-LB / equity curve when the run completes.</t>
+          <t>Identify the 4 tickers; check EODHD eod() response for each on 2026-05-16; if EODHD returned null, document as known-limitation; if EODHD returned a value, fix the ingest. Effort ~20min.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>BUG-MISSING-D1S</t>
+          <t>PARITY-CHANNEL-BAR</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -1828,22 +1828,22 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Bugs / Audit Ledger</t>
+          <t>Chart Indicators / Platform Parity</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>4 missing D1s for May 15 (out of 87)</t>
+          <t>Channel Bar overlay</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>4 of 87 May-15 picks have null D1 (next-day close). Probably thin EODHD coverage on small-caps — acceptable noise band but worth confirming.</t>
+          <t>Donchian / Keltner / Bollinger envelope overlay on the chart — top + bottom band with mid-line.</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Identify the 4 tickers; check EODHD eod() response for each on 2026-05-16; if EODHD returned null, document as known-limitation; if EODHD returned a value, fix the ingest. Effort ~20min.</t>
+          <t>Compute channels via pandas-ta in feature_extractor.py (or live in chart.js using bar data); render as semi-transparent band; toggle in the Chart sub-tab control bar.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>PARITY-CHANNEL-BAR</t>
+          <t>PARITY-RBI-GBI-WINDOW</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -1879,17 +1879,17 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Channel Bar overlay</t>
+          <t>RBI/GBI Window (regime bias bands)</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Donchian / Keltner / Bollinger envelope overlay on the chart — top + bottom band with mid-line.</t>
+          <t>Color-coded vertical bands on the chart timeline showing risk-on (green/GBI) vs risk-off (red/RBI) regime windows so the user can see at-a-glance whether prior price action happened in a hostile or friendly regime.</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Compute channels via pandas-ta in feature_extractor.py (or live in chart.js using bar data); render as semi-transparent band; toggle in the Chart sub-tab control bar.</t>
+          <t>Read cache/regime_history.json and draw vertical color bands at each regime transition on the chart canvas; tooltip explains the regime classification (4-regime model: risk_on_trending / risk_on_choppy / risk_off_trending / panic).</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
@@ -1904,13 +1904,13 @@
       <c r="M26" s="3" t="inlineStr"/>
       <c r="N26" s="8" t="inlineStr"/>
     </row>
-    <row r="27" ht="60" customHeight="1">
+    <row r="27" ht="45" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>PARITY-RBI-GBI-WINDOW</t>
+          <t>CLEAN-HOT-SECTORS-DEAD</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -1920,22 +1920,22 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Chart Indicators / Platform Parity</t>
+          <t>Code Cleanup</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>RBI/GBI Window (regime bias bands)</t>
+          <t>panelHotSectors() dead-code in kairos.html</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Color-coded vertical bands on the chart timeline showing risk-on (green/GBI) vs risk-off (red/RBI) regime windows so the user can see at-a-glance whether prior price action happened in a hostile or friendly regime.</t>
+          <t>Hot Sectors panel was removed from the Signal Scanner grid but the panelHotSectors() function is still defined in kairos.html — dead code.</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Read cache/regime_history.json and draw vertical color bands at each regime transition on the chart canvas; tooltip explains the regime classification (4-regime model: risk_on_trending / risk_on_choppy / risk_off_trending / panic).</t>
+          <t>grep for panelHotSectors callers; delete function + any unused helpers; verify no console errors. Effort ~2min.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr"/>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-HOT-SECTORS-DEAD</t>
+          <t>CLEAN-4</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -1966,27 +1966,39 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>panelHotSectors() dead-code in kairos.html</t>
+          <t>scripts/migrate_role_capabilities.py — cleanup after 2026-05-16</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Hot Sectors panel was removed from the Signal Scanner grid but the panelHotSectors() function is still defined in kairos.html — dead code.</t>
+          <t>One-shot CapStudio backfill. Already run. Tied to OPS-1 cleanup window.</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>grep for panelHotSectors callers; delete function + any unused helpers; verify no console errors. Effort ~2min.</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
+          <t>Delete during OPS-1 cleanup pass after 2026-05-16.</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>1 min</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Win: -X lines.</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>Couples with OPS-1.</t>
+        </is>
+      </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1994,15 +2006,19 @@
       </c>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="3" t="inlineStr"/>
-      <c r="N28" s="8" t="inlineStr"/>
-    </row>
-    <row r="29" ht="45" customHeight="1">
+      <c r="N28" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-4</t>
+          <t>DATA-FUTURE-EARNINGS-CAL-PIT</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -2012,39 +2028,27 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Data / Calendars (future)</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>scripts/migrate_role_capabilities.py — cleanup after 2026-05-16</t>
+          <t>earnings_calendar_pit — point-in-time integrity</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>One-shot CapStudio backfill. Already run. Tied to OPS-1 cleanup window.</t>
+          <t>Earnings calendar with point-in-time integrity (what was expected when). Needed for clean PEAD backtest replay; today's calendar uses the most-recent snapshot only, which leaks future revisions into prior dates.</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Delete during OPS-1 cleanup pass after 2026-05-16.</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>1 min</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>Win: -X lines.</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>Couples with OPS-1.</t>
-        </is>
-      </c>
+          <t>Snapshot the EODHD earnings calendar daily into a versioned earnings_calendar_history table; join on (ticker, report_date, snapshot_date) for PIT correctness in PEAD backtests.</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
       <c r="K29" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -2052,19 +2056,15 @@
       </c>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="3" t="inlineStr"/>
-      <c r="N29" s="8" t="inlineStr">
-        <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="60" customHeight="1">
+      <c r="N29" s="8" t="inlineStr"/>
+    </row>
+    <row r="30" ht="45" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-EARNINGS-CAL-PIT</t>
+          <t>DATA-FUTURE-ECONOMIC-CAL</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -2079,17 +2079,17 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>earnings_calendar_pit — point-in-time integrity</t>
+          <t>economic_calendar — CPI/PCE/NFP/FOMC dates</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Earnings calendar with point-in-time integrity (what was expected when). Needed for clean PEAD backtest replay; today's calendar uses the most-recent snapshot only, which leaks future revisions into prior dates.</t>
+          <t>Macro event calendar with consensus expectations. No source wired today; the pre-FOMC sleeve uses hard-coded FOMC dates and there is no CPI/PCE/NFP awareness.</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Snapshot the EODHD earnings calendar daily into a versioned earnings_calendar_history table; join on (ticker, report_date, snapshot_date) for PIT correctness in PEAD backtests.</t>
+          <t>Investing.com calendar scrape OR Trading Economics free tier; daily refresh; write to economic_calendar; feed pre-FOMC sleeve + risk_off blackout windows.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-ECONOMIC-CAL</t>
+          <t>DATA-FUTURE-FDA-CAL</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -2125,17 +2125,17 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>economic_calendar — CPI/PCE/NFP/FOMC dates</t>
+          <t>fda_calendar — PDUFA / AdCom dates</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Macro event calendar with consensus expectations. No source wired today; the pre-FOMC sleeve uses hard-coded FOMC dates and there is no CPI/PCE/NFP awareness.</t>
+          <t>FDA decision calendar (PDUFA dates, Advisory Committee meetings) for biotech catalyst tracking.</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Investing.com calendar scrape OR Trading Economics free tier; daily refresh; write to economic_calendar; feed pre-FOMC sleeve + risk_off blackout windows.</t>
+          <t>FDA public calendar scrape + BiopharmCatalyst free RSS; write to fda_calendar; surface as catalyst tier in any biotech sleeve.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-FDA-CAL</t>
+          <t>DATA-EMPTY-SPLITS-CALENDAR</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -2166,22 +2166,22 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Data / Calendars (future)</t>
+          <t>Data / Corporate Actions (empty by sample)</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>fda_calendar — PDUFA / AdCom dates</t>
+          <t>splits_calendar — 0 splits in current universe sample</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>FDA decision calendar (PDUFA dates, Advisory Committee meetings) for biotech catalyst tracking.</t>
+          <t>corporate_actions table populates from EODHD but the current universe sample (449 tickers) had 0 splits in the recent window. Calendar reads empty.</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>FDA public calendar scrape + BiopharmCatalyst free RSS; write to fda_calendar; surface as catalyst tier in any biotech sleeve.</t>
+          <t>Expand corporate-actions polling universe to S&amp;P 500 + Russell 1000 (universe list already available); 1-line change in the populator script.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>DATA-EMPTY-SPLITS-CALENDAR</t>
+          <t>DATA-EMPTY-MODEL-CALIBRATION</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
@@ -2212,22 +2212,22 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Data / Corporate Actions (empty by sample)</t>
+          <t>Data / ML (empty by design)</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>splits_calendar — 0 splits in current universe sample</t>
+          <t>model_calibration — waiting on realization</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>corporate_actions table populates from EODHD but the current universe sample (449 tickers) had 0 splits in the recent window. Calendar reads empty.</t>
+          <t>Calibration metrics table has no rows because the 5-20 day prediction horizons have not elapsed yet (today's predictions realize over 1-4 weeks).</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Expand corporate-actions polling universe to S&amp;P 500 + Russell 1000 (universe list already available); 1-line change in the populator script.</t>
+          <t>No code action; populates passively as time passes. Re-check after 2026-06-15 (30d post-shipping).</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr"/>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>DATA-EMPTY-MODEL-CALIBRATION</t>
+          <t>DATA-EMPTY-VAR-BREACHES</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
@@ -2258,22 +2258,22 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Data / ML (empty by design)</t>
+          <t>Data / Risk (empty by design)</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>model_calibration — waiting on realization</t>
+          <t>var_breaches — waiting on snapshots + drawdown</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Calibration metrics table has no rows because the 5-20 day prediction horizons have not elapsed yet (today's predictions realize over 1-4 weeks).</t>
+          <t>VaR breach log empty because (1) daily portfolio_risk snapshots are still ramping up and (2) no real drawdown day has happened to trigger a breach.</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>No code action; populates passively as time passes. Re-check after 2026-06-15 (30d post-shipping).</t>
+          <t>No code action; populates passively. Re-check after first portfolio drawdown &gt;2% or after 60 daily snapshots.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
@@ -2288,13 +2288,13 @@
       <c r="M34" s="3" t="inlineStr"/>
       <c r="N34" s="8" t="inlineStr"/>
     </row>
-    <row r="35" ht="45" customHeight="1">
+    <row r="35" ht="60" customHeight="1">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>DATA-EMPTY-VAR-BREACHES</t>
+          <t>DATA-FUTURE-INSIDER-EDGAR</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
@@ -2304,22 +2304,22 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Data / Risk (empty by design)</t>
+          <t>Data / SEC EDGAR (future)</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>var_breaches — waiting on snapshots + drawdown</t>
+          <t>insider_transactions via Form 4 XBRL</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>VaR breach log empty because (1) daily portfolio_risk snapshots are still ramping up and (2) no real drawdown day has happened to trigger a breach.</t>
+          <t>Per-ticker insider buy/sell stream sourced direct from SEC Form 4 filings. Today sourced indirectly via Finviz Elite bulk; direct EDGAR is point-in-time accurate and free.</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>No code action; populates passively. Re-check after first portfolio drawdown &gt;2% or after 60 daily snapshots.</t>
+          <t>Build Form 4 XBRL parser; daily ingest from efts.sec.gov; write to insider_transactions table; reconcile against Finviz bulk for cross-check.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
@@ -2334,13 +2334,13 @@
       <c r="M35" s="3" t="inlineStr"/>
       <c r="N35" s="8" t="inlineStr"/>
     </row>
-    <row r="36" ht="60" customHeight="1">
+    <row r="36" ht="45" customHeight="1">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-INSIDER-EDGAR</t>
+          <t>DATA-FUTURE-INSTITUTIONAL-EDGAR</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
@@ -2355,17 +2355,17 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>insider_transactions via Form 4 XBRL</t>
+          <t>institutional_holdings via 13F XBRL</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Per-ticker insider buy/sell stream sourced direct from SEC Form 4 filings. Today sourced indirectly via Finviz Elite bulk; direct EDGAR is point-in-time accurate and free.</t>
+          <t>Per-ticker institutional ownership tracking (Form 13F, quarterly). Useful for the Smart Money pillar; today only Finviz inst_own_pct snapshot.</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Build Form 4 XBRL parser; daily ingest from efts.sec.gov; write to insider_transactions table; reconcile against Finviz bulk for cross-check.</t>
+          <t>13F XBRL parser; quarterly ingest from EDGAR; write to institutional_holdings table with the 45-day reporting lag accounted for in any backtest joins.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-INSTITUTIONAL-EDGAR</t>
+          <t>DATA-FUTURE-CONGRESSIONAL-EDGAR</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
@@ -2396,22 +2396,22 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Data / SEC EDGAR (future)</t>
+          <t>Data / SEC EDGAR (future, alt for broken)</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>institutional_holdings via 13F XBRL</t>
+          <t>congressional_trades via EDGAR / House Clerk (alt source)</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Per-ticker institutional ownership tracking (Form 13F, quarterly). Useful for the Smart Money pillar; today only Finviz inst_own_pct snapshot.</t>
+          <t>Alternate sourcing for congressional trades after Senate Stock Watcher death (see DATA-BROKEN-CONGRESSIONAL-TRADES). Direct from House Clerk + Senate eFD.</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>13F XBRL parser; quarterly ingest from EDGAR; write to institutional_holdings table with the 45-day reporting lag accounted for in any backtest joins.</t>
+          <t>Scrape House STOCK Act PTR PDFs (House Clerk site); Senate eFD JSON; merge into normalized congressional_trades table.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-CONGRESSIONAL-EDGAR</t>
+          <t>SUPABASE-SYNC-VERIFY</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
@@ -2442,22 +2442,22 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Data / SEC EDGAR (future, alt for broken)</t>
+          <t>Data / Supabase</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>congressional_trades via EDGAR / House Clerk (alt source)</t>
+          <t>Verify supabase_analysis_sync actually writes</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Alternate sourcing for congressional trades after Senate Stock Watcher death (see DATA-BROKEN-CONGRESSIONAL-TRADES). Direct from House Clerk + Senate eFD.</t>
+          <t>confirm sync_scan writes (psycopg2 raw SQL not .table API); not silent no-op</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Scrape House STOCK Act PTR PDFs (House Clerk site); Senate eFD JSON; merge into normalized congressional_trades table.</t>
+          <t>supabase_analysis_sync.py</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
@@ -2472,13 +2472,13 @@
       <c r="M38" s="3" t="inlineStr"/>
       <c r="N38" s="8" t="inlineStr"/>
     </row>
-    <row r="39" ht="45" customHeight="1">
+    <row r="39" ht="60" customHeight="1">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>SUPABASE-SYNC-VERIFY</t>
+          <t>DATA-EMPTY-PROD-ENGINE-DEFERRED</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
@@ -2488,22 +2488,22 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Data / Supabase</t>
+          <t>Data / Telemetry (deferred for safety)</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Verify supabase_analysis_sync actually writes</t>
+          <t>8 empty slots — production-engine touches deferred</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>confirm sync_scan writes (psycopg2 raw SQL not .table API); not silent no-op</t>
+          <t>8 telemetry/data slots remain empty because populating them requires editing backtest.py / executor.py / signal_filter.py / analysis.py. Deliberately deferred to avoid risk to the live scan + exec paths.</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>supabase_analysis_sync.py</t>
+          <t>Enumerate the 8 specifically and grade each one for in-place vs side-car instrumentation. Side-car (write to telemetry DB without changing decision flow) is preferred over hot-path edits.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr"/>
@@ -2518,13 +2518,13 @@
       <c r="M39" s="3" t="inlineStr"/>
       <c r="N39" s="8" t="inlineStr"/>
     </row>
-    <row r="40" ht="60" customHeight="1">
+    <row r="40" ht="45" customHeight="1">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>DATA-EMPTY-PROD-ENGINE-DEFERRED</t>
+          <t>BARSTORE-4</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
@@ -2534,22 +2534,22 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Data / Telemetry (deferred for safety)</t>
+          <t>Data Infra / Bar-Store</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>8 empty slots — production-engine touches deferred</t>
+          <t>Daily incremental via bulk_eod</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>8 telemetry/data slots remain empty because populating them requires editing backtest.py / executor.py / signal_filter.py / analysis.py. Deliberately deferred to avoid risk to the live scan + exec paths.</t>
+          <t>After backfill, only the latest bar is needed daily; bulk_eod returns the whole exchange in 1 call.</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Enumerate the 8 specifically and grade each one for in-place vs side-car instrumentation. Side-car (write to telemetry DB without changing decision flow) is preferred over hot-path edits.</t>
+          <t>Daily launchd job: 1 bulk_eod(exchange) appends last-day bar for all tickers into daily_bars. Target &lt;=2 EODHD calls/day total for OHLCV.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>BARSTORE-4</t>
+          <t>BARSTORE-5</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
@@ -2585,17 +2585,17 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Daily incremental via bulk_eod</t>
+          <t>Corporate-action re-adjustment</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>After backfill, only the latest bar is needed daily; bulk_eod returns the whole exchange in 1 call.</t>
+          <t>Stored history must stay split/div-adjusted; a new split re-bases all prior bars. This is where data-integrity bugs hide.</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Daily launchd job: 1 bulk_eod(exchange) appends last-day bar for all tickers into daily_bars. Target &lt;=2 EODHD calls/day total for OHLCV.</t>
+          <t>Store raw + adjusted_close; small daily job re-adjusts history on split/div events (EODHD div/splits endpoints). Validate no adjustment drift.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
@@ -2610,13 +2610,13 @@
       <c r="M41" s="3" t="inlineStr"/>
       <c r="N41" s="8" t="inlineStr"/>
     </row>
-    <row r="42" ht="45" customHeight="1">
+    <row r="42" ht="60" customHeight="1">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>BARSTORE-5</t>
+          <t>BARSTORE-6</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
@@ -2631,17 +2631,17 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Corporate-action re-adjustment</t>
+          <t>Delisted backfill -&gt; survivorship fix</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Stored history must stay split/div-adjusted; a new split re-bases all prior bars. This is where data-integrity bugs hide.</t>
+          <t>Honest backtests need delisted tickers' history + point-in-time membership (membership snapshots already DONE via AIPRED-SURVIVORSHIP). Unblocks audit #1.</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>Store raw + adjusted_close; small daily job re-adjusts history on split/div events (EODHD div/splits endpoints). Validate no adjustment drift.</t>
+          <t>Backfill delisted-ticker history into daily_bars; point walk_forward_v2 at DB over 20yr. Enables survivorship-bias-free backtests + free validation of staged accuracy tweaks.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>BARSTORE-6</t>
+          <t>EODHD-WIRES-VALIDATE</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
@@ -2672,22 +2672,22 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Data Infra / Bar-Store</t>
+          <t>Data Wiring (validate)</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Delisted backfill -&gt; survivorship fix</t>
+          <t>Validate EODHD-side wires on quota reset</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Honest backtests need delisted tickers' history + point-in-time membership (membership snapshots already DONE via AIPRED-SURVIVORSHIP). Unblocks audit #1.</t>
+          <t>DCF net-debt/FCF + per-name beta + Book Risk crowding are code-complete + fallback-safe but untested against live EODHD (quota was exhausted). Confirm real values flow after reset.</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Backfill delisted-ticker history into daily_bars; point walk_forward_v2 at DB over 20yr. Enables survivorship-bias-free backtests + free validation of staged accuracy tweaks.</t>
+          <t>Stocksmith.html /api/fundamentals consumers</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
@@ -2702,13 +2702,13 @@
       <c r="M43" s="3" t="inlineStr"/>
       <c r="N43" s="8" t="inlineStr"/>
     </row>
-    <row r="44" ht="60" customHeight="1">
+    <row r="44" ht="75" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>EODHD-WIRES-VALIDATE</t>
+          <t>OVERVIEW-VERDICT-RECON</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
@@ -2718,22 +2718,22 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Data Wiring (validate)</t>
+          <t>Decision Engine</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Validate EODHD-side wires on quota reset</t>
+          <t>Reconcile compute_final_verdict (stage) vs decisions_by_mode</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>DCF net-debt/FCF + per-name beta + Book Risk crowding are code-complete + fallback-safe but untested against live EODHD (quota was exhausted). Confirm real values flow after reset.</t>
+          <t>Two engines emit different swing score+verdict for the same name (FTNT: stage=BUY/67 vs decisions_by_mode.swing=WATCH/57). decisions_by_mode omits the catalyst-sleeve EXTENDED-entry relaxation that compute_final_verdict applies, so they disagree.</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>Stocksmith.html /api/fundamentals consumers</t>
+          <t>Have decisions_by_mode consume the same relaxation OR emit a diverges-from-composite flag; decide direction after the entry-quality EXTENDED/MISSED A/B validation lands. Display already fixed (overview.js binds stage).</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>OVERVIEW-VERDICT-RECON</t>
+          <t>KAIROS-TRAFFIC-LIGHT-INPUTS</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
@@ -2764,22 +2764,22 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Decision Engine</t>
+          <t>Detail Lens / Traffic Lights</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Reconcile compute_final_verdict (stage) vs decisions_by_mode</t>
+          <t>Per-ticker risk/fundamentals inputs for lens dots</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Two engines emit different swing score+verdict for the same name (FTNT: stage=BUY/67 vs decisions_by_mode.swing=WATCH/57). decisions_by_mode omits the catalyst-sleeve EXTENDED-entry relaxation that compute_final_verdict applies, so they disagree.</t>
+          <t>Wire t.f_score · t.altman_z · t.roic · t.wacc · t.sharpe_1y · t.dd_recovery_months · t.peer_rank · t.is_held into build_data.py. _qdComputeLensStatus has cascading fallbacks (PEG → fund_score → F-score; beta → kelly → Sharpe), so dots upgrade automatically as fields land.</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Have decisions_by_mode consume the same relaxation OR emit a diverges-from-composite flag; decide direction after the entry-quality EXTENDED/MISSED A/B validation lands. Display already fixed (overview.js binds stage).</t>
+          <t>Compute in analysis.py / portfolio.py: Piotroski F (existing data), Altman Z (existing data), ROIC vs WACC, 1y Sharpe from price history, peer_rank from cohort, is_held from portfolio_state.json.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
@@ -2794,13 +2794,13 @@
       <c r="M45" s="3" t="inlineStr"/>
       <c r="N45" s="8" t="inlineStr"/>
     </row>
-    <row r="46" ht="75" customHeight="1">
+    <row r="46" ht="60" customHeight="1">
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-TRAFFIC-LIGHT-INPUTS</t>
+          <t>KAIROS-COHORT-SYMPATHY</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -2810,22 +2810,22 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Detail Lens / Traffic Lights</t>
+          <t>Earnings Lens / Cohort</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Per-ticker risk/fundamentals inputs for lens dots</t>
+          <t>Peer cohort sympathy correlations</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Wire t.f_score · t.altman_z · t.roic · t.wacc · t.sharpe_1y · t.dd_recovery_months · t.peer_rank · t.is_held into build_data.py. _qdComputeLensStatus has cascading fallbacks (PEG → fund_score → F-score; beta → kelly → Sharpe), so dots upgrade automatically as fields land.</t>
+          <t>Wire t.cohort_peers[].er_sympathy_corr + er_sympathy_move_1d + t.sympathy_history in build_data.py. Today: renderEarnings_Sympathy shows scaffold rows from t.cohort_peers if populated, else placeholder.</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Compute in analysis.py / portfolio.py: Piotroski F (existing data), Altman Z (existing data), ROIC vs WACC, 1y Sharpe from price history, peer_rank from cohort, is_held from portfolio_state.json.</t>
+          <t>Compute 8-quarter rolling correlation of 1d post-print move between this name and each cohort peer's ER date. Persist to data.json under t.cohort_peers + t.sympathy_history.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
@@ -2840,13 +2840,13 @@
       <c r="M46" s="3" t="inlineStr"/>
       <c r="N46" s="8" t="inlineStr"/>
     </row>
-    <row r="47" ht="60" customHeight="1">
+    <row r="47" ht="75" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-COHORT-SYMPATHY</t>
+          <t>PARITY-IN-APP-TRADING</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
@@ -2856,22 +2856,22 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Earnings Lens / Cohort</t>
+          <t>Execution / Live / Platform Parity</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Peer cohort sympathy correlations</t>
+          <t>In-app Trading (broker-integrated live execution)</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Wire t.cohort_peers[].er_sympathy_corr + er_sympathy_move_1d + t.sympathy_history in build_data.py. Today: renderEarnings_Sympathy shows scaffold rows from t.cohort_peers if populated, else placeholder.</t>
+          <t>One-click BUY/SELL from the dashboard to a live Schwab/Alpaca brokerage account.</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Compute 8-quarter rolling correlation of 1d post-print move between this name and each cohort peer's ER date. Persist to data.json under t.cohort_peers + t.sympathy_history.</t>
+          <t>OAuth-link the Schwab API (already paid stack); surface an 'Execute' button on the Trade Plan card; explicit AUTHORIZE LIVE TRADING gate per CLAUDE.md security protocol; route every order through the existing risk checks (max-loss-pct, drawdown haircut, regime gate).</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>PARITY-IN-APP-TRADING</t>
+          <t>KAIROS-LIVE-D1</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
@@ -2902,22 +2902,22 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Execution / Live / Platform Parity</t>
+          <t>Kairos / Audit Ledger</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>In-app Trading (broker-integrated live execution)</t>
+          <t>Live D1 estimate from Schwab quote during RTH</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>One-click BUY/SELL from the dashboard to a live Schwab/Alpaca brokerage account.</t>
+          <t>Replace placeholder D1 (yesterday's close-to-close) with a live Schwab-quote-based intraday estimate during market hours so the audit ledger D1 column is non-stale. Discussed and deferred as semantically muddy (D1 = next-day close, intraday quote is a forecast not a fill).</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>OAuth-link the Schwab API (already paid stack); surface an 'Execute' button on the Trade Plan card; explicit AUTHORIZE LIVE TRADING gate per CLAUDE.md security protocol; route every order through the existing risk checks (max-loss-pct, drawdown haircut, regime gate).</t>
+          <t>Add a SCHWAB_LIVE_D1=1 env flag; when ON and during RTH, compute D1_est = (live_quote - signal_entry) / signal_entry and annotate the cell with an 'est' chip. Effort ~1hr.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
@@ -2932,13 +2932,13 @@
       <c r="M48" s="3" t="inlineStr"/>
       <c r="N48" s="8" t="inlineStr"/>
     </row>
-    <row r="49" ht="75" customHeight="1">
+    <row r="49" ht="45" customHeight="1">
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-LIVE-D1</t>
+          <t>KAIROS-SCANNER-BEARS</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
@@ -2948,22 +2948,22 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Kairos / Audit Ledger</t>
+          <t>Kairos / Signal Scanner</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Live D1 estimate from Schwab quote during RTH</t>
+          <t>Top 5 Bears panel</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Replace placeholder D1 (yesterday's close-to-close) with a live Schwab-quote-based intraday estimate during market hours so the audit ledger D1 column is non-stale. Discussed and deferred as semantically muddy (D1 = next-day close, intraday quote is a forecast not a fill).</t>
+          <t>Add a 'Top 5 Bears' panel to the Signal Scanner alongside Fresh / Momentum / Earnings / Volume — was proposed but not selected in the initial build.</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Add a SCHWAB_LIVE_D1=1 env flag; when ON and during RTH, compute D1_est = (live_quote - signal_entry) / signal_entry and annotate the cell with an 'est' chip. Effort ~1hr.</t>
+          <t>Mirror existing 4 panels' structure; sort universe by composite bear-score desc; cap at 5; render in the Scanner grid. Effort ~10min.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
@@ -2978,13 +2978,13 @@
       <c r="M49" s="3" t="inlineStr"/>
       <c r="N49" s="8" t="inlineStr"/>
     </row>
-    <row r="50" ht="45" customHeight="1">
+    <row r="50" ht="60" customHeight="1">
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-SCANNER-BEARS</t>
+          <t>KAIROS-SCANNER-FLIPS</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
@@ -2999,17 +2999,17 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Top 5 Bears panel</t>
+          <t>Today's Flips panel</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Add a 'Top 5 Bears' panel to the Signal Scanner alongside Fresh / Momentum / Earnings / Volume — was proposed but not selected in the initial build.</t>
+          <t>Add a 'Today's Flips' panel to the Signal Scanner — tickers whose verdict flipped vs yesterday (e.g., BUY -&gt; WATCH, WATCH -&gt; BUY, AVOID -&gt; WATCH). Proposed in the 'what else' menu, not selected.</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>Mirror existing 4 panels' structure; sort universe by composite bear-score desc; cap at 5; render in the Scanner grid. Effort ~10min.</t>
+          <t>Diff today's bundle.verdict against yesterday.verdict per ticker; surface the 5-10 most material flips. Effort ~30min.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-SCANNER-FLIPS</t>
+          <t>ML-RETRAIN-FINBERT-FEATURE</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
@@ -3040,22 +3040,22 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Kairos / Signal Scanner</t>
+          <t>ML / Features (future)</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Today's Flips panel</t>
+          <t>Add FinBERT as a GBM training feature (leak-free)</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Add a 'Today's Flips' panel to the Signal Scanner — tickers whose verdict flipped vs yesterday (e.g., BUY -&gt; WATCH, WATCH -&gt; BUY, AVOID -&gt; WATCH). Proposed in the 'what else' menu, not selected.</t>
+          <t>needs historical sentiment series — accumulate forward via cache/ml/sentiment_log.jsonl (asof-stamped); add as feature #18 + retrain once ~3-6mo of leak-free history exists</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Diff today's bundle.verdict against yesterday.verdict per ticker; surface the 5-10 most material flips. Effort ~30min.</t>
+          <t>ml/feature_extractor + historical backfill</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>ML-RETRAIN-FINBERT-FEATURE</t>
+          <t>ML-AUTOREFRESH-VALIDATE</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
@@ -3086,22 +3086,22 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>ML / Features (future)</t>
+          <t>ML / Pipeline (validate)</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Add FinBERT as a GBM training feature (leak-free)</t>
+          <t>Validate ML auto-refresh post-scan + cached-bar reuse</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>needs historical sentiment series — accumulate forward via cache/ml/sentiment_log.jsonl (asof-stamped); add as feature #18 + retrain once ~3-6mo of leak-free history exists</t>
+          <t>ml_edge.run_after_scan=true runs ml.run_ml_edge over the fresh bundle; feature_extractor prefers data_archive (no re-fetch). Confirm end-to-end on next clean scan.</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>ml/feature_extractor + historical backfill</t>
+          <t>swing_trade ML hook + ml/feature_extractor</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>ML-AUTOREFRESH-VALIDATE</t>
+          <t>KAIROS-MACRO-EVENTS</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -3132,22 +3132,22 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>ML / Pipeline (validate)</t>
+          <t>Macro Lens / Calendar</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Validate ML auto-refresh post-scan + cached-bar reuse</t>
+          <t>14-day high-impact event window flag</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>ml_edge.run_after_scan=true runs ml.run_ml_edge over the fresh bundle; feature_extractor prefers data_archive (no re-fetch). Confirm end-to-end on next clean scan.</t>
+          <t>Wire t.next_macro_event_days = days to next FOMC/CPI/NFP/jobs. _qdComputeLensStatus reads this and downgrades macro lens to amber when event &lt;= 14d even in risk_on_trending regime.</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>swing_trade ML hook + ml/feature_extractor</t>
+          <t>Add macro_calendar fetch in data_fetcher.py (FRED/Trading Economics free tier or EODHD calendar). Persist to t.next_macro_event_days.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
@@ -3162,13 +3162,13 @@
       <c r="M53" s="3" t="inlineStr"/>
       <c r="N53" s="8" t="inlineStr"/>
     </row>
-    <row r="54" ht="60" customHeight="1">
+    <row r="54" ht="45" customHeight="1">
       <c r="A54" s="2" t="n">
         <v>53</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-MACRO-EVENTS</t>
+          <t>CACHE-RECLAIM</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
@@ -3178,22 +3178,22 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Macro Lens / Calendar</t>
+          <t>Ops / Hygiene</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>14-day high-impact event window flag</t>
+          <t>Reclaim ~6GB cache (stray bak + edgar TTL)</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Wire t.next_macro_event_days = days to next FOMC/CPI/NFP/jobs. _qdComputeLensStatus reads this and downgrades macro lens to amber when event &lt;= 14d even in risk_on_trending regime.</t>
+          <t>delete 300MB last_bundle.json.bak.precap_promote + add edgar companyfacts prune/TTL (6.1GB)</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>Add macro_calendar fetch in data_fetcher.py (FRED/Trading Economics free tier or EODHD calendar). Persist to t.next_macro_event_days.</t>
+          <t>cache cleanup + edgar_client TTL</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>CACHE-RECLAIM</t>
+          <t>JOBS-MOMENTUM-SNAPSHOT</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
@@ -3224,22 +3224,22 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Ops / Hygiene</t>
+          <t>Ops / Launchd</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>Reclaim ~6GB cache (stray bak + edgar TTL)</t>
+          <t>Decide momentum-snapshot job: load or disable</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>delete 300MB last_bundle.json.bak.precap_promote + add edgar companyfacts prune/TTL (6.1GB)</t>
+          <t>valid plist in repo but not currently loaded; decide launchctl bootstrap vs move to disabled/.</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>cache cleanup + edgar_client TTL</t>
+          <t>infra/launchd/com.swingtrade.momentum-snapshot.plist</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
@@ -3254,13 +3254,13 @@
       <c r="M55" s="3" t="inlineStr"/>
       <c r="N55" s="8" t="inlineStr"/>
     </row>
-    <row r="56" ht="45" customHeight="1">
+    <row r="56" ht="60" customHeight="1">
       <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>JOBS-MOMENTUM-SNAPSHOT</t>
+          <t>DATA-FUTURE-OPS-TELEMETRY-6</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
@@ -3270,22 +3270,22 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Ops / Launchd</t>
+          <t>Ops / Telemetry (future)</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>Decide momentum-snapshot job: load or disable</t>
+          <t>6 ops telemetry slots — app-side instrumentation</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>valid plist in repo but not currently loaded; decide launchctl bootstrap vs move to disabled/.</t>
+          <t>6 ops telemetry slots remain unbuilt because they require app-side instrumentation: server middleware, git hooks, scan-time emitters, executor probes, sub-tab render timings, fetch-latency probes.</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd/com.swingtrade.momentum-snapshot.plist</t>
+          <t>Build a shared emitter (lib/telemetry.py) writing to a telemetry SQLite; instrument incrementally — server middleware first, then scan emitters; surface in System Status sub-tab.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-OPS-TELEMETRY-6</t>
+          <t>SCALE-4</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
@@ -3316,22 +3316,22 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Ops / Telemetry (future)</t>
+          <t>Ops · 500-user</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>6 ops telemetry slots — app-side instrumentation</t>
+          <t>Scan reliability so Home is not sparse</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>6 ops telemetry slots remain unbuilt because they require app-side instrumentation: server middleware, git hooks, scan-time emitters, executor probes, sub-tab render timings, fetch-latency probes.</t>
+          <t>When the daily scan is empty (EODHD quota outage), Home shows honest-empty sections + stale-badged regime; users landing mid-outage see little actionable content</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Build a shared emitter (lib/telemetry.py) writing to a telemetry SQLite; instrument incrementally — server middleware first, then scan emitters; surface in System Status sub-tab.</t>
+          <t>Ensure morning scan runs reliably + quota headroom; keep STALE badge UX; consider serving last-good bundle with clear age</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
@@ -3346,13 +3346,13 @@
       <c r="M57" s="3" t="inlineStr"/>
       <c r="N57" s="8" t="inlineStr"/>
     </row>
-    <row r="58" ht="60" customHeight="1">
+    <row r="58" ht="75" customHeight="1">
       <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>SCALE-4</t>
+          <t>OV-INVEST-STRUCT</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
@@ -3362,22 +3362,22 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Ops · 500-user</t>
+          <t>Overview / Target Engine</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Scan reliability so Home is not sparse</t>
+          <t>Real structural invest targets (kill analyst-PT stub)</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>When the daily scan is empty (EODHD quota outage), Home shows honest-empty sections + stale-badged regime; users landing mid-outage see little actionable content</t>
+          <t>Invest-mode targets fall back to analyst 12mo PT (invest_stub) for low-vol names (e.g. AAPL) when no structural level qualifies in the invest R-band off the wider stop -&gt; near T1, poor R:R. Per-mode stop scaling fix (2026-06-08) made invest coherent for higher-vol names (NVDA stub=False) but low-vol names still stub.</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>Ensure morning scan runs reliably + quota headroom; keep STALE badge UX; consider serving last-good bundle with clear age</t>
+          <t>Wire multi-year structural levels (monthly/yearly swing highs, weekly Fib ext) into the invest candidate set so the invest R-band is populated without the analyst-PT fallback; raise invest max_reach_atr to match a 1-5yr horizon.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
@@ -3392,13 +3392,13 @@
       <c r="M58" s="3" t="inlineStr"/>
       <c r="N58" s="8" t="inlineStr"/>
     </row>
-    <row r="59" ht="75" customHeight="1">
+    <row r="59" ht="60" customHeight="1">
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>OV-INVEST-STRUCT</t>
+          <t>SCALE-3</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
@@ -3408,22 +3408,22 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Overview / Target Engine</t>
+          <t>Portfolio · 500-user</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>Real structural invest targets (kill analyst-PT stub)</t>
+          <t>Per-user portfolio vs shared automated book</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Invest-mode targets fall back to analyst 12mo PT (invest_stub) for low-vol names (e.g. AAPL) when no structural level qualifies in the invest R-band off the wider stop -&gt; near T1, poor R:R. Per-mode stop scaling fix (2026-06-08) made invest coherent for higher-vol names (NVDA stub=False) but low-vol names still stub.</t>
+          <t>Home AUTOMATED BOOK is the single shared Alpaca-paper auto-trade account; every viewer sees identical positions; no per-user book (NAV is per-user, positions are not)</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Wire multi-year structural levels (monthly/yearly swing highs, weekly Fib ext) into the invest candidate set so the invest R-band is populated without the analyst-PT fallback; raise invest max_reach_atr to match a 1-5yr horizon.</t>
+          <t>Decide: keep as shared model/track-record book by design, OR add a per-user position store keyed to UserPrefs auth id</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
@@ -3438,13 +3438,13 @@
       <c r="M59" s="3" t="inlineStr"/>
       <c r="N59" s="8" t="inlineStr"/>
     </row>
-    <row r="60" ht="60" customHeight="1">
+    <row r="60" ht="90" customHeight="1">
       <c r="A60" s="2" t="n">
         <v>59</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>SCALE-3</t>
+          <t>QUANT-HMM-FF-LGBM-ROADMAP</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
@@ -3454,22 +3454,22 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Portfolio · 500-user</t>
+          <t>Quant / Modeling Roadmap</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>Per-user portfolio vs shared automated book</t>
+          <t>HMM regime / Fama-French / LightGBM swap (status unclear)</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Home AUTOMATED BOOK is the single shared Alpaca-paper auto-trade account; every viewer sees identical positions; no per-user book (NAV is per-user, positions are not)</t>
+          <t>Roadmap items pasted as a status table — clarification pending whether user wants execution or just context tracking. Three potential upgrades: (a) HMM-based regime classifier replacing the rule-based 4-regime model, (b) Fama-French factor exposure analysis on closed trades, (c) LightGBM swap-in for HistGradientBoosting in ml/train_historical.py. Each 1-3 days.</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>Decide: keep as shared model/track-record book by design, OR add a per-user position store keyed to UserPrefs auth id</t>
+          <t>Confirm intent before executing. If go: HMM first (decouples regime classifier from heuristics, principle #18), then Fama-French attribution (per-strategy factor exposure), then LightGBM swap (likely-marginal accuracy gain vs current HistGB). Each upgrade gated by Wilson-LB validation vs current baseline.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
@@ -3484,13 +3484,13 @@
       <c r="M60" s="3" t="inlineStr"/>
       <c r="N60" s="8" t="inlineStr"/>
     </row>
-    <row r="61" ht="90" customHeight="1">
+    <row r="61" ht="60" customHeight="1">
       <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>QUANT-HMM-FF-LGBM-ROADMAP</t>
+          <t>PARITY-SMART-RISK-LEVELS</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
@@ -3500,22 +3500,22 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Quant / Modeling Roadmap</t>
+          <t>Risk / Targets / Platform Parity</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>HMM regime / Fama-French / LightGBM swap (status unclear)</t>
+          <t>Smart Risk Levels (auto stop + T1/T2)</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Roadmap items pasted as a status table — clarification pending whether user wants execution or just context tracking. Three potential upgrades: (a) HMM-based regime classifier replacing the rule-based 4-regime model, (b) Fama-French factor exposure analysis on closed trades, (c) LightGBM swap-in for HistGradientBoosting in ml/train_historical.py. Each 1-3 days.</t>
+          <t>Auto-place stop / T1 / T2 dots on the chart with confluence reasoning (HVN, AVWAP, fractal, ATR, Fib). Already computed by the structural target engine but not surfaced on the new Chart sub-tab.</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Confirm intent before executing. If go: HMM first (decouples regime classifier from heuristics, principle #18), then Fama-French attribution (per-strategy factor exposure), then LightGBM swap (likely-marginal accuracy gain vs current HistGB). Each upgrade gated by Wilson-LB validation vs current baseline.</t>
+          <t>Read cache/target_engine/{TICKER}_{MODE}.json and overlay the levels on the chart canvas with hover tooltips citing the confluence factors; gated by use_structural_targets flag (M2.5 cutover).</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>PARITY-SMART-RISK-LEVELS</t>
+          <t>KAIROS-L2-BOOK</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
@@ -3546,22 +3546,22 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Risk / Targets / Platform Parity</t>
+          <t>Risk Lens / Execution</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>Smart Risk Levels (auto stop + T1/T2)</t>
+          <t>L2 bid/ask depth at price levels</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Auto-place stop / T1 / T2 dots on the chart with confluence reasoning (HVN, AVWAP, fractal, ATR, Fib). Already computed by the structural target engine but not surfaced on the new Chart sub-tab.</t>
+          <t>Wire t.l2_book from Schwab streaming API → render in renderRisk_LiquidityLadder. Today: ADV-derived size tiers shown as scaffold. Schwab streaming requires WebSocket session — see schwab_client.py.</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>Read cache/target_engine/{TICKER}_{MODE}.json and overlay the levels on the chart canvas with hover tooltips citing the confluence factors; gated by use_structural_targets flag (M2.5 cutover).</t>
+          <t>Subscribe to Schwab Level-II quote stream; persist top-of-book snapshot into t.l2_book = {bid:[{px,size}], ask:[{px,size}]}. Frontend already reads these fields if present.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-L2-BOOK</t>
+          <t>PARITY-AI-SIGNALS-V1</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
@@ -3592,22 +3592,22 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Risk Lens / Execution</t>
+          <t>Signals / Platform Parity</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>L2 bid/ask depth at price levels</t>
+          <t>1st-Gen AI Signals</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Wire t.l2_book from Schwab streaming API → render in renderRisk_LiquidityLadder. Today: ADV-derived size tiers shown as scaffold. Schwab streaming requires WebSocket session — see schwab_client.py.</t>
+          <t>Surface a baseline AI BUY/SELL signal stream on the chart as quick-glance arrows/dots — the competitor-platform feature (TrendSpider, Trade Ideas) users expect to see at a glance, separate from the full ML Edge sub-tab.</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>Subscribe to Schwab Level-II quote stream; persist top-of-book snapshot into t.l2_book = {bid:[{px,size}], ask:[{px,size}]}. Frontend already reads these fields if present.</t>
+          <t>Reuse ML Edge dir-head + cone outputs but render as 1-bar arrows/markers on the new Chart sub-tab; isolate from the 10-section Technicals view; respect cache/ml_edge_predictions.json freshness.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr"/>
@@ -3622,13 +3622,13 @@
       <c r="M63" s="3" t="inlineStr"/>
       <c r="N63" s="8" t="inlineStr"/>
     </row>
-    <row r="64" ht="60" customHeight="1">
+    <row r="64" ht="45" customHeight="1">
       <c r="A64" s="2" t="n">
         <v>63</v>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>PARITY-AI-SIGNALS-V1</t>
+          <t>TEST-AB-PAPER</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
@@ -3638,22 +3638,22 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Signals / Platform Parity</t>
+          <t>Testing / Validation (Tier 2)</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>1st-Gen AI Signals</t>
+          <t>A/B Paper Split — live comparison</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Surface a baseline AI BUY/SELL signal stream on the chart as quick-glance arrows/dots — the competitor-platform feature (TrendSpider, Trade Ideas) users expect to see at a glance, separate from the full ML Edge sub-tab.</t>
+          <t>Run config A on half the paper portfolio and config B on the other half; real-time comparison of WR / PF / equity divergence over 30-60d window.</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>Reuse ML Edge dir-head + cone outputs but render as 1-bar arrows/markers on the new Chart sub-tab; isolate from the 10-section Technicals view; respect cache/ml_edge_predictions.json freshness.</t>
+          <t>Extend executor.py to accept --variant flag; persist per-variant portfolio state; cross-section panel in System Status sub-tab. Effort 3-4hr.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
@@ -3668,13 +3668,13 @@
       <c r="M64" s="3" t="inlineStr"/>
       <c r="N64" s="8" t="inlineStr"/>
     </row>
-    <row r="65" ht="45" customHeight="1">
+    <row r="65" ht="60" customHeight="1">
       <c r="A65" s="2" t="n">
         <v>64</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>TEST-AB-PAPER</t>
+          <t>TEST-BENCHMARK-SPY</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
@@ -3689,17 +3689,17 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>A/B Paper Split — live comparison</t>
+          <t>Benchmark vs SPY — alpha / beta / IR</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>Run config A on half the paper portfolio and config B on the other half; real-time comparison of WR / PF / equity divergence over 30-60d window.</t>
+          <t>Compute strategy alpha, beta, information ratio vs SPY benchmark. Standard performance attribution; turns 'we made +X%' into 'we made +Y% over SPY at lower drawdown'.</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>Extend executor.py to accept --variant flag; persist per-variant portfolio state; cross-section panel in System Status sub-tab. Effort 3-4hr.</t>
+          <t>Daily portfolio_value series joined to SPY adjusted-close; regress daily returns -&gt; SPY returns for beta + alpha; IR = (mean excess return) / (std excess return); render in System Status. Effort ~1hr.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>TEST-BENCHMARK-SPY</t>
+          <t>TEST-DD-DIST</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
@@ -3735,17 +3735,17 @@
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>Benchmark vs SPY — alpha / beta / IR</t>
+          <t>Drawdown Distribution Simulator</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>Compute strategy alpha, beta, information ratio vs SPY benchmark. Standard performance attribution; turns 'we made +X%' into 'we made +Y% over SPY at lower drawdown'.</t>
+          <t>Bootstrap 1000 portfolio paths from closed-trade distribution; measure tail-drawdown probability at p95/p99; supports principle #9 (drawdown asymmetry — losing 50% requires +100% to recover).</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>Daily portfolio_value series joined to SPY adjusted-close; regress daily returns -&gt; SPY returns for beta + alpha; IR = (mean excess return) / (std excess return); render in System Status. Effort ~1hr.</t>
+          <t>Resample trade sequence with replacement; build equity curves; compute max-DD per path; histogram + tail percentiles; feed into position-sizing math. Effort 2-3hr.</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>TEST-DD-DIST</t>
+          <t>TEST-SENSITIVITY</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>Drawdown Distribution Simulator</t>
+          <t>Sensitivity / Robustness Test</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Bootstrap 1000 portfolio paths from closed-trade distribution; measure tail-drawdown probability at p95/p99; supports principle #9 (drawdown asymmetry — losing 50% requires +100% to recover).</t>
+          <t>Perturb each config parameter +/-20% (score floors, stop ATR mult, R:R floor, regime thresholds) and check whether the strategy still passes the gate. Finds overfit knobs that only work at one exact value.</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Resample trade sequence with replacement; build equity curves; compute max-DD per path; histogram + tail percentiles; feed into position-sizing math. Effort 2-3hr.</t>
+          <t>Grid-walk key config thresholds; re-run backtest at each point; build sensitivity heatmap (param vs PF); flag any knob whose +/-20% perturbation collapses PF &gt;50%. Effort ~2hr.</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>TEST-SENSITIVITY</t>
+          <t>TEST-SLIPPAGE-STRESS</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
@@ -3827,17 +3827,17 @@
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>Sensitivity / Robustness Test</t>
+          <t>Slippage Stress Test</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>Perturb each config parameter +/-20% (score floors, stop ATR mult, R:R floor, regime thresholds) and check whether the strategy still passes the gate. Finds overfit knobs that only work at one exact value.</t>
+          <t>Double the slippage assumption (ATR/ADV-scaled model from audit #5) and recompute backtest stats. Validates fragile execution dependence per principle #19 (slippage realism).</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>Grid-walk key config thresholds; re-run backtest at each point; build sensitivity heatmap (param vs PF); flag any knob whose +/-20% perturbation collapses PF &gt;50%. Effort ~2hr.</t>
+          <t>Re-run backtest with SLIPPAGE_MULT=2.0; compare WR/PF/Sharpe deltas; if a strategy collapses at 2x slippage it is execution-fragile and should be down-sized. Effort ~1hr.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>TEST-SLIPPAGE-STRESS</t>
+          <t>TEST-CORRELATED-FAILURE</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
@@ -3868,22 +3868,22 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Testing / Validation (Tier 2)</t>
+          <t>Testing / Validation (Tier 3)</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>Slippage Stress Test</t>
+          <t>Correlated-Failure — what if EODHD goes down 24h?</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Double the slippage assumption (ATR/ADV-scaled model from audit #5) and recompute backtest stats. Validates fragile execution dependence per principle #19 (slippage realism).</t>
+          <t>Simulate the impact of the sole data provider (EODHD) being unavailable for 24-48h during market hours. What happens to (a) the scan, (b) live exec, (c) the dashboard?</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>Re-run backtest with SLIPPAGE_MULT=2.0; compare WR/PF/Sharpe deltas; if a strategy collapses at 2x slippage it is execution-fragile and should be down-sized. Effort ~1hr.</t>
+          <t>Inject EODHD error responses in a paper environment; observe failure modes (fallback to last-known cache vs hard error vs degraded scan); document recovery RTO; tighten any silent-fail paths discovered. Effort 2-3hr.</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr"/>
@@ -3898,13 +3898,13 @@
       <c r="M69" s="3" t="inlineStr"/>
       <c r="N69" s="8" t="inlineStr"/>
     </row>
-    <row r="70" ht="60" customHeight="1">
+    <row r="70" ht="45" customHeight="1">
       <c r="A70" s="2" t="n">
         <v>69</v>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>TEST-CORRELATED-FAILURE</t>
+          <t>TEST-CRASH-REPLAY</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
@@ -3919,17 +3919,17 @@
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>Correlated-Failure — what if EODHD goes down 24h?</t>
+          <t>Crash Replay — 2008/2020/2022 stress</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>Simulate the impact of the sole data provider (EODHD) being unavailable for 24-48h during market hours. What happens to (a) the scan, (b) live exec, (c) the dashboard?</t>
+          <t>Apply current portfolio composition to historical crash days (2008 GFC, 2020 COVID, 2022 rate-shock); measure realized drawdown + recovery time per scenario.</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>Inject EODHD error responses in a paper environment; observe failure modes (fallback to last-known cache vs hard error vs degraded scan); document recovery RTO; tighten any silent-fail paths discovered. Effort 2-3hr.</t>
+          <t>Snapshot today's positions; price-replay against historical daily OHLC from those windows; report per-crisis max-DD and time-to-recovery. Effort 2-3hr.</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
@@ -3944,13 +3944,13 @@
       <c r="M70" s="3" t="inlineStr"/>
       <c r="N70" s="8" t="inlineStr"/>
     </row>
-    <row r="71" ht="45" customHeight="1">
+    <row r="71" ht="60" customHeight="1">
       <c r="A71" s="2" t="n">
         <v>70</v>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>TEST-CRASH-REPLAY</t>
+          <t>TEST-KELLY-SIM</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
@@ -3965,17 +3965,17 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>Crash Replay — 2008/2020/2022 stress</t>
+          <t>Half-Kelly vs Full-Kelly sizing simulation</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Apply current portfolio composition to historical crash days (2008 GFC, 2020 COVID, 2022 rate-shock); measure realized drawdown + recovery time per scenario.</t>
+          <t>Visualize portfolio growth under Half-Kelly (current default) vs Full-Kelly vs Quarter-Kelly sizing rules; quantifies the volatility-vs-CAGR tradeoff that principle #9 codifies.</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>Snapshot today's positions; price-replay against historical daily OHLC from those windows; report per-crisis max-DD and time-to-recovery. Effort 2-3hr.</t>
+          <t>Bootstrap N portfolio paths under each Kelly fraction; chart median equity curve + percentile fans; surface terminal-wealth distribution. Effort ~2hr.</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>TEST-KELLY-SIM</t>
+          <t>TEST-SLIPPAGE-ATTR</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
@@ -4011,17 +4011,17 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>Half-Kelly vs Full-Kelly sizing simulation</t>
+          <t>Slippage Attribution — signal PnL vs realized PnL gap</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>Visualize portfolio growth under Half-Kelly (current default) vs Full-Kelly vs Quarter-Kelly sizing rules; quantifies the volatility-vs-CAGR tradeoff that principle #9 codifies.</t>
+          <t>For each closed trade, compute the gap between the model's predicted entry/exit and the actual fill price. Aggregate by setup/ticker/regime to find where slippage eats edge.</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>Bootstrap N portfolio paths under each Kelly fraction; chart median equity curve + percentile fans; surface terminal-wealth distribution. Effort ~2hr.</t>
+          <t>Read signal_log entries (which has the signal price) and join to paper_fills.json (which has the realized price); compute slippage_bp per trade; group + percentile. Effort ~2hr.</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>TEST-SLIPPAGE-ATTR</t>
+          <t>TEST-TAX-AWARE</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>Slippage Attribution — signal PnL vs realized PnL gap</t>
+          <t>Tax-Aware Backtest — short-term cap-gains haircut</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>For each closed trade, compute the gap between the model's predicted entry/exit and the actual fill price. Aggregate by setup/ticker/regime to find where slippage eats edge.</t>
+          <t>Apply short-term capital-gains tax (35-40% on gains held &lt;1yr) to backtest PnL. Real after-tax return for a US retail account is materially lower than gross.</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>Read signal_log entries (which has the signal price) and join to paper_fills.json (which has the realized price); compute slippage_bp per trade; group + percentile. Effort ~2hr.</t>
+          <t>Add post_tax_pnl column to backtest output; apply 35% haircut to short-term gains (&gt;0 PnL, held &lt;365d) and 15% to long-term; report Sharpe / total-return pre vs post tax. Effort ~2hr.</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr"/>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>TEST-TAX-AWARE</t>
+          <t>WAIT-CALIB-DRIFT-SPARK</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
@@ -4098,22 +4098,22 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Testing / Validation (Tier 3)</t>
+          <t>Time-Dependent / Calibration</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>Tax-Aware Backtest — short-term cap-gains haircut</t>
+          <t>Calibration drift sparkline populates</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>Apply short-term capital-gains tax (35-40% on gains held &lt;1yr) to backtest PnL. Real after-tax return for a US retail account is materially lower than gross.</t>
+          <t>The calibration-drift sparkline in the ML Edge sub-tab needs multiple training cycles to populate (weeks). Each morning scan retrains and appends a calibration row; the sparkline reads from that history table.</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>Add post_tax_pnl column to backtest output; apply 35% haircut to short-term gains (&gt;0 PnL, held &lt;365d) and 15% to long-term; report Sharpe / total-return pre vs post tax. Effort ~2hr.</t>
+          <t>Passive wait. Re-check after 4-6 weekly retrain cycles. If still empty, verify ml.train_historical writes to cache/ml/calibration_history.jsonl on each run.</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
@@ -4128,13 +4128,13 @@
       <c r="M74" s="3" t="inlineStr"/>
       <c r="N74" s="8" t="inlineStr"/>
     </row>
-    <row r="75" ht="60" customHeight="1">
+    <row r="75" ht="45" customHeight="1">
       <c r="A75" s="2" t="n">
         <v>74</v>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>WAIT-CALIB-DRIFT-SPARK</t>
+          <t>WAIT-DRIFT-SNAPSHOTS</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
@@ -4144,22 +4144,22 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Time-Dependent / Calibration</t>
+          <t>Time-Dependent / Drift Tracking</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>Calibration drift sparkline populates</t>
+          <t>Diff vs yesterday + 30-day drift populate</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>The calibration-drift sparkline in the ML Edge sub-tab needs multiple training cycles to populate (weeks). Each morning scan retrains and appends a calibration row; the sparkline reads from that history table.</t>
+          <t>The 'diff vs yesterday' + 30-day drift columns need 2+ daily snapshots stored. Starts populating tomorrow's scan.</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>Passive wait. Re-check after 4-6 weekly retrain cycles. If still empty, verify ml.train_historical writes to cache/ml/calibration_history.jsonl on each run.</t>
+          <t>Passive wait; first populated values appear in the next morning's scan output. Verify the snapshot persister wrote a row today.</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>WAIT-DRIFT-SNAPSHOTS</t>
+          <t>WAIT-ML-PICKS-RESOLVE</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
@@ -4190,22 +4190,22 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Time-Dependent / Drift Tracking</t>
+          <t>Time-Dependent / Picks History</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>Diff vs yesterday + 30-day drift populate</t>
+          <t>Picks-history outcome resolution (resolve_ml_picks.py)</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>The 'diff vs yesterday' + 30-day drift columns need 2+ daily snapshots stored. Starts populating tomorrow's scan.</t>
+          <t>resolve_ml_picks.py needs 5 trading days from each pick to resolve outcomes. First AI Edge batch (picks from ~2026-05-18) resolves around 2026-05-23.</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>Passive wait; first populated values appear in the next morning's scan output. Verify the snapshot persister wrote a row today.</t>
+          <t>Passive wait. Re-check on 2026-05-23; verify resolve_ml_picks.py runs in run_daily_scan.sh and populates picks_history.json outcome columns.</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
@@ -4220,13 +4220,13 @@
       <c r="M76" s="3" t="inlineStr"/>
       <c r="N76" s="8" t="inlineStr"/>
     </row>
-    <row r="77" ht="45" customHeight="1">
+    <row r="77" ht="60" customHeight="1">
       <c r="A77" s="2" t="n">
         <v>76</v>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>WAIT-ML-PICKS-RESOLVE</t>
+          <t>WAIT-SURVIVORSHIP-DECAY</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
@@ -4236,22 +4236,22 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Time-Dependent / Picks History</t>
+          <t>Time-Dependent / Survivorship Haircut</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>Picks-history outcome resolution (resolve_ml_picks.py)</t>
+          <t>Survivorship haircut shrinking 3pp -&gt; 0.5pp</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>resolve_ml_picks.py needs 5 trading days from each pick to resolve outcomes. First AI Edge batch (picks from ~2026-05-18) resolves around 2026-05-23.</t>
+          <t>The -3pp WR survivorship haircut should shrink as monthly S&amp;P 500 / R1000 membership snapshots accumulate (Wikipedia revision history). Once 24+ months of snapshots are stored, the haircut can fade toward 0.5pp.</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>Passive wait. Re-check on 2026-05-23; verify resolve_ml_picks.py runs in run_daily_scan.sh and populates picks_history.json outcome columns.</t>
+          <t>Passive wait — currently only current-membership data. Re-evaluate annually. Until then keep -3pp haircut per CLAUDE.md principle #6.</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>WAIT-SURVIVORSHIP-DECAY</t>
+          <t>WAIT-WF-EQUITY-REAL</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
@@ -4282,22 +4282,22 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Time-Dependent / Survivorship Haircut</t>
+          <t>Time-Dependent / Walk-Forward</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>Survivorship haircut shrinking 3pp -&gt; 0.5pp</t>
+          <t>Walk-forward equity curve switches to REAL track</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>The -3pp WR survivorship haircut should shrink as monthly S&amp;P 500 / R1000 membership snapshots accumulate (Wikipedia revision history). Once 24+ months of snapshots are stored, the haircut can fade toward 0.5pp.</t>
+          <t>Currently the equity curve renders backtest-derived returns. Switches to REAL track once 5+ resolved AI Edge picks are available — first batch resolves ~2026-05-23, so REAL curve activates ~2026-05-24.</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>Passive wait — currently only current-membership data. Re-evaluate annually. Until then keep -3pp haircut per CLAUDE.md principle #6.</t>
+          <t>Passive wait. Re-check on 2026-05-24; verify the equity curve flips from BACKTEST badge to REAL badge once n_resolved &gt;= 5.</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>WAIT-WF-EQUITY-REAL</t>
+          <t>PARITY-10-CHARTS-GRID</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
@@ -4328,22 +4328,22 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>Time-Dependent / Walk-Forward</t>
+          <t>UI / Layout / Platform Parity</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>Walk-forward equity curve switches to REAL track</t>
+          <t>10-chart multi-pane grid</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Currently the equity curve renders backtest-derived returns. Switches to REAL track once 5+ resolved AI Edge picks are available — first batch resolves ~2026-05-23, so REAL curve activates ~2026-05-24.</t>
+          <t>Display up to 10 ticker charts side-by-side in a configurable grid (2x5, 3x4, etc.) for at-a-glance correlation/leadership reads — what TrendSpider and Trade Ideas users default to.</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Passive wait. Re-check on 2026-05-24; verify the equity curve flips from BACKTEST badge to REAL badge once n_resolved &gt;= 5.</t>
+          <t>New 'Grid' workspace in kairos that renders N lightweight-chart canvases; ticker list drag-droppable; persists ticker set per layout.</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr"/>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>PARITY-10-CHARTS-GRID</t>
+          <t>PARITY-CUSTOM-LAYOUTS</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
@@ -4379,17 +4379,17 @@
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>10-chart multi-pane grid</t>
+          <t>Customizable Layouts (save/load workspace presets)</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Display up to 10 ticker charts side-by-side in a configurable grid (2x5, 3x4, etc.) for at-a-glance correlation/leadership reads — what TrendSpider and Trade Ideas users default to.</t>
+          <t>User drags/resizes panels in the kairos workspace and saves the arrangement as a named preset (Day-Trade view / Swing view / Research view) and switches between them.</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>New 'Grid' workspace in kairos that renders N lightweight-chart canvases; ticker list drag-droppable; persists ticker set per layout.</t>
+          <t>Persist layout JSON in cache/user_layouts.json (per-user once auth lands); sidebar dropdown to switch; default presets shipped (Swing / Position / Research).</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr"/>
@@ -4404,13 +4404,13 @@
       <c r="M80" s="3" t="inlineStr"/>
       <c r="N80" s="8" t="inlineStr"/>
     </row>
-    <row r="81" ht="60" customHeight="1">
+    <row r="81" ht="75" customHeight="1">
       <c r="A81" s="2" t="n">
         <v>80</v>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>PARITY-CUSTOM-LAYOUTS</t>
+          <t>STRUCT-TARGETS-PHASE2</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
@@ -4420,35 +4420,51 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>UI / Layout / Platform Parity</t>
+          <t>Strategy / Targets</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>Customizable Layouts (save/load workspace presets)</t>
+          <t>Structural targets Phase 2 — engine uses them as T1/T2</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>User drags/resizes panels in the kairos workspace and saves the arrangement as a named preset (Day-Trade view / Swing view / Research view) and switches between them.</t>
+          <t>Phase 1 (shipped 2026-05-10): structural target sources (fractal, fib, EW Wave-3) display on Plan tab as informational. Phase 2: actually use these as T1/T2 instead of ATR-multiple targets. Needs per-source x regime evidence (&gt;=30 trades each).</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Persist layout JSON in cache/user_layouts.json (per-user once auth lands); sidebar dropdown to switch; default presets shipped (Swing / Position / Research).</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr"/>
-      <c r="I81" s="5" t="inlineStr"/>
-      <c r="J81" s="5" t="inlineStr"/>
-      <c r="K81" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+          <t>Add config flag target_source = atr_multiple | structural. When structural, T1 = nearest_above with R:R&gt;=3 from {fractal_high, fib_127, EW_T1}. Fall back to ATR if R:R floor not met. Backtest side-by-side with current ATR-multiple.</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>1 day + backtest</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>High win potential, medium risk</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>Awaiting evidence. Phase 1 currently just populates display field; need 3-4 weeks of trade data with target_sources captured before Phase 2 is decidable.</t>
+        </is>
+      </c>
+      <c r="K81" s="11" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="3" t="inlineStr"/>
-      <c r="N81" s="8" t="inlineStr"/>
+      <c r="N81" s="8" t="inlineStr">
+        <is>
+          <t>Run backtest with target_source=structural and target_source=atr_multiple on same window. Compare PF/WR/avg_win.</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="75" customHeight="1">
       <c r="A82" s="2" t="n">
@@ -4456,69 +4472,77 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-PHASE2</t>
-        </is>
-      </c>
-      <c r="C82" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>K6</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Targets</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>Structural targets Phase 2 — engine uses them as T1/T2</t>
+          <t>Single canonical trade plan object — every tab reads from one source</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 (shipped 2026-05-10): structural target sources (fractal, fib, EW Wave-3) display on Plan tab as informational. Phase 2: actually use these as T1/T2 instead of ATR-multiple targets. Needs per-source x regime evidence (&gt;=30 trades each).</t>
+          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>Add config flag target_source = atr_multiple | structural. When structural, T1 = nearest_above with R:R&gt;=3 from {fractal_high, fib_127, EW_T1}. Fall back to ATR if R:R floor not met. Backtest side-by-side with current ATR-multiple.</t>
+          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>1 day + backtest</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>High win potential, medium risk</t>
+          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
         </is>
       </c>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t>Awaiting evidence. Phase 1 currently just populates display field; need 3-4 weeks of trade data with target_sources captured before Phase 2 is decidable.</t>
-        </is>
-      </c>
-      <c r="K82" s="11" t="inlineStr">
-        <is>
-          <t>IN_PROGRESS</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr"/>
-      <c r="M82" s="3" t="inlineStr"/>
+          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
+        </is>
+      </c>
+      <c r="K82" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>2c9b9f339</t>
+        </is>
+      </c>
       <c r="N82" s="8" t="inlineStr">
         <is>
-          <t>Run backtest with target_source=structural and target_source=atr_multiple on same window. Compare PF/WR/avg_win.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="75" customHeight="1">
+          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="90" customHeight="1">
       <c r="A83" s="2" t="n">
         <v>82</v>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>B3-WEEKLY-FIX</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -4528,37 +4552,29 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Backtest / Bug Fix</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>Single canonical trade plan object — every tab reads from one source</t>
+          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
+          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I83" s="5" t="inlineStr">
-        <is>
-          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
-        </is>
-      </c>
+          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="5" t="inlineStr"/>
       <c r="J83" s="5" t="inlineStr">
         <is>
-          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
+          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
         </is>
       </c>
       <c r="K83" s="12" t="inlineStr">
@@ -4568,27 +4584,27 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>2c9b9f339</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N83" s="8" t="inlineStr">
         <is>
-          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="90" customHeight="1">
+          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="75" customHeight="1">
       <c r="A84" s="2" t="n">
         <v>83</v>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>B3-WEEKLY-FIX</t>
+          <t>VARIANT-F-BT</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -4598,31 +4614,27 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Bug Fix</t>
+          <t>Backtest Parity</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
+          <t>Variant F regime-conditional multipliers not wired into backtest path</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
+          <t>backtest.py:418 uses tracker.get_setup_weight_multiplier (reading picks_history) but never consults config.setup_score_multiplier_by_regime. So Variant F's TC×bull=0.0 kill never applied in backtest — explains why 105 TC bull trades persisted in 250d backtest despite live kill in config.</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
+          <t>Add Variant F lookup at backtest.py:442 mirroring analysis.py:8867 logic. Same demotion gate (n&gt;=30 + wr_lb&lt;0.30). Comment cross-reference live path.</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="5" t="inlineStr"/>
-      <c r="J84" s="5" t="inlineStr">
-        <is>
-          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
-        </is>
-      </c>
+      <c r="J84" s="5" t="inlineStr"/>
       <c r="K84" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4635,22 +4647,18 @@
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
-        </is>
-      </c>
-      <c r="N84" s="8" t="inlineStr">
-        <is>
-          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="75" customHeight="1">
+          <t>0cdb13340</t>
+        </is>
+      </c>
+      <c r="N84" s="8" t="inlineStr"/>
+    </row>
+    <row r="85" ht="45" customHeight="1">
       <c r="A85" s="2" t="n">
         <v>84</v>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>VARIANT-F-BT</t>
+          <t>P0-WEEKLY</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -4660,27 +4668,39 @@
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Backtest Parity</t>
+          <t>Backtest infra</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>Variant F regime-conditional multipliers not wired into backtest path</t>
+          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:418 uses tracker.get_setup_weight_multiplier (reading picks_history) but never consults config.setup_score_multiplier_by_regime. So Variant F's TC×bull=0.0 kill never applied in backtest — explains why 105 TC bull trades persisted in 250d backtest despite live kill in config.</t>
+          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>Add Variant F lookup at backtest.py:442 mirroring analysis.py:8867 logic. Same demotion gate (n&gt;=30 + wr_lb&lt;0.30). Comment cross-reference live path.</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr"/>
-      <c r="I85" s="5" t="inlineStr"/>
-      <c r="J85" s="5" t="inlineStr"/>
+          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>20 min</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>CRITICAL — system was unable to backtest</t>
+        </is>
+      </c>
+      <c r="J85" s="5" t="inlineStr">
+        <is>
+          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
+        </is>
+      </c>
       <c r="K85" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4693,18 +4713,22 @@
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
-          <t>0cdb13340</t>
-        </is>
-      </c>
-      <c r="N85" s="8" t="inlineStr"/>
-    </row>
-    <row r="86" ht="45" customHeight="1">
+          <t>985cd182b</t>
+        </is>
+      </c>
+      <c r="N85" s="8" t="inlineStr">
+        <is>
+          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="75" customHeight="1">
       <c r="A86" s="2" t="n">
         <v>85</v>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>P0-WEEKLY</t>
+          <t>ROLLING-SHARPE-FIX</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -4714,39 +4738,27 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Backtest infra</t>
+          <t>Decision Engine / Bug</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
+          <t>Rolling-Sharpe brake firing on contaminated data</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
+          <t>Two bugs: (a) WATCH-conviction signals being written with verdict='BUY' inflated loss count; (b) same physical trade re-emitted as fresh daily signal counted 3× in rolling-20 window. Net: false brake activation pausing ALL new BUYs system-wide. Real Sharpe -0.42; system reported -1.732</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>20 min</t>
-        </is>
-      </c>
-      <c r="I86" s="5" t="inlineStr">
-        <is>
-          <t>CRITICAL — system was unable to backtest</t>
-        </is>
-      </c>
-      <c r="J86" s="5" t="inlineStr">
-        <is>
-          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
-        </is>
-      </c>
+          <t>Upstream fix: swing_trade.py line 3110 _resolve_verdict() detects WATCH conviction and overrides bucket label. Read-time fix: decision_engine.compute_rolling_sharpe_kill_state dedupes by (ticker,entry,pnl,exit_reason). Historical cleanup: scripts/dedupe_signal_log.py removed 133 mislabels + 90 dupes (backed up)</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="5" t="inlineStr"/>
+      <c r="J86" s="5" t="inlineStr"/>
       <c r="K86" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4754,27 +4766,23 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
-        </is>
-      </c>
-      <c r="N86" s="8" t="inlineStr">
-        <is>
-          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="75" customHeight="1">
+          <t>27fd646b1</t>
+        </is>
+      </c>
+      <c r="N86" s="8" t="inlineStr"/>
+    </row>
+    <row r="87" ht="90" customHeight="1">
       <c r="A87" s="2" t="n">
         <v>86</v>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>ROLLING-SHARPE-FIX</t>
+          <t>OPERATING-MINDSET</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -4784,27 +4792,39 @@
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Decision Engine / Bug</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>Rolling-Sharpe brake firing on contaminated data</t>
+          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>Two bugs: (a) WATCH-conviction signals being written with verdict='BUY' inflated loss count; (b) same physical trade re-emitted as fresh daily signal counted 3× in rolling-20 window. Net: false brake activation pausing ALL new BUYs system-wide. Real Sharpe -0.42; system reported -1.732</t>
+          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>Upstream fix: swing_trade.py line 3110 _resolve_verdict() detects WATCH conviction and overrides bucket label. Read-time fix: decision_engine.compute_rolling_sharpe_kill_state dedupes by (ticker,entry,pnl,exit_reason). Historical cleanup: scripts/dedupe_signal_log.py removed 133 mislabels + 90 dupes (backed up)</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr"/>
-      <c r="I87" s="5" t="inlineStr"/>
-      <c r="J87" s="5" t="inlineStr"/>
+          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>Win: codified discipline survives session/agent boundaries.</t>
+        </is>
+      </c>
+      <c r="J87" s="5" t="inlineStr">
+        <is>
+          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
+        </is>
+      </c>
       <c r="K87" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4812,23 +4832,27 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
-          <t>27fd646b1</t>
-        </is>
-      </c>
-      <c r="N87" s="8" t="inlineStr"/>
-    </row>
-    <row r="88" ht="90" customHeight="1">
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N87" s="8" t="inlineStr">
+        <is>
+          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="60" customHeight="1">
       <c r="A88" s="2" t="n">
         <v>87</v>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>OPERATING-MINDSET</t>
+          <t>EXEC-TRADABLE-ENUM</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -4838,39 +4862,27 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Execution · Auto-Trade</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
+          <t>Stock executor skipped all active names (enum bug)</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
+          <t>alpaca-py AssetStatus enum stringified to 'AssetStatus.ACTIVE'; check 'assetstatus.active' != 'active' wrongly skipped EVERY tradable stock since ~2026-05-28 → stock auto-trade silently dead, options-only</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I88" s="5" t="inlineStr">
-        <is>
-          <t>Win: codified discipline survives session/agent boundaries.</t>
-        </is>
-      </c>
-      <c r="J88" s="5" t="inlineStr">
-        <is>
-          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
-        </is>
-      </c>
+          <t>executor.py: read enum .value ('active') before lowercasing</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="5" t="inlineStr"/>
+      <c r="J88" s="5" t="inlineStr"/>
       <c r="K88" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4878,27 +4890,23 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N88" s="8" t="inlineStr">
-        <is>
-          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="60" customHeight="1">
+          <t>c7098178a</t>
+        </is>
+      </c>
+      <c r="N88" s="8" t="inlineStr"/>
+    </row>
+    <row r="89" ht="105" customHeight="1">
       <c r="A89" s="2" t="n">
         <v>88</v>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>EXEC-TRADABLE-ENUM</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -4908,27 +4916,39 @@
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Execution · Auto-Trade</t>
+          <t>ML / Data Logging</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>Stock executor skipped all active names (enum bug)</t>
+          <t>Entry-time feature logger in swing_trade.py</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>alpaca-py AssetStatus enum stringified to 'AssetStatus.ACTIVE'; check 'assetstatus.active' != 'active' wrongly skipped EVERY tradable stock since ~2026-05-28 → stock auto-trade silently dead, options-only</t>
+          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>executor.py: read enum .value ('active') before lowercasing</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr"/>
-      <c r="I89" s="5" t="inlineStr"/>
-      <c r="J89" s="5" t="inlineStr"/>
+          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
+        </is>
+      </c>
+      <c r="J89" s="5" t="inlineStr">
+        <is>
+          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
+        </is>
+      </c>
       <c r="K89" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4936,15 +4956,19 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
-          <t>c7098178a</t>
-        </is>
-      </c>
-      <c r="N89" s="8" t="inlineStr"/>
+          <t>0574c60d4</t>
+        </is>
+      </c>
+      <c r="N89" s="8" t="inlineStr">
+        <is>
+          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="105" customHeight="1">
       <c r="A90" s="2" t="n">
@@ -4952,7 +4976,7 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>ML-FEATURE-MISMATCH</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -4962,39 +4986,27 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>ML / Data Logging</t>
+          <t>ML · Inference</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>Entry-time feature logger in swing_trade.py</t>
+          <t>Live predict_one degenerate — 29-feat model vs 17-feat extractor</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
+          <t>Models retrained 2026-06-09 on 29 features but ml.feature_extractor.FEATURE_COLS still emits 17, so live predict_one feeds a mismatched vector and returns ~0 p_up for EVERY ticker (AI Edge 0% bug, all names). Batch ml-predict path extracts 29 correctly. /api/ml now prefers the batch cache + rejects degenerate live; ROOT FIX still needed: align FEATURE_COLS to 29 (or guard retrain to the live feature set). Also cache 4d stale.</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I90" s="5" t="inlineStr">
-        <is>
-          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
-        </is>
-      </c>
-      <c r="J90" s="5" t="inlineStr">
-        <is>
-          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
-        </is>
-      </c>
+          <t>server /api/ml cache-first + degenerate guard (done); align ml/feature_extractor.FEATURE_COLS to model n_features_in_ (pending)</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="5" t="inlineStr"/>
+      <c r="J90" s="5" t="inlineStr"/>
       <c r="K90" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5002,19 +5014,15 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>0574c60d4</t>
-        </is>
-      </c>
-      <c r="N90" s="8" t="inlineStr">
-        <is>
-          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
-        </is>
-      </c>
+          <t>33877186c</t>
+        </is>
+      </c>
+      <c r="N90" s="8" t="inlineStr"/>
     </row>
     <row r="91" ht="45" customHeight="1">
       <c r="A91" s="2" t="n">
@@ -15715,7 +15723,7 @@
         </is>
       </c>
       <c r="B2" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="18" t="n">
         <v>20</v>
@@ -15724,7 +15732,7 @@
         <v>58</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3">
@@ -15753,7 +15761,7 @@
         </is>
       </c>
       <c r="B4" s="18" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" s="18" t="n">
         <v>77</v>
@@ -15762,7 +15770,7 @@
         <v>68</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5">

--- a/cache/open_items_2026-06-09.xlsx
+++ b/cache/open_items_2026-06-09.xlsx
@@ -706,13 +706,13 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="90" customHeight="1">
+    <row r="2" ht="105" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-M25-CUTOVER</t>
+          <t>ML-FEATURE-MISMATCH</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -722,22 +722,22 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Targets</t>
+          <t>ML · Inference</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>Structural targets · M2.5 — cutover gate (flip use_structural_targets=true)</t>
+          <t>Live predict_one degenerate — 29-feat model vs 17-feat extractor</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>Pending. After M2.1-2.4 settle in production (one week of nightly precompute + dashboard observation with flag=false), flip use_structural_targets=true in config/config.json so build_data.py overlays structural fields into data.json. Frontend consumers (Plan tab, candidate ladder, target behavior) start picking up t1_structural/t2_structural in parallel with legacy t1/t2.</t>
+          <t>Models retrained 2026-06-09 on 29 features but ml.feature_extractor.FEATURE_COLS still emits 17, so live predict_one feeds a mismatched vector and returns ~0 p_up for EVERY ticker (AI Edge 0% bug, all names). Batch ml-predict path extracts 29 correctly. /api/ml now prefers the batch cache + rejects degenerate live; ROOT FIX still needed: align FEATURE_COLS to 29 (or guard retrain to the live feature set). Also cache 4d stale.</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>Cutover requires: (1) one week of clean nightly precompute (no &gt;10 percent failure rate per scripts/precompute_targets.py exit code), (2) one clean te_regression run with errors &lt;= 1, (3) v2 dashboard frontend updated to read t1_structural fields when present (still falls back to t1 legacy when not). Until all three pass, leave flag=false.</t>
+          <t>server /api/ml cache-first + degenerate guard (done); align ml/feature_extractor.FEATURE_COLS to model n_features_in_ (pending)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -752,38 +752,38 @@
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="8" t="inlineStr"/>
     </row>
-    <row r="3" ht="60" customHeight="1">
+    <row r="3" ht="90" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>SCALE-2</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>STRUCT-TARGETS-M25-CUTOVER</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Auth · 500-user</t>
+          <t>Strategy / Targets</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Enforce per-user Supabase login (not shared basic-auth)</t>
+          <t>Structural targets · M2.5 — cutover gate (flip use_structural_targets=true)</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Per-user UserPrefs isolation (NAV/plans/watchlist) only holds when users authenticate via Supabase; if they share the single basic-auth (gari/Swing2026), UserPrefs falls back to per-browser localStorage = no true per-user separation</t>
+          <t>Pending. After M2.1-2.4 settle in production (one week of nightly precompute + dashboard observation with flag=false), flip use_structural_targets=true in config/config.json so build_data.py overlays structural fields into data.json. Frontend consumers (Plan tab, candidate ladder, target behavior) start picking up t1_structural/t2_structural in parallel with legacy t1/t2.</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Require Supabase login for multi-user; verify UserPrefs keys per auth id end-to-end (user-prefs.jsx setUser binds sb.auth.getUser)</t>
+          <t>Cutover requires: (1) one week of clean nightly precompute (no &gt;10 percent failure rate per scripts/precompute_targets.py exit code), (2) one clean te_regression run with errors &lt;= 1, (3) v2 dashboard frontend updated to read t1_structural fields when present (still falls back to t1 legacy when not). Until all three pass, leave flag=false.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
@@ -798,13 +798,13 @@
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="8" t="inlineStr"/>
     </row>
-    <row r="4" ht="75" customHeight="1">
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>BUG-WEEKEND-PHANTOM-PICKS</t>
+          <t>SCALE-2</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
@@ -814,22 +814,22 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Bugs / Audit Ledger</t>
+          <t>Auth · 500-user</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Weekend phantom picks in audit ledger</t>
+          <t>Enforce per-user Supabase login (not shared basic-auth)</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Audit ledger shows phantom picks on May 10 (Sun), May 16 (Sat), May 17 (Sun) — markets closed. Likely a scan-date assignment bug (writing today's date to a Friday pick that re-scans on Sat/Sun, or weekend cron runs that should skip).</t>
+          <t>Per-user UserPrefs isolation (NAV/plans/watchlist) only holds when users authenticate via Supabase; if they share the single basic-auth (gari/Swing2026), UserPrefs falls back to per-browser localStorage = no true per-user separation</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Trace which writer emits these entries: check run_daily_scan.sh weekday gate, swing_trade.py scan-date logic, and infra/prototype/build_audit_ledger.py date assignment. Weekend launchd should be gated; if it runs intentionally for paper-resolve, mark those rows as REPLAY not PICK.</t>
+          <t>Require Supabase login for multi-user; verify UserPrefs keys per auth id end-to-end (user-prefs.jsx setUser binds sb.auth.getUser)</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -844,13 +844,13 @@
       <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="8" t="inlineStr"/>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="75" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>DATA-BROKEN-IPO-CALENDAR</t>
+          <t>BUG-WEEKEND-PHANTOM-PICKS</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Data / Calendars (broken)</t>
+          <t>Bugs / Audit Ledger</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>ipo_calendar — NASDAQ API times out</t>
+          <t>Weekend phantom picks in audit ledger</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>NASDAQ public IPO API times out from this host (~30s no response). Calendar slot is wired but produces 0 rows.</t>
+          <t>Audit ledger shows phantom picks on May 10 (Sun), May 16 (Sat), May 17 (Sun) — markets closed. Likely a scan-date assignment bug (writing today's date to a Friday pick that re-scans on Sat/Sun, or weekend cron runs that should skip).</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Investigate timeout first (UA headers / proxy / rate-limited IP) before alt-source. Candidate alternates: SEC S-1 filings via EDGAR full-text-search, IPO Monitor RSS, Yahoo Finance IPO page.</t>
+          <t>Trace which writer emits these entries: check run_daily_scan.sh weekday gate, swing_trade.py scan-date logic, and infra/prototype/build_audit_ledger.py date assignment. Weekend launchd should be gated; if it runs intentionally for paper-resolve, mark those rows as REPLAY not PICK.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -896,7 +896,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>DATA-BROKEN-CONGRESSIONAL-TRADES</t>
+          <t>DATA-BROKEN-IPO-CALENDAR</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -906,22 +906,22 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Data / Catalysts (broken)</t>
+          <t>Data / Calendars (broken)</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>congressional_trades — sources dead</t>
+          <t>ipo_calendar — NASDAQ API times out</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Senate Stock Watcher GitHub + S3 mirror both return dead/empty responses. The catalysts slot is wired but the scraper produces 0 rows.</t>
+          <t>NASDAQ public IPO API times out from this host (~30s no response). Calendar slot is wired but produces 0 rows.</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Replace dead source with direct efts.sec.gov integration (Form 4 XBRL parsing); add House Clerk site fallback for House STOCK Act filings. Scope: 1-2d dev + XBRL schema work. Free-data only per CLAUDE.md.</t>
+          <t>Investigate timeout first (UA headers / proxy / rate-limited IP) before alt-source. Candidate alternates: SEC S-1 filings via EDGAR full-text-search, IPO Monitor RSS, Yahoo Finance IPO page.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -942,7 +942,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>PARITY-REALTIME-DATA</t>
+          <t>DATA-BROKEN-CONGRESSIONAL-TRADES</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -952,22 +952,22 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Data / Infrastructure / Platform Parity</t>
+          <t>Data / Catalysts (broken)</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Real-Time Data (streaming quotes)</t>
+          <t>congressional_trades — sources dead</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Replace the 5-minute batch refresh with sub-second streaming quotes during market hours so charts + price ladder + Trade Plan PnL update in real time.</t>
+          <t>Senate Stock Watcher GitHub + S3 mirror both return dead/empty responses. The catalysts slot is wired but the scraper produces 0 rows.</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Use the Schwab websocket feed (already in the paid stack — no new license per CLAUDE.md) into a local pub/sub buffer; kairos sub-tabs subscribe via SSE/WebSocket from server.py; cache TTL pinned at 1s during RTH.</t>
+          <t>Replace dead source with direct efts.sec.gov integration (Form 4 XBRL parsing); add House Clerk site fallback for House STOCK Act filings. Scope: 1-2d dev + XBRL schema work. Free-data only per CLAUDE.md.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
@@ -988,7 +988,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>BARSTORE-1</t>
+          <t>PARITY-REALTIME-DATA</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -998,22 +998,22 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Data Infra / Bar-Store</t>
+          <t>Data / Infrastructure / Platform Parity</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>SQLite daily_bars schema + read/write</t>
+          <t>Real-Time Data (streaming quotes)</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>No local OHLCV history store exists; scans re-fetch per-ticker daily bars from EODHD (~10K calls/day, ~68% of 2026-06-08 usage; tripped 95K quota guard). See docs/scope_bar_store.md.</t>
+          <t>Replace the 5-minute batch refresh with sub-second streaming quotes during market hours so charts + price ladder + Trade Plan PnL update in real time.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Add daily_bars(ticker,date,o,h,l,c,v,adjusted_close,source,ingested_at) to data/swingtrade.db (PK ticker+date, idx). Idempotent upsert writer + DB reader + tests. SQLite stays primary; no new deps.</t>
+          <t>Use the Schwab websocket feed (already in the paid stack — no new license per CLAUDE.md) into a local pub/sub buffer; kairos sub-tabs subscribe via SSE/WebSocket from server.py; cache TTL pinned at 1s during RTH.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>BARSTORE-2</t>
+          <t>BARSTORE-1</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -1049,17 +1049,17 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>One-time 20yr backfill</t>
+          <t>SQLite daily_bars schema + read/write</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>One eod(ticker,from_date=2005) returns full history = 1 call/ticker; backfilling the universe is ~6-8K calls ONCE vs ~10K/day recurring.</t>
+          <t>No local OHLCV history store exists; scans re-fetch per-ticker daily bars from EODHD (~10K calls/day, ~68% of 2026-06-08 usage; tripped 95K quota guard). See docs/scope_bar_store.md.</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>eodhd_client.backfill_history() pages the universe 1-call/ticker, paced under EODHD_SHARED_LIMITER (950/min), overnight launchd only, resumable. NO new license (uses existing EODHD).</t>
+          <t>Add daily_bars(ticker,date,o,h,l,c,v,adjusted_close,source,ingested_at) to data/swingtrade.db (PK ticker+date, idx). Idempotent upsert writer + DB reader + tests. SQLite stays primary; no new deps.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>BARSTORE-3</t>
+          <t>BARSTORE-2</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -1095,17 +1095,17 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>DB-first failover in fetch_ohlcv_with_failover</t>
+          <t>One-time 20yr backfill</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Once history is local, scans/backtests must read DB-first and hit EODHD only for the current incomplete day + gaps.</t>
+          <t>One eod(ticker,from_date=2005) returns full history = 1 call/ticker; backfilling the universe is ~6-8K calls ONCE vs ~10K/day recurring.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Repoint data_fetcher.fetch_ohlcv_with_failover to read daily_bars first; EODHD fallback for today/gaps. Parity-check 100 tickers vs current cache/eodhd within float tol.</t>
+          <t>eodhd_client.backfill_history() pages the universe 1-call/ticker, paced under EODHD_SHARED_LIMITER (950/min), overnight launchd only, resumable. NO new license (uses existing EODHD).</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
@@ -1120,13 +1120,13 @@
       <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="8" t="inlineStr"/>
     </row>
-    <row r="11" ht="75" customHeight="1">
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>MODE-4</t>
+          <t>BARSTORE-3</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -1136,22 +1136,22 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Decision Engine</t>
+          <t>Data Infra / Bar-Store</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Walk-forward validation of Phase-3 per-mode pillar weights</t>
+          <t>DB-first failover in fetch_ohlcv_with_failover</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>MODE-3 shipped intuition-based pillar weights without backtest evidence (principle 7 override). Need walk-forward validation that the per-mode weights don't degrade vs the single-set baseline.</t>
+          <t>Once history is local, scans/backtests must read DB-first and hit EODHD only for the current incomplete day + gaps.</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>scripts/validate_per_mode_weights.py: runs baseline backtest + 3 mode-weighted backtests (252d, min_score=50), compares WR/PF/maxDD/Sharpe per mode. Revert criterion: any mode ≤1.0× PF or ≤-5pp WR vs baseline → flip per_mode_pillar_reweight._enabled to false. See docs/per_mode_decisions_roadmap.md Phase 3.</t>
+          <t>Repoint data_fetcher.fetch_ohlcv_with_failover to read daily_bars first; EODHD fallback for today/gaps. Parity-check 100 tickers vs current cache/eodhd within float tol.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
@@ -1166,13 +1166,13 @@
       <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="8" t="inlineStr"/>
     </row>
-    <row r="12" ht="60" customHeight="1">
+    <row r="12" ht="75" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>SCALE-1</t>
+          <t>MODE-4</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -1182,22 +1182,22 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Deployment · 500-user</t>
+          <t>Decision Engine</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Multi-worker server + concurrency load test</t>
+          <t>Walk-forward validation of Phase-3 per-mode pillar weights</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Single uvicorn worker (uvicorn.run, no workers=); CPU-bound paths (65MB ML-file parse, scoring) block the event loop; untested at 500 concurrent on one Cloudflare tunnel</t>
+          <t>MODE-3 shipped intuition-based pillar weights without backtest evidence (principle 7 override). Need walk-forward validation that the per-mode weights don't degrade vs the single-set baseline.</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>gunicorn/uvicorn --workers N (or app server), profile + offload blocking calls, run a 500-concurrent load test before certifying</t>
+          <t>scripts/validate_per_mode_weights.py: runs baseline backtest + 3 mode-weighted backtests (252d, min_score=50), compares WR/PF/maxDD/Sharpe per mode. Revert criterion: any mode ≤1.0× PF or ≤-5pp WR vs baseline → flip per_mode_pillar_reweight._enabled to false. See docs/per_mode_decisions_roadmap.md Phase 3.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
@@ -1212,13 +1212,13 @@
       <c r="M12" s="3" t="inlineStr"/>
       <c r="N12" s="8" t="inlineStr"/>
     </row>
-    <row r="13" ht="75" customHeight="1">
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>PARITY-PAPER-TRADING-RT</t>
+          <t>SCALE-1</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -1228,22 +1228,22 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Execution / Paper / Platform Parity</t>
+          <t>Deployment · 500-user</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Real-Time Paper Trading</t>
+          <t>Multi-worker server + concurrency load test</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Execute simulated trades against live market prices via the Alpaca paper account; track fills, slippage and PnL in real time so paper validation mirrors what live trading would look like.</t>
+          <t>Single uvicorn worker (uvicorn.run, no workers=); CPU-bound paths (65MB ML-file parse, scoring) block the event loop; untested at 500 concurrent on one Cloudflare tunnel</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Extend executor.py to route signals through the Alpaca paper REST + websocket API; webhook fills back into cache/portfolio.json; expose a 'Paper Trade' toggle on the Trade Plan card. Partially built (executor.py --submit), needs always-on wrapper.</t>
+          <t>gunicorn/uvicorn --workers N (or app server), profile + offload blocking calls, run a 500-concurrent load test before certifying</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
@@ -1258,13 +1258,13 @@
       <c r="M13" s="3" t="inlineStr"/>
       <c r="N13" s="8" t="inlineStr"/>
     </row>
-    <row r="14" ht="45" customHeight="1">
+    <row r="14" ht="75" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>REGIME-CONDITIONAL-MODELS</t>
+          <t>PARITY-PAPER-TRADING-RT</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -1274,22 +1274,22 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>ML / Accuracy</t>
+          <t>Execution / Paper / Platform Parity</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional ML models (principle 5)</t>
+          <t>Real-Time Paper Trading</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>train separate direction models per regime instead of one spanning all; #1 accuracy lever</t>
+          <t>Execute simulated trades against live market prices via the Alpaca paper account; track fills, slippage and PnL in real time so paper validation mirrors what live trading would look like.</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>ml/train.py regime split</t>
+          <t>Extend executor.py to route signals through the Alpaca paper REST + websocket API; webhook fills back into cache/portfolio.json; expose a 'Paper Trade' toggle on the Trade Plan card. Partially built (executor.py --submit), needs always-on wrapper.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>OPS-1</t>
+          <t>REGIME-CONDITIONAL-MODELS</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -1320,39 +1320,27 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>ML / Accuracy</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Snapshot cleanup (scripts/cleanup_after_2026_05_16.sh)</t>
+          <t>Regime-conditional ML models (principle 5)</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Pre-Saturday session migration created intermediate snapshot files safe to remove after a week.</t>
+          <t>train separate direction models per regime instead of one spanning all; #1 accuracy lever</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Run scripts/cleanup_after_2026_05_16.sh after 2026-05-16 cutoff.</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>2 min</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>Win: cleaner repo.</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>Calendar reminder for 2026-05-16.</t>
-        </is>
-      </c>
+          <t>ml/train.py regime split</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
       <c r="K15" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1360,19 +1348,15 @@
       </c>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="3" t="inlineStr"/>
-      <c r="N15" s="8" t="inlineStr">
-        <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="60" customHeight="1">
+      <c r="N15" s="8" t="inlineStr"/>
+    </row>
+    <row r="16" ht="45" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>SCHWAB-REAUTH-PENDING</t>
+          <t>OPS-1</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -1382,27 +1366,39 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Ops / Schwab (operational)</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Schwab re-auth to unlock option Greeks</t>
+          <t>Snapshot cleanup (scripts/cleanup_after_2026_05_16.sh)</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>refresh token expired (invalid_grant, 7-day). Run python3 schwab_auth.py oauth -&gt; real option premiums/Greeks flow into the Options calc (currently honest BS-model fallback).</t>
+          <t>Pre-Saturday session migration created intermediate snapshot files safe to remove after a week.</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>user action: schwab_auth.py oauth</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
+          <t>Run scripts/cleanup_after_2026_05_16.sh after 2026-05-16 cutoff.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2 min</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Win: cleaner repo.</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Calendar reminder for 2026-05-16.</t>
+        </is>
+      </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1410,7 +1406,11 @@
       </c>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="3" t="inlineStr"/>
-      <c r="N16" s="8" t="inlineStr"/>
+      <c r="N16" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="60" customHeight="1">
       <c r="A17" s="2" t="n">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>QUANT-5</t>
+          <t>SCHWAB-REAUTH-PENDING</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -1428,39 +1428,27 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Ops / Schwab (operational)</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Mover predictor v3 — NLP earnings tone + options flow features</t>
+          <t>Schwab re-auth to unlock option Greeks</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>v1 had leakage. v2 fixed leakage but AUC stuck at 0.546 — pure technical features at entry don't predict mover success.</t>
+          <t>refresh token expired (invalid_grant, 7-day). Run python3 schwab_auth.py oauth -&gt; real option premiums/Greeks flow into the Options calc (currently honest BS-model fallback).</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Build v3 with NEW feature classes (don't retrain): NLP earnings-call tone embeddings, options-flow IV skew + UOA put/call delta, catalyst-conditional models (subset by tag). A6 logger captures most inputs going forward.</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>days</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>Caveat: exploratory research, not config-tuning.</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>Don't retrain v1/v2 — both definitive AUC 0.546 negative.</t>
-        </is>
-      </c>
+          <t>user action: schwab_auth.py oauth</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
       <c r="K17" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1468,19 +1456,15 @@
       </c>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="3" t="inlineStr"/>
-      <c r="N17" s="8" t="inlineStr">
-        <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="165" customHeight="1">
+      <c r="N17" s="8" t="inlineStr"/>
+    </row>
+    <row r="18" ht="60" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>TV-RATING-CROSS-CHECK</t>
+          <t>QUANT-5</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -1490,37 +1474,37 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Signals / Cross-Check</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Validate (or zero out) the ±3 TV-rating tech-score bonus</t>
+          <t>Mover predictor v3 — NLP earnings tone + options flow features</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>DISCOVERY 2026-05-11: TV-rating ±3 score bonus has been live in analysis.py:8627 for some time, modifying every BUY signal's technical pillar score. NO _validations entry, NO Wilson-CI, NO walk-forward justification for the ±3 magnitude. Worse: tv_rating was never captured on the 689 closed trades in picks_history or 1,301 signal_log entries — retroactive validation is impossible. Violates Principle 1 (n&lt;30 refusal) + Principle 7 (no knob-tweaking without evidence).</t>
+          <t>v1 had leakage. v2 fixed leakage but AUC stuck at 0.546 — pure technical features at entry don't predict mover success.</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 (SHIPPED 2026-05-11): (a) tv_bonus zeroed in analysis.py:8627 — score no longer mutated; (b) tv_recommendation + tv_rec_value + buy/sell/neutral counts now logged per signal in signal_tracker.log_signals() so prospective evidence accumulates; (c) tv_rating still surfaced in tech['details'] as INFORMATIONAL only — no score impact. Phase 2 (PENDING n&gt;=30, est. 6-12 weeks): run Wilson-LB(BUY|TV STRONG_BUY) vs Wilson-LB(BUY) over the prospectively-logged signals. If the agreement-conditional Wilson-LB beats unconditional by a meaningful margin (&gt;=3pp), re-enable with a magnitude justified by the regression. If not, kill the cross-check permanently (Principle 4 falsification — do not retune, do not lower the threshold).</t>
+          <t>Build v3 with NEW feature classes (don't retrain): NLP earnings-call tone embeddings, options-flow IV skew + UOA put/call delta, catalyst-conditional models (subset by tag). A6 logger captures most inputs going forward.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Phase 1: hours (done). Phase 2: hours of analysis + calendar wait for n&gt;=30.</t>
+          <t>days</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Mechanism (Principle 2): TV rating is an independent server-side aggregation of ~26 indicators. Two independent technical aggregations may improve precision over our 5-pillar score alone. Falsification (Principle 4): if agreement-conditional Wilson-LB &lt;= unconditional after n&gt;=30, the cross-check has no edge — kill, don't retune. Risk of CURRENT state (Phase 1): we have been over-weighting TV-STRONG_BUY signals by +3 tech-pts with zero evidence; this could have systematically biased BUY selection. Capping at 0 removes that bias going forward but does not undo past trade selection bias.</t>
+          <t>Caveat: exploratory research, not config-tuning.</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Default apply_to_score=false locked. Validation requires logged tv_rating on &gt;=30 CLOSED BUY trades (currently 0). Earliest Phase-2 validation window: ~6-12 weeks of scans from 2026-05-11. Pairs with the v2 dashboard TV sub-tab (infra/prototype/subtabs/tv/) which is iframe-only today. Do NOT add per-mode / per-regime elaboration until Phase 2 evidence justifies even the basic bonus.</t>
+          <t>Don't retrain v1/v2 — both definitive AUC 0.546 negative.</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
@@ -1532,17 +1516,17 @@
       <c r="M18" s="3" t="inlineStr"/>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t>Phase 1 smoke: run python3 swing_trade.py and confirm (1) tech['details']['tv_rating'] still appears in deep-dive output labeled 'informational — bonus disabled pending validation'; (2) signal_log.json entries for new scans contain tv_recommendation + tv_rec_value + buy/sell/neutral_count populated. Phase 2 trigger: when `python3 -c 'import json; print(sum(1 for r in json.load(open("data/signal_log.json")) if r.get("tv_recommendation") and r.get("result")))'` &gt;= 30, run the agreement-conditional Wilson-LB analysis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="90" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="165" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>TEST-MAE-MFE</t>
+          <t>TV-RATING-CROSS-CHECK</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -1552,27 +1536,39 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Testing / Validation (Tier 1)</t>
+          <t>Signals / Cross-Check</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>MAE / MFE Analyzer — tune stops + targets from data</t>
+          <t>Validate (or zero out) the ±3 TV-rating tech-score bonus</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Maximum Adverse Excursion vs Maximum Favorable Excursion analyzer. signal_log.json already tracks mae_pct + mfe_pct for closed trades. Output: 'Stops triggered at -5% on winners that later hit +20% → stops too tight' or 'Trades exited at +6% target left avg +12% on table → targets too conservative'. Directly improves trade-plan math.</t>
+          <t>DISCOVERY 2026-05-11: TV-rating ±3 score bonus has been live in analysis.py:8627 for some time, modifying every BUY signal's technical pillar score. NO _validations entry, NO Wilson-CI, NO walk-forward justification for the ±3 magnitude. Worse: tv_rating was never captured on the 689 closed trades in picks_history or 1,301 signal_log entries — retroactive validation is impossible. Violates Principle 1 (n&lt;30 refusal) + Principle 7 (no knob-tweaking without evidence).</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Read signal_log.json closed entries; scatter-plot mae vs realized PnL + mfe vs realized PnL; quantile bins (10/25/50/75/90); render as a new Testing tab card. Effort ~30min — data already there.</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="5" t="inlineStr"/>
-      <c r="J19" s="5" t="inlineStr"/>
+          <t>Phase 1 (SHIPPED 2026-05-11): (a) tv_bonus zeroed in analysis.py:8627 — score no longer mutated; (b) tv_recommendation + tv_rec_value + buy/sell/neutral counts now logged per signal in signal_tracker.log_signals() so prospective evidence accumulates; (c) tv_rating still surfaced in tech['details'] as INFORMATIONAL only — no score impact. Phase 2 (PENDING n&gt;=30, est. 6-12 weeks): run Wilson-LB(BUY|TV STRONG_BUY) vs Wilson-LB(BUY) over the prospectively-logged signals. If the agreement-conditional Wilson-LB beats unconditional by a meaningful margin (&gt;=3pp), re-enable with a magnitude justified by the regression. If not, kill the cross-check permanently (Principle 4 falsification — do not retune, do not lower the threshold).</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1: hours (done). Phase 2: hours of analysis + calendar wait for n&gt;=30.</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Mechanism (Principle 2): TV rating is an independent server-side aggregation of ~26 indicators. Two independent technical aggregations may improve precision over our 5-pillar score alone. Falsification (Principle 4): if agreement-conditional Wilson-LB &lt;= unconditional after n&gt;=30, the cross-check has no edge — kill, don't retune. Risk of CURRENT state (Phase 1): we have been over-weighting TV-STRONG_BUY signals by +3 tech-pts with zero evidence; this could have systematically biased BUY selection. Capping at 0 removes that bias going forward but does not undo past trade selection bias.</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Default apply_to_score=false locked. Validation requires logged tv_rating on &gt;=30 CLOSED BUY trades (currently 0). Earliest Phase-2 validation window: ~6-12 weeks of scans from 2026-05-11. Pairs with the v2 dashboard TV sub-tab (infra/prototype/subtabs/tv/) which is iframe-only today. Do NOT add per-mode / per-regime elaboration until Phase 2 evidence justifies even the basic bonus.</t>
+        </is>
+      </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1580,7 +1576,11 @@
       </c>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="3" t="inlineStr"/>
-      <c r="N19" s="8" t="inlineStr"/>
+      <c r="N19" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1 smoke: run python3 swing_trade.py and confirm (1) tech['details']['tv_rating'] still appears in deep-dive output labeled 'informational — bonus disabled pending validation'; (2) signal_log.json entries for new scans contain tv_recommendation + tv_rec_value + buy/sell/neutral_count populated. Phase 2 trigger: when `python3 -c 'import json; print(sum(1 for r in json.load(open("data/signal_log.json")) if r.get("tv_recommendation") and r.get("result")))'` &gt;= 30, run the agreement-conditional Wilson-LB analysis.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="90" customHeight="1">
       <c r="A20" s="2" t="n">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>TEST-MC-BOOTSTRAP</t>
+          <t>TEST-MAE-MFE</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -1603,17 +1603,17 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Monte Carlo Bootstrap — confidence intervals on Sharpe/PF/WR</t>
+          <t>MAE / MFE Analyzer — tune stops + targets from data</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Randomly resample closed trades 10,000x to build distributions over each metric. Wilson LB only covers WR; this covers Sharpe, Sortino, PF, max-DD, hit-rate, payoff ratio. Output: 'Sharpe 1.42, 95% CI [0.88, 1.94]' — you would know whether 1.42 is robust or noise. Standard hedge-fund metric, supports principle #1 (statistical rigor).</t>
+          <t>Maximum Adverse Excursion vs Maximum Favorable Excursion analyzer. signal_log.json already tracks mae_pct + mfe_pct for closed trades. Output: 'Stops triggered at -5% on winners that later hit +20% → stops too tight' or 'Trades exited at +6% target left avg +12% on table → targets too conservative'. Directly improves trade-plan math.</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Numpy bootstrap on signal_log trade PnL array, k=10000 resamples; compute distributions over each metric; render percentile bands. Effort 1-2hr.</t>
+          <t>Read signal_log.json closed entries; scatter-plot mae vs realized PnL + mfe vs realized PnL; quantile bins (10/25/50/75/90); render as a new Testing tab card. Effort ~30min — data already there.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>TEST-PERMUTATION</t>
+          <t>TEST-MC-BOOTSTRAP</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -1649,17 +1649,17 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Permutation Test — is the edge REAL or coin flip?</t>
+          <t>Monte Carlo Bootstrap — confidence intervals on Sharpe/PF/WR</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Randomly shuffle BUY/SELL/AVOID labels on historical signals 1000x, recompute strategy returns. If real returns are not significantly better than scrambled returns, there is no edge. Direct test of principle #4 (adversarial mindset / falsification). Output: 'Real strategy: +18.7%. Random labels (1000 sims): +0.2% +/- 4.1%. p-value: 0.0001'.</t>
+          <t>Randomly resample closed trades 10,000x to build distributions over each metric. Wilson LB only covers WR; this covers Sharpe, Sortino, PF, max-DD, hit-rate, payoff ratio. Output: 'Sharpe 1.42, 95% CI [0.88, 1.94]' — you would know whether 1.42 is robust or noise. Standard hedge-fund metric, supports principle #1 (statistical rigor).</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Shuffle decision-column of signal_log 1000x; recompute portfolio return per shuffle; rank real return vs null distribution; report p-value. Effort ~1hr.</t>
+          <t>Numpy bootstrap on signal_log trade PnL array, k=10000 resamples; compute distributions over each metric; render percentile bands. Effort 1-2hr.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>TEST-REGIME-COND</t>
+          <t>TEST-PERMUTATION</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Regime-Conditional Performance — where does it work?</t>
+          <t>Permutation Test — is the edge REAL or coin flip?</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Partition closed trades by regime (risk_on_trending / choppy / risk_off / panic) and compute WR / PF / Sharpe per regime. Per principle #5 (regime conditioning over averages). Example output: 'Trend Continuation WR: 41% overall · 62% in risk_on_trending · 18% in choppy'. Tells you which sleeves to size up/down per regime.</t>
+          <t>Randomly shuffle BUY/SELL/AVOID labels on historical signals 1000x, recompute strategy returns. If real returns are not significantly better than scrambled returns, there is no edge. Direct test of principle #4 (adversarial mindset / falsification). Output: 'Real strategy: +18.7%. Random labels (1000 sims): +0.2% +/- 4.1%. p-value: 0.0001'.</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Group signal_log entries by regime_at_signal (already logged); compute Wilson LB on WR + bootstrapped PF/Sharpe per regime; output a (setup x regime) heatmap. Effort ~1hr.</t>
+          <t>Shuffle decision-column of signal_log 1000x; recompute portfolio return per shuffle; rank real return vs null distribution; report p-value. Effort ~1hr.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
@@ -1720,38 +1720,38 @@
       <c r="M22" s="3" t="inlineStr"/>
       <c r="N22" s="8" t="inlineStr"/>
     </row>
-    <row r="23" ht="60" customHeight="1">
+    <row r="23" ht="90" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>PARITY-BACKTEST-UI</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TEST-REGIME-COND</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Backtesting / Platform Parity</t>
+          <t>Testing / Validation (Tier 1)</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>In-app Backtesting UI</t>
+          <t>Regime-Conditional Performance — where does it work?</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Expose backtest.py + walk_forward_v2.py inside the kairos UI — a user picks a strategy/date range/universe and runs it without dropping to the terminal.</t>
+          <t>Partition closed trades by regime (risk_on_trending / choppy / risk_off / panic) and compute WR / PF / Sharpe per regime. Per principle #5 (regime conditioning over averages). Example output: 'Trend Continuation WR: 41% overall · 62% in risk_on_trending · 18% in choppy'. Tells you which sleeves to size up/down per regime.</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Add a 'Backtest' workspace in the kairos sidebar; wire a form to a /v2/backtest endpoint that shells out to backtest.py and streams stdout via SSE; render Sharpe / PF / Wilson-LB / equity curve when the run completes.</t>
+          <t>Group signal_log entries by regime_at_signal (already logged); compute Wilson LB on WR + bootstrapped PF/Sharpe per regime; output a (setup x regime) heatmap. Effort ~1hr.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>BUG-MISSING-D1S</t>
+          <t>PARITY-BACKTEST-UI</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
@@ -1782,22 +1782,22 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Bugs / Audit Ledger</t>
+          <t>Backtesting / Platform Parity</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>4 missing D1s for May 15 (out of 87)</t>
+          <t>In-app Backtesting UI</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>4 of 87 May-15 picks have null D1 (next-day close). Probably thin EODHD coverage on small-caps — acceptable noise band but worth confirming.</t>
+          <t>Expose backtest.py + walk_forward_v2.py inside the kairos UI — a user picks a strategy/date range/universe and runs it without dropping to the terminal.</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Identify the 4 tickers; check EODHD eod() response for each on 2026-05-16; if EODHD returned null, document as known-limitation; if EODHD returned a value, fix the ingest. Effort ~20min.</t>
+          <t>Add a 'Backtest' workspace in the kairos sidebar; wire a form to a /v2/backtest endpoint that shells out to backtest.py and streams stdout via SSE; render Sharpe / PF / Wilson-LB / equity curve when the run completes.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>PARITY-CHANNEL-BAR</t>
+          <t>BUG-MISSING-D1S</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -1828,22 +1828,22 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Chart Indicators / Platform Parity</t>
+          <t>Bugs / Audit Ledger</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Channel Bar overlay</t>
+          <t>4 missing D1s for May 15 (out of 87)</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Donchian / Keltner / Bollinger envelope overlay on the chart — top + bottom band with mid-line.</t>
+          <t>4 of 87 May-15 picks have null D1 (next-day close). Probably thin EODHD coverage on small-caps — acceptable noise band but worth confirming.</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Compute channels via pandas-ta in feature_extractor.py (or live in chart.js using bar data); render as semi-transparent band; toggle in the Chart sub-tab control bar.</t>
+          <t>Identify the 4 tickers; check EODHD eod() response for each on 2026-05-16; if EODHD returned null, document as known-limitation; if EODHD returned a value, fix the ingest. Effort ~20min.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>PARITY-RBI-GBI-WINDOW</t>
+          <t>PARITY-CHANNEL-BAR</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -1879,17 +1879,17 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>RBI/GBI Window (regime bias bands)</t>
+          <t>Channel Bar overlay</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Color-coded vertical bands on the chart timeline showing risk-on (green/GBI) vs risk-off (red/RBI) regime windows so the user can see at-a-glance whether prior price action happened in a hostile or friendly regime.</t>
+          <t>Donchian / Keltner / Bollinger envelope overlay on the chart — top + bottom band with mid-line.</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Read cache/regime_history.json and draw vertical color bands at each regime transition on the chart canvas; tooltip explains the regime classification (4-regime model: risk_on_trending / risk_on_choppy / risk_off_trending / panic).</t>
+          <t>Compute channels via pandas-ta in feature_extractor.py (or live in chart.js using bar data); render as semi-transparent band; toggle in the Chart sub-tab control bar.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
@@ -1904,13 +1904,13 @@
       <c r="M26" s="3" t="inlineStr"/>
       <c r="N26" s="8" t="inlineStr"/>
     </row>
-    <row r="27" ht="45" customHeight="1">
+    <row r="27" ht="60" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-HOT-SECTORS-DEAD</t>
+          <t>PARITY-RBI-GBI-WINDOW</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -1920,22 +1920,22 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup</t>
+          <t>Chart Indicators / Platform Parity</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>panelHotSectors() dead-code in kairos.html</t>
+          <t>RBI/GBI Window (regime bias bands)</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Hot Sectors panel was removed from the Signal Scanner grid but the panelHotSectors() function is still defined in kairos.html — dead code.</t>
+          <t>Color-coded vertical bands on the chart timeline showing risk-on (green/GBI) vs risk-off (red/RBI) regime windows so the user can see at-a-glance whether prior price action happened in a hostile or friendly regime.</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>grep for panelHotSectors callers; delete function + any unused helpers; verify no console errors. Effort ~2min.</t>
+          <t>Read cache/regime_history.json and draw vertical color bands at each regime transition on the chart canvas; tooltip explains the regime classification (4-regime model: risk_on_trending / risk_on_choppy / risk_off_trending / panic).</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr"/>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-4</t>
+          <t>CLEAN-HOT-SECTORS-DEAD</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -1966,39 +1966,27 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Code Cleanup</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>scripts/migrate_role_capabilities.py — cleanup after 2026-05-16</t>
+          <t>panelHotSectors() dead-code in kairos.html</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>One-shot CapStudio backfill. Already run. Tied to OPS-1 cleanup window.</t>
+          <t>Hot Sectors panel was removed from the Signal Scanner grid but the panelHotSectors() function is still defined in kairos.html — dead code.</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Delete during OPS-1 cleanup pass after 2026-05-16.</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>1 min</t>
-        </is>
-      </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>Win: -X lines.</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>Couples with OPS-1.</t>
-        </is>
-      </c>
+          <t>grep for panelHotSectors callers; delete function + any unused helpers; verify no console errors. Effort ~2min.</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
       <c r="K28" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -2006,19 +1994,15 @@
       </c>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="3" t="inlineStr"/>
-      <c r="N28" s="8" t="inlineStr">
-        <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="60" customHeight="1">
+      <c r="N28" s="8" t="inlineStr"/>
+    </row>
+    <row r="29" ht="45" customHeight="1">
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-EARNINGS-CAL-PIT</t>
+          <t>CLEAN-4</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -2028,27 +2012,39 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Data / Calendars (future)</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>earnings_calendar_pit — point-in-time integrity</t>
+          <t>scripts/migrate_role_capabilities.py — cleanup after 2026-05-16</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Earnings calendar with point-in-time integrity (what was expected when). Needed for clean PEAD backtest replay; today's calendar uses the most-recent snapshot only, which leaks future revisions into prior dates.</t>
+          <t>One-shot CapStudio backfill. Already run. Tied to OPS-1 cleanup window.</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Snapshot the EODHD earnings calendar daily into a versioned earnings_calendar_history table; join on (ticker, report_date, snapshot_date) for PIT correctness in PEAD backtests.</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
+          <t>Delete during OPS-1 cleanup pass after 2026-05-16.</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>1 min</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Win: -X lines.</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>Couples with OPS-1.</t>
+        </is>
+      </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -2056,15 +2052,19 @@
       </c>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="3" t="inlineStr"/>
-      <c r="N29" s="8" t="inlineStr"/>
-    </row>
-    <row r="30" ht="45" customHeight="1">
+      <c r="N29" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-ECONOMIC-CAL</t>
+          <t>DATA-FUTURE-EARNINGS-CAL-PIT</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -2079,17 +2079,17 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>economic_calendar — CPI/PCE/NFP/FOMC dates</t>
+          <t>earnings_calendar_pit — point-in-time integrity</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Macro event calendar with consensus expectations. No source wired today; the pre-FOMC sleeve uses hard-coded FOMC dates and there is no CPI/PCE/NFP awareness.</t>
+          <t>Earnings calendar with point-in-time integrity (what was expected when). Needed for clean PEAD backtest replay; today's calendar uses the most-recent snapshot only, which leaks future revisions into prior dates.</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Investing.com calendar scrape OR Trading Economics free tier; daily refresh; write to economic_calendar; feed pre-FOMC sleeve + risk_off blackout windows.</t>
+          <t>Snapshot the EODHD earnings calendar daily into a versioned earnings_calendar_history table; join on (ticker, report_date, snapshot_date) for PIT correctness in PEAD backtests.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-FDA-CAL</t>
+          <t>DATA-FUTURE-ECONOMIC-CAL</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -2125,17 +2125,17 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>fda_calendar — PDUFA / AdCom dates</t>
+          <t>economic_calendar — CPI/PCE/NFP/FOMC dates</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>FDA decision calendar (PDUFA dates, Advisory Committee meetings) for biotech catalyst tracking.</t>
+          <t>Macro event calendar with consensus expectations. No source wired today; the pre-FOMC sleeve uses hard-coded FOMC dates and there is no CPI/PCE/NFP awareness.</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>FDA public calendar scrape + BiopharmCatalyst free RSS; write to fda_calendar; surface as catalyst tier in any biotech sleeve.</t>
+          <t>Investing.com calendar scrape OR Trading Economics free tier; daily refresh; write to economic_calendar; feed pre-FOMC sleeve + risk_off blackout windows.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>DATA-EMPTY-SPLITS-CALENDAR</t>
+          <t>DATA-FUTURE-FDA-CAL</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -2166,22 +2166,22 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Data / Corporate Actions (empty by sample)</t>
+          <t>Data / Calendars (future)</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>splits_calendar — 0 splits in current universe sample</t>
+          <t>fda_calendar — PDUFA / AdCom dates</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>corporate_actions table populates from EODHD but the current universe sample (449 tickers) had 0 splits in the recent window. Calendar reads empty.</t>
+          <t>FDA decision calendar (PDUFA dates, Advisory Committee meetings) for biotech catalyst tracking.</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Expand corporate-actions polling universe to S&amp;P 500 + Russell 1000 (universe list already available); 1-line change in the populator script.</t>
+          <t>FDA public calendar scrape + BiopharmCatalyst free RSS; write to fda_calendar; surface as catalyst tier in any biotech sleeve.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>DATA-EMPTY-MODEL-CALIBRATION</t>
+          <t>DATA-EMPTY-SPLITS-CALENDAR</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
@@ -2212,22 +2212,22 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Data / ML (empty by design)</t>
+          <t>Data / Corporate Actions (empty by sample)</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>model_calibration — waiting on realization</t>
+          <t>splits_calendar — 0 splits in current universe sample</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Calibration metrics table has no rows because the 5-20 day prediction horizons have not elapsed yet (today's predictions realize over 1-4 weeks).</t>
+          <t>corporate_actions table populates from EODHD but the current universe sample (449 tickers) had 0 splits in the recent window. Calendar reads empty.</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>No code action; populates passively as time passes. Re-check after 2026-06-15 (30d post-shipping).</t>
+          <t>Expand corporate-actions polling universe to S&amp;P 500 + Russell 1000 (universe list already available); 1-line change in the populator script.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr"/>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>DATA-EMPTY-VAR-BREACHES</t>
+          <t>DATA-EMPTY-MODEL-CALIBRATION</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
@@ -2258,22 +2258,22 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Data / Risk (empty by design)</t>
+          <t>Data / ML (empty by design)</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>var_breaches — waiting on snapshots + drawdown</t>
+          <t>model_calibration — waiting on realization</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>VaR breach log empty because (1) daily portfolio_risk snapshots are still ramping up and (2) no real drawdown day has happened to trigger a breach.</t>
+          <t>Calibration metrics table has no rows because the 5-20 day prediction horizons have not elapsed yet (today's predictions realize over 1-4 weeks).</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>No code action; populates passively. Re-check after first portfolio drawdown &gt;2% or after 60 daily snapshots.</t>
+          <t>No code action; populates passively as time passes. Re-check after 2026-06-15 (30d post-shipping).</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
@@ -2288,13 +2288,13 @@
       <c r="M34" s="3" t="inlineStr"/>
       <c r="N34" s="8" t="inlineStr"/>
     </row>
-    <row r="35" ht="60" customHeight="1">
+    <row r="35" ht="45" customHeight="1">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-INSIDER-EDGAR</t>
+          <t>DATA-EMPTY-VAR-BREACHES</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
@@ -2304,22 +2304,22 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Data / SEC EDGAR (future)</t>
+          <t>Data / Risk (empty by design)</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>insider_transactions via Form 4 XBRL</t>
+          <t>var_breaches — waiting on snapshots + drawdown</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Per-ticker insider buy/sell stream sourced direct from SEC Form 4 filings. Today sourced indirectly via Finviz Elite bulk; direct EDGAR is point-in-time accurate and free.</t>
+          <t>VaR breach log empty because (1) daily portfolio_risk snapshots are still ramping up and (2) no real drawdown day has happened to trigger a breach.</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Build Form 4 XBRL parser; daily ingest from efts.sec.gov; write to insider_transactions table; reconcile against Finviz bulk for cross-check.</t>
+          <t>No code action; populates passively. Re-check after first portfolio drawdown &gt;2% or after 60 daily snapshots.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
@@ -2334,13 +2334,13 @@
       <c r="M35" s="3" t="inlineStr"/>
       <c r="N35" s="8" t="inlineStr"/>
     </row>
-    <row r="36" ht="45" customHeight="1">
+    <row r="36" ht="60" customHeight="1">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-INSTITUTIONAL-EDGAR</t>
+          <t>DATA-FUTURE-INSIDER-EDGAR</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
@@ -2355,17 +2355,17 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>institutional_holdings via 13F XBRL</t>
+          <t>insider_transactions via Form 4 XBRL</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Per-ticker institutional ownership tracking (Form 13F, quarterly). Useful for the Smart Money pillar; today only Finviz inst_own_pct snapshot.</t>
+          <t>Per-ticker insider buy/sell stream sourced direct from SEC Form 4 filings. Today sourced indirectly via Finviz Elite bulk; direct EDGAR is point-in-time accurate and free.</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>13F XBRL parser; quarterly ingest from EDGAR; write to institutional_holdings table with the 45-day reporting lag accounted for in any backtest joins.</t>
+          <t>Build Form 4 XBRL parser; daily ingest from efts.sec.gov; write to insider_transactions table; reconcile against Finviz bulk for cross-check.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-CONGRESSIONAL-EDGAR</t>
+          <t>DATA-FUTURE-INSTITUTIONAL-EDGAR</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
@@ -2396,22 +2396,22 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Data / SEC EDGAR (future, alt for broken)</t>
+          <t>Data / SEC EDGAR (future)</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>congressional_trades via EDGAR / House Clerk (alt source)</t>
+          <t>institutional_holdings via 13F XBRL</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Alternate sourcing for congressional trades after Senate Stock Watcher death (see DATA-BROKEN-CONGRESSIONAL-TRADES). Direct from House Clerk + Senate eFD.</t>
+          <t>Per-ticker institutional ownership tracking (Form 13F, quarterly). Useful for the Smart Money pillar; today only Finviz inst_own_pct snapshot.</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Scrape House STOCK Act PTR PDFs (House Clerk site); Senate eFD JSON; merge into normalized congressional_trades table.</t>
+          <t>13F XBRL parser; quarterly ingest from EDGAR; write to institutional_holdings table with the 45-day reporting lag accounted for in any backtest joins.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>SUPABASE-SYNC-VERIFY</t>
+          <t>DATA-FUTURE-CONGRESSIONAL-EDGAR</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
@@ -2442,22 +2442,22 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Data / Supabase</t>
+          <t>Data / SEC EDGAR (future, alt for broken)</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Verify supabase_analysis_sync actually writes</t>
+          <t>congressional_trades via EDGAR / House Clerk (alt source)</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>confirm sync_scan writes (psycopg2 raw SQL not .table API); not silent no-op</t>
+          <t>Alternate sourcing for congressional trades after Senate Stock Watcher death (see DATA-BROKEN-CONGRESSIONAL-TRADES). Direct from House Clerk + Senate eFD.</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>supabase_analysis_sync.py</t>
+          <t>Scrape House STOCK Act PTR PDFs (House Clerk site); Senate eFD JSON; merge into normalized congressional_trades table.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
@@ -2472,13 +2472,13 @@
       <c r="M38" s="3" t="inlineStr"/>
       <c r="N38" s="8" t="inlineStr"/>
     </row>
-    <row r="39" ht="60" customHeight="1">
+    <row r="39" ht="45" customHeight="1">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>DATA-EMPTY-PROD-ENGINE-DEFERRED</t>
+          <t>SUPABASE-SYNC-VERIFY</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
@@ -2488,22 +2488,22 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Data / Telemetry (deferred for safety)</t>
+          <t>Data / Supabase</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>8 empty slots — production-engine touches deferred</t>
+          <t>Verify supabase_analysis_sync actually writes</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>8 telemetry/data slots remain empty because populating them requires editing backtest.py / executor.py / signal_filter.py / analysis.py. Deliberately deferred to avoid risk to the live scan + exec paths.</t>
+          <t>confirm sync_scan writes (psycopg2 raw SQL not .table API); not silent no-op</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Enumerate the 8 specifically and grade each one for in-place vs side-car instrumentation. Side-car (write to telemetry DB without changing decision flow) is preferred over hot-path edits.</t>
+          <t>supabase_analysis_sync.py</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr"/>
@@ -2518,13 +2518,13 @@
       <c r="M39" s="3" t="inlineStr"/>
       <c r="N39" s="8" t="inlineStr"/>
     </row>
-    <row r="40" ht="45" customHeight="1">
+    <row r="40" ht="60" customHeight="1">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>BARSTORE-4</t>
+          <t>DATA-EMPTY-PROD-ENGINE-DEFERRED</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
@@ -2534,22 +2534,22 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Data Infra / Bar-Store</t>
+          <t>Data / Telemetry (deferred for safety)</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Daily incremental via bulk_eod</t>
+          <t>8 empty slots — production-engine touches deferred</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>After backfill, only the latest bar is needed daily; bulk_eod returns the whole exchange in 1 call.</t>
+          <t>8 telemetry/data slots remain empty because populating them requires editing backtest.py / executor.py / signal_filter.py / analysis.py. Deliberately deferred to avoid risk to the live scan + exec paths.</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Daily launchd job: 1 bulk_eod(exchange) appends last-day bar for all tickers into daily_bars. Target &lt;=2 EODHD calls/day total for OHLCV.</t>
+          <t>Enumerate the 8 specifically and grade each one for in-place vs side-car instrumentation. Side-car (write to telemetry DB without changing decision flow) is preferred over hot-path edits.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>BARSTORE-5</t>
+          <t>BARSTORE-4</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
@@ -2585,17 +2585,17 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Corporate-action re-adjustment</t>
+          <t>Daily incremental via bulk_eod</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Stored history must stay split/div-adjusted; a new split re-bases all prior bars. This is where data-integrity bugs hide.</t>
+          <t>After backfill, only the latest bar is needed daily; bulk_eod returns the whole exchange in 1 call.</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Store raw + adjusted_close; small daily job re-adjusts history on split/div events (EODHD div/splits endpoints). Validate no adjustment drift.</t>
+          <t>Daily launchd job: 1 bulk_eod(exchange) appends last-day bar for all tickers into daily_bars. Target &lt;=2 EODHD calls/day total for OHLCV.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
@@ -2610,13 +2610,13 @@
       <c r="M41" s="3" t="inlineStr"/>
       <c r="N41" s="8" t="inlineStr"/>
     </row>
-    <row r="42" ht="60" customHeight="1">
+    <row r="42" ht="45" customHeight="1">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>BARSTORE-6</t>
+          <t>BARSTORE-5</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
@@ -2631,17 +2631,17 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Delisted backfill -&gt; survivorship fix</t>
+          <t>Corporate-action re-adjustment</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Honest backtests need delisted tickers' history + point-in-time membership (membership snapshots already DONE via AIPRED-SURVIVORSHIP). Unblocks audit #1.</t>
+          <t>Stored history must stay split/div-adjusted; a new split re-bases all prior bars. This is where data-integrity bugs hide.</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>Backfill delisted-ticker history into daily_bars; point walk_forward_v2 at DB over 20yr. Enables survivorship-bias-free backtests + free validation of staged accuracy tweaks.</t>
+          <t>Store raw + adjusted_close; small daily job re-adjusts history on split/div events (EODHD div/splits endpoints). Validate no adjustment drift.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>EODHD-WIRES-VALIDATE</t>
+          <t>BARSTORE-6</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
@@ -2672,22 +2672,22 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Data Wiring (validate)</t>
+          <t>Data Infra / Bar-Store</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Validate EODHD-side wires on quota reset</t>
+          <t>Delisted backfill -&gt; survivorship fix</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>DCF net-debt/FCF + per-name beta + Book Risk crowding are code-complete + fallback-safe but untested against live EODHD (quota was exhausted). Confirm real values flow after reset.</t>
+          <t>Honest backtests need delisted tickers' history + point-in-time membership (membership snapshots already DONE via AIPRED-SURVIVORSHIP). Unblocks audit #1.</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Stocksmith.html /api/fundamentals consumers</t>
+          <t>Backfill delisted-ticker history into daily_bars; point walk_forward_v2 at DB over 20yr. Enables survivorship-bias-free backtests + free validation of staged accuracy tweaks.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
@@ -2702,13 +2702,13 @@
       <c r="M43" s="3" t="inlineStr"/>
       <c r="N43" s="8" t="inlineStr"/>
     </row>
-    <row r="44" ht="75" customHeight="1">
+    <row r="44" ht="60" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>OVERVIEW-VERDICT-RECON</t>
+          <t>EODHD-WIRES-VALIDATE</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
@@ -2718,22 +2718,22 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Decision Engine</t>
+          <t>Data Wiring (validate)</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Reconcile compute_final_verdict (stage) vs decisions_by_mode</t>
+          <t>Validate EODHD-side wires on quota reset</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Two engines emit different swing score+verdict for the same name (FTNT: stage=BUY/67 vs decisions_by_mode.swing=WATCH/57). decisions_by_mode omits the catalyst-sleeve EXTENDED-entry relaxation that compute_final_verdict applies, so they disagree.</t>
+          <t>DCF net-debt/FCF + per-name beta + Book Risk crowding are code-complete + fallback-safe but untested against live EODHD (quota was exhausted). Confirm real values flow after reset.</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>Have decisions_by_mode consume the same relaxation OR emit a diverges-from-composite flag; decide direction after the entry-quality EXTENDED/MISSED A/B validation lands. Display already fixed (overview.js binds stage).</t>
+          <t>Stocksmith.html /api/fundamentals consumers</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-TRAFFIC-LIGHT-INPUTS</t>
+          <t>OVERVIEW-VERDICT-RECON</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
@@ -2764,22 +2764,22 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Detail Lens / Traffic Lights</t>
+          <t>Decision Engine</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Per-ticker risk/fundamentals inputs for lens dots</t>
+          <t>Reconcile compute_final_verdict (stage) vs decisions_by_mode</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Wire t.f_score · t.altman_z · t.roic · t.wacc · t.sharpe_1y · t.dd_recovery_months · t.peer_rank · t.is_held into build_data.py. _qdComputeLensStatus has cascading fallbacks (PEG → fund_score → F-score; beta → kelly → Sharpe), so dots upgrade automatically as fields land.</t>
+          <t>Two engines emit different swing score+verdict for the same name (FTNT: stage=BUY/67 vs decisions_by_mode.swing=WATCH/57). decisions_by_mode omits the catalyst-sleeve EXTENDED-entry relaxation that compute_final_verdict applies, so they disagree.</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Compute in analysis.py / portfolio.py: Piotroski F (existing data), Altman Z (existing data), ROIC vs WACC, 1y Sharpe from price history, peer_rank from cohort, is_held from portfolio_state.json.</t>
+          <t>Have decisions_by_mode consume the same relaxation OR emit a diverges-from-composite flag; decide direction after the entry-quality EXTENDED/MISSED A/B validation lands. Display already fixed (overview.js binds stage).</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
@@ -2794,13 +2794,13 @@
       <c r="M45" s="3" t="inlineStr"/>
       <c r="N45" s="8" t="inlineStr"/>
     </row>
-    <row r="46" ht="60" customHeight="1">
+    <row r="46" ht="75" customHeight="1">
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-COHORT-SYMPATHY</t>
+          <t>KAIROS-TRAFFIC-LIGHT-INPUTS</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -2810,22 +2810,22 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Earnings Lens / Cohort</t>
+          <t>Detail Lens / Traffic Lights</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Peer cohort sympathy correlations</t>
+          <t>Per-ticker risk/fundamentals inputs for lens dots</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Wire t.cohort_peers[].er_sympathy_corr + er_sympathy_move_1d + t.sympathy_history in build_data.py. Today: renderEarnings_Sympathy shows scaffold rows from t.cohort_peers if populated, else placeholder.</t>
+          <t>Wire t.f_score · t.altman_z · t.roic · t.wacc · t.sharpe_1y · t.dd_recovery_months · t.peer_rank · t.is_held into build_data.py. _qdComputeLensStatus has cascading fallbacks (PEG → fund_score → F-score; beta → kelly → Sharpe), so dots upgrade automatically as fields land.</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Compute 8-quarter rolling correlation of 1d post-print move between this name and each cohort peer's ER date. Persist to data.json under t.cohort_peers + t.sympathy_history.</t>
+          <t>Compute in analysis.py / portfolio.py: Piotroski F (existing data), Altman Z (existing data), ROIC vs WACC, 1y Sharpe from price history, peer_rank from cohort, is_held from portfolio_state.json.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
@@ -2840,13 +2840,13 @@
       <c r="M46" s="3" t="inlineStr"/>
       <c r="N46" s="8" t="inlineStr"/>
     </row>
-    <row r="47" ht="75" customHeight="1">
+    <row r="47" ht="60" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>PARITY-IN-APP-TRADING</t>
+          <t>KAIROS-COHORT-SYMPATHY</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
@@ -2856,22 +2856,22 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Execution / Live / Platform Parity</t>
+          <t>Earnings Lens / Cohort</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>In-app Trading (broker-integrated live execution)</t>
+          <t>Peer cohort sympathy correlations</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>One-click BUY/SELL from the dashboard to a live Schwab/Alpaca brokerage account.</t>
+          <t>Wire t.cohort_peers[].er_sympathy_corr + er_sympathy_move_1d + t.sympathy_history in build_data.py. Today: renderEarnings_Sympathy shows scaffold rows from t.cohort_peers if populated, else placeholder.</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>OAuth-link the Schwab API (already paid stack); surface an 'Execute' button on the Trade Plan card; explicit AUTHORIZE LIVE TRADING gate per CLAUDE.md security protocol; route every order through the existing risk checks (max-loss-pct, drawdown haircut, regime gate).</t>
+          <t>Compute 8-quarter rolling correlation of 1d post-print move between this name and each cohort peer's ER date. Persist to data.json under t.cohort_peers + t.sympathy_history.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-LIVE-D1</t>
+          <t>PARITY-IN-APP-TRADING</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
@@ -2902,22 +2902,22 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Kairos / Audit Ledger</t>
+          <t>Execution / Live / Platform Parity</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Live D1 estimate from Schwab quote during RTH</t>
+          <t>In-app Trading (broker-integrated live execution)</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Replace placeholder D1 (yesterday's close-to-close) with a live Schwab-quote-based intraday estimate during market hours so the audit ledger D1 column is non-stale. Discussed and deferred as semantically muddy (D1 = next-day close, intraday quote is a forecast not a fill).</t>
+          <t>One-click BUY/SELL from the dashboard to a live Schwab/Alpaca brokerage account.</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>Add a SCHWAB_LIVE_D1=1 env flag; when ON and during RTH, compute D1_est = (live_quote - signal_entry) / signal_entry and annotate the cell with an 'est' chip. Effort ~1hr.</t>
+          <t>OAuth-link the Schwab API (already paid stack); surface an 'Execute' button on the Trade Plan card; explicit AUTHORIZE LIVE TRADING gate per CLAUDE.md security protocol; route every order through the existing risk checks (max-loss-pct, drawdown haircut, regime gate).</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
@@ -2932,13 +2932,13 @@
       <c r="M48" s="3" t="inlineStr"/>
       <c r="N48" s="8" t="inlineStr"/>
     </row>
-    <row r="49" ht="45" customHeight="1">
+    <row r="49" ht="75" customHeight="1">
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-SCANNER-BEARS</t>
+          <t>KAIROS-LIVE-D1</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
@@ -2948,22 +2948,22 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Kairos / Signal Scanner</t>
+          <t>Kairos / Audit Ledger</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Top 5 Bears panel</t>
+          <t>Live D1 estimate from Schwab quote during RTH</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Add a 'Top 5 Bears' panel to the Signal Scanner alongside Fresh / Momentum / Earnings / Volume — was proposed but not selected in the initial build.</t>
+          <t>Replace placeholder D1 (yesterday's close-to-close) with a live Schwab-quote-based intraday estimate during market hours so the audit ledger D1 column is non-stale. Discussed and deferred as semantically muddy (D1 = next-day close, intraday quote is a forecast not a fill).</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Mirror existing 4 panels' structure; sort universe by composite bear-score desc; cap at 5; render in the Scanner grid. Effort ~10min.</t>
+          <t>Add a SCHWAB_LIVE_D1=1 env flag; when ON and during RTH, compute D1_est = (live_quote - signal_entry) / signal_entry and annotate the cell with an 'est' chip. Effort ~1hr.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
@@ -2978,13 +2978,13 @@
       <c r="M49" s="3" t="inlineStr"/>
       <c r="N49" s="8" t="inlineStr"/>
     </row>
-    <row r="50" ht="60" customHeight="1">
+    <row r="50" ht="45" customHeight="1">
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-SCANNER-FLIPS</t>
+          <t>KAIROS-SCANNER-BEARS</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
@@ -2999,17 +2999,17 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Today's Flips panel</t>
+          <t>Top 5 Bears panel</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Add a 'Today's Flips' panel to the Signal Scanner — tickers whose verdict flipped vs yesterday (e.g., BUY -&gt; WATCH, WATCH -&gt; BUY, AVOID -&gt; WATCH). Proposed in the 'what else' menu, not selected.</t>
+          <t>Add a 'Top 5 Bears' panel to the Signal Scanner alongside Fresh / Momentum / Earnings / Volume — was proposed but not selected in the initial build.</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>Diff today's bundle.verdict against yesterday.verdict per ticker; surface the 5-10 most material flips. Effort ~30min.</t>
+          <t>Mirror existing 4 panels' structure; sort universe by composite bear-score desc; cap at 5; render in the Scanner grid. Effort ~10min.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>ML-RETRAIN-FINBERT-FEATURE</t>
+          <t>KAIROS-SCANNER-FLIPS</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
@@ -3040,22 +3040,22 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>ML / Features (future)</t>
+          <t>Kairos / Signal Scanner</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Add FinBERT as a GBM training feature (leak-free)</t>
+          <t>Today's Flips panel</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>needs historical sentiment series — accumulate forward via cache/ml/sentiment_log.jsonl (asof-stamped); add as feature #18 + retrain once ~3-6mo of leak-free history exists</t>
+          <t>Add a 'Today's Flips' panel to the Signal Scanner — tickers whose verdict flipped vs yesterday (e.g., BUY -&gt; WATCH, WATCH -&gt; BUY, AVOID -&gt; WATCH). Proposed in the 'what else' menu, not selected.</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>ml/feature_extractor + historical backfill</t>
+          <t>Diff today's bundle.verdict against yesterday.verdict per ticker; surface the 5-10 most material flips. Effort ~30min.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>ML-AUTOREFRESH-VALIDATE</t>
+          <t>ML-RETRAIN-FINBERT-FEATURE</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
@@ -3086,22 +3086,22 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>ML / Pipeline (validate)</t>
+          <t>ML / Features (future)</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Validate ML auto-refresh post-scan + cached-bar reuse</t>
+          <t>Add FinBERT as a GBM training feature (leak-free)</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>ml_edge.run_after_scan=true runs ml.run_ml_edge over the fresh bundle; feature_extractor prefers data_archive (no re-fetch). Confirm end-to-end on next clean scan.</t>
+          <t>needs historical sentiment series — accumulate forward via cache/ml/sentiment_log.jsonl (asof-stamped); add as feature #18 + retrain once ~3-6mo of leak-free history exists</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>swing_trade ML hook + ml/feature_extractor</t>
+          <t>ml/feature_extractor + historical backfill</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-MACRO-EVENTS</t>
+          <t>ML-AUTOREFRESH-VALIDATE</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -3132,22 +3132,22 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Macro Lens / Calendar</t>
+          <t>ML / Pipeline (validate)</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>14-day high-impact event window flag</t>
+          <t>Validate ML auto-refresh post-scan + cached-bar reuse</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Wire t.next_macro_event_days = days to next FOMC/CPI/NFP/jobs. _qdComputeLensStatus reads this and downgrades macro lens to amber when event &lt;= 14d even in risk_on_trending regime.</t>
+          <t>ml_edge.run_after_scan=true runs ml.run_ml_edge over the fresh bundle; feature_extractor prefers data_archive (no re-fetch). Confirm end-to-end on next clean scan.</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Add macro_calendar fetch in data_fetcher.py (FRED/Trading Economics free tier or EODHD calendar). Persist to t.next_macro_event_days.</t>
+          <t>swing_trade ML hook + ml/feature_extractor</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
@@ -3162,13 +3162,13 @@
       <c r="M53" s="3" t="inlineStr"/>
       <c r="N53" s="8" t="inlineStr"/>
     </row>
-    <row r="54" ht="45" customHeight="1">
+    <row r="54" ht="60" customHeight="1">
       <c r="A54" s="2" t="n">
         <v>53</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>CACHE-RECLAIM</t>
+          <t>KAIROS-MACRO-EVENTS</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
@@ -3178,22 +3178,22 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Ops / Hygiene</t>
+          <t>Macro Lens / Calendar</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Reclaim ~6GB cache (stray bak + edgar TTL)</t>
+          <t>14-day high-impact event window flag</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>delete 300MB last_bundle.json.bak.precap_promote + add edgar companyfacts prune/TTL (6.1GB)</t>
+          <t>Wire t.next_macro_event_days = days to next FOMC/CPI/NFP/jobs. _qdComputeLensStatus reads this and downgrades macro lens to amber when event &lt;= 14d even in risk_on_trending regime.</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>cache cleanup + edgar_client TTL</t>
+          <t>Add macro_calendar fetch in data_fetcher.py (FRED/Trading Economics free tier or EODHD calendar). Persist to t.next_macro_event_days.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>JOBS-MOMENTUM-SNAPSHOT</t>
+          <t>CACHE-RECLAIM</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
@@ -3224,22 +3224,22 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Ops / Launchd</t>
+          <t>Ops / Hygiene</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>Decide momentum-snapshot job: load or disable</t>
+          <t>Reclaim ~6GB cache (stray bak + edgar TTL)</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>valid plist in repo but not currently loaded; decide launchctl bootstrap vs move to disabled/.</t>
+          <t>delete 300MB last_bundle.json.bak.precap_promote + add edgar companyfacts prune/TTL (6.1GB)</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd/com.swingtrade.momentum-snapshot.plist</t>
+          <t>cache cleanup + edgar_client TTL</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
@@ -3254,13 +3254,13 @@
       <c r="M55" s="3" t="inlineStr"/>
       <c r="N55" s="8" t="inlineStr"/>
     </row>
-    <row r="56" ht="60" customHeight="1">
+    <row r="56" ht="45" customHeight="1">
       <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-OPS-TELEMETRY-6</t>
+          <t>JOBS-MOMENTUM-SNAPSHOT</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
@@ -3270,22 +3270,22 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Ops / Telemetry (future)</t>
+          <t>Ops / Launchd</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>6 ops telemetry slots — app-side instrumentation</t>
+          <t>Decide momentum-snapshot job: load or disable</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>6 ops telemetry slots remain unbuilt because they require app-side instrumentation: server middleware, git hooks, scan-time emitters, executor probes, sub-tab render timings, fetch-latency probes.</t>
+          <t>valid plist in repo but not currently loaded; decide launchctl bootstrap vs move to disabled/.</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>Build a shared emitter (lib/telemetry.py) writing to a telemetry SQLite; instrument incrementally — server middleware first, then scan emitters; surface in System Status sub-tab.</t>
+          <t>infra/launchd/com.swingtrade.momentum-snapshot.plist</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>SCALE-4</t>
+          <t>DATA-FUTURE-OPS-TELEMETRY-6</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
@@ -3316,22 +3316,22 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Ops · 500-user</t>
+          <t>Ops / Telemetry (future)</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>Scan reliability so Home is not sparse</t>
+          <t>6 ops telemetry slots — app-side instrumentation</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>When the daily scan is empty (EODHD quota outage), Home shows honest-empty sections + stale-badged regime; users landing mid-outage see little actionable content</t>
+          <t>6 ops telemetry slots remain unbuilt because they require app-side instrumentation: server middleware, git hooks, scan-time emitters, executor probes, sub-tab render timings, fetch-latency probes.</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Ensure morning scan runs reliably + quota headroom; keep STALE badge UX; consider serving last-good bundle with clear age</t>
+          <t>Build a shared emitter (lib/telemetry.py) writing to a telemetry SQLite; instrument incrementally — server middleware first, then scan emitters; surface in System Status sub-tab.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
@@ -3346,13 +3346,13 @@
       <c r="M57" s="3" t="inlineStr"/>
       <c r="N57" s="8" t="inlineStr"/>
     </row>
-    <row r="58" ht="75" customHeight="1">
+    <row r="58" ht="60" customHeight="1">
       <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>OV-INVEST-STRUCT</t>
+          <t>SCALE-4</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
@@ -3362,22 +3362,22 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Overview / Target Engine</t>
+          <t>Ops · 500-user</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Real structural invest targets (kill analyst-PT stub)</t>
+          <t>Scan reliability so Home is not sparse</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Invest-mode targets fall back to analyst 12mo PT (invest_stub) for low-vol names (e.g. AAPL) when no structural level qualifies in the invest R-band off the wider stop -&gt; near T1, poor R:R. Per-mode stop scaling fix (2026-06-08) made invest coherent for higher-vol names (NVDA stub=False) but low-vol names still stub.</t>
+          <t>When the daily scan is empty (EODHD quota outage), Home shows honest-empty sections + stale-badged regime; users landing mid-outage see little actionable content</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>Wire multi-year structural levels (monthly/yearly swing highs, weekly Fib ext) into the invest candidate set so the invest R-band is populated without the analyst-PT fallback; raise invest max_reach_atr to match a 1-5yr horizon.</t>
+          <t>Ensure morning scan runs reliably + quota headroom; keep STALE badge UX; consider serving last-good bundle with clear age</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
@@ -3392,13 +3392,13 @@
       <c r="M58" s="3" t="inlineStr"/>
       <c r="N58" s="8" t="inlineStr"/>
     </row>
-    <row r="59" ht="60" customHeight="1">
+    <row r="59" ht="75" customHeight="1">
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>SCALE-3</t>
+          <t>OV-INVEST-STRUCT</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
@@ -3408,22 +3408,22 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Portfolio · 500-user</t>
+          <t>Overview / Target Engine</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>Per-user portfolio vs shared automated book</t>
+          <t>Real structural invest targets (kill analyst-PT stub)</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Home AUTOMATED BOOK is the single shared Alpaca-paper auto-trade account; every viewer sees identical positions; no per-user book (NAV is per-user, positions are not)</t>
+          <t>Invest-mode targets fall back to analyst 12mo PT (invest_stub) for low-vol names (e.g. AAPL) when no structural level qualifies in the invest R-band off the wider stop -&gt; near T1, poor R:R. Per-mode stop scaling fix (2026-06-08) made invest coherent for higher-vol names (NVDA stub=False) but low-vol names still stub.</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Decide: keep as shared model/track-record book by design, OR add a per-user position store keyed to UserPrefs auth id</t>
+          <t>Wire multi-year structural levels (monthly/yearly swing highs, weekly Fib ext) into the invest candidate set so the invest R-band is populated without the analyst-PT fallback; raise invest max_reach_atr to match a 1-5yr horizon.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
@@ -3438,13 +3438,13 @@
       <c r="M59" s="3" t="inlineStr"/>
       <c r="N59" s="8" t="inlineStr"/>
     </row>
-    <row r="60" ht="90" customHeight="1">
+    <row r="60" ht="60" customHeight="1">
       <c r="A60" s="2" t="n">
         <v>59</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>QUANT-HMM-FF-LGBM-ROADMAP</t>
+          <t>SCALE-3</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
@@ -3454,22 +3454,22 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Quant / Modeling Roadmap</t>
+          <t>Portfolio · 500-user</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>HMM regime / Fama-French / LightGBM swap (status unclear)</t>
+          <t>Per-user portfolio vs shared automated book</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Roadmap items pasted as a status table — clarification pending whether user wants execution or just context tracking. Three potential upgrades: (a) HMM-based regime classifier replacing the rule-based 4-regime model, (b) Fama-French factor exposure analysis on closed trades, (c) LightGBM swap-in for HistGradientBoosting in ml/train_historical.py. Each 1-3 days.</t>
+          <t>Home AUTOMATED BOOK is the single shared Alpaca-paper auto-trade account; every viewer sees identical positions; no per-user book (NAV is per-user, positions are not)</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>Confirm intent before executing. If go: HMM first (decouples regime classifier from heuristics, principle #18), then Fama-French attribution (per-strategy factor exposure), then LightGBM swap (likely-marginal accuracy gain vs current HistGB). Each upgrade gated by Wilson-LB validation vs current baseline.</t>
+          <t>Decide: keep as shared model/track-record book by design, OR add a per-user position store keyed to UserPrefs auth id</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
@@ -3484,13 +3484,13 @@
       <c r="M60" s="3" t="inlineStr"/>
       <c r="N60" s="8" t="inlineStr"/>
     </row>
-    <row r="61" ht="60" customHeight="1">
+    <row r="61" ht="90" customHeight="1">
       <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>PARITY-SMART-RISK-LEVELS</t>
+          <t>QUANT-HMM-FF-LGBM-ROADMAP</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
@@ -3500,22 +3500,22 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Risk / Targets / Platform Parity</t>
+          <t>Quant / Modeling Roadmap</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>Smart Risk Levels (auto stop + T1/T2)</t>
+          <t>HMM regime / Fama-French / LightGBM swap (status unclear)</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Auto-place stop / T1 / T2 dots on the chart with confluence reasoning (HVN, AVWAP, fractal, ATR, Fib). Already computed by the structural target engine but not surfaced on the new Chart sub-tab.</t>
+          <t>Roadmap items pasted as a status table — clarification pending whether user wants execution or just context tracking. Three potential upgrades: (a) HMM-based regime classifier replacing the rule-based 4-regime model, (b) Fama-French factor exposure analysis on closed trades, (c) LightGBM swap-in for HistGradientBoosting in ml/train_historical.py. Each 1-3 days.</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Read cache/target_engine/{TICKER}_{MODE}.json and overlay the levels on the chart canvas with hover tooltips citing the confluence factors; gated by use_structural_targets flag (M2.5 cutover).</t>
+          <t>Confirm intent before executing. If go: HMM first (decouples regime classifier from heuristics, principle #18), then Fama-French attribution (per-strategy factor exposure), then LightGBM swap (likely-marginal accuracy gain vs current HistGB). Each upgrade gated by Wilson-LB validation vs current baseline.</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-L2-BOOK</t>
+          <t>PARITY-SMART-RISK-LEVELS</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
@@ -3546,22 +3546,22 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Risk Lens / Execution</t>
+          <t>Risk / Targets / Platform Parity</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>L2 bid/ask depth at price levels</t>
+          <t>Smart Risk Levels (auto stop + T1/T2)</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Wire t.l2_book from Schwab streaming API → render in renderRisk_LiquidityLadder. Today: ADV-derived size tiers shown as scaffold. Schwab streaming requires WebSocket session — see schwab_client.py.</t>
+          <t>Auto-place stop / T1 / T2 dots on the chart with confluence reasoning (HVN, AVWAP, fractal, ATR, Fib). Already computed by the structural target engine but not surfaced on the new Chart sub-tab.</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>Subscribe to Schwab Level-II quote stream; persist top-of-book snapshot into t.l2_book = {bid:[{px,size}], ask:[{px,size}]}. Frontend already reads these fields if present.</t>
+          <t>Read cache/target_engine/{TICKER}_{MODE}.json and overlay the levels on the chart canvas with hover tooltips citing the confluence factors; gated by use_structural_targets flag (M2.5 cutover).</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>PARITY-AI-SIGNALS-V1</t>
+          <t>KAIROS-L2-BOOK</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
@@ -3592,22 +3592,22 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Signals / Platform Parity</t>
+          <t>Risk Lens / Execution</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>1st-Gen AI Signals</t>
+          <t>L2 bid/ask depth at price levels</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Surface a baseline AI BUY/SELL signal stream on the chart as quick-glance arrows/dots — the competitor-platform feature (TrendSpider, Trade Ideas) users expect to see at a glance, separate from the full ML Edge sub-tab.</t>
+          <t>Wire t.l2_book from Schwab streaming API → render in renderRisk_LiquidityLadder. Today: ADV-derived size tiers shown as scaffold. Schwab streaming requires WebSocket session — see schwab_client.py.</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>Reuse ML Edge dir-head + cone outputs but render as 1-bar arrows/markers on the new Chart sub-tab; isolate from the 10-section Technicals view; respect cache/ml_edge_predictions.json freshness.</t>
+          <t>Subscribe to Schwab Level-II quote stream; persist top-of-book snapshot into t.l2_book = {bid:[{px,size}], ask:[{px,size}]}. Frontend already reads these fields if present.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr"/>
@@ -3622,13 +3622,13 @@
       <c r="M63" s="3" t="inlineStr"/>
       <c r="N63" s="8" t="inlineStr"/>
     </row>
-    <row r="64" ht="45" customHeight="1">
+    <row r="64" ht="60" customHeight="1">
       <c r="A64" s="2" t="n">
         <v>63</v>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>TEST-AB-PAPER</t>
+          <t>PARITY-AI-SIGNALS-V1</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
@@ -3638,22 +3638,22 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Testing / Validation (Tier 2)</t>
+          <t>Signals / Platform Parity</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>A/B Paper Split — live comparison</t>
+          <t>1st-Gen AI Signals</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Run config A on half the paper portfolio and config B on the other half; real-time comparison of WR / PF / equity divergence over 30-60d window.</t>
+          <t>Surface a baseline AI BUY/SELL signal stream on the chart as quick-glance arrows/dots — the competitor-platform feature (TrendSpider, Trade Ideas) users expect to see at a glance, separate from the full ML Edge sub-tab.</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>Extend executor.py to accept --variant flag; persist per-variant portfolio state; cross-section panel in System Status sub-tab. Effort 3-4hr.</t>
+          <t>Reuse ML Edge dir-head + cone outputs but render as 1-bar arrows/markers on the new Chart sub-tab; isolate from the 10-section Technicals view; respect cache/ml_edge_predictions.json freshness.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
@@ -3668,13 +3668,13 @@
       <c r="M64" s="3" t="inlineStr"/>
       <c r="N64" s="8" t="inlineStr"/>
     </row>
-    <row r="65" ht="60" customHeight="1">
+    <row r="65" ht="45" customHeight="1">
       <c r="A65" s="2" t="n">
         <v>64</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>TEST-BENCHMARK-SPY</t>
+          <t>TEST-AB-PAPER</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
@@ -3689,17 +3689,17 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>Benchmark vs SPY — alpha / beta / IR</t>
+          <t>A/B Paper Split — live comparison</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>Compute strategy alpha, beta, information ratio vs SPY benchmark. Standard performance attribution; turns 'we made +X%' into 'we made +Y% over SPY at lower drawdown'.</t>
+          <t>Run config A on half the paper portfolio and config B on the other half; real-time comparison of WR / PF / equity divergence over 30-60d window.</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>Daily portfolio_value series joined to SPY adjusted-close; regress daily returns -&gt; SPY returns for beta + alpha; IR = (mean excess return) / (std excess return); render in System Status. Effort ~1hr.</t>
+          <t>Extend executor.py to accept --variant flag; persist per-variant portfolio state; cross-section panel in System Status sub-tab. Effort 3-4hr.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>TEST-DD-DIST</t>
+          <t>TEST-BENCHMARK-SPY</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
@@ -3735,17 +3735,17 @@
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>Drawdown Distribution Simulator</t>
+          <t>Benchmark vs SPY — alpha / beta / IR</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>Bootstrap 1000 portfolio paths from closed-trade distribution; measure tail-drawdown probability at p95/p99; supports principle #9 (drawdown asymmetry — losing 50% requires +100% to recover).</t>
+          <t>Compute strategy alpha, beta, information ratio vs SPY benchmark. Standard performance attribution; turns 'we made +X%' into 'we made +Y% over SPY at lower drawdown'.</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>Resample trade sequence with replacement; build equity curves; compute max-DD per path; histogram + tail percentiles; feed into position-sizing math. Effort 2-3hr.</t>
+          <t>Daily portfolio_value series joined to SPY adjusted-close; regress daily returns -&gt; SPY returns for beta + alpha; IR = (mean excess return) / (std excess return); render in System Status. Effort ~1hr.</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>TEST-SENSITIVITY</t>
+          <t>TEST-DD-DIST</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>Sensitivity / Robustness Test</t>
+          <t>Drawdown Distribution Simulator</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Perturb each config parameter +/-20% (score floors, stop ATR mult, R:R floor, regime thresholds) and check whether the strategy still passes the gate. Finds overfit knobs that only work at one exact value.</t>
+          <t>Bootstrap 1000 portfolio paths from closed-trade distribution; measure tail-drawdown probability at p95/p99; supports principle #9 (drawdown asymmetry — losing 50% requires +100% to recover).</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Grid-walk key config thresholds; re-run backtest at each point; build sensitivity heatmap (param vs PF); flag any knob whose +/-20% perturbation collapses PF &gt;50%. Effort ~2hr.</t>
+          <t>Resample trade sequence with replacement; build equity curves; compute max-DD per path; histogram + tail percentiles; feed into position-sizing math. Effort 2-3hr.</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>TEST-SLIPPAGE-STRESS</t>
+          <t>TEST-SENSITIVITY</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
@@ -3827,17 +3827,17 @@
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>Slippage Stress Test</t>
+          <t>Sensitivity / Robustness Test</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>Double the slippage assumption (ATR/ADV-scaled model from audit #5) and recompute backtest stats. Validates fragile execution dependence per principle #19 (slippage realism).</t>
+          <t>Perturb each config parameter +/-20% (score floors, stop ATR mult, R:R floor, regime thresholds) and check whether the strategy still passes the gate. Finds overfit knobs that only work at one exact value.</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>Re-run backtest with SLIPPAGE_MULT=2.0; compare WR/PF/Sharpe deltas; if a strategy collapses at 2x slippage it is execution-fragile and should be down-sized. Effort ~1hr.</t>
+          <t>Grid-walk key config thresholds; re-run backtest at each point; build sensitivity heatmap (param vs PF); flag any knob whose +/-20% perturbation collapses PF &gt;50%. Effort ~2hr.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>TEST-CORRELATED-FAILURE</t>
+          <t>TEST-SLIPPAGE-STRESS</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
@@ -3868,22 +3868,22 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Testing / Validation (Tier 3)</t>
+          <t>Testing / Validation (Tier 2)</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>Correlated-Failure — what if EODHD goes down 24h?</t>
+          <t>Slippage Stress Test</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Simulate the impact of the sole data provider (EODHD) being unavailable for 24-48h during market hours. What happens to (a) the scan, (b) live exec, (c) the dashboard?</t>
+          <t>Double the slippage assumption (ATR/ADV-scaled model from audit #5) and recompute backtest stats. Validates fragile execution dependence per principle #19 (slippage realism).</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>Inject EODHD error responses in a paper environment; observe failure modes (fallback to last-known cache vs hard error vs degraded scan); document recovery RTO; tighten any silent-fail paths discovered. Effort 2-3hr.</t>
+          <t>Re-run backtest with SLIPPAGE_MULT=2.0; compare WR/PF/Sharpe deltas; if a strategy collapses at 2x slippage it is execution-fragile and should be down-sized. Effort ~1hr.</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr"/>
@@ -3898,13 +3898,13 @@
       <c r="M69" s="3" t="inlineStr"/>
       <c r="N69" s="8" t="inlineStr"/>
     </row>
-    <row r="70" ht="45" customHeight="1">
+    <row r="70" ht="60" customHeight="1">
       <c r="A70" s="2" t="n">
         <v>69</v>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>TEST-CRASH-REPLAY</t>
+          <t>TEST-CORRELATED-FAILURE</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
@@ -3919,17 +3919,17 @@
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>Crash Replay — 2008/2020/2022 stress</t>
+          <t>Correlated-Failure — what if EODHD goes down 24h?</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>Apply current portfolio composition to historical crash days (2008 GFC, 2020 COVID, 2022 rate-shock); measure realized drawdown + recovery time per scenario.</t>
+          <t>Simulate the impact of the sole data provider (EODHD) being unavailable for 24-48h during market hours. What happens to (a) the scan, (b) live exec, (c) the dashboard?</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>Snapshot today's positions; price-replay against historical daily OHLC from those windows; report per-crisis max-DD and time-to-recovery. Effort 2-3hr.</t>
+          <t>Inject EODHD error responses in a paper environment; observe failure modes (fallback to last-known cache vs hard error vs degraded scan); document recovery RTO; tighten any silent-fail paths discovered. Effort 2-3hr.</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
@@ -3944,13 +3944,13 @@
       <c r="M70" s="3" t="inlineStr"/>
       <c r="N70" s="8" t="inlineStr"/>
     </row>
-    <row r="71" ht="60" customHeight="1">
+    <row r="71" ht="45" customHeight="1">
       <c r="A71" s="2" t="n">
         <v>70</v>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>TEST-KELLY-SIM</t>
+          <t>TEST-CRASH-REPLAY</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
@@ -3965,17 +3965,17 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>Half-Kelly vs Full-Kelly sizing simulation</t>
+          <t>Crash Replay — 2008/2020/2022 stress</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Visualize portfolio growth under Half-Kelly (current default) vs Full-Kelly vs Quarter-Kelly sizing rules; quantifies the volatility-vs-CAGR tradeoff that principle #9 codifies.</t>
+          <t>Apply current portfolio composition to historical crash days (2008 GFC, 2020 COVID, 2022 rate-shock); measure realized drawdown + recovery time per scenario.</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>Bootstrap N portfolio paths under each Kelly fraction; chart median equity curve + percentile fans; surface terminal-wealth distribution. Effort ~2hr.</t>
+          <t>Snapshot today's positions; price-replay against historical daily OHLC from those windows; report per-crisis max-DD and time-to-recovery. Effort 2-3hr.</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>TEST-SLIPPAGE-ATTR</t>
+          <t>TEST-KELLY-SIM</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
@@ -4011,17 +4011,17 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>Slippage Attribution — signal PnL vs realized PnL gap</t>
+          <t>Half-Kelly vs Full-Kelly sizing simulation</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>For each closed trade, compute the gap between the model's predicted entry/exit and the actual fill price. Aggregate by setup/ticker/regime to find where slippage eats edge.</t>
+          <t>Visualize portfolio growth under Half-Kelly (current default) vs Full-Kelly vs Quarter-Kelly sizing rules; quantifies the volatility-vs-CAGR tradeoff that principle #9 codifies.</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>Read signal_log entries (which has the signal price) and join to paper_fills.json (which has the realized price); compute slippage_bp per trade; group + percentile. Effort ~2hr.</t>
+          <t>Bootstrap N portfolio paths under each Kelly fraction; chart median equity curve + percentile fans; surface terminal-wealth distribution. Effort ~2hr.</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>TEST-TAX-AWARE</t>
+          <t>TEST-SLIPPAGE-ATTR</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>Tax-Aware Backtest — short-term cap-gains haircut</t>
+          <t>Slippage Attribution — signal PnL vs realized PnL gap</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Apply short-term capital-gains tax (35-40% on gains held &lt;1yr) to backtest PnL. Real after-tax return for a US retail account is materially lower than gross.</t>
+          <t>For each closed trade, compute the gap between the model's predicted entry/exit and the actual fill price. Aggregate by setup/ticker/regime to find where slippage eats edge.</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>Add post_tax_pnl column to backtest output; apply 35% haircut to short-term gains (&gt;0 PnL, held &lt;365d) and 15% to long-term; report Sharpe / total-return pre vs post tax. Effort ~2hr.</t>
+          <t>Read signal_log entries (which has the signal price) and join to paper_fills.json (which has the realized price); compute slippage_bp per trade; group + percentile. Effort ~2hr.</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr"/>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>WAIT-CALIB-DRIFT-SPARK</t>
+          <t>TEST-TAX-AWARE</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
@@ -4098,22 +4098,22 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Time-Dependent / Calibration</t>
+          <t>Testing / Validation (Tier 3)</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>Calibration drift sparkline populates</t>
+          <t>Tax-Aware Backtest — short-term cap-gains haircut</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>The calibration-drift sparkline in the ML Edge sub-tab needs multiple training cycles to populate (weeks). Each morning scan retrains and appends a calibration row; the sparkline reads from that history table.</t>
+          <t>Apply short-term capital-gains tax (35-40% on gains held &lt;1yr) to backtest PnL. Real after-tax return for a US retail account is materially lower than gross.</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>Passive wait. Re-check after 4-6 weekly retrain cycles. If still empty, verify ml.train_historical writes to cache/ml/calibration_history.jsonl on each run.</t>
+          <t>Add post_tax_pnl column to backtest output; apply 35% haircut to short-term gains (&gt;0 PnL, held &lt;365d) and 15% to long-term; report Sharpe / total-return pre vs post tax. Effort ~2hr.</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
@@ -4128,13 +4128,13 @@
       <c r="M74" s="3" t="inlineStr"/>
       <c r="N74" s="8" t="inlineStr"/>
     </row>
-    <row r="75" ht="45" customHeight="1">
+    <row r="75" ht="60" customHeight="1">
       <c r="A75" s="2" t="n">
         <v>74</v>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>WAIT-DRIFT-SNAPSHOTS</t>
+          <t>WAIT-CALIB-DRIFT-SPARK</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
@@ -4144,22 +4144,22 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Time-Dependent / Drift Tracking</t>
+          <t>Time-Dependent / Calibration</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>Diff vs yesterday + 30-day drift populate</t>
+          <t>Calibration drift sparkline populates</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>The 'diff vs yesterday' + 30-day drift columns need 2+ daily snapshots stored. Starts populating tomorrow's scan.</t>
+          <t>The calibration-drift sparkline in the ML Edge sub-tab needs multiple training cycles to populate (weeks). Each morning scan retrains and appends a calibration row; the sparkline reads from that history table.</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>Passive wait; first populated values appear in the next morning's scan output. Verify the snapshot persister wrote a row today.</t>
+          <t>Passive wait. Re-check after 4-6 weekly retrain cycles. If still empty, verify ml.train_historical writes to cache/ml/calibration_history.jsonl on each run.</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>WAIT-ML-PICKS-RESOLVE</t>
+          <t>WAIT-DRIFT-SNAPSHOTS</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
@@ -4190,22 +4190,22 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Time-Dependent / Picks History</t>
+          <t>Time-Dependent / Drift Tracking</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>Picks-history outcome resolution (resolve_ml_picks.py)</t>
+          <t>Diff vs yesterday + 30-day drift populate</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>resolve_ml_picks.py needs 5 trading days from each pick to resolve outcomes. First AI Edge batch (picks from ~2026-05-18) resolves around 2026-05-23.</t>
+          <t>The 'diff vs yesterday' + 30-day drift columns need 2+ daily snapshots stored. Starts populating tomorrow's scan.</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>Passive wait. Re-check on 2026-05-23; verify resolve_ml_picks.py runs in run_daily_scan.sh and populates picks_history.json outcome columns.</t>
+          <t>Passive wait; first populated values appear in the next morning's scan output. Verify the snapshot persister wrote a row today.</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
@@ -4220,13 +4220,13 @@
       <c r="M76" s="3" t="inlineStr"/>
       <c r="N76" s="8" t="inlineStr"/>
     </row>
-    <row r="77" ht="60" customHeight="1">
+    <row r="77" ht="45" customHeight="1">
       <c r="A77" s="2" t="n">
         <v>76</v>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>WAIT-SURVIVORSHIP-DECAY</t>
+          <t>WAIT-ML-PICKS-RESOLVE</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
@@ -4236,22 +4236,22 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Time-Dependent / Survivorship Haircut</t>
+          <t>Time-Dependent / Picks History</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>Survivorship haircut shrinking 3pp -&gt; 0.5pp</t>
+          <t>Picks-history outcome resolution (resolve_ml_picks.py)</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>The -3pp WR survivorship haircut should shrink as monthly S&amp;P 500 / R1000 membership snapshots accumulate (Wikipedia revision history). Once 24+ months of snapshots are stored, the haircut can fade toward 0.5pp.</t>
+          <t>resolve_ml_picks.py needs 5 trading days from each pick to resolve outcomes. First AI Edge batch (picks from ~2026-05-18) resolves around 2026-05-23.</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>Passive wait — currently only current-membership data. Re-evaluate annually. Until then keep -3pp haircut per CLAUDE.md principle #6.</t>
+          <t>Passive wait. Re-check on 2026-05-23; verify resolve_ml_picks.py runs in run_daily_scan.sh and populates picks_history.json outcome columns.</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>WAIT-WF-EQUITY-REAL</t>
+          <t>WAIT-SURVIVORSHIP-DECAY</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
@@ -4282,22 +4282,22 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Time-Dependent / Walk-Forward</t>
+          <t>Time-Dependent / Survivorship Haircut</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>Walk-forward equity curve switches to REAL track</t>
+          <t>Survivorship haircut shrinking 3pp -&gt; 0.5pp</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>Currently the equity curve renders backtest-derived returns. Switches to REAL track once 5+ resolved AI Edge picks are available — first batch resolves ~2026-05-23, so REAL curve activates ~2026-05-24.</t>
+          <t>The -3pp WR survivorship haircut should shrink as monthly S&amp;P 500 / R1000 membership snapshots accumulate (Wikipedia revision history). Once 24+ months of snapshots are stored, the haircut can fade toward 0.5pp.</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>Passive wait. Re-check on 2026-05-24; verify the equity curve flips from BACKTEST badge to REAL badge once n_resolved &gt;= 5.</t>
+          <t>Passive wait — currently only current-membership data. Re-evaluate annually. Until then keep -3pp haircut per CLAUDE.md principle #6.</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>PARITY-10-CHARTS-GRID</t>
+          <t>WAIT-WF-EQUITY-REAL</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
@@ -4328,22 +4328,22 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>UI / Layout / Platform Parity</t>
+          <t>Time-Dependent / Walk-Forward</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>10-chart multi-pane grid</t>
+          <t>Walk-forward equity curve switches to REAL track</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Display up to 10 ticker charts side-by-side in a configurable grid (2x5, 3x4, etc.) for at-a-glance correlation/leadership reads — what TrendSpider and Trade Ideas users default to.</t>
+          <t>Currently the equity curve renders backtest-derived returns. Switches to REAL track once 5+ resolved AI Edge picks are available — first batch resolves ~2026-05-23, so REAL curve activates ~2026-05-24.</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>New 'Grid' workspace in kairos that renders N lightweight-chart canvases; ticker list drag-droppable; persists ticker set per layout.</t>
+          <t>Passive wait. Re-check on 2026-05-24; verify the equity curve flips from BACKTEST badge to REAL badge once n_resolved &gt;= 5.</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr"/>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>PARITY-CUSTOM-LAYOUTS</t>
+          <t>PARITY-10-CHARTS-GRID</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
@@ -4379,17 +4379,17 @@
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>Customizable Layouts (save/load workspace presets)</t>
+          <t>10-chart multi-pane grid</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>User drags/resizes panels in the kairos workspace and saves the arrangement as a named preset (Day-Trade view / Swing view / Research view) and switches between them.</t>
+          <t>Display up to 10 ticker charts side-by-side in a configurable grid (2x5, 3x4, etc.) for at-a-glance correlation/leadership reads — what TrendSpider and Trade Ideas users default to.</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Persist layout JSON in cache/user_layouts.json (per-user once auth lands); sidebar dropdown to switch; default presets shipped (Swing / Position / Research).</t>
+          <t>New 'Grid' workspace in kairos that renders N lightweight-chart canvases; ticker list drag-droppable; persists ticker set per layout.</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr"/>
@@ -4404,13 +4404,13 @@
       <c r="M80" s="3" t="inlineStr"/>
       <c r="N80" s="8" t="inlineStr"/>
     </row>
-    <row r="81" ht="75" customHeight="1">
+    <row r="81" ht="60" customHeight="1">
       <c r="A81" s="2" t="n">
         <v>80</v>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-PHASE2</t>
+          <t>PARITY-CUSTOM-LAYOUTS</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
@@ -4420,51 +4420,35 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Targets</t>
+          <t>UI / Layout / Platform Parity</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>Structural targets Phase 2 — engine uses them as T1/T2</t>
+          <t>Customizable Layouts (save/load workspace presets)</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 (shipped 2026-05-10): structural target sources (fractal, fib, EW Wave-3) display on Plan tab as informational. Phase 2: actually use these as T1/T2 instead of ATR-multiple targets. Needs per-source x regime evidence (&gt;=30 trades each).</t>
+          <t>User drags/resizes panels in the kairos workspace and saves the arrangement as a named preset (Day-Trade view / Swing view / Research view) and switches between them.</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Add config flag target_source = atr_multiple | structural. When structural, T1 = nearest_above with R:R&gt;=3 from {fractal_high, fib_127, EW_T1}. Fall back to ATR if R:R floor not met. Backtest side-by-side with current ATR-multiple.</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>1 day + backtest</t>
-        </is>
-      </c>
-      <c r="I81" s="5" t="inlineStr">
-        <is>
-          <t>High win potential, medium risk</t>
-        </is>
-      </c>
-      <c r="J81" s="5" t="inlineStr">
-        <is>
-          <t>Awaiting evidence. Phase 1 currently just populates display field; need 3-4 weeks of trade data with target_sources captured before Phase 2 is decidable.</t>
-        </is>
-      </c>
-      <c r="K81" s="11" t="inlineStr">
-        <is>
-          <t>IN_PROGRESS</t>
+          <t>Persist layout JSON in cache/user_layouts.json (per-user once auth lands); sidebar dropdown to switch; default presets shipped (Swing / Position / Research).</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="5" t="inlineStr"/>
+      <c r="J81" s="5" t="inlineStr"/>
+      <c r="K81" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="3" t="inlineStr"/>
-      <c r="N81" s="8" t="inlineStr">
-        <is>
-          <t>Run backtest with target_source=structural and target_source=atr_multiple on same window. Compare PF/WR/avg_win.</t>
-        </is>
-      </c>
+      <c r="N81" s="8" t="inlineStr"/>
     </row>
     <row r="82" ht="75" customHeight="1">
       <c r="A82" s="2" t="n">
@@ -4472,77 +4456,69 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>K6</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>STRUCT-TARGETS-PHASE2</t>
+        </is>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Strategy / Targets</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>Single canonical trade plan object — every tab reads from one source</t>
+          <t>Structural targets Phase 2 — engine uses them as T1/T2</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
+          <t>Phase 1 (shipped 2026-05-10): structural target sources (fractal, fib, EW Wave-3) display on Plan tab as informational. Phase 2: actually use these as T1/T2 instead of ATR-multiple targets. Needs per-source x regime evidence (&gt;=30 trades each).</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
+          <t>Add config flag target_source = atr_multiple | structural. When structural, T1 = nearest_above with R:R&gt;=3 from {fractal_high, fib_127, EW_T1}. Fall back to ATR if R:R floor not met. Backtest side-by-side with current ATR-multiple.</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>1 day + backtest</t>
         </is>
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
+          <t>High win potential, medium risk</t>
         </is>
       </c>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
-        </is>
-      </c>
-      <c r="K82" s="12" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M82" s="3" t="inlineStr">
-        <is>
-          <t>2c9b9f339</t>
-        </is>
-      </c>
+          <t>Awaiting evidence. Phase 1 currently just populates display field; need 3-4 weeks of trade data with target_sources captured before Phase 2 is decidable.</t>
+        </is>
+      </c>
+      <c r="K82" s="11" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="3" t="inlineStr"/>
       <c r="N82" s="8" t="inlineStr">
         <is>
-          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="90" customHeight="1">
+          <t>Run backtest with target_source=structural and target_source=atr_multiple on same window. Compare PF/WR/avg_win.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="75" customHeight="1">
       <c r="A83" s="2" t="n">
         <v>82</v>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>B3-WEEKLY-FIX</t>
+          <t>K6</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -4552,29 +4528,37 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Bug Fix</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
+          <t>Single canonical trade plan object — every tab reads from one source</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
+          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr"/>
-      <c r="I83" s="5" t="inlineStr"/>
+          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
+        </is>
+      </c>
       <c r="J83" s="5" t="inlineStr">
         <is>
-          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
+          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
         </is>
       </c>
       <c r="K83" s="12" t="inlineStr">
@@ -4584,27 +4568,27 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
+          <t>2c9b9f339</t>
         </is>
       </c>
       <c r="N83" s="8" t="inlineStr">
         <is>
-          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="75" customHeight="1">
+          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="90" customHeight="1">
       <c r="A84" s="2" t="n">
         <v>83</v>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>VARIANT-F-BT</t>
+          <t>B3-WEEKLY-FIX</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -4614,27 +4598,31 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Backtest Parity</t>
+          <t>Backtest / Bug Fix</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>Variant F regime-conditional multipliers not wired into backtest path</t>
+          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:418 uses tracker.get_setup_weight_multiplier (reading picks_history) but never consults config.setup_score_multiplier_by_regime. So Variant F's TC×bull=0.0 kill never applied in backtest — explains why 105 TC bull trades persisted in 250d backtest despite live kill in config.</t>
+          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>Add Variant F lookup at backtest.py:442 mirroring analysis.py:8867 logic. Same demotion gate (n&gt;=30 + wr_lb&lt;0.30). Comment cross-reference live path.</t>
+          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="5" t="inlineStr"/>
-      <c r="J84" s="5" t="inlineStr"/>
+      <c r="J84" s="5" t="inlineStr">
+        <is>
+          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
+        </is>
+      </c>
       <c r="K84" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4647,18 +4635,22 @@
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>0cdb13340</t>
-        </is>
-      </c>
-      <c r="N84" s="8" t="inlineStr"/>
-    </row>
-    <row r="85" ht="45" customHeight="1">
+          <t>985cd182b</t>
+        </is>
+      </c>
+      <c r="N84" s="8" t="inlineStr">
+        <is>
+          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="75" customHeight="1">
       <c r="A85" s="2" t="n">
         <v>84</v>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>P0-WEEKLY</t>
+          <t>VARIANT-F-BT</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -4668,39 +4660,27 @@
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Backtest infra</t>
+          <t>Backtest Parity</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
+          <t>Variant F regime-conditional multipliers not wired into backtest path</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
+          <t>backtest.py:418 uses tracker.get_setup_weight_multiplier (reading picks_history) but never consults config.setup_score_multiplier_by_regime. So Variant F's TC×bull=0.0 kill never applied in backtest — explains why 105 TC bull trades persisted in 250d backtest despite live kill in config.</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>20 min</t>
-        </is>
-      </c>
-      <c r="I85" s="5" t="inlineStr">
-        <is>
-          <t>CRITICAL — system was unable to backtest</t>
-        </is>
-      </c>
-      <c r="J85" s="5" t="inlineStr">
-        <is>
-          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
-        </is>
-      </c>
+          <t>Add Variant F lookup at backtest.py:442 mirroring analysis.py:8867 logic. Same demotion gate (n&gt;=30 + wr_lb&lt;0.30). Comment cross-reference live path.</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="5" t="inlineStr"/>
+      <c r="J85" s="5" t="inlineStr"/>
       <c r="K85" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4713,22 +4693,18 @@
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
-        </is>
-      </c>
-      <c r="N85" s="8" t="inlineStr">
-        <is>
-          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="75" customHeight="1">
+          <t>0cdb13340</t>
+        </is>
+      </c>
+      <c r="N85" s="8" t="inlineStr"/>
+    </row>
+    <row r="86" ht="45" customHeight="1">
       <c r="A86" s="2" t="n">
         <v>85</v>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>ROLLING-SHARPE-FIX</t>
+          <t>P0-WEEKLY</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -4738,27 +4714,39 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Decision Engine / Bug</t>
+          <t>Backtest infra</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>Rolling-Sharpe brake firing on contaminated data</t>
+          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>Two bugs: (a) WATCH-conviction signals being written with verdict='BUY' inflated loss count; (b) same physical trade re-emitted as fresh daily signal counted 3× in rolling-20 window. Net: false brake activation pausing ALL new BUYs system-wide. Real Sharpe -0.42; system reported -1.732</t>
+          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>Upstream fix: swing_trade.py line 3110 _resolve_verdict() detects WATCH conviction and overrides bucket label. Read-time fix: decision_engine.compute_rolling_sharpe_kill_state dedupes by (ticker,entry,pnl,exit_reason). Historical cleanup: scripts/dedupe_signal_log.py removed 133 mislabels + 90 dupes (backed up)</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr"/>
-      <c r="I86" s="5" t="inlineStr"/>
-      <c r="J86" s="5" t="inlineStr"/>
+          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>20 min</t>
+        </is>
+      </c>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>CRITICAL — system was unable to backtest</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="inlineStr">
+        <is>
+          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
+        </is>
+      </c>
       <c r="K86" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4766,23 +4754,27 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>27fd646b1</t>
-        </is>
-      </c>
-      <c r="N86" s="8" t="inlineStr"/>
-    </row>
-    <row r="87" ht="90" customHeight="1">
+          <t>985cd182b</t>
+        </is>
+      </c>
+      <c r="N86" s="8" t="inlineStr">
+        <is>
+          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="75" customHeight="1">
       <c r="A87" s="2" t="n">
         <v>86</v>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>OPERATING-MINDSET</t>
+          <t>ROLLING-SHARPE-FIX</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -4792,39 +4784,27 @@
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Decision Engine / Bug</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
+          <t>Rolling-Sharpe brake firing on contaminated data</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
+          <t>Two bugs: (a) WATCH-conviction signals being written with verdict='BUY' inflated loss count; (b) same physical trade re-emitted as fresh daily signal counted 3× in rolling-20 window. Net: false brake activation pausing ALL new BUYs system-wide. Real Sharpe -0.42; system reported -1.732</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I87" s="5" t="inlineStr">
-        <is>
-          <t>Win: codified discipline survives session/agent boundaries.</t>
-        </is>
-      </c>
-      <c r="J87" s="5" t="inlineStr">
-        <is>
-          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
-        </is>
-      </c>
+          <t>Upstream fix: swing_trade.py line 3110 _resolve_verdict() detects WATCH conviction and overrides bucket label. Read-time fix: decision_engine.compute_rolling_sharpe_kill_state dedupes by (ticker,entry,pnl,exit_reason). Historical cleanup: scripts/dedupe_signal_log.py removed 133 mislabels + 90 dupes (backed up)</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="5" t="inlineStr"/>
+      <c r="J87" s="5" t="inlineStr"/>
       <c r="K87" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4832,27 +4812,23 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N87" s="8" t="inlineStr">
-        <is>
-          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="60" customHeight="1">
+          <t>27fd646b1</t>
+        </is>
+      </c>
+      <c r="N87" s="8" t="inlineStr"/>
+    </row>
+    <row r="88" ht="90" customHeight="1">
       <c r="A88" s="2" t="n">
         <v>87</v>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>EXEC-TRADABLE-ENUM</t>
+          <t>OPERATING-MINDSET</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -4862,27 +4838,39 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Execution · Auto-Trade</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>Stock executor skipped all active names (enum bug)</t>
+          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>alpaca-py AssetStatus enum stringified to 'AssetStatus.ACTIVE'; check 'assetstatus.active' != 'active' wrongly skipped EVERY tradable stock since ~2026-05-28 → stock auto-trade silently dead, options-only</t>
+          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>executor.py: read enum .value ('active') before lowercasing</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr"/>
-      <c r="I88" s="5" t="inlineStr"/>
-      <c r="J88" s="5" t="inlineStr"/>
+          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>Win: codified discipline survives session/agent boundaries.</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
+        </is>
+      </c>
       <c r="K88" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4890,23 +4878,27 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>c7098178a</t>
-        </is>
-      </c>
-      <c r="N88" s="8" t="inlineStr"/>
-    </row>
-    <row r="89" ht="105" customHeight="1">
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N88" s="8" t="inlineStr">
+        <is>
+          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="60" customHeight="1">
       <c r="A89" s="2" t="n">
         <v>88</v>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>EXEC-TRADABLE-ENUM</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -4916,39 +4908,27 @@
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>ML / Data Logging</t>
+          <t>Execution · Auto-Trade</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>Entry-time feature logger in swing_trade.py</t>
+          <t>Stock executor skipped all active names (enum bug)</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
+          <t>alpaca-py AssetStatus enum stringified to 'AssetStatus.ACTIVE'; check 'assetstatus.active' != 'active' wrongly skipped EVERY tradable stock since ~2026-05-28 → stock auto-trade silently dead, options-only</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I89" s="5" t="inlineStr">
-        <is>
-          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
-        </is>
-      </c>
-      <c r="J89" s="5" t="inlineStr">
-        <is>
-          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
-        </is>
-      </c>
+          <t>executor.py: read enum .value ('active') before lowercasing</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr"/>
+      <c r="I89" s="5" t="inlineStr"/>
+      <c r="J89" s="5" t="inlineStr"/>
       <c r="K89" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4956,19 +4936,15 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
-          <t>0574c60d4</t>
-        </is>
-      </c>
-      <c r="N89" s="8" t="inlineStr">
-        <is>
-          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
-        </is>
-      </c>
+          <t>c7098178a</t>
+        </is>
+      </c>
+      <c r="N89" s="8" t="inlineStr"/>
     </row>
     <row r="90" ht="105" customHeight="1">
       <c r="A90" s="2" t="n">
@@ -4976,7 +4952,7 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>ML-FEATURE-MISMATCH</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -4986,27 +4962,39 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>ML · Inference</t>
+          <t>ML / Data Logging</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>Live predict_one degenerate — 29-feat model vs 17-feat extractor</t>
+          <t>Entry-time feature logger in swing_trade.py</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>Models retrained 2026-06-09 on 29 features but ml.feature_extractor.FEATURE_COLS still emits 17, so live predict_one feeds a mismatched vector and returns ~0 p_up for EVERY ticker (AI Edge 0% bug, all names). Batch ml-predict path extracts 29 correctly. /api/ml now prefers the batch cache + rejects degenerate live; ROOT FIX still needed: align FEATURE_COLS to 29 (or guard retrain to the live feature set). Also cache 4d stale.</t>
+          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>server /api/ml cache-first + degenerate guard (done); align ml/feature_extractor.FEATURE_COLS to model n_features_in_ (pending)</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr"/>
-      <c r="I90" s="5" t="inlineStr"/>
-      <c r="J90" s="5" t="inlineStr"/>
+          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
+        </is>
+      </c>
+      <c r="J90" s="5" t="inlineStr">
+        <is>
+          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
+        </is>
+      </c>
       <c r="K90" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5014,15 +5002,19 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>33877186c</t>
-        </is>
-      </c>
-      <c r="N90" s="8" t="inlineStr"/>
+          <t>0574c60d4</t>
+        </is>
+      </c>
+      <c r="N90" s="8" t="inlineStr">
+        <is>
+          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="45" customHeight="1">
       <c r="A91" s="2" t="n">
@@ -15723,7 +15715,7 @@
         </is>
       </c>
       <c r="B2" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="18" t="n">
         <v>20</v>
@@ -15732,7 +15724,7 @@
         <v>58</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3">
@@ -15761,7 +15753,7 @@
         </is>
       </c>
       <c r="B4" s="18" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C4" s="18" t="n">
         <v>77</v>
@@ -15770,7 +15762,7 @@
         <v>68</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5">

--- a/cache/open_items_2026-06-09.xlsx
+++ b/cache/open_items_2026-06-09.xlsx
@@ -706,13 +706,13 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="105" customHeight="1">
+    <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>ML-FEATURE-MISMATCH</t>
+          <t>STRUCT-TARGETS-M25-CUTOVER</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -722,22 +722,22 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>ML · Inference</t>
+          <t>Strategy / Targets</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>Live predict_one degenerate — 29-feat model vs 17-feat extractor</t>
+          <t>Structural targets · M2.5 — cutover gate (flip use_structural_targets=true)</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>Models retrained 2026-06-09 on 29 features but ml.feature_extractor.FEATURE_COLS still emits 17, so live predict_one feeds a mismatched vector and returns ~0 p_up for EVERY ticker (AI Edge 0% bug, all names). Batch ml-predict path extracts 29 correctly. /api/ml now prefers the batch cache + rejects degenerate live; ROOT FIX still needed: align FEATURE_COLS to 29 (or guard retrain to the live feature set). Also cache 4d stale.</t>
+          <t>Pending. After M2.1-2.4 settle in production (one week of nightly precompute + dashboard observation with flag=false), flip use_structural_targets=true in config/config.json so build_data.py overlays structural fields into data.json. Frontend consumers (Plan tab, candidate ladder, target behavior) start picking up t1_structural/t2_structural in parallel with legacy t1/t2.</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>server /api/ml cache-first + degenerate guard (done); align ml/feature_extractor.FEATURE_COLS to model n_features_in_ (pending)</t>
+          <t>Cutover requires: (1) one week of clean nightly precompute (no &gt;10 percent failure rate per scripts/precompute_targets.py exit code), (2) one clean te_regression run with errors &lt;= 1, (3) v2 dashboard frontend updated to read t1_structural fields when present (still falls back to t1 legacy when not). Until all three pass, leave flag=false.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -752,38 +752,38 @@
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="8" t="inlineStr"/>
     </row>
-    <row r="3" ht="90" customHeight="1">
+    <row r="3" ht="60" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-M25-CUTOVER</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>SCALE-2</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Targets</t>
+          <t>Auth · 500-user</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Structural targets · M2.5 — cutover gate (flip use_structural_targets=true)</t>
+          <t>Enforce per-user Supabase login (not shared basic-auth)</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Pending. After M2.1-2.4 settle in production (one week of nightly precompute + dashboard observation with flag=false), flip use_structural_targets=true in config/config.json so build_data.py overlays structural fields into data.json. Frontend consumers (Plan tab, candidate ladder, target behavior) start picking up t1_structural/t2_structural in parallel with legacy t1/t2.</t>
+          <t>Per-user UserPrefs isolation (NAV/plans/watchlist) only holds when users authenticate via Supabase; if they share the single basic-auth (gari/Swing2026), UserPrefs falls back to per-browser localStorage = no true per-user separation</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Cutover requires: (1) one week of clean nightly precompute (no &gt;10 percent failure rate per scripts/precompute_targets.py exit code), (2) one clean te_regression run with errors &lt;= 1, (3) v2 dashboard frontend updated to read t1_structural fields when present (still falls back to t1 legacy when not). Until all three pass, leave flag=false.</t>
+          <t>Require Supabase login for multi-user; verify UserPrefs keys per auth id end-to-end (user-prefs.jsx setUser binds sb.auth.getUser)</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
@@ -798,13 +798,13 @@
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="8" t="inlineStr"/>
     </row>
-    <row r="4" ht="60" customHeight="1">
+    <row r="4" ht="75" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>SCALE-2</t>
+          <t>BUG-WEEKEND-PHANTOM-PICKS</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
@@ -814,22 +814,22 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Auth · 500-user</t>
+          <t>Bugs / Audit Ledger</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Enforce per-user Supabase login (not shared basic-auth)</t>
+          <t>Weekend phantom picks in audit ledger</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Per-user UserPrefs isolation (NAV/plans/watchlist) only holds when users authenticate via Supabase; if they share the single basic-auth (gari/Swing2026), UserPrefs falls back to per-browser localStorage = no true per-user separation</t>
+          <t>Audit ledger shows phantom picks on May 10 (Sun), May 16 (Sat), May 17 (Sun) — markets closed. Likely a scan-date assignment bug (writing today's date to a Friday pick that re-scans on Sat/Sun, or weekend cron runs that should skip).</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Require Supabase login for multi-user; verify UserPrefs keys per auth id end-to-end (user-prefs.jsx setUser binds sb.auth.getUser)</t>
+          <t>Trace which writer emits these entries: check run_daily_scan.sh weekday gate, swing_trade.py scan-date logic, and infra/prototype/build_audit_ledger.py date assignment. Weekend launchd should be gated; if it runs intentionally for paper-resolve, mark those rows as REPLAY not PICK.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -844,13 +844,13 @@
       <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="8" t="inlineStr"/>
     </row>
-    <row r="5" ht="75" customHeight="1">
+    <row r="5" ht="60" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>BUG-WEEKEND-PHANTOM-PICKS</t>
+          <t>DATA-BROKEN-IPO-CALENDAR</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Bugs / Audit Ledger</t>
+          <t>Data / Calendars (broken)</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Weekend phantom picks in audit ledger</t>
+          <t>ipo_calendar — NASDAQ API times out</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Audit ledger shows phantom picks on May 10 (Sun), May 16 (Sat), May 17 (Sun) — markets closed. Likely a scan-date assignment bug (writing today's date to a Friday pick that re-scans on Sat/Sun, or weekend cron runs that should skip).</t>
+          <t>NASDAQ public IPO API times out from this host (~30s no response). Calendar slot is wired but produces 0 rows.</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Trace which writer emits these entries: check run_daily_scan.sh weekday gate, swing_trade.py scan-date logic, and infra/prototype/build_audit_ledger.py date assignment. Weekend launchd should be gated; if it runs intentionally for paper-resolve, mark those rows as REPLAY not PICK.</t>
+          <t>Investigate timeout first (UA headers / proxy / rate-limited IP) before alt-source. Candidate alternates: SEC S-1 filings via EDGAR full-text-search, IPO Monitor RSS, Yahoo Finance IPO page.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -896,7 +896,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>DATA-BROKEN-IPO-CALENDAR</t>
+          <t>DATA-BROKEN-CONGRESSIONAL-TRADES</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -906,22 +906,22 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Data / Calendars (broken)</t>
+          <t>Data / Catalysts (broken)</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>ipo_calendar — NASDAQ API times out</t>
+          <t>congressional_trades — sources dead</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>NASDAQ public IPO API times out from this host (~30s no response). Calendar slot is wired but produces 0 rows.</t>
+          <t>Senate Stock Watcher GitHub + S3 mirror both return dead/empty responses. The catalysts slot is wired but the scraper produces 0 rows.</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Investigate timeout first (UA headers / proxy / rate-limited IP) before alt-source. Candidate alternates: SEC S-1 filings via EDGAR full-text-search, IPO Monitor RSS, Yahoo Finance IPO page.</t>
+          <t>Replace dead source with direct efts.sec.gov integration (Form 4 XBRL parsing); add House Clerk site fallback for House STOCK Act filings. Scope: 1-2d dev + XBRL schema work. Free-data only per CLAUDE.md.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -942,7 +942,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>DATA-BROKEN-CONGRESSIONAL-TRADES</t>
+          <t>PARITY-REALTIME-DATA</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -952,22 +952,22 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Data / Catalysts (broken)</t>
+          <t>Data / Infrastructure / Platform Parity</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>congressional_trades — sources dead</t>
+          <t>Real-Time Data (streaming quotes)</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Senate Stock Watcher GitHub + S3 mirror both return dead/empty responses. The catalysts slot is wired but the scraper produces 0 rows.</t>
+          <t>Replace the 5-minute batch refresh with sub-second streaming quotes during market hours so charts + price ladder + Trade Plan PnL update in real time.</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Replace dead source with direct efts.sec.gov integration (Form 4 XBRL parsing); add House Clerk site fallback for House STOCK Act filings. Scope: 1-2d dev + XBRL schema work. Free-data only per CLAUDE.md.</t>
+          <t>Use the Schwab websocket feed (already in the paid stack — no new license per CLAUDE.md) into a local pub/sub buffer; kairos sub-tabs subscribe via SSE/WebSocket from server.py; cache TTL pinned at 1s during RTH.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
@@ -988,7 +988,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>PARITY-REALTIME-DATA</t>
+          <t>BARSTORE-1</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -998,22 +998,22 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Data / Infrastructure / Platform Parity</t>
+          <t>Data Infra / Bar-Store</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Real-Time Data (streaming quotes)</t>
+          <t>SQLite daily_bars schema + read/write</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Replace the 5-minute batch refresh with sub-second streaming quotes during market hours so charts + price ladder + Trade Plan PnL update in real time.</t>
+          <t>No local OHLCV history store exists; scans re-fetch per-ticker daily bars from EODHD (~10K calls/day, ~68% of 2026-06-08 usage; tripped 95K quota guard). See docs/scope_bar_store.md.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Use the Schwab websocket feed (already in the paid stack — no new license per CLAUDE.md) into a local pub/sub buffer; kairos sub-tabs subscribe via SSE/WebSocket from server.py; cache TTL pinned at 1s during RTH.</t>
+          <t>Add daily_bars(ticker,date,o,h,l,c,v,adjusted_close,source,ingested_at) to data/swingtrade.db (PK ticker+date, idx). Idempotent upsert writer + DB reader + tests. SQLite stays primary; no new deps.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>BARSTORE-1</t>
+          <t>BARSTORE-2</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -1049,17 +1049,17 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>SQLite daily_bars schema + read/write</t>
+          <t>One-time 20yr backfill</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>No local OHLCV history store exists; scans re-fetch per-ticker daily bars from EODHD (~10K calls/day, ~68% of 2026-06-08 usage; tripped 95K quota guard). See docs/scope_bar_store.md.</t>
+          <t>One eod(ticker,from_date=2005) returns full history = 1 call/ticker; backfilling the universe is ~6-8K calls ONCE vs ~10K/day recurring.</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Add daily_bars(ticker,date,o,h,l,c,v,adjusted_close,source,ingested_at) to data/swingtrade.db (PK ticker+date, idx). Idempotent upsert writer + DB reader + tests. SQLite stays primary; no new deps.</t>
+          <t>eodhd_client.backfill_history() pages the universe 1-call/ticker, paced under EODHD_SHARED_LIMITER (950/min), overnight launchd only, resumable. NO new license (uses existing EODHD).</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>BARSTORE-2</t>
+          <t>BARSTORE-3</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -1095,17 +1095,17 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>One-time 20yr backfill</t>
+          <t>DB-first failover in fetch_ohlcv_with_failover</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>One eod(ticker,from_date=2005) returns full history = 1 call/ticker; backfilling the universe is ~6-8K calls ONCE vs ~10K/day recurring.</t>
+          <t>Once history is local, scans/backtests must read DB-first and hit EODHD only for the current incomplete day + gaps.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>eodhd_client.backfill_history() pages the universe 1-call/ticker, paced under EODHD_SHARED_LIMITER (950/min), overnight launchd only, resumable. NO new license (uses existing EODHD).</t>
+          <t>Repoint data_fetcher.fetch_ohlcv_with_failover to read daily_bars first; EODHD fallback for today/gaps. Parity-check 100 tickers vs current cache/eodhd within float tol.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
@@ -1120,13 +1120,13 @@
       <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="8" t="inlineStr"/>
     </row>
-    <row r="11" ht="60" customHeight="1">
+    <row r="11" ht="75" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>BARSTORE-3</t>
+          <t>MODE-4</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -1136,22 +1136,22 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Data Infra / Bar-Store</t>
+          <t>Decision Engine</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>DB-first failover in fetch_ohlcv_with_failover</t>
+          <t>Walk-forward validation of Phase-3 per-mode pillar weights</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Once history is local, scans/backtests must read DB-first and hit EODHD only for the current incomplete day + gaps.</t>
+          <t>MODE-3 shipped intuition-based pillar weights without backtest evidence (principle 7 override). Need walk-forward validation that the per-mode weights don't degrade vs the single-set baseline.</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Repoint data_fetcher.fetch_ohlcv_with_failover to read daily_bars first; EODHD fallback for today/gaps. Parity-check 100 tickers vs current cache/eodhd within float tol.</t>
+          <t>scripts/validate_per_mode_weights.py: runs baseline backtest + 3 mode-weighted backtests (252d, min_score=50), compares WR/PF/maxDD/Sharpe per mode. Revert criterion: any mode ≤1.0× PF or ≤-5pp WR vs baseline → flip per_mode_pillar_reweight._enabled to false. See docs/per_mode_decisions_roadmap.md Phase 3.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
@@ -1166,13 +1166,13 @@
       <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="8" t="inlineStr"/>
     </row>
-    <row r="12" ht="75" customHeight="1">
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>MODE-4</t>
+          <t>SCALE-1</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -1182,22 +1182,22 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Decision Engine</t>
+          <t>Deployment · 500-user</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Walk-forward validation of Phase-3 per-mode pillar weights</t>
+          <t>Multi-worker server + concurrency load test</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>MODE-3 shipped intuition-based pillar weights without backtest evidence (principle 7 override). Need walk-forward validation that the per-mode weights don't degrade vs the single-set baseline.</t>
+          <t>Single uvicorn worker (uvicorn.run, no workers=); CPU-bound paths (65MB ML-file parse, scoring) block the event loop; untested at 500 concurrent on one Cloudflare tunnel</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>scripts/validate_per_mode_weights.py: runs baseline backtest + 3 mode-weighted backtests (252d, min_score=50), compares WR/PF/maxDD/Sharpe per mode. Revert criterion: any mode ≤1.0× PF or ≤-5pp WR vs baseline → flip per_mode_pillar_reweight._enabled to false. See docs/per_mode_decisions_roadmap.md Phase 3.</t>
+          <t>gunicorn/uvicorn --workers N (or app server), profile + offload blocking calls, run a 500-concurrent load test before certifying</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
@@ -1212,13 +1212,13 @@
       <c r="M12" s="3" t="inlineStr"/>
       <c r="N12" s="8" t="inlineStr"/>
     </row>
-    <row r="13" ht="60" customHeight="1">
+    <row r="13" ht="75" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>SCALE-1</t>
+          <t>PARITY-PAPER-TRADING-RT</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -1228,22 +1228,22 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Deployment · 500-user</t>
+          <t>Execution / Paper / Platform Parity</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Multi-worker server + concurrency load test</t>
+          <t>Real-Time Paper Trading</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Single uvicorn worker (uvicorn.run, no workers=); CPU-bound paths (65MB ML-file parse, scoring) block the event loop; untested at 500 concurrent on one Cloudflare tunnel</t>
+          <t>Execute simulated trades against live market prices via the Alpaca paper account; track fills, slippage and PnL in real time so paper validation mirrors what live trading would look like.</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>gunicorn/uvicorn --workers N (or app server), profile + offload blocking calls, run a 500-concurrent load test before certifying</t>
+          <t>Extend executor.py to route signals through the Alpaca paper REST + websocket API; webhook fills back into cache/portfolio.json; expose a 'Paper Trade' toggle on the Trade Plan card. Partially built (executor.py --submit), needs always-on wrapper.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
@@ -1258,13 +1258,13 @@
       <c r="M13" s="3" t="inlineStr"/>
       <c r="N13" s="8" t="inlineStr"/>
     </row>
-    <row r="14" ht="75" customHeight="1">
+    <row r="14" ht="45" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>PARITY-PAPER-TRADING-RT</t>
+          <t>REGIME-CONDITIONAL-MODELS</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -1274,22 +1274,22 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Execution / Paper / Platform Parity</t>
+          <t>ML / Accuracy</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Real-Time Paper Trading</t>
+          <t>Regime-conditional ML models (principle 5)</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Execute simulated trades against live market prices via the Alpaca paper account; track fills, slippage and PnL in real time so paper validation mirrors what live trading would look like.</t>
+          <t>train separate direction models per regime instead of one spanning all; #1 accuracy lever</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Extend executor.py to route signals through the Alpaca paper REST + websocket API; webhook fills back into cache/portfolio.json; expose a 'Paper Trade' toggle on the Trade Plan card. Partially built (executor.py --submit), needs always-on wrapper.</t>
+          <t>ml/train.py regime split</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>REGIME-CONDITIONAL-MODELS</t>
+          <t>OPS-1</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -1320,27 +1320,39 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>ML / Accuracy</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional ML models (principle 5)</t>
+          <t>Snapshot cleanup (scripts/cleanup_after_2026_05_16.sh)</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>train separate direction models per regime instead of one spanning all; #1 accuracy lever</t>
+          <t>Pre-Saturday session migration created intermediate snapshot files safe to remove after a week.</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>ml/train.py regime split</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="5" t="inlineStr"/>
-      <c r="J15" s="5" t="inlineStr"/>
+          <t>Run scripts/cleanup_after_2026_05_16.sh after 2026-05-16 cutoff.</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2 min</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Win: cleaner repo.</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Calendar reminder for 2026-05-16.</t>
+        </is>
+      </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1348,15 +1360,19 @@
       </c>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="3" t="inlineStr"/>
-      <c r="N15" s="8" t="inlineStr"/>
-    </row>
-    <row r="16" ht="45" customHeight="1">
+      <c r="N15" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>OPS-1</t>
+          <t>SCHWAB-REAUTH-PENDING</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -1366,39 +1382,27 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Ops / Schwab (operational)</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Snapshot cleanup (scripts/cleanup_after_2026_05_16.sh)</t>
+          <t>Schwab re-auth to unlock option Greeks</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Pre-Saturday session migration created intermediate snapshot files safe to remove after a week.</t>
+          <t>refresh token expired (invalid_grant, 7-day). Run python3 schwab_auth.py oauth -&gt; real option premiums/Greeks flow into the Options calc (currently honest BS-model fallback).</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Run scripts/cleanup_after_2026_05_16.sh after 2026-05-16 cutoff.</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2 min</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>Win: cleaner repo.</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>Calendar reminder for 2026-05-16.</t>
-        </is>
-      </c>
+          <t>user action: schwab_auth.py oauth</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
       <c r="K16" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1406,11 +1410,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="3" t="inlineStr"/>
-      <c r="N16" s="8" t="inlineStr">
-        <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
+      <c r="N16" s="8" t="inlineStr"/>
     </row>
     <row r="17" ht="60" customHeight="1">
       <c r="A17" s="2" t="n">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>SCHWAB-REAUTH-PENDING</t>
+          <t>QUANT-5</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -1428,27 +1428,39 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Ops / Schwab (operational)</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Schwab re-auth to unlock option Greeks</t>
+          <t>Mover predictor v3 — NLP earnings tone + options flow features</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>refresh token expired (invalid_grant, 7-day). Run python3 schwab_auth.py oauth -&gt; real option premiums/Greeks flow into the Options calc (currently honest BS-model fallback).</t>
+          <t>v1 had leakage. v2 fixed leakage but AUC stuck at 0.546 — pure technical features at entry don't predict mover success.</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>user action: schwab_auth.py oauth</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
+          <t>Build v3 with NEW feature classes (don't retrain): NLP earnings-call tone embeddings, options-flow IV skew + UOA put/call delta, catalyst-conditional models (subset by tag). A6 logger captures most inputs going forward.</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Caveat: exploratory research, not config-tuning.</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Don't retrain v1/v2 — both definitive AUC 0.546 negative.</t>
+        </is>
+      </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1456,15 +1468,19 @@
       </c>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="3" t="inlineStr"/>
-      <c r="N17" s="8" t="inlineStr"/>
-    </row>
-    <row r="18" ht="60" customHeight="1">
+      <c r="N17" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="165" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>QUANT-5</t>
+          <t>TV-RATING-CROSS-CHECK</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -1474,37 +1490,37 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Signals / Cross-Check</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Mover predictor v3 — NLP earnings tone + options flow features</t>
+          <t>Validate (or zero out) the ±3 TV-rating tech-score bonus</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>v1 had leakage. v2 fixed leakage but AUC stuck at 0.546 — pure technical features at entry don't predict mover success.</t>
+          <t>DISCOVERY 2026-05-11: TV-rating ±3 score bonus has been live in analysis.py:8627 for some time, modifying every BUY signal's technical pillar score. NO _validations entry, NO Wilson-CI, NO walk-forward justification for the ±3 magnitude. Worse: tv_rating was never captured on the 689 closed trades in picks_history or 1,301 signal_log entries — retroactive validation is impossible. Violates Principle 1 (n&lt;30 refusal) + Principle 7 (no knob-tweaking without evidence).</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Build v3 with NEW feature classes (don't retrain): NLP earnings-call tone embeddings, options-flow IV skew + UOA put/call delta, catalyst-conditional models (subset by tag). A6 logger captures most inputs going forward.</t>
+          <t>Phase 1 (SHIPPED 2026-05-11): (a) tv_bonus zeroed in analysis.py:8627 — score no longer mutated; (b) tv_recommendation + tv_rec_value + buy/sell/neutral counts now logged per signal in signal_tracker.log_signals() so prospective evidence accumulates; (c) tv_rating still surfaced in tech['details'] as INFORMATIONAL only — no score impact. Phase 2 (PENDING n&gt;=30, est. 6-12 weeks): run Wilson-LB(BUY|TV STRONG_BUY) vs Wilson-LB(BUY) over the prospectively-logged signals. If the agreement-conditional Wilson-LB beats unconditional by a meaningful margin (&gt;=3pp), re-enable with a magnitude justified by the regression. If not, kill the cross-check permanently (Principle 4 falsification — do not retune, do not lower the threshold).</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>Phase 1: hours (done). Phase 2: hours of analysis + calendar wait for n&gt;=30.</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Caveat: exploratory research, not config-tuning.</t>
+          <t>Mechanism (Principle 2): TV rating is an independent server-side aggregation of ~26 indicators. Two independent technical aggregations may improve precision over our 5-pillar score alone. Falsification (Principle 4): if agreement-conditional Wilson-LB &lt;= unconditional after n&gt;=30, the cross-check has no edge — kill, don't retune. Risk of CURRENT state (Phase 1): we have been over-weighting TV-STRONG_BUY signals by +3 tech-pts with zero evidence; this could have systematically biased BUY selection. Capping at 0 removes that bias going forward but does not undo past trade selection bias.</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Don't retrain v1/v2 — both definitive AUC 0.546 negative.</t>
+          <t>Default apply_to_score=false locked. Validation requires logged tv_rating on &gt;=30 CLOSED BUY trades (currently 0). Earliest Phase-2 validation window: ~6-12 weeks of scans from 2026-05-11. Pairs with the v2 dashboard TV sub-tab (infra/prototype/subtabs/tv/) which is iframe-only today. Do NOT add per-mode / per-regime elaboration until Phase 2 evidence justifies even the basic bonus.</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
@@ -1516,17 +1532,17 @@
       <c r="M18" s="3" t="inlineStr"/>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="165" customHeight="1">
+          <t>Phase 1 smoke: run python3 swing_trade.py and confirm (1) tech['details']['tv_rating'] still appears in deep-dive output labeled 'informational — bonus disabled pending validation'; (2) signal_log.json entries for new scans contain tv_recommendation + tv_rec_value + buy/sell/neutral_count populated. Phase 2 trigger: when `python3 -c 'import json; print(sum(1 for r in json.load(open("data/signal_log.json")) if r.get("tv_recommendation") and r.get("result")))'` &gt;= 30, run the agreement-conditional Wilson-LB analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="90" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>TV-RATING-CROSS-CHECK</t>
+          <t>TEST-MAE-MFE</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -1536,39 +1552,27 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Signals / Cross-Check</t>
+          <t>Testing / Validation (Tier 1)</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Validate (or zero out) the ±3 TV-rating tech-score bonus</t>
+          <t>MAE / MFE Analyzer — tune stops + targets from data</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>DISCOVERY 2026-05-11: TV-rating ±3 score bonus has been live in analysis.py:8627 for some time, modifying every BUY signal's technical pillar score. NO _validations entry, NO Wilson-CI, NO walk-forward justification for the ±3 magnitude. Worse: tv_rating was never captured on the 689 closed trades in picks_history or 1,301 signal_log entries — retroactive validation is impossible. Violates Principle 1 (n&lt;30 refusal) + Principle 7 (no knob-tweaking without evidence).</t>
+          <t>Maximum Adverse Excursion vs Maximum Favorable Excursion analyzer. signal_log.json already tracks mae_pct + mfe_pct for closed trades. Output: 'Stops triggered at -5% on winners that later hit +20% → stops too tight' or 'Trades exited at +6% target left avg +12% on table → targets too conservative'. Directly improves trade-plan math.</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 (SHIPPED 2026-05-11): (a) tv_bonus zeroed in analysis.py:8627 — score no longer mutated; (b) tv_recommendation + tv_rec_value + buy/sell/neutral counts now logged per signal in signal_tracker.log_signals() so prospective evidence accumulates; (c) tv_rating still surfaced in tech['details'] as INFORMATIONAL only — no score impact. Phase 2 (PENDING n&gt;=30, est. 6-12 weeks): run Wilson-LB(BUY|TV STRONG_BUY) vs Wilson-LB(BUY) over the prospectively-logged signals. If the agreement-conditional Wilson-LB beats unconditional by a meaningful margin (&gt;=3pp), re-enable with a magnitude justified by the regression. If not, kill the cross-check permanently (Principle 4 falsification — do not retune, do not lower the threshold).</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Phase 1: hours (done). Phase 2: hours of analysis + calendar wait for n&gt;=30.</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>Mechanism (Principle 2): TV rating is an independent server-side aggregation of ~26 indicators. Two independent technical aggregations may improve precision over our 5-pillar score alone. Falsification (Principle 4): if agreement-conditional Wilson-LB &lt;= unconditional after n&gt;=30, the cross-check has no edge — kill, don't retune. Risk of CURRENT state (Phase 1): we have been over-weighting TV-STRONG_BUY signals by +3 tech-pts with zero evidence; this could have systematically biased BUY selection. Capping at 0 removes that bias going forward but does not undo past trade selection bias.</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>Default apply_to_score=false locked. Validation requires logged tv_rating on &gt;=30 CLOSED BUY trades (currently 0). Earliest Phase-2 validation window: ~6-12 weeks of scans from 2026-05-11. Pairs with the v2 dashboard TV sub-tab (infra/prototype/subtabs/tv/) which is iframe-only today. Do NOT add per-mode / per-regime elaboration until Phase 2 evidence justifies even the basic bonus.</t>
-        </is>
-      </c>
+          <t>Read signal_log.json closed entries; scatter-plot mae vs realized PnL + mfe vs realized PnL; quantile bins (10/25/50/75/90); render as a new Testing tab card. Effort ~30min — data already there.</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
       <c r="K19" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1576,11 +1580,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="3" t="inlineStr"/>
-      <c r="N19" s="8" t="inlineStr">
-        <is>
-          <t>Phase 1 smoke: run python3 swing_trade.py and confirm (1) tech['details']['tv_rating'] still appears in deep-dive output labeled 'informational — bonus disabled pending validation'; (2) signal_log.json entries for new scans contain tv_recommendation + tv_rec_value + buy/sell/neutral_count populated. Phase 2 trigger: when `python3 -c 'import json; print(sum(1 for r in json.load(open("data/signal_log.json")) if r.get("tv_recommendation") and r.get("result")))'` &gt;= 30, run the agreement-conditional Wilson-LB analysis.</t>
-        </is>
-      </c>
+      <c r="N19" s="8" t="inlineStr"/>
     </row>
     <row r="20" ht="90" customHeight="1">
       <c r="A20" s="2" t="n">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>TEST-MAE-MFE</t>
+          <t>TEST-MC-BOOTSTRAP</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -1603,17 +1603,17 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>MAE / MFE Analyzer — tune stops + targets from data</t>
+          <t>Monte Carlo Bootstrap — confidence intervals on Sharpe/PF/WR</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Maximum Adverse Excursion vs Maximum Favorable Excursion analyzer. signal_log.json already tracks mae_pct + mfe_pct for closed trades. Output: 'Stops triggered at -5% on winners that later hit +20% → stops too tight' or 'Trades exited at +6% target left avg +12% on table → targets too conservative'. Directly improves trade-plan math.</t>
+          <t>Randomly resample closed trades 10,000x to build distributions over each metric. Wilson LB only covers WR; this covers Sharpe, Sortino, PF, max-DD, hit-rate, payoff ratio. Output: 'Sharpe 1.42, 95% CI [0.88, 1.94]' — you would know whether 1.42 is robust or noise. Standard hedge-fund metric, supports principle #1 (statistical rigor).</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Read signal_log.json closed entries; scatter-plot mae vs realized PnL + mfe vs realized PnL; quantile bins (10/25/50/75/90); render as a new Testing tab card. Effort ~30min — data already there.</t>
+          <t>Numpy bootstrap on signal_log trade PnL array, k=10000 resamples; compute distributions over each metric; render percentile bands. Effort 1-2hr.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>TEST-MC-BOOTSTRAP</t>
+          <t>TEST-PERMUTATION</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -1649,17 +1649,17 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Monte Carlo Bootstrap — confidence intervals on Sharpe/PF/WR</t>
+          <t>Permutation Test — is the edge REAL or coin flip?</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Randomly resample closed trades 10,000x to build distributions over each metric. Wilson LB only covers WR; this covers Sharpe, Sortino, PF, max-DD, hit-rate, payoff ratio. Output: 'Sharpe 1.42, 95% CI [0.88, 1.94]' — you would know whether 1.42 is robust or noise. Standard hedge-fund metric, supports principle #1 (statistical rigor).</t>
+          <t>Randomly shuffle BUY/SELL/AVOID labels on historical signals 1000x, recompute strategy returns. If real returns are not significantly better than scrambled returns, there is no edge. Direct test of principle #4 (adversarial mindset / falsification). Output: 'Real strategy: +18.7%. Random labels (1000 sims): +0.2% +/- 4.1%. p-value: 0.0001'.</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Numpy bootstrap on signal_log trade PnL array, k=10000 resamples; compute distributions over each metric; render percentile bands. Effort 1-2hr.</t>
+          <t>Shuffle decision-column of signal_log 1000x; recompute portfolio return per shuffle; rank real return vs null distribution; report p-value. Effort ~1hr.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>TEST-PERMUTATION</t>
+          <t>TEST-REGIME-COND</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Permutation Test — is the edge REAL or coin flip?</t>
+          <t>Regime-Conditional Performance — where does it work?</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Randomly shuffle BUY/SELL/AVOID labels on historical signals 1000x, recompute strategy returns. If real returns are not significantly better than scrambled returns, there is no edge. Direct test of principle #4 (adversarial mindset / falsification). Output: 'Real strategy: +18.7%. Random labels (1000 sims): +0.2% +/- 4.1%. p-value: 0.0001'.</t>
+          <t>Partition closed trades by regime (risk_on_trending / choppy / risk_off / panic) and compute WR / PF / Sharpe per regime. Per principle #5 (regime conditioning over averages). Example output: 'Trend Continuation WR: 41% overall · 62% in risk_on_trending · 18% in choppy'. Tells you which sleeves to size up/down per regime.</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Shuffle decision-column of signal_log 1000x; recompute portfolio return per shuffle; rank real return vs null distribution; report p-value. Effort ~1hr.</t>
+          <t>Group signal_log entries by regime_at_signal (already logged); compute Wilson LB on WR + bootstrapped PF/Sharpe per regime; output a (setup x regime) heatmap. Effort ~1hr.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
@@ -1720,38 +1720,38 @@
       <c r="M22" s="3" t="inlineStr"/>
       <c r="N22" s="8" t="inlineStr"/>
     </row>
-    <row r="23" ht="90" customHeight="1">
+    <row r="23" ht="60" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>TEST-REGIME-COND</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>PARITY-BACKTEST-UI</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Testing / Validation (Tier 1)</t>
+          <t>Backtesting / Platform Parity</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Regime-Conditional Performance — where does it work?</t>
+          <t>In-app Backtesting UI</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Partition closed trades by regime (risk_on_trending / choppy / risk_off / panic) and compute WR / PF / Sharpe per regime. Per principle #5 (regime conditioning over averages). Example output: 'Trend Continuation WR: 41% overall · 62% in risk_on_trending · 18% in choppy'. Tells you which sleeves to size up/down per regime.</t>
+          <t>Expose backtest.py + walk_forward_v2.py inside the kairos UI — a user picks a strategy/date range/universe and runs it without dropping to the terminal.</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Group signal_log entries by regime_at_signal (already logged); compute Wilson LB on WR + bootstrapped PF/Sharpe per regime; output a (setup x regime) heatmap. Effort ~1hr.</t>
+          <t>Add a 'Backtest' workspace in the kairos sidebar; wire a form to a /v2/backtest endpoint that shells out to backtest.py and streams stdout via SSE; render Sharpe / PF / Wilson-LB / equity curve when the run completes.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>PARITY-BACKTEST-UI</t>
+          <t>BUG-MISSING-D1S</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
@@ -1782,22 +1782,22 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Backtesting / Platform Parity</t>
+          <t>Bugs / Audit Ledger</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>In-app Backtesting UI</t>
+          <t>4 missing D1s for May 15 (out of 87)</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Expose backtest.py + walk_forward_v2.py inside the kairos UI — a user picks a strategy/date range/universe and runs it without dropping to the terminal.</t>
+          <t>4 of 87 May-15 picks have null D1 (next-day close). Probably thin EODHD coverage on small-caps — acceptable noise band but worth confirming.</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Add a 'Backtest' workspace in the kairos sidebar; wire a form to a /v2/backtest endpoint that shells out to backtest.py and streams stdout via SSE; render Sharpe / PF / Wilson-LB / equity curve when the run completes.</t>
+          <t>Identify the 4 tickers; check EODHD eod() response for each on 2026-05-16; if EODHD returned null, document as known-limitation; if EODHD returned a value, fix the ingest. Effort ~20min.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>BUG-MISSING-D1S</t>
+          <t>PARITY-CHANNEL-BAR</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -1828,22 +1828,22 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Bugs / Audit Ledger</t>
+          <t>Chart Indicators / Platform Parity</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>4 missing D1s for May 15 (out of 87)</t>
+          <t>Channel Bar overlay</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>4 of 87 May-15 picks have null D1 (next-day close). Probably thin EODHD coverage on small-caps — acceptable noise band but worth confirming.</t>
+          <t>Donchian / Keltner / Bollinger envelope overlay on the chart — top + bottom band with mid-line.</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Identify the 4 tickers; check EODHD eod() response for each on 2026-05-16; if EODHD returned null, document as known-limitation; if EODHD returned a value, fix the ingest. Effort ~20min.</t>
+          <t>Compute channels via pandas-ta in feature_extractor.py (or live in chart.js using bar data); render as semi-transparent band; toggle in the Chart sub-tab control bar.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>PARITY-CHANNEL-BAR</t>
+          <t>PARITY-RBI-GBI-WINDOW</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -1879,17 +1879,17 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Channel Bar overlay</t>
+          <t>RBI/GBI Window (regime bias bands)</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Donchian / Keltner / Bollinger envelope overlay on the chart — top + bottom band with mid-line.</t>
+          <t>Color-coded vertical bands on the chart timeline showing risk-on (green/GBI) vs risk-off (red/RBI) regime windows so the user can see at-a-glance whether prior price action happened in a hostile or friendly regime.</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Compute channels via pandas-ta in feature_extractor.py (or live in chart.js using bar data); render as semi-transparent band; toggle in the Chart sub-tab control bar.</t>
+          <t>Read cache/regime_history.json and draw vertical color bands at each regime transition on the chart canvas; tooltip explains the regime classification (4-regime model: risk_on_trending / risk_on_choppy / risk_off_trending / panic).</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
@@ -1904,13 +1904,13 @@
       <c r="M26" s="3" t="inlineStr"/>
       <c r="N26" s="8" t="inlineStr"/>
     </row>
-    <row r="27" ht="60" customHeight="1">
+    <row r="27" ht="45" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>PARITY-RBI-GBI-WINDOW</t>
+          <t>CLEAN-HOT-SECTORS-DEAD</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -1920,22 +1920,22 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Chart Indicators / Platform Parity</t>
+          <t>Code Cleanup</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>RBI/GBI Window (regime bias bands)</t>
+          <t>panelHotSectors() dead-code in kairos.html</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Color-coded vertical bands on the chart timeline showing risk-on (green/GBI) vs risk-off (red/RBI) regime windows so the user can see at-a-glance whether prior price action happened in a hostile or friendly regime.</t>
+          <t>Hot Sectors panel was removed from the Signal Scanner grid but the panelHotSectors() function is still defined in kairos.html — dead code.</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Read cache/regime_history.json and draw vertical color bands at each regime transition on the chart canvas; tooltip explains the regime classification (4-regime model: risk_on_trending / risk_on_choppy / risk_off_trending / panic).</t>
+          <t>grep for panelHotSectors callers; delete function + any unused helpers; verify no console errors. Effort ~2min.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr"/>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-HOT-SECTORS-DEAD</t>
+          <t>CLEAN-4</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -1966,27 +1966,39 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>panelHotSectors() dead-code in kairos.html</t>
+          <t>scripts/migrate_role_capabilities.py — cleanup after 2026-05-16</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Hot Sectors panel was removed from the Signal Scanner grid but the panelHotSectors() function is still defined in kairos.html — dead code.</t>
+          <t>One-shot CapStudio backfill. Already run. Tied to OPS-1 cleanup window.</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>grep for panelHotSectors callers; delete function + any unused helpers; verify no console errors. Effort ~2min.</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
+          <t>Delete during OPS-1 cleanup pass after 2026-05-16.</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>1 min</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Win: -X lines.</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>Couples with OPS-1.</t>
+        </is>
+      </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1994,15 +2006,19 @@
       </c>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="3" t="inlineStr"/>
-      <c r="N28" s="8" t="inlineStr"/>
-    </row>
-    <row r="29" ht="45" customHeight="1">
+      <c r="N28" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-4</t>
+          <t>DATA-FUTURE-EARNINGS-CAL-PIT</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -2012,39 +2028,27 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Data / Calendars (future)</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>scripts/migrate_role_capabilities.py — cleanup after 2026-05-16</t>
+          <t>earnings_calendar_pit — point-in-time integrity</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>One-shot CapStudio backfill. Already run. Tied to OPS-1 cleanup window.</t>
+          <t>Earnings calendar with point-in-time integrity (what was expected when). Needed for clean PEAD backtest replay; today's calendar uses the most-recent snapshot only, which leaks future revisions into prior dates.</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Delete during OPS-1 cleanup pass after 2026-05-16.</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>1 min</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>Win: -X lines.</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>Couples with OPS-1.</t>
-        </is>
-      </c>
+          <t>Snapshot the EODHD earnings calendar daily into a versioned earnings_calendar_history table; join on (ticker, report_date, snapshot_date) for PIT correctness in PEAD backtests.</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
       <c r="K29" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -2052,19 +2056,15 @@
       </c>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="3" t="inlineStr"/>
-      <c r="N29" s="8" t="inlineStr">
-        <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="60" customHeight="1">
+      <c r="N29" s="8" t="inlineStr"/>
+    </row>
+    <row r="30" ht="45" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-EARNINGS-CAL-PIT</t>
+          <t>DATA-FUTURE-ECONOMIC-CAL</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -2079,17 +2079,17 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>earnings_calendar_pit — point-in-time integrity</t>
+          <t>economic_calendar — CPI/PCE/NFP/FOMC dates</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Earnings calendar with point-in-time integrity (what was expected when). Needed for clean PEAD backtest replay; today's calendar uses the most-recent snapshot only, which leaks future revisions into prior dates.</t>
+          <t>Macro event calendar with consensus expectations. No source wired today; the pre-FOMC sleeve uses hard-coded FOMC dates and there is no CPI/PCE/NFP awareness.</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Snapshot the EODHD earnings calendar daily into a versioned earnings_calendar_history table; join on (ticker, report_date, snapshot_date) for PIT correctness in PEAD backtests.</t>
+          <t>Investing.com calendar scrape OR Trading Economics free tier; daily refresh; write to economic_calendar; feed pre-FOMC sleeve + risk_off blackout windows.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-ECONOMIC-CAL</t>
+          <t>DATA-FUTURE-FDA-CAL</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -2125,17 +2125,17 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>economic_calendar — CPI/PCE/NFP/FOMC dates</t>
+          <t>fda_calendar — PDUFA / AdCom dates</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Macro event calendar with consensus expectations. No source wired today; the pre-FOMC sleeve uses hard-coded FOMC dates and there is no CPI/PCE/NFP awareness.</t>
+          <t>FDA decision calendar (PDUFA dates, Advisory Committee meetings) for biotech catalyst tracking.</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Investing.com calendar scrape OR Trading Economics free tier; daily refresh; write to economic_calendar; feed pre-FOMC sleeve + risk_off blackout windows.</t>
+          <t>FDA public calendar scrape + BiopharmCatalyst free RSS; write to fda_calendar; surface as catalyst tier in any biotech sleeve.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-FDA-CAL</t>
+          <t>DATA-EMPTY-SPLITS-CALENDAR</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -2166,22 +2166,22 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Data / Calendars (future)</t>
+          <t>Data / Corporate Actions (empty by sample)</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>fda_calendar — PDUFA / AdCom dates</t>
+          <t>splits_calendar — 0 splits in current universe sample</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>FDA decision calendar (PDUFA dates, Advisory Committee meetings) for biotech catalyst tracking.</t>
+          <t>corporate_actions table populates from EODHD but the current universe sample (449 tickers) had 0 splits in the recent window. Calendar reads empty.</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>FDA public calendar scrape + BiopharmCatalyst free RSS; write to fda_calendar; surface as catalyst tier in any biotech sleeve.</t>
+          <t>Expand corporate-actions polling universe to S&amp;P 500 + Russell 1000 (universe list already available); 1-line change in the populator script.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>DATA-EMPTY-SPLITS-CALENDAR</t>
+          <t>DATA-EMPTY-MODEL-CALIBRATION</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
@@ -2212,22 +2212,22 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Data / Corporate Actions (empty by sample)</t>
+          <t>Data / ML (empty by design)</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>splits_calendar — 0 splits in current universe sample</t>
+          <t>model_calibration — waiting on realization</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>corporate_actions table populates from EODHD but the current universe sample (449 tickers) had 0 splits in the recent window. Calendar reads empty.</t>
+          <t>Calibration metrics table has no rows because the 5-20 day prediction horizons have not elapsed yet (today's predictions realize over 1-4 weeks).</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Expand corporate-actions polling universe to S&amp;P 500 + Russell 1000 (universe list already available); 1-line change in the populator script.</t>
+          <t>No code action; populates passively as time passes. Re-check after 2026-06-15 (30d post-shipping).</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr"/>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>DATA-EMPTY-MODEL-CALIBRATION</t>
+          <t>DATA-EMPTY-VAR-BREACHES</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
@@ -2258,22 +2258,22 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Data / ML (empty by design)</t>
+          <t>Data / Risk (empty by design)</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>model_calibration — waiting on realization</t>
+          <t>var_breaches — waiting on snapshots + drawdown</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Calibration metrics table has no rows because the 5-20 day prediction horizons have not elapsed yet (today's predictions realize over 1-4 weeks).</t>
+          <t>VaR breach log empty because (1) daily portfolio_risk snapshots are still ramping up and (2) no real drawdown day has happened to trigger a breach.</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>No code action; populates passively as time passes. Re-check after 2026-06-15 (30d post-shipping).</t>
+          <t>No code action; populates passively. Re-check after first portfolio drawdown &gt;2% or after 60 daily snapshots.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
@@ -2288,13 +2288,13 @@
       <c r="M34" s="3" t="inlineStr"/>
       <c r="N34" s="8" t="inlineStr"/>
     </row>
-    <row r="35" ht="45" customHeight="1">
+    <row r="35" ht="60" customHeight="1">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>DATA-EMPTY-VAR-BREACHES</t>
+          <t>DATA-FUTURE-INSIDER-EDGAR</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
@@ -2304,22 +2304,22 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Data / Risk (empty by design)</t>
+          <t>Data / SEC EDGAR (future)</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>var_breaches — waiting on snapshots + drawdown</t>
+          <t>insider_transactions via Form 4 XBRL</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>VaR breach log empty because (1) daily portfolio_risk snapshots are still ramping up and (2) no real drawdown day has happened to trigger a breach.</t>
+          <t>Per-ticker insider buy/sell stream sourced direct from SEC Form 4 filings. Today sourced indirectly via Finviz Elite bulk; direct EDGAR is point-in-time accurate and free.</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>No code action; populates passively. Re-check after first portfolio drawdown &gt;2% or after 60 daily snapshots.</t>
+          <t>Build Form 4 XBRL parser; daily ingest from efts.sec.gov; write to insider_transactions table; reconcile against Finviz bulk for cross-check.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
@@ -2334,13 +2334,13 @@
       <c r="M35" s="3" t="inlineStr"/>
       <c r="N35" s="8" t="inlineStr"/>
     </row>
-    <row r="36" ht="60" customHeight="1">
+    <row r="36" ht="45" customHeight="1">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-INSIDER-EDGAR</t>
+          <t>DATA-FUTURE-INSTITUTIONAL-EDGAR</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
@@ -2355,17 +2355,17 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>insider_transactions via Form 4 XBRL</t>
+          <t>institutional_holdings via 13F XBRL</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Per-ticker insider buy/sell stream sourced direct from SEC Form 4 filings. Today sourced indirectly via Finviz Elite bulk; direct EDGAR is point-in-time accurate and free.</t>
+          <t>Per-ticker institutional ownership tracking (Form 13F, quarterly). Useful for the Smart Money pillar; today only Finviz inst_own_pct snapshot.</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Build Form 4 XBRL parser; daily ingest from efts.sec.gov; write to insider_transactions table; reconcile against Finviz bulk for cross-check.</t>
+          <t>13F XBRL parser; quarterly ingest from EDGAR; write to institutional_holdings table with the 45-day reporting lag accounted for in any backtest joins.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-INSTITUTIONAL-EDGAR</t>
+          <t>DATA-FUTURE-CONGRESSIONAL-EDGAR</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
@@ -2396,22 +2396,22 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Data / SEC EDGAR (future)</t>
+          <t>Data / SEC EDGAR (future, alt for broken)</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>institutional_holdings via 13F XBRL</t>
+          <t>congressional_trades via EDGAR / House Clerk (alt source)</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Per-ticker institutional ownership tracking (Form 13F, quarterly). Useful for the Smart Money pillar; today only Finviz inst_own_pct snapshot.</t>
+          <t>Alternate sourcing for congressional trades after Senate Stock Watcher death (see DATA-BROKEN-CONGRESSIONAL-TRADES). Direct from House Clerk + Senate eFD.</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>13F XBRL parser; quarterly ingest from EDGAR; write to institutional_holdings table with the 45-day reporting lag accounted for in any backtest joins.</t>
+          <t>Scrape House STOCK Act PTR PDFs (House Clerk site); Senate eFD JSON; merge into normalized congressional_trades table.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-CONGRESSIONAL-EDGAR</t>
+          <t>SUPABASE-SYNC-VERIFY</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
@@ -2442,22 +2442,22 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Data / SEC EDGAR (future, alt for broken)</t>
+          <t>Data / Supabase</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>congressional_trades via EDGAR / House Clerk (alt source)</t>
+          <t>Verify supabase_analysis_sync actually writes</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Alternate sourcing for congressional trades after Senate Stock Watcher death (see DATA-BROKEN-CONGRESSIONAL-TRADES). Direct from House Clerk + Senate eFD.</t>
+          <t>confirm sync_scan writes (psycopg2 raw SQL not .table API); not silent no-op</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Scrape House STOCK Act PTR PDFs (House Clerk site); Senate eFD JSON; merge into normalized congressional_trades table.</t>
+          <t>supabase_analysis_sync.py</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
@@ -2472,13 +2472,13 @@
       <c r="M38" s="3" t="inlineStr"/>
       <c r="N38" s="8" t="inlineStr"/>
     </row>
-    <row r="39" ht="45" customHeight="1">
+    <row r="39" ht="60" customHeight="1">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>SUPABASE-SYNC-VERIFY</t>
+          <t>DATA-EMPTY-PROD-ENGINE-DEFERRED</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
@@ -2488,22 +2488,22 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Data / Supabase</t>
+          <t>Data / Telemetry (deferred for safety)</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Verify supabase_analysis_sync actually writes</t>
+          <t>8 empty slots — production-engine touches deferred</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>confirm sync_scan writes (psycopg2 raw SQL not .table API); not silent no-op</t>
+          <t>8 telemetry/data slots remain empty because populating them requires editing backtest.py / executor.py / signal_filter.py / analysis.py. Deliberately deferred to avoid risk to the live scan + exec paths.</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>supabase_analysis_sync.py</t>
+          <t>Enumerate the 8 specifically and grade each one for in-place vs side-car instrumentation. Side-car (write to telemetry DB without changing decision flow) is preferred over hot-path edits.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr"/>
@@ -2518,13 +2518,13 @@
       <c r="M39" s="3" t="inlineStr"/>
       <c r="N39" s="8" t="inlineStr"/>
     </row>
-    <row r="40" ht="60" customHeight="1">
+    <row r="40" ht="45" customHeight="1">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>DATA-EMPTY-PROD-ENGINE-DEFERRED</t>
+          <t>BARSTORE-4</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
@@ -2534,22 +2534,22 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Data / Telemetry (deferred for safety)</t>
+          <t>Data Infra / Bar-Store</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>8 empty slots — production-engine touches deferred</t>
+          <t>Daily incremental via bulk_eod</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>8 telemetry/data slots remain empty because populating them requires editing backtest.py / executor.py / signal_filter.py / analysis.py. Deliberately deferred to avoid risk to the live scan + exec paths.</t>
+          <t>After backfill, only the latest bar is needed daily; bulk_eod returns the whole exchange in 1 call.</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Enumerate the 8 specifically and grade each one for in-place vs side-car instrumentation. Side-car (write to telemetry DB without changing decision flow) is preferred over hot-path edits.</t>
+          <t>Daily launchd job: 1 bulk_eod(exchange) appends last-day bar for all tickers into daily_bars. Target &lt;=2 EODHD calls/day total for OHLCV.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>BARSTORE-4</t>
+          <t>BARSTORE-5</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
@@ -2585,17 +2585,17 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Daily incremental via bulk_eod</t>
+          <t>Corporate-action re-adjustment</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>After backfill, only the latest bar is needed daily; bulk_eod returns the whole exchange in 1 call.</t>
+          <t>Stored history must stay split/div-adjusted; a new split re-bases all prior bars. This is where data-integrity bugs hide.</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Daily launchd job: 1 bulk_eod(exchange) appends last-day bar for all tickers into daily_bars. Target &lt;=2 EODHD calls/day total for OHLCV.</t>
+          <t>Store raw + adjusted_close; small daily job re-adjusts history on split/div events (EODHD div/splits endpoints). Validate no adjustment drift.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
@@ -2610,13 +2610,13 @@
       <c r="M41" s="3" t="inlineStr"/>
       <c r="N41" s="8" t="inlineStr"/>
     </row>
-    <row r="42" ht="45" customHeight="1">
+    <row r="42" ht="60" customHeight="1">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>BARSTORE-5</t>
+          <t>BARSTORE-6</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
@@ -2631,17 +2631,17 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Corporate-action re-adjustment</t>
+          <t>Delisted backfill -&gt; survivorship fix</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Stored history must stay split/div-adjusted; a new split re-bases all prior bars. This is where data-integrity bugs hide.</t>
+          <t>Honest backtests need delisted tickers' history + point-in-time membership (membership snapshots already DONE via AIPRED-SURVIVORSHIP). Unblocks audit #1.</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>Store raw + adjusted_close; small daily job re-adjusts history on split/div events (EODHD div/splits endpoints). Validate no adjustment drift.</t>
+          <t>Backfill delisted-ticker history into daily_bars; point walk_forward_v2 at DB over 20yr. Enables survivorship-bias-free backtests + free validation of staged accuracy tweaks.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>BARSTORE-6</t>
+          <t>EODHD-WIRES-VALIDATE</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
@@ -2672,22 +2672,22 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Data Infra / Bar-Store</t>
+          <t>Data Wiring (validate)</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Delisted backfill -&gt; survivorship fix</t>
+          <t>Validate EODHD-side wires on quota reset</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Honest backtests need delisted tickers' history + point-in-time membership (membership snapshots already DONE via AIPRED-SURVIVORSHIP). Unblocks audit #1.</t>
+          <t>DCF net-debt/FCF + per-name beta + Book Risk crowding are code-complete + fallback-safe but untested against live EODHD (quota was exhausted). Confirm real values flow after reset.</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Backfill delisted-ticker history into daily_bars; point walk_forward_v2 at DB over 20yr. Enables survivorship-bias-free backtests + free validation of staged accuracy tweaks.</t>
+          <t>Stocksmith.html /api/fundamentals consumers</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
@@ -2702,13 +2702,13 @@
       <c r="M43" s="3" t="inlineStr"/>
       <c r="N43" s="8" t="inlineStr"/>
     </row>
-    <row r="44" ht="60" customHeight="1">
+    <row r="44" ht="105" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>EODHD-WIRES-VALIDATE</t>
+          <t>OVERVIEW-VERDICT-RECON</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
@@ -2718,27 +2718,31 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Data Wiring (validate)</t>
+          <t>Decision Engine</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Validate EODHD-side wires on quota reset</t>
+          <t>Reconcile compute_final_verdict (stage) vs decisions_by_mode</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>DCF net-debt/FCF + per-name beta + Book Risk crowding are code-complete + fallback-safe but untested against live EODHD (quota was exhausted). Confirm real values flow after reset.</t>
+          <t>Two engines emit different swing score+verdict for the same name (FTNT: stage=BUY/67 vs decisions_by_mode.swing=WATCH/57). decisions_by_mode omits the catalyst-sleeve EXTENDED-entry relaxation that compute_final_verdict applies, so they disagree.</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>Stocksmith.html /api/fundamentals consumers</t>
+          <t>Have decisions_by_mode consume the same relaxation OR emit a diverges-from-composite flag; decide direction after the entry-quality EXTENDED/MISSED A/B validation lands. Display already fixed (overview.js binds stage).</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="5" t="inlineStr"/>
-      <c r="J44" s="5" t="inlineStr"/>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>PATH B (2026-06-09): also propagate the engine per-mode composite_score (analysis.py:8387 mode_score) into decisions_by_mode so composite-verdict.jsx + Overview can BIND a real per-mode score instead of recomputing. composite-verdict.jsx Path A shipped (binds canonical ticker.score as headline, lenses=why only); per-mode engine score is the deferred Path B. Resolve alongside the stage-vs-decisions_by_mode verdict question.</t>
+        </is>
+      </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -2754,7 +2758,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>OVERVIEW-VERDICT-RECON</t>
+          <t>KAIROS-TRAFFIC-LIGHT-INPUTS</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
@@ -2764,22 +2768,22 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Decision Engine</t>
+          <t>Detail Lens / Traffic Lights</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Reconcile compute_final_verdict (stage) vs decisions_by_mode</t>
+          <t>Per-ticker risk/fundamentals inputs for lens dots</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Two engines emit different swing score+verdict for the same name (FTNT: stage=BUY/67 vs decisions_by_mode.swing=WATCH/57). decisions_by_mode omits the catalyst-sleeve EXTENDED-entry relaxation that compute_final_verdict applies, so they disagree.</t>
+          <t>Wire t.f_score · t.altman_z · t.roic · t.wacc · t.sharpe_1y · t.dd_recovery_months · t.peer_rank · t.is_held into build_data.py. _qdComputeLensStatus has cascading fallbacks (PEG → fund_score → F-score; beta → kelly → Sharpe), so dots upgrade automatically as fields land.</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Have decisions_by_mode consume the same relaxation OR emit a diverges-from-composite flag; decide direction after the entry-quality EXTENDED/MISSED A/B validation lands. Display already fixed (overview.js binds stage).</t>
+          <t>Compute in analysis.py / portfolio.py: Piotroski F (existing data), Altman Z (existing data), ROIC vs WACC, 1y Sharpe from price history, peer_rank from cohort, is_held from portfolio_state.json.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
@@ -2794,13 +2798,13 @@
       <c r="M45" s="3" t="inlineStr"/>
       <c r="N45" s="8" t="inlineStr"/>
     </row>
-    <row r="46" ht="75" customHeight="1">
+    <row r="46" ht="60" customHeight="1">
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-TRAFFIC-LIGHT-INPUTS</t>
+          <t>KAIROS-COHORT-SYMPATHY</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -2810,22 +2814,22 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Detail Lens / Traffic Lights</t>
+          <t>Earnings Lens / Cohort</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Per-ticker risk/fundamentals inputs for lens dots</t>
+          <t>Peer cohort sympathy correlations</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Wire t.f_score · t.altman_z · t.roic · t.wacc · t.sharpe_1y · t.dd_recovery_months · t.peer_rank · t.is_held into build_data.py. _qdComputeLensStatus has cascading fallbacks (PEG → fund_score → F-score; beta → kelly → Sharpe), so dots upgrade automatically as fields land.</t>
+          <t>Wire t.cohort_peers[].er_sympathy_corr + er_sympathy_move_1d + t.sympathy_history in build_data.py. Today: renderEarnings_Sympathy shows scaffold rows from t.cohort_peers if populated, else placeholder.</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Compute in analysis.py / portfolio.py: Piotroski F (existing data), Altman Z (existing data), ROIC vs WACC, 1y Sharpe from price history, peer_rank from cohort, is_held from portfolio_state.json.</t>
+          <t>Compute 8-quarter rolling correlation of 1d post-print move between this name and each cohort peer's ER date. Persist to data.json under t.cohort_peers + t.sympathy_history.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
@@ -2840,13 +2844,13 @@
       <c r="M46" s="3" t="inlineStr"/>
       <c r="N46" s="8" t="inlineStr"/>
     </row>
-    <row r="47" ht="60" customHeight="1">
+    <row r="47" ht="75" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-COHORT-SYMPATHY</t>
+          <t>PARITY-IN-APP-TRADING</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
@@ -2856,22 +2860,22 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Earnings Lens / Cohort</t>
+          <t>Execution / Live / Platform Parity</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Peer cohort sympathy correlations</t>
+          <t>In-app Trading (broker-integrated live execution)</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Wire t.cohort_peers[].er_sympathy_corr + er_sympathy_move_1d + t.sympathy_history in build_data.py. Today: renderEarnings_Sympathy shows scaffold rows from t.cohort_peers if populated, else placeholder.</t>
+          <t>One-click BUY/SELL from the dashboard to a live Schwab/Alpaca brokerage account.</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Compute 8-quarter rolling correlation of 1d post-print move between this name and each cohort peer's ER date. Persist to data.json under t.cohort_peers + t.sympathy_history.</t>
+          <t>OAuth-link the Schwab API (already paid stack); surface an 'Execute' button on the Trade Plan card; explicit AUTHORIZE LIVE TRADING gate per CLAUDE.md security protocol; route every order through the existing risk checks (max-loss-pct, drawdown haircut, regime gate).</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
@@ -2892,7 +2896,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>PARITY-IN-APP-TRADING</t>
+          <t>KAIROS-LIVE-D1</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
@@ -2902,22 +2906,22 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Execution / Live / Platform Parity</t>
+          <t>Kairos / Audit Ledger</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>In-app Trading (broker-integrated live execution)</t>
+          <t>Live D1 estimate from Schwab quote during RTH</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>One-click BUY/SELL from the dashboard to a live Schwab/Alpaca brokerage account.</t>
+          <t>Replace placeholder D1 (yesterday's close-to-close) with a live Schwab-quote-based intraday estimate during market hours so the audit ledger D1 column is non-stale. Discussed and deferred as semantically muddy (D1 = next-day close, intraday quote is a forecast not a fill).</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>OAuth-link the Schwab API (already paid stack); surface an 'Execute' button on the Trade Plan card; explicit AUTHORIZE LIVE TRADING gate per CLAUDE.md security protocol; route every order through the existing risk checks (max-loss-pct, drawdown haircut, regime gate).</t>
+          <t>Add a SCHWAB_LIVE_D1=1 env flag; when ON and during RTH, compute D1_est = (live_quote - signal_entry) / signal_entry and annotate the cell with an 'est' chip. Effort ~1hr.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
@@ -2932,13 +2936,13 @@
       <c r="M48" s="3" t="inlineStr"/>
       <c r="N48" s="8" t="inlineStr"/>
     </row>
-    <row r="49" ht="75" customHeight="1">
+    <row r="49" ht="45" customHeight="1">
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-LIVE-D1</t>
+          <t>KAIROS-SCANNER-BEARS</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
@@ -2948,22 +2952,22 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Kairos / Audit Ledger</t>
+          <t>Kairos / Signal Scanner</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Live D1 estimate from Schwab quote during RTH</t>
+          <t>Top 5 Bears panel</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Replace placeholder D1 (yesterday's close-to-close) with a live Schwab-quote-based intraday estimate during market hours so the audit ledger D1 column is non-stale. Discussed and deferred as semantically muddy (D1 = next-day close, intraday quote is a forecast not a fill).</t>
+          <t>Add a 'Top 5 Bears' panel to the Signal Scanner alongside Fresh / Momentum / Earnings / Volume — was proposed but not selected in the initial build.</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Add a SCHWAB_LIVE_D1=1 env flag; when ON and during RTH, compute D1_est = (live_quote - signal_entry) / signal_entry and annotate the cell with an 'est' chip. Effort ~1hr.</t>
+          <t>Mirror existing 4 panels' structure; sort universe by composite bear-score desc; cap at 5; render in the Scanner grid. Effort ~10min.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
@@ -2978,13 +2982,13 @@
       <c r="M49" s="3" t="inlineStr"/>
       <c r="N49" s="8" t="inlineStr"/>
     </row>
-    <row r="50" ht="45" customHeight="1">
+    <row r="50" ht="60" customHeight="1">
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-SCANNER-BEARS</t>
+          <t>KAIROS-SCANNER-FLIPS</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
@@ -2999,17 +3003,17 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Top 5 Bears panel</t>
+          <t>Today's Flips panel</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Add a 'Top 5 Bears' panel to the Signal Scanner alongside Fresh / Momentum / Earnings / Volume — was proposed but not selected in the initial build.</t>
+          <t>Add a 'Today's Flips' panel to the Signal Scanner — tickers whose verdict flipped vs yesterday (e.g., BUY -&gt; WATCH, WATCH -&gt; BUY, AVOID -&gt; WATCH). Proposed in the 'what else' menu, not selected.</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>Mirror existing 4 panels' structure; sort universe by composite bear-score desc; cap at 5; render in the Scanner grid. Effort ~10min.</t>
+          <t>Diff today's bundle.verdict against yesterday.verdict per ticker; surface the 5-10 most material flips. Effort ~30min.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
@@ -3030,7 +3034,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-SCANNER-FLIPS</t>
+          <t>ML-RETRAIN-FINBERT-FEATURE</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
@@ -3040,22 +3044,22 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Kairos / Signal Scanner</t>
+          <t>ML / Features (future)</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Today's Flips panel</t>
+          <t>Add FinBERT as a GBM training feature (leak-free)</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Add a 'Today's Flips' panel to the Signal Scanner — tickers whose verdict flipped vs yesterday (e.g., BUY -&gt; WATCH, WATCH -&gt; BUY, AVOID -&gt; WATCH). Proposed in the 'what else' menu, not selected.</t>
+          <t>needs historical sentiment series — accumulate forward via cache/ml/sentiment_log.jsonl (asof-stamped); add as feature #18 + retrain once ~3-6mo of leak-free history exists</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Diff today's bundle.verdict against yesterday.verdict per ticker; surface the 5-10 most material flips. Effort ~30min.</t>
+          <t>ml/feature_extractor + historical backfill</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
@@ -3076,7 +3080,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>ML-RETRAIN-FINBERT-FEATURE</t>
+          <t>ML-AUTOREFRESH-VALIDATE</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
@@ -3086,22 +3090,22 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>ML / Features (future)</t>
+          <t>ML / Pipeline (validate)</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Add FinBERT as a GBM training feature (leak-free)</t>
+          <t>Validate ML auto-refresh post-scan + cached-bar reuse</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>needs historical sentiment series — accumulate forward via cache/ml/sentiment_log.jsonl (asof-stamped); add as feature #18 + retrain once ~3-6mo of leak-free history exists</t>
+          <t>ml_edge.run_after_scan=true runs ml.run_ml_edge over the fresh bundle; feature_extractor prefers data_archive (no re-fetch). Confirm end-to-end on next clean scan.</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>ml/feature_extractor + historical backfill</t>
+          <t>swing_trade ML hook + ml/feature_extractor</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
@@ -3122,7 +3126,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>ML-AUTOREFRESH-VALIDATE</t>
+          <t>KAIROS-MACRO-EVENTS</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -3132,22 +3136,22 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>ML / Pipeline (validate)</t>
+          <t>Macro Lens / Calendar</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Validate ML auto-refresh post-scan + cached-bar reuse</t>
+          <t>14-day high-impact event window flag</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>ml_edge.run_after_scan=true runs ml.run_ml_edge over the fresh bundle; feature_extractor prefers data_archive (no re-fetch). Confirm end-to-end on next clean scan.</t>
+          <t>Wire t.next_macro_event_days = days to next FOMC/CPI/NFP/jobs. _qdComputeLensStatus reads this and downgrades macro lens to amber when event &lt;= 14d even in risk_on_trending regime.</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>swing_trade ML hook + ml/feature_extractor</t>
+          <t>Add macro_calendar fetch in data_fetcher.py (FRED/Trading Economics free tier or EODHD calendar). Persist to t.next_macro_event_days.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
@@ -3162,13 +3166,13 @@
       <c r="M53" s="3" t="inlineStr"/>
       <c r="N53" s="8" t="inlineStr"/>
     </row>
-    <row r="54" ht="60" customHeight="1">
+    <row r="54" ht="45" customHeight="1">
       <c r="A54" s="2" t="n">
         <v>53</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-MACRO-EVENTS</t>
+          <t>CACHE-RECLAIM</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
@@ -3178,22 +3182,22 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Macro Lens / Calendar</t>
+          <t>Ops / Hygiene</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>14-day high-impact event window flag</t>
+          <t>Reclaim ~6GB cache (stray bak + edgar TTL)</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Wire t.next_macro_event_days = days to next FOMC/CPI/NFP/jobs. _qdComputeLensStatus reads this and downgrades macro lens to amber when event &lt;= 14d even in risk_on_trending regime.</t>
+          <t>delete 300MB last_bundle.json.bak.precap_promote + add edgar companyfacts prune/TTL (6.1GB)</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>Add macro_calendar fetch in data_fetcher.py (FRED/Trading Economics free tier or EODHD calendar). Persist to t.next_macro_event_days.</t>
+          <t>cache cleanup + edgar_client TTL</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
@@ -3214,7 +3218,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>CACHE-RECLAIM</t>
+          <t>JOBS-MOMENTUM-SNAPSHOT</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
@@ -3224,22 +3228,22 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Ops / Hygiene</t>
+          <t>Ops / Launchd</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>Reclaim ~6GB cache (stray bak + edgar TTL)</t>
+          <t>Decide momentum-snapshot job: load or disable</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>delete 300MB last_bundle.json.bak.precap_promote + add edgar companyfacts prune/TTL (6.1GB)</t>
+          <t>valid plist in repo but not currently loaded; decide launchctl bootstrap vs move to disabled/.</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>cache cleanup + edgar_client TTL</t>
+          <t>infra/launchd/com.swingtrade.momentum-snapshot.plist</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
@@ -3254,13 +3258,13 @@
       <c r="M55" s="3" t="inlineStr"/>
       <c r="N55" s="8" t="inlineStr"/>
     </row>
-    <row r="56" ht="45" customHeight="1">
+    <row r="56" ht="60" customHeight="1">
       <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>JOBS-MOMENTUM-SNAPSHOT</t>
+          <t>DATA-FUTURE-OPS-TELEMETRY-6</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
@@ -3270,22 +3274,22 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Ops / Launchd</t>
+          <t>Ops / Telemetry (future)</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>Decide momentum-snapshot job: load or disable</t>
+          <t>6 ops telemetry slots — app-side instrumentation</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>valid plist in repo but not currently loaded; decide launchctl bootstrap vs move to disabled/.</t>
+          <t>6 ops telemetry slots remain unbuilt because they require app-side instrumentation: server middleware, git hooks, scan-time emitters, executor probes, sub-tab render timings, fetch-latency probes.</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd/com.swingtrade.momentum-snapshot.plist</t>
+          <t>Build a shared emitter (lib/telemetry.py) writing to a telemetry SQLite; instrument incrementally — server middleware first, then scan emitters; surface in System Status sub-tab.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
@@ -3306,7 +3310,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-OPS-TELEMETRY-6</t>
+          <t>SCALE-4</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
@@ -3316,22 +3320,22 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Ops / Telemetry (future)</t>
+          <t>Ops · 500-user</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>6 ops telemetry slots — app-side instrumentation</t>
+          <t>Scan reliability so Home is not sparse</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>6 ops telemetry slots remain unbuilt because they require app-side instrumentation: server middleware, git hooks, scan-time emitters, executor probes, sub-tab render timings, fetch-latency probes.</t>
+          <t>When the daily scan is empty (EODHD quota outage), Home shows honest-empty sections + stale-badged regime; users landing mid-outage see little actionable content</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Build a shared emitter (lib/telemetry.py) writing to a telemetry SQLite; instrument incrementally — server middleware first, then scan emitters; surface in System Status sub-tab.</t>
+          <t>Ensure morning scan runs reliably + quota headroom; keep STALE badge UX; consider serving last-good bundle with clear age</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
@@ -3346,13 +3350,13 @@
       <c r="M57" s="3" t="inlineStr"/>
       <c r="N57" s="8" t="inlineStr"/>
     </row>
-    <row r="58" ht="60" customHeight="1">
+    <row r="58" ht="75" customHeight="1">
       <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>SCALE-4</t>
+          <t>OV-INVEST-STRUCT</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
@@ -3362,22 +3366,22 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Ops · 500-user</t>
+          <t>Overview / Target Engine</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Scan reliability so Home is not sparse</t>
+          <t>Real structural invest targets (kill analyst-PT stub)</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>When the daily scan is empty (EODHD quota outage), Home shows honest-empty sections + stale-badged regime; users landing mid-outage see little actionable content</t>
+          <t>Invest-mode targets fall back to analyst 12mo PT (invest_stub) for low-vol names (e.g. AAPL) when no structural level qualifies in the invest R-band off the wider stop -&gt; near T1, poor R:R. Per-mode stop scaling fix (2026-06-08) made invest coherent for higher-vol names (NVDA stub=False) but low-vol names still stub.</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>Ensure morning scan runs reliably + quota headroom; keep STALE badge UX; consider serving last-good bundle with clear age</t>
+          <t>Wire multi-year structural levels (monthly/yearly swing highs, weekly Fib ext) into the invest candidate set so the invest R-band is populated without the analyst-PT fallback; raise invest max_reach_atr to match a 1-5yr horizon.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
@@ -3392,13 +3396,13 @@
       <c r="M58" s="3" t="inlineStr"/>
       <c r="N58" s="8" t="inlineStr"/>
     </row>
-    <row r="59" ht="75" customHeight="1">
+    <row r="59" ht="60" customHeight="1">
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>OV-INVEST-STRUCT</t>
+          <t>SCALE-3</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
@@ -3408,22 +3412,22 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Overview / Target Engine</t>
+          <t>Portfolio · 500-user</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>Real structural invest targets (kill analyst-PT stub)</t>
+          <t>Per-user portfolio vs shared automated book</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Invest-mode targets fall back to analyst 12mo PT (invest_stub) for low-vol names (e.g. AAPL) when no structural level qualifies in the invest R-band off the wider stop -&gt; near T1, poor R:R. Per-mode stop scaling fix (2026-06-08) made invest coherent for higher-vol names (NVDA stub=False) but low-vol names still stub.</t>
+          <t>Home AUTOMATED BOOK is the single shared Alpaca-paper auto-trade account; every viewer sees identical positions; no per-user book (NAV is per-user, positions are not)</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Wire multi-year structural levels (monthly/yearly swing highs, weekly Fib ext) into the invest candidate set so the invest R-band is populated without the analyst-PT fallback; raise invest max_reach_atr to match a 1-5yr horizon.</t>
+          <t>Decide: keep as shared model/track-record book by design, OR add a per-user position store keyed to UserPrefs auth id</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
@@ -3438,13 +3442,13 @@
       <c r="M59" s="3" t="inlineStr"/>
       <c r="N59" s="8" t="inlineStr"/>
     </row>
-    <row r="60" ht="60" customHeight="1">
+    <row r="60" ht="90" customHeight="1">
       <c r="A60" s="2" t="n">
         <v>59</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>SCALE-3</t>
+          <t>QUANT-HMM-FF-LGBM-ROADMAP</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
@@ -3454,22 +3458,22 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Portfolio · 500-user</t>
+          <t>Quant / Modeling Roadmap</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>Per-user portfolio vs shared automated book</t>
+          <t>HMM regime / Fama-French / LightGBM swap (status unclear)</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Home AUTOMATED BOOK is the single shared Alpaca-paper auto-trade account; every viewer sees identical positions; no per-user book (NAV is per-user, positions are not)</t>
+          <t>Roadmap items pasted as a status table — clarification pending whether user wants execution or just context tracking. Three potential upgrades: (a) HMM-based regime classifier replacing the rule-based 4-regime model, (b) Fama-French factor exposure analysis on closed trades, (c) LightGBM swap-in for HistGradientBoosting in ml/train_historical.py. Each 1-3 days.</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>Decide: keep as shared model/track-record book by design, OR add a per-user position store keyed to UserPrefs auth id</t>
+          <t>Confirm intent before executing. If go: HMM first (decouples regime classifier from heuristics, principle #18), then Fama-French attribution (per-strategy factor exposure), then LightGBM swap (likely-marginal accuracy gain vs current HistGB). Each upgrade gated by Wilson-LB validation vs current baseline.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
@@ -3484,13 +3488,13 @@
       <c r="M60" s="3" t="inlineStr"/>
       <c r="N60" s="8" t="inlineStr"/>
     </row>
-    <row r="61" ht="90" customHeight="1">
+    <row r="61" ht="60" customHeight="1">
       <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>QUANT-HMM-FF-LGBM-ROADMAP</t>
+          <t>PARITY-SMART-RISK-LEVELS</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
@@ -3500,22 +3504,22 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Quant / Modeling Roadmap</t>
+          <t>Risk / Targets / Platform Parity</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>HMM regime / Fama-French / LightGBM swap (status unclear)</t>
+          <t>Smart Risk Levels (auto stop + T1/T2)</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Roadmap items pasted as a status table — clarification pending whether user wants execution or just context tracking. Three potential upgrades: (a) HMM-based regime classifier replacing the rule-based 4-regime model, (b) Fama-French factor exposure analysis on closed trades, (c) LightGBM swap-in for HistGradientBoosting in ml/train_historical.py. Each 1-3 days.</t>
+          <t>Auto-place stop / T1 / T2 dots on the chart with confluence reasoning (HVN, AVWAP, fractal, ATR, Fib). Already computed by the structural target engine but not surfaced on the new Chart sub-tab.</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Confirm intent before executing. If go: HMM first (decouples regime classifier from heuristics, principle #18), then Fama-French attribution (per-strategy factor exposure), then LightGBM swap (likely-marginal accuracy gain vs current HistGB). Each upgrade gated by Wilson-LB validation vs current baseline.</t>
+          <t>Read cache/target_engine/{TICKER}_{MODE}.json and overlay the levels on the chart canvas with hover tooltips citing the confluence factors; gated by use_structural_targets flag (M2.5 cutover).</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
@@ -3536,7 +3540,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>PARITY-SMART-RISK-LEVELS</t>
+          <t>KAIROS-L2-BOOK</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
@@ -3546,22 +3550,22 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Risk / Targets / Platform Parity</t>
+          <t>Risk Lens / Execution</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>Smart Risk Levels (auto stop + T1/T2)</t>
+          <t>L2 bid/ask depth at price levels</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Auto-place stop / T1 / T2 dots on the chart with confluence reasoning (HVN, AVWAP, fractal, ATR, Fib). Already computed by the structural target engine but not surfaced on the new Chart sub-tab.</t>
+          <t>Wire t.l2_book from Schwab streaming API → render in renderRisk_LiquidityLadder. Today: ADV-derived size tiers shown as scaffold. Schwab streaming requires WebSocket session — see schwab_client.py.</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>Read cache/target_engine/{TICKER}_{MODE}.json and overlay the levels on the chart canvas with hover tooltips citing the confluence factors; gated by use_structural_targets flag (M2.5 cutover).</t>
+          <t>Subscribe to Schwab Level-II quote stream; persist top-of-book snapshot into t.l2_book = {bid:[{px,size}], ask:[{px,size}]}. Frontend already reads these fields if present.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
@@ -3582,7 +3586,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-L2-BOOK</t>
+          <t>PARITY-AI-SIGNALS-V1</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
@@ -3592,22 +3596,22 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Risk Lens / Execution</t>
+          <t>Signals / Platform Parity</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>L2 bid/ask depth at price levels</t>
+          <t>1st-Gen AI Signals</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Wire t.l2_book from Schwab streaming API → render in renderRisk_LiquidityLadder. Today: ADV-derived size tiers shown as scaffold. Schwab streaming requires WebSocket session — see schwab_client.py.</t>
+          <t>Surface a baseline AI BUY/SELL signal stream on the chart as quick-glance arrows/dots — the competitor-platform feature (TrendSpider, Trade Ideas) users expect to see at a glance, separate from the full ML Edge sub-tab.</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>Subscribe to Schwab Level-II quote stream; persist top-of-book snapshot into t.l2_book = {bid:[{px,size}], ask:[{px,size}]}. Frontend already reads these fields if present.</t>
+          <t>Reuse ML Edge dir-head + cone outputs but render as 1-bar arrows/markers on the new Chart sub-tab; isolate from the 10-section Technicals view; respect cache/ml_edge_predictions.json freshness.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr"/>
@@ -3622,13 +3626,13 @@
       <c r="M63" s="3" t="inlineStr"/>
       <c r="N63" s="8" t="inlineStr"/>
     </row>
-    <row r="64" ht="60" customHeight="1">
+    <row r="64" ht="45" customHeight="1">
       <c r="A64" s="2" t="n">
         <v>63</v>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>PARITY-AI-SIGNALS-V1</t>
+          <t>TEST-AB-PAPER</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
@@ -3638,22 +3642,22 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Signals / Platform Parity</t>
+          <t>Testing / Validation (Tier 2)</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>1st-Gen AI Signals</t>
+          <t>A/B Paper Split — live comparison</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Surface a baseline AI BUY/SELL signal stream on the chart as quick-glance arrows/dots — the competitor-platform feature (TrendSpider, Trade Ideas) users expect to see at a glance, separate from the full ML Edge sub-tab.</t>
+          <t>Run config A on half the paper portfolio and config B on the other half; real-time comparison of WR / PF / equity divergence over 30-60d window.</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>Reuse ML Edge dir-head + cone outputs but render as 1-bar arrows/markers on the new Chart sub-tab; isolate from the 10-section Technicals view; respect cache/ml_edge_predictions.json freshness.</t>
+          <t>Extend executor.py to accept --variant flag; persist per-variant portfolio state; cross-section panel in System Status sub-tab. Effort 3-4hr.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
@@ -3668,13 +3672,13 @@
       <c r="M64" s="3" t="inlineStr"/>
       <c r="N64" s="8" t="inlineStr"/>
     </row>
-    <row r="65" ht="45" customHeight="1">
+    <row r="65" ht="60" customHeight="1">
       <c r="A65" s="2" t="n">
         <v>64</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>TEST-AB-PAPER</t>
+          <t>TEST-BENCHMARK-SPY</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
@@ -3689,17 +3693,17 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>A/B Paper Split — live comparison</t>
+          <t>Benchmark vs SPY — alpha / beta / IR</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>Run config A on half the paper portfolio and config B on the other half; real-time comparison of WR / PF / equity divergence over 30-60d window.</t>
+          <t>Compute strategy alpha, beta, information ratio vs SPY benchmark. Standard performance attribution; turns 'we made +X%' into 'we made +Y% over SPY at lower drawdown'.</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>Extend executor.py to accept --variant flag; persist per-variant portfolio state; cross-section panel in System Status sub-tab. Effort 3-4hr.</t>
+          <t>Daily portfolio_value series joined to SPY adjusted-close; regress daily returns -&gt; SPY returns for beta + alpha; IR = (mean excess return) / (std excess return); render in System Status. Effort ~1hr.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
@@ -3720,7 +3724,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>TEST-BENCHMARK-SPY</t>
+          <t>TEST-DD-DIST</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
@@ -3735,17 +3739,17 @@
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>Benchmark vs SPY — alpha / beta / IR</t>
+          <t>Drawdown Distribution Simulator</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>Compute strategy alpha, beta, information ratio vs SPY benchmark. Standard performance attribution; turns 'we made +X%' into 'we made +Y% over SPY at lower drawdown'.</t>
+          <t>Bootstrap 1000 portfolio paths from closed-trade distribution; measure tail-drawdown probability at p95/p99; supports principle #9 (drawdown asymmetry — losing 50% requires +100% to recover).</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>Daily portfolio_value series joined to SPY adjusted-close; regress daily returns -&gt; SPY returns for beta + alpha; IR = (mean excess return) / (std excess return); render in System Status. Effort ~1hr.</t>
+          <t>Resample trade sequence with replacement; build equity curves; compute max-DD per path; histogram + tail percentiles; feed into position-sizing math. Effort 2-3hr.</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
@@ -3766,7 +3770,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>TEST-DD-DIST</t>
+          <t>TEST-SENSITIVITY</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
@@ -3781,17 +3785,17 @@
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>Drawdown Distribution Simulator</t>
+          <t>Sensitivity / Robustness Test</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Bootstrap 1000 portfolio paths from closed-trade distribution; measure tail-drawdown probability at p95/p99; supports principle #9 (drawdown asymmetry — losing 50% requires +100% to recover).</t>
+          <t>Perturb each config parameter +/-20% (score floors, stop ATR mult, R:R floor, regime thresholds) and check whether the strategy still passes the gate. Finds overfit knobs that only work at one exact value.</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Resample trade sequence with replacement; build equity curves; compute max-DD per path; histogram + tail percentiles; feed into position-sizing math. Effort 2-3hr.</t>
+          <t>Grid-walk key config thresholds; re-run backtest at each point; build sensitivity heatmap (param vs PF); flag any knob whose +/-20% perturbation collapses PF &gt;50%. Effort ~2hr.</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
@@ -3812,7 +3816,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>TEST-SENSITIVITY</t>
+          <t>TEST-SLIPPAGE-STRESS</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
@@ -3827,17 +3831,17 @@
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>Sensitivity / Robustness Test</t>
+          <t>Slippage Stress Test</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>Perturb each config parameter +/-20% (score floors, stop ATR mult, R:R floor, regime thresholds) and check whether the strategy still passes the gate. Finds overfit knobs that only work at one exact value.</t>
+          <t>Double the slippage assumption (ATR/ADV-scaled model from audit #5) and recompute backtest stats. Validates fragile execution dependence per principle #19 (slippage realism).</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>Grid-walk key config thresholds; re-run backtest at each point; build sensitivity heatmap (param vs PF); flag any knob whose +/-20% perturbation collapses PF &gt;50%. Effort ~2hr.</t>
+          <t>Re-run backtest with SLIPPAGE_MULT=2.0; compare WR/PF/Sharpe deltas; if a strategy collapses at 2x slippage it is execution-fragile and should be down-sized. Effort ~1hr.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
@@ -3858,7 +3862,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>TEST-SLIPPAGE-STRESS</t>
+          <t>TEST-CORRELATED-FAILURE</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
@@ -3868,22 +3872,22 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Testing / Validation (Tier 2)</t>
+          <t>Testing / Validation (Tier 3)</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>Slippage Stress Test</t>
+          <t>Correlated-Failure — what if EODHD goes down 24h?</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Double the slippage assumption (ATR/ADV-scaled model from audit #5) and recompute backtest stats. Validates fragile execution dependence per principle #19 (slippage realism).</t>
+          <t>Simulate the impact of the sole data provider (EODHD) being unavailable for 24-48h during market hours. What happens to (a) the scan, (b) live exec, (c) the dashboard?</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>Re-run backtest with SLIPPAGE_MULT=2.0; compare WR/PF/Sharpe deltas; if a strategy collapses at 2x slippage it is execution-fragile and should be down-sized. Effort ~1hr.</t>
+          <t>Inject EODHD error responses in a paper environment; observe failure modes (fallback to last-known cache vs hard error vs degraded scan); document recovery RTO; tighten any silent-fail paths discovered. Effort 2-3hr.</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr"/>
@@ -3898,13 +3902,13 @@
       <c r="M69" s="3" t="inlineStr"/>
       <c r="N69" s="8" t="inlineStr"/>
     </row>
-    <row r="70" ht="60" customHeight="1">
+    <row r="70" ht="45" customHeight="1">
       <c r="A70" s="2" t="n">
         <v>69</v>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>TEST-CORRELATED-FAILURE</t>
+          <t>TEST-CRASH-REPLAY</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
@@ -3919,17 +3923,17 @@
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>Correlated-Failure — what if EODHD goes down 24h?</t>
+          <t>Crash Replay — 2008/2020/2022 stress</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>Simulate the impact of the sole data provider (EODHD) being unavailable for 24-48h during market hours. What happens to (a) the scan, (b) live exec, (c) the dashboard?</t>
+          <t>Apply current portfolio composition to historical crash days (2008 GFC, 2020 COVID, 2022 rate-shock); measure realized drawdown + recovery time per scenario.</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>Inject EODHD error responses in a paper environment; observe failure modes (fallback to last-known cache vs hard error vs degraded scan); document recovery RTO; tighten any silent-fail paths discovered. Effort 2-3hr.</t>
+          <t>Snapshot today's positions; price-replay against historical daily OHLC from those windows; report per-crisis max-DD and time-to-recovery. Effort 2-3hr.</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
@@ -3944,13 +3948,13 @@
       <c r="M70" s="3" t="inlineStr"/>
       <c r="N70" s="8" t="inlineStr"/>
     </row>
-    <row r="71" ht="45" customHeight="1">
+    <row r="71" ht="60" customHeight="1">
       <c r="A71" s="2" t="n">
         <v>70</v>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>TEST-CRASH-REPLAY</t>
+          <t>TEST-KELLY-SIM</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
@@ -3965,17 +3969,17 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>Crash Replay — 2008/2020/2022 stress</t>
+          <t>Half-Kelly vs Full-Kelly sizing simulation</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Apply current portfolio composition to historical crash days (2008 GFC, 2020 COVID, 2022 rate-shock); measure realized drawdown + recovery time per scenario.</t>
+          <t>Visualize portfolio growth under Half-Kelly (current default) vs Full-Kelly vs Quarter-Kelly sizing rules; quantifies the volatility-vs-CAGR tradeoff that principle #9 codifies.</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>Snapshot today's positions; price-replay against historical daily OHLC from those windows; report per-crisis max-DD and time-to-recovery. Effort 2-3hr.</t>
+          <t>Bootstrap N portfolio paths under each Kelly fraction; chart median equity curve + percentile fans; surface terminal-wealth distribution. Effort ~2hr.</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
@@ -3996,7 +4000,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>TEST-KELLY-SIM</t>
+          <t>TEST-SLIPPAGE-ATTR</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
@@ -4011,17 +4015,17 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>Half-Kelly vs Full-Kelly sizing simulation</t>
+          <t>Slippage Attribution — signal PnL vs realized PnL gap</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>Visualize portfolio growth under Half-Kelly (current default) vs Full-Kelly vs Quarter-Kelly sizing rules; quantifies the volatility-vs-CAGR tradeoff that principle #9 codifies.</t>
+          <t>For each closed trade, compute the gap between the model's predicted entry/exit and the actual fill price. Aggregate by setup/ticker/regime to find where slippage eats edge.</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>Bootstrap N portfolio paths under each Kelly fraction; chart median equity curve + percentile fans; surface terminal-wealth distribution. Effort ~2hr.</t>
+          <t>Read signal_log entries (which has the signal price) and join to paper_fills.json (which has the realized price); compute slippage_bp per trade; group + percentile. Effort ~2hr.</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
@@ -4042,7 +4046,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>TEST-SLIPPAGE-ATTR</t>
+          <t>TEST-TAX-AWARE</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
@@ -4057,17 +4061,17 @@
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>Slippage Attribution — signal PnL vs realized PnL gap</t>
+          <t>Tax-Aware Backtest — short-term cap-gains haircut</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>For each closed trade, compute the gap between the model's predicted entry/exit and the actual fill price. Aggregate by setup/ticker/regime to find where slippage eats edge.</t>
+          <t>Apply short-term capital-gains tax (35-40% on gains held &lt;1yr) to backtest PnL. Real after-tax return for a US retail account is materially lower than gross.</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>Read signal_log entries (which has the signal price) and join to paper_fills.json (which has the realized price); compute slippage_bp per trade; group + percentile. Effort ~2hr.</t>
+          <t>Add post_tax_pnl column to backtest output; apply 35% haircut to short-term gains (&gt;0 PnL, held &lt;365d) and 15% to long-term; report Sharpe / total-return pre vs post tax. Effort ~2hr.</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr"/>
@@ -4088,7 +4092,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>TEST-TAX-AWARE</t>
+          <t>WAIT-CALIB-DRIFT-SPARK</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
@@ -4098,22 +4102,22 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Testing / Validation (Tier 3)</t>
+          <t>Time-Dependent / Calibration</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>Tax-Aware Backtest — short-term cap-gains haircut</t>
+          <t>Calibration drift sparkline populates</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>Apply short-term capital-gains tax (35-40% on gains held &lt;1yr) to backtest PnL. Real after-tax return for a US retail account is materially lower than gross.</t>
+          <t>The calibration-drift sparkline in the ML Edge sub-tab needs multiple training cycles to populate (weeks). Each morning scan retrains and appends a calibration row; the sparkline reads from that history table.</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>Add post_tax_pnl column to backtest output; apply 35% haircut to short-term gains (&gt;0 PnL, held &lt;365d) and 15% to long-term; report Sharpe / total-return pre vs post tax. Effort ~2hr.</t>
+          <t>Passive wait. Re-check after 4-6 weekly retrain cycles. If still empty, verify ml.train_historical writes to cache/ml/calibration_history.jsonl on each run.</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
@@ -4128,13 +4132,13 @@
       <c r="M74" s="3" t="inlineStr"/>
       <c r="N74" s="8" t="inlineStr"/>
     </row>
-    <row r="75" ht="60" customHeight="1">
+    <row r="75" ht="45" customHeight="1">
       <c r="A75" s="2" t="n">
         <v>74</v>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>WAIT-CALIB-DRIFT-SPARK</t>
+          <t>WAIT-DRIFT-SNAPSHOTS</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
@@ -4144,22 +4148,22 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Time-Dependent / Calibration</t>
+          <t>Time-Dependent / Drift Tracking</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>Calibration drift sparkline populates</t>
+          <t>Diff vs yesterday + 30-day drift populate</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>The calibration-drift sparkline in the ML Edge sub-tab needs multiple training cycles to populate (weeks). Each morning scan retrains and appends a calibration row; the sparkline reads from that history table.</t>
+          <t>The 'diff vs yesterday' + 30-day drift columns need 2+ daily snapshots stored. Starts populating tomorrow's scan.</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>Passive wait. Re-check after 4-6 weekly retrain cycles. If still empty, verify ml.train_historical writes to cache/ml/calibration_history.jsonl on each run.</t>
+          <t>Passive wait; first populated values appear in the next morning's scan output. Verify the snapshot persister wrote a row today.</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
@@ -4180,7 +4184,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>WAIT-DRIFT-SNAPSHOTS</t>
+          <t>WAIT-ML-PICKS-RESOLVE</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
@@ -4190,22 +4194,22 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Time-Dependent / Drift Tracking</t>
+          <t>Time-Dependent / Picks History</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>Diff vs yesterday + 30-day drift populate</t>
+          <t>Picks-history outcome resolution (resolve_ml_picks.py)</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>The 'diff vs yesterday' + 30-day drift columns need 2+ daily snapshots stored. Starts populating tomorrow's scan.</t>
+          <t>resolve_ml_picks.py needs 5 trading days from each pick to resolve outcomes. First AI Edge batch (picks from ~2026-05-18) resolves around 2026-05-23.</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>Passive wait; first populated values appear in the next morning's scan output. Verify the snapshot persister wrote a row today.</t>
+          <t>Passive wait. Re-check on 2026-05-23; verify resolve_ml_picks.py runs in run_daily_scan.sh and populates picks_history.json outcome columns.</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
@@ -4220,13 +4224,13 @@
       <c r="M76" s="3" t="inlineStr"/>
       <c r="N76" s="8" t="inlineStr"/>
     </row>
-    <row r="77" ht="45" customHeight="1">
+    <row r="77" ht="60" customHeight="1">
       <c r="A77" s="2" t="n">
         <v>76</v>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>WAIT-ML-PICKS-RESOLVE</t>
+          <t>WAIT-SURVIVORSHIP-DECAY</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
@@ -4236,22 +4240,22 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Time-Dependent / Picks History</t>
+          <t>Time-Dependent / Survivorship Haircut</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>Picks-history outcome resolution (resolve_ml_picks.py)</t>
+          <t>Survivorship haircut shrinking 3pp -&gt; 0.5pp</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>resolve_ml_picks.py needs 5 trading days from each pick to resolve outcomes. First AI Edge batch (picks from ~2026-05-18) resolves around 2026-05-23.</t>
+          <t>The -3pp WR survivorship haircut should shrink as monthly S&amp;P 500 / R1000 membership snapshots accumulate (Wikipedia revision history). Once 24+ months of snapshots are stored, the haircut can fade toward 0.5pp.</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>Passive wait. Re-check on 2026-05-23; verify resolve_ml_picks.py runs in run_daily_scan.sh and populates picks_history.json outcome columns.</t>
+          <t>Passive wait — currently only current-membership data. Re-evaluate annually. Until then keep -3pp haircut per CLAUDE.md principle #6.</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
@@ -4272,7 +4276,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>WAIT-SURVIVORSHIP-DECAY</t>
+          <t>WAIT-WF-EQUITY-REAL</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
@@ -4282,22 +4286,22 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Time-Dependent / Survivorship Haircut</t>
+          <t>Time-Dependent / Walk-Forward</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>Survivorship haircut shrinking 3pp -&gt; 0.5pp</t>
+          <t>Walk-forward equity curve switches to REAL track</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>The -3pp WR survivorship haircut should shrink as monthly S&amp;P 500 / R1000 membership snapshots accumulate (Wikipedia revision history). Once 24+ months of snapshots are stored, the haircut can fade toward 0.5pp.</t>
+          <t>Currently the equity curve renders backtest-derived returns. Switches to REAL track once 5+ resolved AI Edge picks are available — first batch resolves ~2026-05-23, so REAL curve activates ~2026-05-24.</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>Passive wait — currently only current-membership data. Re-evaluate annually. Until then keep -3pp haircut per CLAUDE.md principle #6.</t>
+          <t>Passive wait. Re-check on 2026-05-24; verify the equity curve flips from BACKTEST badge to REAL badge once n_resolved &gt;= 5.</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
@@ -4318,7 +4322,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>WAIT-WF-EQUITY-REAL</t>
+          <t>PARITY-10-CHARTS-GRID</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
@@ -4328,22 +4332,22 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>Time-Dependent / Walk-Forward</t>
+          <t>UI / Layout / Platform Parity</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>Walk-forward equity curve switches to REAL track</t>
+          <t>10-chart multi-pane grid</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Currently the equity curve renders backtest-derived returns. Switches to REAL track once 5+ resolved AI Edge picks are available — first batch resolves ~2026-05-23, so REAL curve activates ~2026-05-24.</t>
+          <t>Display up to 10 ticker charts side-by-side in a configurable grid (2x5, 3x4, etc.) for at-a-glance correlation/leadership reads — what TrendSpider and Trade Ideas users default to.</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Passive wait. Re-check on 2026-05-24; verify the equity curve flips from BACKTEST badge to REAL badge once n_resolved &gt;= 5.</t>
+          <t>New 'Grid' workspace in kairos that renders N lightweight-chart canvases; ticker list drag-droppable; persists ticker set per layout.</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr"/>
@@ -4364,7 +4368,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>PARITY-10-CHARTS-GRID</t>
+          <t>PARITY-CUSTOM-LAYOUTS</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
@@ -4379,17 +4383,17 @@
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>10-chart multi-pane grid</t>
+          <t>Customizable Layouts (save/load workspace presets)</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Display up to 10 ticker charts side-by-side in a configurable grid (2x5, 3x4, etc.) for at-a-glance correlation/leadership reads — what TrendSpider and Trade Ideas users default to.</t>
+          <t>User drags/resizes panels in the kairos workspace and saves the arrangement as a named preset (Day-Trade view / Swing view / Research view) and switches between them.</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>New 'Grid' workspace in kairos that renders N lightweight-chart canvases; ticker list drag-droppable; persists ticker set per layout.</t>
+          <t>Persist layout JSON in cache/user_layouts.json (per-user once auth lands); sidebar dropdown to switch; default presets shipped (Swing / Position / Research).</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr"/>
@@ -4404,13 +4408,13 @@
       <c r="M80" s="3" t="inlineStr"/>
       <c r="N80" s="8" t="inlineStr"/>
     </row>
-    <row r="81" ht="60" customHeight="1">
+    <row r="81" ht="75" customHeight="1">
       <c r="A81" s="2" t="n">
         <v>80</v>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>PARITY-CUSTOM-LAYOUTS</t>
+          <t>STRUCT-TARGETS-PHASE2</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
@@ -4420,35 +4424,51 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>UI / Layout / Platform Parity</t>
+          <t>Strategy / Targets</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>Customizable Layouts (save/load workspace presets)</t>
+          <t>Structural targets Phase 2 — engine uses them as T1/T2</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>User drags/resizes panels in the kairos workspace and saves the arrangement as a named preset (Day-Trade view / Swing view / Research view) and switches between them.</t>
+          <t>Phase 1 (shipped 2026-05-10): structural target sources (fractal, fib, EW Wave-3) display on Plan tab as informational. Phase 2: actually use these as T1/T2 instead of ATR-multiple targets. Needs per-source x regime evidence (&gt;=30 trades each).</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Persist layout JSON in cache/user_layouts.json (per-user once auth lands); sidebar dropdown to switch; default presets shipped (Swing / Position / Research).</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr"/>
-      <c r="I81" s="5" t="inlineStr"/>
-      <c r="J81" s="5" t="inlineStr"/>
-      <c r="K81" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+          <t>Add config flag target_source = atr_multiple | structural. When structural, T1 = nearest_above with R:R&gt;=3 from {fractal_high, fib_127, EW_T1}. Fall back to ATR if R:R floor not met. Backtest side-by-side with current ATR-multiple.</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>1 day + backtest</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>High win potential, medium risk</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>Awaiting evidence. Phase 1 currently just populates display field; need 3-4 weeks of trade data with target_sources captured before Phase 2 is decidable.</t>
+        </is>
+      </c>
+      <c r="K81" s="11" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="3" t="inlineStr"/>
-      <c r="N81" s="8" t="inlineStr"/>
+      <c r="N81" s="8" t="inlineStr">
+        <is>
+          <t>Run backtest with target_source=structural and target_source=atr_multiple on same window. Compare PF/WR/avg_win.</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="75" customHeight="1">
       <c r="A82" s="2" t="n">
@@ -4456,69 +4476,77 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-PHASE2</t>
-        </is>
-      </c>
-      <c r="C82" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>K6</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Targets</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>Structural targets Phase 2 — engine uses them as T1/T2</t>
+          <t>Single canonical trade plan object — every tab reads from one source</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 (shipped 2026-05-10): structural target sources (fractal, fib, EW Wave-3) display on Plan tab as informational. Phase 2: actually use these as T1/T2 instead of ATR-multiple targets. Needs per-source x regime evidence (&gt;=30 trades each).</t>
+          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>Add config flag target_source = atr_multiple | structural. When structural, T1 = nearest_above with R:R&gt;=3 from {fractal_high, fib_127, EW_T1}. Fall back to ATR if R:R floor not met. Backtest side-by-side with current ATR-multiple.</t>
+          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>1 day + backtest</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>High win potential, medium risk</t>
+          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
         </is>
       </c>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t>Awaiting evidence. Phase 1 currently just populates display field; need 3-4 weeks of trade data with target_sources captured before Phase 2 is decidable.</t>
-        </is>
-      </c>
-      <c r="K82" s="11" t="inlineStr">
-        <is>
-          <t>IN_PROGRESS</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr"/>
-      <c r="M82" s="3" t="inlineStr"/>
+          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
+        </is>
+      </c>
+      <c r="K82" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>2c9b9f339</t>
+        </is>
+      </c>
       <c r="N82" s="8" t="inlineStr">
         <is>
-          <t>Run backtest with target_source=structural and target_source=atr_multiple on same window. Compare PF/WR/avg_win.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="75" customHeight="1">
+          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="90" customHeight="1">
       <c r="A83" s="2" t="n">
         <v>82</v>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>B3-WEEKLY-FIX</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -4528,37 +4556,29 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Backtest / Bug Fix</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>Single canonical trade plan object — every tab reads from one source</t>
+          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
+          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I83" s="5" t="inlineStr">
-        <is>
-          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
-        </is>
-      </c>
+          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="5" t="inlineStr"/>
       <c r="J83" s="5" t="inlineStr">
         <is>
-          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
+          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
         </is>
       </c>
       <c r="K83" s="12" t="inlineStr">
@@ -4568,27 +4588,27 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>2c9b9f339</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N83" s="8" t="inlineStr">
         <is>
-          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="90" customHeight="1">
+          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="75" customHeight="1">
       <c r="A84" s="2" t="n">
         <v>83</v>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>B3-WEEKLY-FIX</t>
+          <t>VARIANT-F-BT</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -4598,31 +4618,27 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Bug Fix</t>
+          <t>Backtest Parity</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
+          <t>Variant F regime-conditional multipliers not wired into backtest path</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
+          <t>backtest.py:418 uses tracker.get_setup_weight_multiplier (reading picks_history) but never consults config.setup_score_multiplier_by_regime. So Variant F's TC×bull=0.0 kill never applied in backtest — explains why 105 TC bull trades persisted in 250d backtest despite live kill in config.</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
+          <t>Add Variant F lookup at backtest.py:442 mirroring analysis.py:8867 logic. Same demotion gate (n&gt;=30 + wr_lb&lt;0.30). Comment cross-reference live path.</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="5" t="inlineStr"/>
-      <c r="J84" s="5" t="inlineStr">
-        <is>
-          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
-        </is>
-      </c>
+      <c r="J84" s="5" t="inlineStr"/>
       <c r="K84" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4635,22 +4651,18 @@
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
-        </is>
-      </c>
-      <c r="N84" s="8" t="inlineStr">
-        <is>
-          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="75" customHeight="1">
+          <t>0cdb13340</t>
+        </is>
+      </c>
+      <c r="N84" s="8" t="inlineStr"/>
+    </row>
+    <row r="85" ht="45" customHeight="1">
       <c r="A85" s="2" t="n">
         <v>84</v>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>VARIANT-F-BT</t>
+          <t>P0-WEEKLY</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -4660,27 +4672,39 @@
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Backtest Parity</t>
+          <t>Backtest infra</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>Variant F regime-conditional multipliers not wired into backtest path</t>
+          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:418 uses tracker.get_setup_weight_multiplier (reading picks_history) but never consults config.setup_score_multiplier_by_regime. So Variant F's TC×bull=0.0 kill never applied in backtest — explains why 105 TC bull trades persisted in 250d backtest despite live kill in config.</t>
+          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>Add Variant F lookup at backtest.py:442 mirroring analysis.py:8867 logic. Same demotion gate (n&gt;=30 + wr_lb&lt;0.30). Comment cross-reference live path.</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr"/>
-      <c r="I85" s="5" t="inlineStr"/>
-      <c r="J85" s="5" t="inlineStr"/>
+          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>20 min</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>CRITICAL — system was unable to backtest</t>
+        </is>
+      </c>
+      <c r="J85" s="5" t="inlineStr">
+        <is>
+          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
+        </is>
+      </c>
       <c r="K85" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4693,18 +4717,22 @@
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
-          <t>0cdb13340</t>
-        </is>
-      </c>
-      <c r="N85" s="8" t="inlineStr"/>
-    </row>
-    <row r="86" ht="45" customHeight="1">
+          <t>985cd182b</t>
+        </is>
+      </c>
+      <c r="N85" s="8" t="inlineStr">
+        <is>
+          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="75" customHeight="1">
       <c r="A86" s="2" t="n">
         <v>85</v>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>P0-WEEKLY</t>
+          <t>ROLLING-SHARPE-FIX</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -4714,39 +4742,27 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Backtest infra</t>
+          <t>Decision Engine / Bug</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
+          <t>Rolling-Sharpe brake firing on contaminated data</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
+          <t>Two bugs: (a) WATCH-conviction signals being written with verdict='BUY' inflated loss count; (b) same physical trade re-emitted as fresh daily signal counted 3× in rolling-20 window. Net: false brake activation pausing ALL new BUYs system-wide. Real Sharpe -0.42; system reported -1.732</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>20 min</t>
-        </is>
-      </c>
-      <c r="I86" s="5" t="inlineStr">
-        <is>
-          <t>CRITICAL — system was unable to backtest</t>
-        </is>
-      </c>
-      <c r="J86" s="5" t="inlineStr">
-        <is>
-          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
-        </is>
-      </c>
+          <t>Upstream fix: swing_trade.py line 3110 _resolve_verdict() detects WATCH conviction and overrides bucket label. Read-time fix: decision_engine.compute_rolling_sharpe_kill_state dedupes by (ticker,entry,pnl,exit_reason). Historical cleanup: scripts/dedupe_signal_log.py removed 133 mislabels + 90 dupes (backed up)</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="5" t="inlineStr"/>
+      <c r="J86" s="5" t="inlineStr"/>
       <c r="K86" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4754,27 +4770,23 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
-        </is>
-      </c>
-      <c r="N86" s="8" t="inlineStr">
-        <is>
-          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="75" customHeight="1">
+          <t>27fd646b1</t>
+        </is>
+      </c>
+      <c r="N86" s="8" t="inlineStr"/>
+    </row>
+    <row r="87" ht="90" customHeight="1">
       <c r="A87" s="2" t="n">
         <v>86</v>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>ROLLING-SHARPE-FIX</t>
+          <t>OPERATING-MINDSET</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -4784,27 +4796,39 @@
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Decision Engine / Bug</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>Rolling-Sharpe brake firing on contaminated data</t>
+          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>Two bugs: (a) WATCH-conviction signals being written with verdict='BUY' inflated loss count; (b) same physical trade re-emitted as fresh daily signal counted 3× in rolling-20 window. Net: false brake activation pausing ALL new BUYs system-wide. Real Sharpe -0.42; system reported -1.732</t>
+          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>Upstream fix: swing_trade.py line 3110 _resolve_verdict() detects WATCH conviction and overrides bucket label. Read-time fix: decision_engine.compute_rolling_sharpe_kill_state dedupes by (ticker,entry,pnl,exit_reason). Historical cleanup: scripts/dedupe_signal_log.py removed 133 mislabels + 90 dupes (backed up)</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr"/>
-      <c r="I87" s="5" t="inlineStr"/>
-      <c r="J87" s="5" t="inlineStr"/>
+          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>Win: codified discipline survives session/agent boundaries.</t>
+        </is>
+      </c>
+      <c r="J87" s="5" t="inlineStr">
+        <is>
+          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
+        </is>
+      </c>
       <c r="K87" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4812,23 +4836,27 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
-          <t>27fd646b1</t>
-        </is>
-      </c>
-      <c r="N87" s="8" t="inlineStr"/>
-    </row>
-    <row r="88" ht="90" customHeight="1">
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N87" s="8" t="inlineStr">
+        <is>
+          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="60" customHeight="1">
       <c r="A88" s="2" t="n">
         <v>87</v>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>OPERATING-MINDSET</t>
+          <t>EXEC-TRADABLE-ENUM</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -4838,39 +4866,27 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Execution · Auto-Trade</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
+          <t>Stock executor skipped all active names (enum bug)</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
+          <t>alpaca-py AssetStatus enum stringified to 'AssetStatus.ACTIVE'; check 'assetstatus.active' != 'active' wrongly skipped EVERY tradable stock since ~2026-05-28 → stock auto-trade silently dead, options-only</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I88" s="5" t="inlineStr">
-        <is>
-          <t>Win: codified discipline survives session/agent boundaries.</t>
-        </is>
-      </c>
-      <c r="J88" s="5" t="inlineStr">
-        <is>
-          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
-        </is>
-      </c>
+          <t>executor.py: read enum .value ('active') before lowercasing</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="5" t="inlineStr"/>
+      <c r="J88" s="5" t="inlineStr"/>
       <c r="K88" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4878,27 +4894,23 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N88" s="8" t="inlineStr">
-        <is>
-          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="60" customHeight="1">
+          <t>c7098178a</t>
+        </is>
+      </c>
+      <c r="N88" s="8" t="inlineStr"/>
+    </row>
+    <row r="89" ht="105" customHeight="1">
       <c r="A89" s="2" t="n">
         <v>88</v>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>EXEC-TRADABLE-ENUM</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -4908,27 +4920,39 @@
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Execution · Auto-Trade</t>
+          <t>ML / Data Logging</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>Stock executor skipped all active names (enum bug)</t>
+          <t>Entry-time feature logger in swing_trade.py</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>alpaca-py AssetStatus enum stringified to 'AssetStatus.ACTIVE'; check 'assetstatus.active' != 'active' wrongly skipped EVERY tradable stock since ~2026-05-28 → stock auto-trade silently dead, options-only</t>
+          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>executor.py: read enum .value ('active') before lowercasing</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr"/>
-      <c r="I89" s="5" t="inlineStr"/>
-      <c r="J89" s="5" t="inlineStr"/>
+          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
+        </is>
+      </c>
+      <c r="J89" s="5" t="inlineStr">
+        <is>
+          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
+        </is>
+      </c>
       <c r="K89" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4936,15 +4960,19 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
-          <t>c7098178a</t>
-        </is>
-      </c>
-      <c r="N89" s="8" t="inlineStr"/>
+          <t>0574c60d4</t>
+        </is>
+      </c>
+      <c r="N89" s="8" t="inlineStr">
+        <is>
+          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="105" customHeight="1">
       <c r="A90" s="2" t="n">
@@ -4952,7 +4980,7 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>ML-FEATURE-MISMATCH</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -4962,39 +4990,27 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>ML / Data Logging</t>
+          <t>ML · Inference</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>Entry-time feature logger in swing_trade.py</t>
+          <t>Live predict_one degenerate — 29-feat model vs 17-feat extractor</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
+          <t>Models retrained 2026-06-09 on 29 features but ml.feature_extractor.FEATURE_COLS still emits 17, so live predict_one feeds a mismatched vector and returns ~0 p_up for EVERY ticker (AI Edge 0% bug, all names). Batch ml-predict path extracts 29 correctly. /api/ml now prefers the batch cache + rejects degenerate live; ROOT FIX still needed: align FEATURE_COLS to 29 (or guard retrain to the live feature set). Also cache 4d stale.</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I90" s="5" t="inlineStr">
-        <is>
-          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
-        </is>
-      </c>
-      <c r="J90" s="5" t="inlineStr">
-        <is>
-          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
-        </is>
-      </c>
+          <t>server /api/ml cache-first + degenerate guard (done); align ml/feature_extractor.FEATURE_COLS to model n_features_in_ (pending)</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="5" t="inlineStr"/>
+      <c r="J90" s="5" t="inlineStr"/>
       <c r="K90" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5002,19 +5018,15 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>0574c60d4</t>
-        </is>
-      </c>
-      <c r="N90" s="8" t="inlineStr">
-        <is>
-          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
-        </is>
-      </c>
+          <t>33877186c</t>
+        </is>
+      </c>
+      <c r="N90" s="8" t="inlineStr"/>
     </row>
     <row r="91" ht="45" customHeight="1">
       <c r="A91" s="2" t="n">
@@ -15715,7 +15727,7 @@
         </is>
       </c>
       <c r="B2" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="18" t="n">
         <v>20</v>
@@ -15724,7 +15736,7 @@
         <v>58</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3">
@@ -15753,7 +15765,7 @@
         </is>
       </c>
       <c r="B4" s="18" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" s="18" t="n">
         <v>77</v>
@@ -15762,7 +15774,7 @@
         <v>68</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5">
